--- a/Staffdata.xlsx
+++ b/Staffdata.xlsx
@@ -1,15 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3113719057d24bf/Desktop/HR-Forms-Site/HRFORMAS/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_05E48499FC67680F1964AE368160343238AA41AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F39E4F8-EC7F-4B82-A65E-7BCB1AF9CCFE}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2174,7 +2185,7 @@
     <t>-</t>
   </si>
   <si>
-    <t xml:space="preserve"> 966577040481</t>
+    <t> 966577040481</t>
   </si>
   <si>
     <t>malbatil@outlook.sa</t>
@@ -2485,10 +2496,10 @@
     <t>HAMDILLHJ038@GMAIL.COM</t>
   </si>
   <si>
-    <t xml:space="preserve"> omarzar392@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ark870725@gmail.com</t>
+    <t> omarzar392@gmail.com</t>
+  </si>
+  <si>
+    <t> ark870725@gmail.com</t>
   </si>
   <si>
     <t>waelgomaa1wg@gmail.com</t>
@@ -2561,7 +2572,7 @@
     <t>INFO2@HAIL-HOUSE.SA</t>
   </si>
   <si>
-    <t xml:space="preserve"> Sarah_elkhatib@outlook.com</t>
+    <t> Sarah_elkhatib@outlook.com</t>
   </si>
   <si>
     <t xml:space="preserve"> mohannad.fakhry00@gmail.com</t>
@@ -3905,11 +3916,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3955,18 +3966,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ارتباط تشعبي" xfId="1" builtinId="8"/>
+    <cellStyle name="عادي" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4004,7 +4023,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4038,6 +4057,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4072,9 +4092,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4247,11 +4268,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AQ187"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:43">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4382,7 +4403,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:43">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4483,7 +4504,7 @@
         <v>46259</v>
       </c>
       <c r="AH2">
-        <v>8.726027397260275</v>
+        <v>8.7260273972602747</v>
       </c>
       <c r="AI2">
         <v>30</v>
@@ -4513,7 +4534,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="3" spans="1:43">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4614,7 +4635,7 @@
         <v>46259</v>
       </c>
       <c r="AH3">
-        <v>13.63561643835616</v>
+        <v>13.635616438356161</v>
       </c>
       <c r="AI3">
         <v>30</v>
@@ -4644,7 +4665,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="4" spans="1:43">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4745,7 +4766,7 @@
         <v>46259</v>
       </c>
       <c r="AH4">
-        <v>5.890410958904109</v>
+        <v>5.8904109589041092</v>
       </c>
       <c r="AI4">
         <v>30</v>
@@ -4775,7 +4796,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="5" spans="1:43">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4876,7 +4897,7 @@
         <v>46259</v>
       </c>
       <c r="AH5">
-        <v>6.046575342465753</v>
+        <v>6.0465753424657533</v>
       </c>
       <c r="AI5">
         <v>21</v>
@@ -4906,7 +4927,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="6" spans="1:43">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5007,7 +5028,7 @@
         <v>46259</v>
       </c>
       <c r="AH6">
-        <v>6.402739726027397</v>
+        <v>6.4027397260273968</v>
       </c>
       <c r="AI6">
         <v>21</v>
@@ -5037,7 +5058,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="7" spans="1:43">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5138,7 +5159,7 @@
         <v>46259</v>
       </c>
       <c r="AH7">
-        <v>5.704109589041096</v>
+        <v>5.7041095890410958</v>
       </c>
       <c r="AI7">
         <v>30</v>
@@ -5168,7 +5189,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="8" spans="1:43">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5299,7 +5320,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="9" spans="1:43">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5430,7 +5451,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="10" spans="1:43">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5531,7 +5552,7 @@
         <v>46259</v>
       </c>
       <c r="AH10">
-        <v>6.753424657534246</v>
+        <v>6.7534246575342456</v>
       </c>
       <c r="AI10">
         <v>30</v>
@@ -5561,7 +5582,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="11" spans="1:43">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5692,7 +5713,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="12" spans="1:43">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5793,7 +5814,7 @@
         <v>46259</v>
       </c>
       <c r="AH12">
-        <v>5.750684931506849</v>
+        <v>5.7506849315068491</v>
       </c>
       <c r="AI12">
         <v>21</v>
@@ -5823,7 +5844,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="13" spans="1:43">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5954,7 +5975,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="14" spans="1:43">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6055,7 +6076,7 @@
         <v>46259</v>
       </c>
       <c r="AH14">
-        <v>0.3041095890410959</v>
+        <v>0.30410958904109592</v>
       </c>
       <c r="AI14">
         <v>21</v>
@@ -6085,7 +6106,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="15" spans="1:43">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6186,7 +6207,7 @@
         <v>46259</v>
       </c>
       <c r="AH15">
-        <v>3.983561643835616</v>
+        <v>3.9835616438356158</v>
       </c>
       <c r="AI15">
         <v>21</v>
@@ -6216,7 +6237,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="16" spans="1:43">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6317,7 +6338,7 @@
         <v>46259</v>
       </c>
       <c r="AH16">
-        <v>2.898630136986301</v>
+        <v>2.8986301369863008</v>
       </c>
       <c r="AI16">
         <v>21</v>
@@ -6347,7 +6368,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="17" spans="1:43">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -6448,7 +6469,7 @@
         <v>46259</v>
       </c>
       <c r="AH17">
-        <v>1.673972602739726</v>
+        <v>1.6739726027397259</v>
       </c>
       <c r="AI17">
         <v>21</v>
@@ -6478,7 +6499,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="18" spans="1:43">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6579,7 +6600,7 @@
         <v>46259</v>
       </c>
       <c r="AH18">
-        <v>2.049315068493151</v>
+        <v>2.0493150684931511</v>
       </c>
       <c r="AI18">
         <v>21</v>
@@ -6609,7 +6630,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="19" spans="1:43">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -6710,7 +6731,7 @@
         <v>46259</v>
       </c>
       <c r="AH19">
-        <v>2.035616438356164</v>
+        <v>2.0356164383561639</v>
       </c>
       <c r="AI19">
         <v>21</v>
@@ -6740,7 +6761,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="20" spans="1:43">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -6841,7 +6862,7 @@
         <v>46259</v>
       </c>
       <c r="AH20">
-        <v>1.512328767123288</v>
+        <v>1.5123287671232879</v>
       </c>
       <c r="AI20">
         <v>21</v>
@@ -6871,7 +6892,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="21" spans="1:43">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -6972,7 +6993,7 @@
         <v>46259</v>
       </c>
       <c r="AH21">
-        <v>2.035616438356164</v>
+        <v>2.0356164383561639</v>
       </c>
       <c r="AI21">
         <v>21</v>
@@ -7002,7 +7023,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="22" spans="1:43">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -7133,7 +7154,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="23" spans="1:43">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -7264,7 +7285,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="24" spans="1:43">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -7395,7 +7416,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="25" spans="1:43">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -7496,7 +7517,7 @@
         <v>46259</v>
       </c>
       <c r="AH25">
-        <v>0.7616438356164383</v>
+        <v>0.76164383561643834</v>
       </c>
       <c r="AI25">
         <v>21</v>
@@ -7526,7 +7547,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="26" spans="1:43">
+    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -7627,7 +7648,7 @@
         <v>46259</v>
       </c>
       <c r="AH26">
-        <v>0.7616438356164383</v>
+        <v>0.76164383561643834</v>
       </c>
       <c r="AI26">
         <v>21</v>
@@ -7657,7 +7678,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="27" spans="1:43">
+    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -7758,7 +7779,7 @@
         <v>46259</v>
       </c>
       <c r="AH27">
-        <v>6.736986301369863</v>
+        <v>6.7369863013698632</v>
       </c>
       <c r="AI27">
         <v>30</v>
@@ -7788,7 +7809,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="28" spans="1:43">
+    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -7889,7 +7910,7 @@
         <v>46259</v>
       </c>
       <c r="AH28">
-        <v>12.11232876712329</v>
+        <v>12.112328767123291</v>
       </c>
       <c r="AI28">
         <v>30</v>
@@ -7919,7 +7940,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="29" spans="1:43">
+    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -8020,7 +8041,7 @@
         <v>46259</v>
       </c>
       <c r="AH29">
-        <v>3.487671232876712</v>
+        <v>3.4876712328767119</v>
       </c>
       <c r="AI29">
         <v>21</v>
@@ -8050,7 +8071,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="30" spans="1:43">
+    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -8151,7 +8172,7 @@
         <v>46259</v>
       </c>
       <c r="AH30">
-        <v>15.07671232876712</v>
+        <v>15.076712328767121</v>
       </c>
       <c r="AI30">
         <v>30</v>
@@ -8181,7 +8202,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="31" spans="1:43">
+    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -8282,7 +8303,7 @@
         <v>46259</v>
       </c>
       <c r="AH31">
-        <v>15.07671232876712</v>
+        <v>15.076712328767121</v>
       </c>
       <c r="AI31">
         <v>30</v>
@@ -8312,7 +8333,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="32" spans="1:43">
+    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -8443,7 +8464,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="33" spans="1:43">
+    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -8544,7 +8565,7 @@
         <v>46259</v>
       </c>
       <c r="AH33">
-        <v>15.16712328767123</v>
+        <v>15.167123287671229</v>
       </c>
       <c r="AI33">
         <v>30</v>
@@ -8574,7 +8595,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="34" spans="1:43">
+    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -8675,7 +8696,7 @@
         <v>46259</v>
       </c>
       <c r="AH34">
-        <v>4.610958904109589</v>
+        <v>4.6109589041095891</v>
       </c>
       <c r="AI34">
         <v>21</v>
@@ -8705,7 +8726,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="35" spans="1:43">
+    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -8806,7 +8827,7 @@
         <v>46259</v>
       </c>
       <c r="AH35">
-        <v>4.542465753424658</v>
+        <v>4.5424657534246577</v>
       </c>
       <c r="AI35">
         <v>21</v>
@@ -8836,7 +8857,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="36" spans="1:43">
+    <row r="36" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -8937,7 +8958,7 @@
         <v>46259</v>
       </c>
       <c r="AH36">
-        <v>13.24109589041096</v>
+        <v>13.241095890410961</v>
       </c>
       <c r="AI36">
         <v>30</v>
@@ -8967,7 +8988,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="37" spans="1:43">
+    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -9098,7 +9119,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="38" spans="1:43">
+    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -9229,7 +9250,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="39" spans="1:43">
+    <row r="39" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -9330,7 +9351,7 @@
         <v>46259</v>
       </c>
       <c r="AH39">
-        <v>6.70958904109589</v>
+        <v>6.7095890410958896</v>
       </c>
       <c r="AI39">
         <v>30</v>
@@ -9360,7 +9381,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="40" spans="1:43">
+    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -9461,7 +9482,7 @@
         <v>46259</v>
       </c>
       <c r="AH40">
-        <v>6.50958904109589</v>
+        <v>6.5095890410958903</v>
       </c>
       <c r="AI40">
         <v>30</v>
@@ -9491,7 +9512,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="41" spans="1:43">
+    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -9592,7 +9613,7 @@
         <v>46259</v>
       </c>
       <c r="AH41">
-        <v>6.550684931506849</v>
+        <v>6.5506849315068489</v>
       </c>
       <c r="AI41">
         <v>21</v>
@@ -9622,7 +9643,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="42" spans="1:43">
+    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -9753,7 +9774,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="43" spans="1:43">
+    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -9854,7 +9875,7 @@
         <v>46259</v>
       </c>
       <c r="AH43">
-        <v>8.753424657534246</v>
+        <v>8.7534246575342465</v>
       </c>
       <c r="AI43">
         <v>30</v>
@@ -9884,7 +9905,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="44" spans="1:43">
+    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -9985,7 +10006,7 @@
         <v>46259</v>
       </c>
       <c r="AH44">
-        <v>5.753424657534246</v>
+        <v>5.7534246575342456</v>
       </c>
       <c r="AI44">
         <v>21</v>
@@ -10015,7 +10036,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="45" spans="1:43">
+    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -10116,7 +10137,7 @@
         <v>46259</v>
       </c>
       <c r="AH45">
-        <v>5.734246575342466</v>
+        <v>5.7342465753424658</v>
       </c>
       <c r="AI45">
         <v>21</v>
@@ -10146,7 +10167,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="46" spans="1:43">
+    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -10247,7 +10268,7 @@
         <v>46259</v>
       </c>
       <c r="AH46">
-        <v>5.627397260273972</v>
+        <v>5.6273972602739724</v>
       </c>
       <c r="AI46">
         <v>30</v>
@@ -10277,7 +10298,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="47" spans="1:43">
+    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -10378,7 +10399,7 @@
         <v>46259</v>
       </c>
       <c r="AH47">
-        <v>4.227397260273973</v>
+        <v>4.2273972602739729</v>
       </c>
       <c r="AI47">
         <v>21</v>
@@ -10408,7 +10429,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="48" spans="1:43">
+    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -10539,7 +10560,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="49" spans="1:43">
+    <row r="49" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -10640,7 +10661,7 @@
         <v>46259</v>
       </c>
       <c r="AH49">
-        <v>4.158904109589041</v>
+        <v>4.1589041095890407</v>
       </c>
       <c r="AI49">
         <v>21</v>
@@ -10670,7 +10691,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="50" spans="1:43">
+    <row r="50" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -10771,7 +10792,7 @@
         <v>46259</v>
       </c>
       <c r="AH50">
-        <v>3.986301369863014</v>
+        <v>3.9863013698630141</v>
       </c>
       <c r="AI50">
         <v>21</v>
@@ -10801,7 +10822,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="51" spans="1:43">
+    <row r="51" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -10902,7 +10923,7 @@
         <v>46259</v>
       </c>
       <c r="AH51">
-        <v>3.964383561643836</v>
+        <v>3.9643835616438361</v>
       </c>
       <c r="AI51">
         <v>21</v>
@@ -10932,7 +10953,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="52" spans="1:43">
+    <row r="52" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -11033,7 +11054,7 @@
         <v>46259</v>
       </c>
       <c r="AH52">
-        <v>3.964383561643836</v>
+        <v>3.9643835616438361</v>
       </c>
       <c r="AI52">
         <v>21</v>
@@ -11063,7 +11084,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="53" spans="1:43">
+    <row r="53" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -11194,7 +11215,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="54" spans="1:43">
+    <row r="54" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -11295,7 +11316,7 @@
         <v>46259</v>
       </c>
       <c r="AH54">
-        <v>1.96986301369863</v>
+        <v>1.9698630136986299</v>
       </c>
       <c r="AI54">
         <v>21</v>
@@ -11325,7 +11346,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="55" spans="1:43">
+    <row r="55" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -11426,7 +11447,7 @@
         <v>46259</v>
       </c>
       <c r="AH55">
-        <v>0.5835616438356165</v>
+        <v>0.58356164383561648</v>
       </c>
       <c r="AI55">
         <v>21</v>
@@ -11456,7 +11477,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="56" spans="1:43">
+    <row r="56" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -11557,7 +11578,7 @@
         <v>46259</v>
       </c>
       <c r="AH56">
-        <v>0.5835616438356165</v>
+        <v>0.58356164383561648</v>
       </c>
       <c r="AI56">
         <v>21</v>
@@ -11587,7 +11608,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="57" spans="1:43">
+    <row r="57" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -11688,7 +11709,7 @@
         <v>46259</v>
       </c>
       <c r="AH57">
-        <v>7.150684931506849</v>
+        <v>7.1506849315068486</v>
       </c>
       <c r="AI57">
         <v>30</v>
@@ -11718,7 +11739,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="58" spans="1:43">
+    <row r="58" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -11819,7 +11840,7 @@
         <v>46259</v>
       </c>
       <c r="AH58">
-        <v>7.482191780821918</v>
+        <v>7.4821917808219176</v>
       </c>
       <c r="AI58">
         <v>30</v>
@@ -11849,7 +11870,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="59" spans="1:43">
+    <row r="59" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -11950,7 +11971,7 @@
         <v>46259</v>
       </c>
       <c r="AH59">
-        <v>0.06575342465753424</v>
+        <v>6.575342465753424E-2</v>
       </c>
       <c r="AI59">
         <v>21</v>
@@ -11980,7 +12001,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="60" spans="1:43">
+    <row r="60" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -12081,7 +12102,7 @@
         <v>46259</v>
       </c>
       <c r="AH60">
-        <v>0.06575342465753424</v>
+        <v>6.575342465753424E-2</v>
       </c>
       <c r="AI60">
         <v>21</v>
@@ -12111,7 +12132,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="61" spans="1:43">
+    <row r="61" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
@@ -12212,7 +12233,7 @@
         <v>46259</v>
       </c>
       <c r="AH61">
-        <v>18.26301369863014</v>
+        <v>18.263013698630139</v>
       </c>
       <c r="AI61">
         <v>30</v>
@@ -12242,7 +12263,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="62" spans="1:43">
+    <row r="62" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
@@ -12343,7 +12364,7 @@
         <v>46259</v>
       </c>
       <c r="AH62">
-        <v>15.07671232876712</v>
+        <v>15.076712328767121</v>
       </c>
       <c r="AI62">
         <v>30</v>
@@ -12373,7 +12394,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="63" spans="1:43">
+    <row r="63" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
@@ -12474,7 +12495,7 @@
         <v>46259</v>
       </c>
       <c r="AH63">
-        <v>34.04931506849315</v>
+        <v>34.049315068493151</v>
       </c>
       <c r="AI63">
         <v>30</v>
@@ -12504,7 +12525,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="64" spans="1:43">
+    <row r="64" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
@@ -12605,7 +12626,7 @@
         <v>46259</v>
       </c>
       <c r="AH64">
-        <v>6.175342465753425</v>
+        <v>6.1753424657534248</v>
       </c>
       <c r="AI64">
         <v>30</v>
@@ -12635,7 +12656,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="65" spans="1:43">
+    <row r="65" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
@@ -12736,7 +12757,7 @@
         <v>46259</v>
       </c>
       <c r="AH65">
-        <v>1.873972602739726</v>
+        <v>1.8739726027397261</v>
       </c>
       <c r="AI65">
         <v>21</v>
@@ -12766,7 +12787,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="66" spans="1:43">
+    <row r="66" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
@@ -12867,7 +12888,7 @@
         <v>46259</v>
       </c>
       <c r="AH66">
-        <v>5.753424657534246</v>
+        <v>5.7534246575342456</v>
       </c>
       <c r="AI66">
         <v>21</v>
@@ -12897,7 +12918,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="67" spans="1:43">
+    <row r="67" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
@@ -12998,7 +13019,7 @@
         <v>46259</v>
       </c>
       <c r="AH67">
-        <v>18.04657534246575</v>
+        <v>18.046575342465751</v>
       </c>
       <c r="AI67">
         <v>30</v>
@@ -13028,7 +13049,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="68" spans="1:43">
+    <row r="68" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
@@ -13129,7 +13150,7 @@
         <v>46259</v>
       </c>
       <c r="AH68">
-        <v>9.531506849315068</v>
+        <v>9.5315068493150683</v>
       </c>
       <c r="AI68">
         <v>30</v>
@@ -13159,7 +13180,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="69" spans="1:43">
+    <row r="69" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
@@ -13290,7 +13311,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="70" spans="1:43">
+    <row r="70" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
@@ -13391,7 +13412,7 @@
         <v>46259</v>
       </c>
       <c r="AH70">
-        <v>10.60821917808219</v>
+        <v>10.608219178082191</v>
       </c>
       <c r="AI70">
         <v>30</v>
@@ -13421,7 +13442,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="71" spans="1:43">
+    <row r="71" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
@@ -13522,7 +13543,7 @@
         <v>46259</v>
       </c>
       <c r="AH71">
-        <v>0.3342465753424658</v>
+        <v>0.33424657534246582</v>
       </c>
       <c r="AI71">
         <v>21</v>
@@ -13552,7 +13573,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="72" spans="1:43">
+    <row r="72" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
@@ -13653,7 +13674,7 @@
         <v>46259</v>
       </c>
       <c r="AH72">
-        <v>0.3342465753424658</v>
+        <v>0.33424657534246582</v>
       </c>
       <c r="AI72">
         <v>21</v>
@@ -13683,7 +13704,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="73" spans="1:43">
+    <row r="73" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
@@ -13784,7 +13805,7 @@
         <v>46259</v>
       </c>
       <c r="AH73">
-        <v>2.96986301369863</v>
+        <v>2.9698630136986299</v>
       </c>
       <c r="AI73">
         <v>21</v>
@@ -13814,7 +13835,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="74" spans="1:43">
+    <row r="74" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>71</v>
       </c>
@@ -13945,7 +13966,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="75" spans="1:43">
+    <row r="75" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>72</v>
       </c>
@@ -14046,7 +14067,7 @@
         <v>46259</v>
       </c>
       <c r="AH75">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AI75">
         <v>21</v>
@@ -14076,7 +14097,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="76" spans="1:43">
+    <row r="76" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>73</v>
       </c>
@@ -14177,7 +14198,7 @@
         <v>46259</v>
       </c>
       <c r="AH76">
-        <v>4.068493150684931</v>
+        <v>4.0684931506849313</v>
       </c>
       <c r="AI76">
         <v>21</v>
@@ -14207,7 +14228,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="77" spans="1:43">
+    <row r="77" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>74</v>
       </c>
@@ -14338,7 +14359,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="78" spans="1:43">
+    <row r="78" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>75</v>
       </c>
@@ -14469,7 +14490,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="79" spans="1:43">
+    <row r="79" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>76</v>
       </c>
@@ -14570,7 +14591,7 @@
         <v>46259</v>
       </c>
       <c r="AH79">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AI79">
         <v>21</v>
@@ -14600,7 +14621,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="80" spans="1:43">
+    <row r="80" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>77</v>
       </c>
@@ -14701,7 +14722,7 @@
         <v>46259</v>
       </c>
       <c r="AH80">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AI80">
         <v>21</v>
@@ -14731,7 +14752,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="81" spans="1:43">
+    <row r="81" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>78</v>
       </c>
@@ -14832,7 +14853,7 @@
         <v>46259</v>
       </c>
       <c r="AH81">
-        <v>1.819178082191781</v>
+        <v>1.8191780821917809</v>
       </c>
       <c r="AI81">
         <v>21</v>
@@ -14862,7 +14883,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="82" spans="1:43">
+    <row r="82" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>79</v>
       </c>
@@ -14963,7 +14984,7 @@
         <v>46259</v>
       </c>
       <c r="AH82">
-        <v>1.654794520547945</v>
+        <v>1.6547945205479451</v>
       </c>
       <c r="AI82">
         <v>21</v>
@@ -14993,7 +15014,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="83" spans="1:43">
+    <row r="83" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>80</v>
       </c>
@@ -15094,7 +15115,7 @@
         <v>46259</v>
       </c>
       <c r="AH83">
-        <v>15.16712328767123</v>
+        <v>15.167123287671229</v>
       </c>
       <c r="AI83">
         <v>30</v>
@@ -15124,7 +15145,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="84" spans="1:43">
+    <row r="84" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>80</v>
       </c>
@@ -15165,7 +15186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:43">
+    <row r="85" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>81</v>
       </c>
@@ -15266,7 +15287,7 @@
         <v>46259</v>
       </c>
       <c r="AH85">
-        <v>8.975342465753425</v>
+        <v>8.9753424657534246</v>
       </c>
       <c r="AI85">
         <v>30</v>
@@ -15296,7 +15317,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="86" spans="1:43">
+    <row r="86" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>82</v>
       </c>
@@ -15397,7 +15418,7 @@
         <v>46259</v>
       </c>
       <c r="AH86">
-        <v>6.70958904109589</v>
+        <v>6.7095890410958896</v>
       </c>
       <c r="AI86">
         <v>30</v>
@@ -15427,7 +15448,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="87" spans="1:43">
+    <row r="87" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>83</v>
       </c>
@@ -15528,7 +15549,7 @@
         <v>46259</v>
       </c>
       <c r="AH87">
-        <v>9.323287671232876</v>
+        <v>9.3232876712328761</v>
       </c>
       <c r="AI87">
         <v>30</v>
@@ -15558,7 +15579,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="88" spans="1:43">
+    <row r="88" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>84</v>
       </c>
@@ -15659,7 +15680,7 @@
         <v>46259</v>
       </c>
       <c r="AH88">
-        <v>14.03561643835616</v>
+        <v>14.035616438356159</v>
       </c>
       <c r="AI88">
         <v>30</v>
@@ -15689,7 +15710,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="89" spans="1:43">
+    <row r="89" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>85</v>
       </c>
@@ -15790,7 +15811,7 @@
         <v>46259</v>
       </c>
       <c r="AH89">
-        <v>1.772602739726027</v>
+        <v>1.7726027397260271</v>
       </c>
       <c r="AI89">
         <v>21</v>
@@ -15820,7 +15841,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="90" spans="1:43">
+    <row r="90" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>86</v>
       </c>
@@ -15921,7 +15942,7 @@
         <v>46259</v>
       </c>
       <c r="AH90">
-        <v>8.408219178082192</v>
+        <v>8.4082191780821915</v>
       </c>
       <c r="AI90">
         <v>30</v>
@@ -15951,7 +15972,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="91" spans="1:43">
+    <row r="91" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>87</v>
       </c>
@@ -16052,7 +16073,7 @@
         <v>46259</v>
       </c>
       <c r="AH91">
-        <v>10.95068493150685</v>
+        <v>10.950684931506849</v>
       </c>
       <c r="AI91">
         <v>30</v>
@@ -16082,7 +16103,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="92" spans="1:43">
+    <row r="92" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>88</v>
       </c>
@@ -16183,7 +16204,7 @@
         <v>46259</v>
       </c>
       <c r="AH92">
-        <v>6.682191780821918</v>
+        <v>6.6821917808219178</v>
       </c>
       <c r="AI92">
         <v>21</v>
@@ -16213,7 +16234,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="93" spans="1:43">
+    <row r="93" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>89</v>
       </c>
@@ -16314,7 +16335,7 @@
         <v>46259</v>
       </c>
       <c r="AH93">
-        <v>5.627397260273972</v>
+        <v>5.6273972602739724</v>
       </c>
       <c r="AI93">
         <v>21</v>
@@ -16344,7 +16365,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="94" spans="1:43">
+    <row r="94" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>90</v>
       </c>
@@ -16445,7 +16466,7 @@
         <v>46259</v>
       </c>
       <c r="AH94">
-        <v>5.315068493150685</v>
+        <v>5.3150684931506849</v>
       </c>
       <c r="AI94">
         <v>30</v>
@@ -16475,7 +16496,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="95" spans="1:43">
+    <row r="95" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>91</v>
       </c>
@@ -16576,7 +16597,7 @@
         <v>46259</v>
       </c>
       <c r="AH95">
-        <v>5.06027397260274</v>
+        <v>5.0602739726027401</v>
       </c>
       <c r="AI95">
         <v>30</v>
@@ -16606,7 +16627,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="96" spans="1:43">
+    <row r="96" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>92</v>
       </c>
@@ -16707,7 +16728,7 @@
         <v>46259</v>
       </c>
       <c r="AH96">
-        <v>5.06027397260274</v>
+        <v>5.0602739726027401</v>
       </c>
       <c r="AI96">
         <v>21</v>
@@ -16737,7 +16758,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="97" spans="1:43">
+    <row r="97" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>93</v>
       </c>
@@ -16838,7 +16859,7 @@
         <v>46259</v>
       </c>
       <c r="AH97">
-        <v>4.753424657534246</v>
+        <v>4.7534246575342456</v>
       </c>
       <c r="AI97">
         <v>21</v>
@@ -16868,7 +16889,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="98" spans="1:43">
+    <row r="98" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>94</v>
       </c>
@@ -16969,7 +16990,7 @@
         <v>46259</v>
       </c>
       <c r="AH98">
-        <v>0.5835616438356165</v>
+        <v>0.58356164383561648</v>
       </c>
       <c r="AI98">
         <v>21</v>
@@ -16999,7 +17020,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="99" spans="1:43">
+    <row r="99" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>95</v>
       </c>
@@ -17100,7 +17121,7 @@
         <v>46259</v>
       </c>
       <c r="AH99">
-        <v>0.5835616438356165</v>
+        <v>0.58356164383561648</v>
       </c>
       <c r="AI99">
         <v>21</v>
@@ -17130,7 +17151,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="100" spans="1:43">
+    <row r="100" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>96</v>
       </c>
@@ -17231,7 +17252,7 @@
         <v>46259</v>
       </c>
       <c r="AH100">
-        <v>4.739726027397261</v>
+        <v>4.7397260273972606</v>
       </c>
       <c r="AI100">
         <v>21</v>
@@ -17261,7 +17282,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="101" spans="1:43">
+    <row r="101" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>97</v>
       </c>
@@ -17362,7 +17383,7 @@
         <v>46259</v>
       </c>
       <c r="AH101">
-        <v>4.67945205479452</v>
+        <v>4.6794520547945204</v>
       </c>
       <c r="AI101">
         <v>21</v>
@@ -17392,7 +17413,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="102" spans="1:43">
+    <row r="102" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>98</v>
       </c>
@@ -17493,7 +17514,7 @@
         <v>46259</v>
       </c>
       <c r="AH102">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AI102">
         <v>21</v>
@@ -17523,7 +17544,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="103" spans="1:43">
+    <row r="103" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>99</v>
       </c>
@@ -17624,7 +17645,7 @@
         <v>46259</v>
       </c>
       <c r="AH103">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AI103">
         <v>21</v>
@@ -17654,7 +17675,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="104" spans="1:43">
+    <row r="104" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>100</v>
       </c>
@@ -17755,7 +17776,7 @@
         <v>46259</v>
       </c>
       <c r="AH104">
-        <v>3.964383561643836</v>
+        <v>3.9643835616438361</v>
       </c>
       <c r="AI104">
         <v>21</v>
@@ -17785,7 +17806,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="105" spans="1:43">
+    <row r="105" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>101</v>
       </c>
@@ -17886,7 +17907,7 @@
         <v>46259</v>
       </c>
       <c r="AH105">
-        <v>7.523287671232877</v>
+        <v>7.5232876712328771</v>
       </c>
       <c r="AI105">
         <v>30</v>
@@ -17916,7 +17937,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="106" spans="1:43">
+    <row r="106" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>102</v>
       </c>
@@ -18017,7 +18038,7 @@
         <v>46259</v>
       </c>
       <c r="AH106">
-        <v>4.972602739726027</v>
+        <v>4.9726027397260273</v>
       </c>
       <c r="AI106">
         <v>21</v>
@@ -18047,7 +18068,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="107" spans="1:43">
+    <row r="107" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>103</v>
       </c>
@@ -18148,7 +18169,7 @@
         <v>46259</v>
       </c>
       <c r="AH107">
-        <v>1.96986301369863</v>
+        <v>1.9698630136986299</v>
       </c>
       <c r="AI107">
         <v>21</v>
@@ -18178,7 +18199,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="108" spans="1:43">
+    <row r="108" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>104</v>
       </c>
@@ -18279,7 +18300,7 @@
         <v>46259</v>
       </c>
       <c r="AH108">
-        <v>22.44657534246575</v>
+        <v>22.446575342465749</v>
       </c>
       <c r="AI108">
         <v>30</v>
@@ -18309,7 +18330,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="109" spans="1:43">
+    <row r="109" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>105</v>
       </c>
@@ -18410,7 +18431,7 @@
         <v>46259</v>
       </c>
       <c r="AH109">
-        <v>3.986301369863014</v>
+        <v>3.9863013698630141</v>
       </c>
       <c r="AI109">
         <v>21</v>
@@ -18440,7 +18461,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="110" spans="1:43">
+    <row r="110" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>106</v>
       </c>
@@ -18493,7 +18514,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="111" spans="1:43">
+    <row r="111" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>107</v>
       </c>
@@ -18594,7 +18615,7 @@
         <v>46259</v>
       </c>
       <c r="AH111">
-        <v>0.3589041095890411</v>
+        <v>0.35890410958904112</v>
       </c>
       <c r="AI111">
         <v>21</v>
@@ -18624,7 +18645,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="112" spans="1:43">
+    <row r="112" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>108</v>
       </c>
@@ -18725,7 +18746,7 @@
         <v>46259</v>
       </c>
       <c r="AH112">
-        <v>5.372602739726028</v>
+        <v>5.3726027397260276</v>
       </c>
       <c r="AI112">
         <v>21</v>
@@ -18755,7 +18776,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="113" spans="1:43">
+    <row r="113" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>109</v>
       </c>
@@ -18856,7 +18877,7 @@
         <v>46259</v>
       </c>
       <c r="AH113">
-        <v>4.528767123287671</v>
+        <v>4.5287671232876709</v>
       </c>
       <c r="AI113">
         <v>21</v>
@@ -18886,7 +18907,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="114" spans="1:43">
+    <row r="114" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>110</v>
       </c>
@@ -18987,7 +19008,7 @@
         <v>46259</v>
       </c>
       <c r="AH114">
-        <v>4.583561643835616</v>
+        <v>4.5835616438356164</v>
       </c>
       <c r="AI114">
         <v>21</v>
@@ -19017,7 +19038,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="115" spans="1:43">
+    <row r="115" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>111</v>
       </c>
@@ -19118,7 +19139,7 @@
         <v>46259</v>
       </c>
       <c r="AH115">
-        <v>4.526027397260274</v>
+        <v>4.5260273972602736</v>
       </c>
       <c r="AI115">
         <v>21</v>
@@ -19148,7 +19169,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="116" spans="1:43">
+    <row r="116" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>112</v>
       </c>
@@ -19249,7 +19270,7 @@
         <v>46259</v>
       </c>
       <c r="AH116">
-        <v>4.528767123287671</v>
+        <v>4.5287671232876709</v>
       </c>
       <c r="AI116">
         <v>21</v>
@@ -19279,7 +19300,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="117" spans="1:43">
+    <row r="117" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B117">
         <v>1336</v>
       </c>
@@ -19407,7 +19428,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="118" spans="1:43">
+    <row r="118" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>113</v>
       </c>
@@ -19538,7 +19559,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="119" spans="1:43">
+    <row r="119" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>114</v>
       </c>
@@ -19639,7 +19660,7 @@
         <v>46259</v>
       </c>
       <c r="AH119">
-        <v>2.63013698630137</v>
+        <v>2.6301369863013702</v>
       </c>
       <c r="AI119">
         <v>21</v>
@@ -19669,7 +19690,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="120" spans="1:43">
+    <row r="120" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>115</v>
       </c>
@@ -19770,7 +19791,7 @@
         <v>46259</v>
       </c>
       <c r="AH120">
-        <v>2.410958904109589</v>
+        <v>2.4109589041095889</v>
       </c>
       <c r="AI120">
         <v>21</v>
@@ -19800,7 +19821,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="121" spans="1:43">
+    <row r="121" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>116</v>
       </c>
@@ -19931,7 +19952,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="122" spans="1:43">
+    <row r="122" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>117</v>
       </c>
@@ -20062,7 +20083,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="123" spans="1:43">
+    <row r="123" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>118</v>
       </c>
@@ -20193,7 +20214,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="124" spans="1:43">
+    <row r="124" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>119</v>
       </c>
@@ -20294,7 +20315,7 @@
         <v>46259</v>
       </c>
       <c r="AH124">
-        <v>2.263013698630137</v>
+        <v>2.2630136986301368</v>
       </c>
       <c r="AI124">
         <v>21</v>
@@ -20324,7 +20345,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="125" spans="1:43">
+    <row r="125" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>120</v>
       </c>
@@ -20425,7 +20446,7 @@
         <v>46259</v>
       </c>
       <c r="AH125">
-        <v>6.586301369863014</v>
+        <v>6.5863013698630137</v>
       </c>
       <c r="AI125">
         <v>30</v>
@@ -20455,7 +20476,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="126" spans="1:43">
+    <row r="126" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>120</v>
       </c>
@@ -20478,7 +20499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:43">
+    <row r="127" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>121</v>
       </c>
@@ -20579,7 +20600,7 @@
         <v>46259</v>
       </c>
       <c r="AH127">
-        <v>12.26575342465753</v>
+        <v>12.265753424657531</v>
       </c>
       <c r="AI127">
         <v>30</v>
@@ -20609,7 +20630,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="128" spans="1:43">
+    <row r="128" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>122</v>
       </c>
@@ -20710,7 +20731,7 @@
         <v>46259</v>
       </c>
       <c r="AH128">
-        <v>5.964383561643835</v>
+        <v>5.9643835616438352</v>
       </c>
       <c r="AI128">
         <v>30</v>
@@ -20740,7 +20761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:43">
+    <row r="129" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>123</v>
       </c>
@@ -20841,7 +20862,7 @@
         <v>46259</v>
       </c>
       <c r="AH129">
-        <v>5.797260273972602</v>
+        <v>5.7972602739726016</v>
       </c>
       <c r="AI129">
         <v>21</v>
@@ -20871,7 +20892,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="130" spans="1:43">
+    <row r="130" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>124</v>
       </c>
@@ -20972,7 +20993,7 @@
         <v>46259</v>
       </c>
       <c r="AH130">
-        <v>5.153424657534247</v>
+        <v>5.1534246575342468</v>
       </c>
       <c r="AI130">
         <v>30</v>
@@ -21002,7 +21023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:43">
+    <row r="131" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>125</v>
       </c>
@@ -21103,7 +21124,7 @@
         <v>46259</v>
       </c>
       <c r="AH131">
-        <v>5.178082191780822</v>
+        <v>5.1780821917808222</v>
       </c>
       <c r="AI131">
         <v>30</v>
@@ -21133,7 +21154,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="132" spans="1:43">
+    <row r="132" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B132">
         <v>1135</v>
       </c>
@@ -21231,7 +21252,7 @@
         <v>46259</v>
       </c>
       <c r="AH132">
-        <v>0.1506849315068493</v>
+        <v>0.15068493150684931</v>
       </c>
       <c r="AI132">
         <v>21</v>
@@ -21261,7 +21282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:43">
+    <row r="133" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>126</v>
       </c>
@@ -21362,7 +21383,7 @@
         <v>46259</v>
       </c>
       <c r="AH133">
-        <v>4.235616438356164</v>
+        <v>4.2356164383561641</v>
       </c>
       <c r="AI133">
         <v>21</v>
@@ -21392,7 +21413,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="134" spans="1:43">
+    <row r="134" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>127</v>
       </c>
@@ -21493,7 +21514,7 @@
         <v>46259</v>
       </c>
       <c r="AH134">
-        <v>4.235616438356164</v>
+        <v>4.2356164383561641</v>
       </c>
       <c r="AI134">
         <v>21</v>
@@ -21523,7 +21544,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="135" spans="1:43">
+    <row r="135" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>128</v>
       </c>
@@ -21624,7 +21645,7 @@
         <v>46259</v>
       </c>
       <c r="AH135">
-        <v>4.723287671232876</v>
+        <v>4.7232876712328764</v>
       </c>
       <c r="AI135">
         <v>21</v>
@@ -21654,7 +21675,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="136" spans="1:43">
+    <row r="136" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>129</v>
       </c>
@@ -21755,7 +21776,7 @@
         <v>46259</v>
       </c>
       <c r="AH136">
-        <v>4.29041095890411</v>
+        <v>4.2904109589041104</v>
       </c>
       <c r="AI136">
         <v>21</v>
@@ -21785,7 +21806,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="137" spans="1:43">
+    <row r="137" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>130</v>
       </c>
@@ -21886,7 +21907,7 @@
         <v>46259</v>
       </c>
       <c r="AH137">
-        <v>4.553424657534246</v>
+        <v>4.5534246575342463</v>
       </c>
       <c r="AI137">
         <v>21</v>
@@ -21916,7 +21937,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="138" spans="1:43">
+    <row r="138" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>131</v>
       </c>
@@ -22017,7 +22038,7 @@
         <v>46259</v>
       </c>
       <c r="AH138">
-        <v>1.498630136986301</v>
+        <v>1.4986301369863011</v>
       </c>
       <c r="AI138">
         <v>21</v>
@@ -22047,7 +22068,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="139" spans="1:43">
+    <row r="139" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>132</v>
       </c>
@@ -22178,7 +22199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:43">
+    <row r="140" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>133</v>
       </c>
@@ -22309,7 +22330,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="141" spans="1:43">
+    <row r="141" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>134</v>
       </c>
@@ -22440,7 +22461,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="142" spans="1:43">
+    <row r="142" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>135</v>
       </c>
@@ -22571,7 +22592,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="143" spans="1:43">
+    <row r="143" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>136</v>
       </c>
@@ -22672,7 +22693,7 @@
         <v>46259</v>
       </c>
       <c r="AH143">
-        <v>4.487671232876712</v>
+        <v>4.4876712328767123</v>
       </c>
       <c r="AI143">
         <v>21</v>
@@ -22702,7 +22723,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="144" spans="1:43">
+    <row r="144" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>137</v>
       </c>
@@ -22803,7 +22824,7 @@
         <v>46259</v>
       </c>
       <c r="AH144">
-        <v>4.468493150684932</v>
+        <v>4.4684931506849317</v>
       </c>
       <c r="AI144">
         <v>21</v>
@@ -22833,7 +22854,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="145" spans="1:43">
+    <row r="145" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>138</v>
       </c>
@@ -22934,7 +22955,7 @@
         <v>46259</v>
       </c>
       <c r="AH145">
-        <v>1.857534246575342</v>
+        <v>1.8575342465753419</v>
       </c>
       <c r="AI145">
         <v>21</v>
@@ -22964,7 +22985,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="146" spans="1:43">
+    <row r="146" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>139</v>
       </c>
@@ -23065,7 +23086,7 @@
         <v>46259</v>
       </c>
       <c r="AH146">
-        <v>4.389041095890411</v>
+        <v>4.3890410958904109</v>
       </c>
       <c r="AI146">
         <v>21</v>
@@ -23095,7 +23116,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="147" spans="1:43">
+    <row r="147" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>140</v>
       </c>
@@ -23196,7 +23217,7 @@
         <v>46259</v>
       </c>
       <c r="AH147">
-        <v>3.791780821917808</v>
+        <v>3.7917808219178082</v>
       </c>
       <c r="AI147">
         <v>21</v>
@@ -23226,7 +23247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:43">
+    <row r="148" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>141</v>
       </c>
@@ -23327,7 +23348,7 @@
         <v>46259</v>
       </c>
       <c r="AH148">
-        <v>3.786301369863014</v>
+        <v>3.7863013698630139</v>
       </c>
       <c r="AI148">
         <v>21</v>
@@ -23357,7 +23378,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="149" spans="1:43">
+    <row r="149" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>142</v>
       </c>
@@ -23458,7 +23479,7 @@
         <v>46259</v>
       </c>
       <c r="AH149">
-        <v>3.736986301369863</v>
+        <v>3.7369863013698632</v>
       </c>
       <c r="AI149">
         <v>21</v>
@@ -23488,7 +23509,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="150" spans="1:43">
+    <row r="150" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>143</v>
       </c>
@@ -23589,7 +23610,7 @@
         <v>46259</v>
       </c>
       <c r="AH150">
-        <v>2.545205479452055</v>
+        <v>2.5452054794520551</v>
       </c>
       <c r="AI150">
         <v>21</v>
@@ -23619,7 +23640,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="151" spans="1:43">
+    <row r="151" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>144</v>
       </c>
@@ -23720,7 +23741,7 @@
         <v>46259</v>
       </c>
       <c r="AH151">
-        <v>5.967123287671233</v>
+        <v>5.9671232876712326</v>
       </c>
       <c r="AI151">
         <v>21</v>
@@ -23750,7 +23771,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="152" spans="1:43">
+    <row r="152" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>145</v>
       </c>
@@ -23851,7 +23872,7 @@
         <v>46259</v>
       </c>
       <c r="AH152">
-        <v>3.101369863013699</v>
+        <v>3.1013698630136992</v>
       </c>
       <c r="AI152">
         <v>21</v>
@@ -23881,7 +23902,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="153" spans="1:43">
+    <row r="153" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>146</v>
       </c>
@@ -23982,7 +24003,7 @@
         <v>46259</v>
       </c>
       <c r="AH153">
-        <v>5.64931506849315</v>
+        <v>5.6493150684931503</v>
       </c>
       <c r="AI153">
         <v>21</v>
@@ -24012,7 +24033,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="154" spans="1:43">
+    <row r="154" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>147</v>
       </c>
@@ -24113,7 +24134,7 @@
         <v>46259</v>
       </c>
       <c r="AH154">
-        <v>5.402739726027397</v>
+        <v>5.4027397260273968</v>
       </c>
       <c r="AI154">
         <v>21</v>
@@ -24143,7 +24164,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="155" spans="1:43">
+    <row r="155" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>148</v>
       </c>
@@ -24244,7 +24265,7 @@
         <v>46259</v>
       </c>
       <c r="AH155">
-        <v>5.30958904109589</v>
+        <v>5.3095890410958901</v>
       </c>
       <c r="AI155">
         <v>21</v>
@@ -24274,7 +24295,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="156" spans="1:43">
+    <row r="156" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>149</v>
       </c>
@@ -24375,7 +24396,7 @@
         <v>46259</v>
       </c>
       <c r="AH156">
-        <v>5.038356164383561</v>
+        <v>5.0383561643835613</v>
       </c>
       <c r="AI156">
         <v>21</v>
@@ -24405,7 +24426,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="157" spans="1:43">
+    <row r="157" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>150</v>
       </c>
@@ -24506,7 +24527,7 @@
         <v>46259</v>
       </c>
       <c r="AH157">
-        <v>5.038356164383561</v>
+        <v>5.0383561643835613</v>
       </c>
       <c r="AI157">
         <v>21</v>
@@ -24536,7 +24557,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="158" spans="1:43">
+    <row r="158" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>151</v>
       </c>
@@ -24637,7 +24658,7 @@
         <v>46259</v>
       </c>
       <c r="AH158">
-        <v>5.038356164383561</v>
+        <v>5.0383561643835613</v>
       </c>
       <c r="AI158">
         <v>21</v>
@@ -24667,7 +24688,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="159" spans="1:43">
+    <row r="159" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>152</v>
       </c>
@@ -24768,7 +24789,7 @@
         <v>46259</v>
       </c>
       <c r="AH159">
-        <v>5.038356164383561</v>
+        <v>5.0383561643835613</v>
       </c>
       <c r="AI159">
         <v>21</v>
@@ -24798,7 +24819,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="160" spans="1:43">
+    <row r="160" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>153</v>
       </c>
@@ -24899,7 +24920,7 @@
         <v>46259</v>
       </c>
       <c r="AH160">
-        <v>1.83013698630137</v>
+        <v>1.8301369863013699</v>
       </c>
       <c r="AI160">
         <v>21</v>
@@ -24929,7 +24950,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="161" spans="1:43">
+    <row r="161" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>154</v>
       </c>
@@ -25030,7 +25051,7 @@
         <v>46259</v>
       </c>
       <c r="AH161">
-        <v>4.528767123287671</v>
+        <v>4.5287671232876709</v>
       </c>
       <c r="AI161">
         <v>21</v>
@@ -25060,7 +25081,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="162" spans="1:43">
+    <row r="162" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>155</v>
       </c>
@@ -25161,7 +25182,7 @@
         <v>46259</v>
       </c>
       <c r="AH162">
-        <v>4.389041095890411</v>
+        <v>4.3890410958904109</v>
       </c>
       <c r="AI162">
         <v>21</v>
@@ -25191,7 +25212,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="163" spans="1:43">
+    <row r="163" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>156</v>
       </c>
@@ -25292,7 +25313,7 @@
         <v>46259</v>
       </c>
       <c r="AH163">
-        <v>4.389041095890411</v>
+        <v>4.3890410958904109</v>
       </c>
       <c r="AI163">
         <v>21</v>
@@ -25322,7 +25343,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="164" spans="1:43">
+    <row r="164" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>157</v>
       </c>
@@ -25453,7 +25474,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="165" spans="1:43">
+    <row r="165" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>158</v>
       </c>
@@ -25554,7 +25575,7 @@
         <v>46259</v>
       </c>
       <c r="AH165">
-        <v>3.994520547945205</v>
+        <v>3.9945205479452048</v>
       </c>
       <c r="AI165">
         <v>21</v>
@@ -25584,7 +25605,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="166" spans="1:43">
+    <row r="166" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>159</v>
       </c>
@@ -25685,7 +25706,7 @@
         <v>46259</v>
       </c>
       <c r="AH166">
-        <v>3.964383561643836</v>
+        <v>3.9643835616438361</v>
       </c>
       <c r="AI166">
         <v>21</v>
@@ -25715,7 +25736,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="167" spans="1:43">
+    <row r="167" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>161</v>
       </c>
@@ -25816,7 +25837,7 @@
         <v>46259</v>
       </c>
       <c r="AH167">
-        <v>2.33972602739726</v>
+        <v>2.3397260273972602</v>
       </c>
       <c r="AI167">
         <v>21</v>
@@ -25846,7 +25867,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="168" spans="1:43">
+    <row r="168" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>162</v>
       </c>
@@ -25947,7 +25968,7 @@
         <v>46259</v>
       </c>
       <c r="AH168">
-        <v>13.54794520547945</v>
+        <v>13.547945205479451</v>
       </c>
       <c r="AI168">
         <v>30</v>
@@ -25977,7 +25998,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="169" spans="1:43">
+    <row r="169" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>163</v>
       </c>
@@ -26078,7 +26099,7 @@
         <v>46259</v>
       </c>
       <c r="AH169">
-        <v>5.153424657534247</v>
+        <v>5.1534246575342468</v>
       </c>
       <c r="AI169">
         <v>30</v>
@@ -26108,7 +26129,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="170" spans="1:43">
+    <row r="170" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>164</v>
       </c>
@@ -26209,7 +26230,7 @@
         <v>46259</v>
       </c>
       <c r="AH170">
-        <v>5.345205479452055</v>
+        <v>5.3452054794520549</v>
       </c>
       <c r="AI170">
         <v>30</v>
@@ -26239,7 +26260,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="171" spans="1:43">
+    <row r="171" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>165</v>
       </c>
@@ -26370,7 +26391,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="172" spans="1:43">
+    <row r="172" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>166</v>
       </c>
@@ -26471,7 +26492,7 @@
         <v>46259</v>
       </c>
       <c r="AH172">
-        <v>2.843835616438356</v>
+        <v>2.8438356164383558</v>
       </c>
       <c r="AI172">
         <v>21</v>
@@ -26501,7 +26522,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="173" spans="1:43">
+    <row r="173" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>167</v>
       </c>
@@ -26632,7 +26653,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="174" spans="1:43">
+    <row r="174" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>168</v>
       </c>
@@ -26733,7 +26754,7 @@
         <v>46259</v>
       </c>
       <c r="AH174">
-        <v>1.96986301369863</v>
+        <v>1.9698630136986299</v>
       </c>
       <c r="AI174">
         <v>21</v>
@@ -26763,7 +26784,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="175" spans="1:43">
+    <row r="175" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>169</v>
       </c>
@@ -26870,13 +26891,13 @@
         <v>21</v>
       </c>
       <c r="AJ175">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="AK175">
-        <v>241</v>
+        <v>375</v>
       </c>
       <c r="AL175">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="AM175">
         <v>0</v>
@@ -26894,7 +26915,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="176" spans="1:43">
+    <row r="176" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>170</v>
       </c>
@@ -26995,7 +27016,7 @@
         <v>46259</v>
       </c>
       <c r="AH176">
-        <v>5.876712328767123</v>
+        <v>5.8767123287671232</v>
       </c>
       <c r="AI176">
         <v>30</v>
@@ -27025,7 +27046,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="177" spans="1:43">
+    <row r="177" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>171</v>
       </c>
@@ -27156,7 +27177,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="178" spans="1:43">
+    <row r="178" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>172</v>
       </c>
@@ -27257,7 +27278,7 @@
         <v>46259</v>
       </c>
       <c r="AH178">
-        <v>2.961643835616438</v>
+        <v>2.9616438356164378</v>
       </c>
       <c r="AI178">
         <v>21</v>
@@ -27287,7 +27308,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="179" spans="1:43">
+    <row r="179" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>173</v>
       </c>
@@ -27388,7 +27409,7 @@
         <v>46259</v>
       </c>
       <c r="AH179">
-        <v>2.468493150684932</v>
+        <v>2.4684931506849321</v>
       </c>
       <c r="AI179">
         <v>21</v>
@@ -27418,7 +27439,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="180" spans="1:43">
+    <row r="180" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>174</v>
       </c>
@@ -27519,7 +27540,7 @@
         <v>46259</v>
       </c>
       <c r="AH180">
-        <v>2.252054794520548</v>
+        <v>2.2520547945205478</v>
       </c>
       <c r="AI180">
         <v>21</v>
@@ -27549,7 +27570,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="181" spans="1:43">
+    <row r="181" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>175</v>
       </c>
@@ -27680,7 +27701,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="182" spans="1:43">
+    <row r="182" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>176</v>
       </c>
@@ -27811,7 +27832,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="183" spans="1:43">
+    <row r="183" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>177</v>
       </c>
@@ -27942,7 +27963,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="184" spans="1:43">
+    <row r="184" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>178</v>
       </c>
@@ -28073,7 +28094,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="185" spans="1:43">
+    <row r="185" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>179</v>
       </c>
@@ -28204,7 +28225,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="186" spans="1:43">
+    <row r="186" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>180</v>
       </c>
@@ -28305,7 +28326,7 @@
         <v>46259</v>
       </c>
       <c r="AH186">
-        <v>1.745205479452055</v>
+        <v>1.7452054794520551</v>
       </c>
       <c r="AI186">
         <v>21</v>
@@ -28335,7 +28356,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="187" spans="1:43">
+    <row r="187" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>181</v>
       </c>
@@ -28436,7 +28457,7 @@
         <v>46259</v>
       </c>
       <c r="AH187">
-        <v>1.389041095890411</v>
+        <v>1.3890410958904109</v>
       </c>
       <c r="AI187">
         <v>21</v>
@@ -28468,7 +28489,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="S170" r:id="rId1"/>
+    <hyperlink ref="S170" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Staffdata.xlsx
+++ b/Staffdata.xlsx
@@ -1,26 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3113719057d24bf/Desktop/HR-Forms-Site/HRFORMAS/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_05E48499FC67680F1964AE368160343238AA41AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F39E4F8-EC7F-4B82-A65E-7BCB1AF9CCFE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -2185,7 +2174,7 @@
     <t>-</t>
   </si>
   <si>
-    <t> 966577040481</t>
+    <t xml:space="preserve"> 966577040481</t>
   </si>
   <si>
     <t>malbatil@outlook.sa</t>
@@ -2496,10 +2485,10 @@
     <t>HAMDILLHJ038@GMAIL.COM</t>
   </si>
   <si>
-    <t> omarzar392@gmail.com</t>
-  </si>
-  <si>
-    <t> ark870725@gmail.com</t>
+    <t xml:space="preserve"> omarzar392@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ark870725@gmail.com</t>
   </si>
   <si>
     <t>waelgomaa1wg@gmail.com</t>
@@ -2572,7 +2561,7 @@
     <t>INFO2@HAIL-HOUSE.SA</t>
   </si>
   <si>
-    <t> Sarah_elkhatib@outlook.com</t>
+    <t xml:space="preserve"> Sarah_elkhatib@outlook.com</t>
   </si>
   <si>
     <t xml:space="preserve"> mohannad.fakhry00@gmail.com</t>
@@ -3916,11 +3905,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3966,26 +3955,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="ارتباط تشعبي" xfId="1" builtinId="8"/>
-    <cellStyle name="عادي" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4023,7 +4004,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4057,7 +4038,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4092,10 +4072,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4268,11 +4247,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AQ187"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4403,7 +4382,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4504,7 +4483,7 @@
         <v>46259</v>
       </c>
       <c r="AH2">
-        <v>8.7260273972602747</v>
+        <v>8.726027397260275</v>
       </c>
       <c r="AI2">
         <v>30</v>
@@ -4534,7 +4513,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4635,7 +4614,7 @@
         <v>46259</v>
       </c>
       <c r="AH3">
-        <v>13.635616438356161</v>
+        <v>13.63561643835616</v>
       </c>
       <c r="AI3">
         <v>30</v>
@@ -4665,7 +4644,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4766,7 +4745,7 @@
         <v>46259</v>
       </c>
       <c r="AH4">
-        <v>5.8904109589041092</v>
+        <v>5.890410958904109</v>
       </c>
       <c r="AI4">
         <v>30</v>
@@ -4796,7 +4775,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4897,7 +4876,7 @@
         <v>46259</v>
       </c>
       <c r="AH5">
-        <v>6.0465753424657533</v>
+        <v>6.046575342465753</v>
       </c>
       <c r="AI5">
         <v>21</v>
@@ -4927,7 +4906,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5028,7 +5007,7 @@
         <v>46259</v>
       </c>
       <c r="AH6">
-        <v>6.4027397260273968</v>
+        <v>6.402739726027397</v>
       </c>
       <c r="AI6">
         <v>21</v>
@@ -5058,7 +5037,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5159,7 +5138,7 @@
         <v>46259</v>
       </c>
       <c r="AH7">
-        <v>5.7041095890410958</v>
+        <v>5.704109589041096</v>
       </c>
       <c r="AI7">
         <v>30</v>
@@ -5189,7 +5168,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5320,7 +5299,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5451,7 +5430,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5552,7 +5531,7 @@
         <v>46259</v>
       </c>
       <c r="AH10">
-        <v>6.7534246575342456</v>
+        <v>6.753424657534246</v>
       </c>
       <c r="AI10">
         <v>30</v>
@@ -5582,7 +5561,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5713,7 +5692,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5814,7 +5793,7 @@
         <v>46259</v>
       </c>
       <c r="AH12">
-        <v>5.7506849315068491</v>
+        <v>5.750684931506849</v>
       </c>
       <c r="AI12">
         <v>21</v>
@@ -5844,7 +5823,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5975,7 +5954,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6076,7 +6055,7 @@
         <v>46259</v>
       </c>
       <c r="AH14">
-        <v>0.30410958904109592</v>
+        <v>0.3041095890410959</v>
       </c>
       <c r="AI14">
         <v>21</v>
@@ -6106,7 +6085,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6207,7 +6186,7 @@
         <v>46259</v>
       </c>
       <c r="AH15">
-        <v>3.9835616438356158</v>
+        <v>3.983561643835616</v>
       </c>
       <c r="AI15">
         <v>21</v>
@@ -6237,7 +6216,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6338,7 +6317,7 @@
         <v>46259</v>
       </c>
       <c r="AH16">
-        <v>2.8986301369863008</v>
+        <v>2.898630136986301</v>
       </c>
       <c r="AI16">
         <v>21</v>
@@ -6368,7 +6347,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:43">
       <c r="A17">
         <v>16</v>
       </c>
@@ -6469,7 +6448,7 @@
         <v>46259</v>
       </c>
       <c r="AH17">
-        <v>1.6739726027397259</v>
+        <v>1.673972602739726</v>
       </c>
       <c r="AI17">
         <v>21</v>
@@ -6499,7 +6478,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:43">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6600,7 +6579,7 @@
         <v>46259</v>
       </c>
       <c r="AH18">
-        <v>2.0493150684931511</v>
+        <v>2.049315068493151</v>
       </c>
       <c r="AI18">
         <v>21</v>
@@ -6630,7 +6609,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:43">
       <c r="A19">
         <v>18</v>
       </c>
@@ -6731,7 +6710,7 @@
         <v>46259</v>
       </c>
       <c r="AH19">
-        <v>2.0356164383561639</v>
+        <v>2.035616438356164</v>
       </c>
       <c r="AI19">
         <v>21</v>
@@ -6761,7 +6740,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43">
       <c r="A20">
         <v>19</v>
       </c>
@@ -6862,7 +6841,7 @@
         <v>46259</v>
       </c>
       <c r="AH20">
-        <v>1.5123287671232879</v>
+        <v>1.512328767123288</v>
       </c>
       <c r="AI20">
         <v>21</v>
@@ -6892,7 +6871,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:43">
       <c r="A21">
         <v>20</v>
       </c>
@@ -6993,7 +6972,7 @@
         <v>46259</v>
       </c>
       <c r="AH21">
-        <v>2.0356164383561639</v>
+        <v>2.035616438356164</v>
       </c>
       <c r="AI21">
         <v>21</v>
@@ -7023,7 +7002,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43">
       <c r="A22">
         <v>21</v>
       </c>
@@ -7154,7 +7133,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:43">
       <c r="A23">
         <v>22</v>
       </c>
@@ -7285,7 +7264,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:43">
       <c r="A24">
         <v>23</v>
       </c>
@@ -7416,7 +7395,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:43">
       <c r="A25">
         <v>24</v>
       </c>
@@ -7517,7 +7496,7 @@
         <v>46259</v>
       </c>
       <c r="AH25">
-        <v>0.76164383561643834</v>
+        <v>0.7616438356164383</v>
       </c>
       <c r="AI25">
         <v>21</v>
@@ -7547,7 +7526,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:43">
       <c r="A26">
         <v>25</v>
       </c>
@@ -7648,7 +7627,7 @@
         <v>46259</v>
       </c>
       <c r="AH26">
-        <v>0.76164383561643834</v>
+        <v>0.7616438356164383</v>
       </c>
       <c r="AI26">
         <v>21</v>
@@ -7678,7 +7657,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:43">
       <c r="A27">
         <v>26</v>
       </c>
@@ -7779,7 +7758,7 @@
         <v>46259</v>
       </c>
       <c r="AH27">
-        <v>6.7369863013698632</v>
+        <v>6.736986301369863</v>
       </c>
       <c r="AI27">
         <v>30</v>
@@ -7809,7 +7788,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:43">
       <c r="A28">
         <v>27</v>
       </c>
@@ -7910,7 +7889,7 @@
         <v>46259</v>
       </c>
       <c r="AH28">
-        <v>12.112328767123291</v>
+        <v>12.11232876712329</v>
       </c>
       <c r="AI28">
         <v>30</v>
@@ -7940,7 +7919,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:43">
       <c r="A29">
         <v>28</v>
       </c>
@@ -8041,7 +8020,7 @@
         <v>46259</v>
       </c>
       <c r="AH29">
-        <v>3.4876712328767119</v>
+        <v>3.487671232876712</v>
       </c>
       <c r="AI29">
         <v>21</v>
@@ -8071,7 +8050,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:43">
       <c r="A30">
         <v>29</v>
       </c>
@@ -8172,7 +8151,7 @@
         <v>46259</v>
       </c>
       <c r="AH30">
-        <v>15.076712328767121</v>
+        <v>15.07671232876712</v>
       </c>
       <c r="AI30">
         <v>30</v>
@@ -8202,7 +8181,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:43">
       <c r="A31">
         <v>30</v>
       </c>
@@ -8303,7 +8282,7 @@
         <v>46259</v>
       </c>
       <c r="AH31">
-        <v>15.076712328767121</v>
+        <v>15.07671232876712</v>
       </c>
       <c r="AI31">
         <v>30</v>
@@ -8333,7 +8312,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:43">
       <c r="A32">
         <v>31</v>
       </c>
@@ -8464,7 +8443,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:43">
       <c r="A33">
         <v>32</v>
       </c>
@@ -8565,7 +8544,7 @@
         <v>46259</v>
       </c>
       <c r="AH33">
-        <v>15.167123287671229</v>
+        <v>15.16712328767123</v>
       </c>
       <c r="AI33">
         <v>30</v>
@@ -8595,7 +8574,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:43">
       <c r="A34">
         <v>33</v>
       </c>
@@ -8696,7 +8675,7 @@
         <v>46259</v>
       </c>
       <c r="AH34">
-        <v>4.6109589041095891</v>
+        <v>4.610958904109589</v>
       </c>
       <c r="AI34">
         <v>21</v>
@@ -8726,7 +8705,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:43">
       <c r="A35">
         <v>34</v>
       </c>
@@ -8827,7 +8806,7 @@
         <v>46259</v>
       </c>
       <c r="AH35">
-        <v>4.5424657534246577</v>
+        <v>4.542465753424658</v>
       </c>
       <c r="AI35">
         <v>21</v>
@@ -8857,7 +8836,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="36" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:43">
       <c r="A36">
         <v>35</v>
       </c>
@@ -8958,7 +8937,7 @@
         <v>46259</v>
       </c>
       <c r="AH36">
-        <v>13.241095890410961</v>
+        <v>13.24109589041096</v>
       </c>
       <c r="AI36">
         <v>30</v>
@@ -8988,7 +8967,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:43">
       <c r="A37">
         <v>36</v>
       </c>
@@ -9119,7 +9098,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:43">
       <c r="A38">
         <v>37</v>
       </c>
@@ -9250,7 +9229,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="39" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:43">
       <c r="A39">
         <v>38</v>
       </c>
@@ -9351,7 +9330,7 @@
         <v>46259</v>
       </c>
       <c r="AH39">
-        <v>6.7095890410958896</v>
+        <v>6.70958904109589</v>
       </c>
       <c r="AI39">
         <v>30</v>
@@ -9381,7 +9360,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:43">
       <c r="A40">
         <v>39</v>
       </c>
@@ -9482,7 +9461,7 @@
         <v>46259</v>
       </c>
       <c r="AH40">
-        <v>6.5095890410958903</v>
+        <v>6.50958904109589</v>
       </c>
       <c r="AI40">
         <v>30</v>
@@ -9512,7 +9491,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:43">
       <c r="A41">
         <v>40</v>
       </c>
@@ -9613,7 +9592,7 @@
         <v>46259</v>
       </c>
       <c r="AH41">
-        <v>6.5506849315068489</v>
+        <v>6.550684931506849</v>
       </c>
       <c r="AI41">
         <v>21</v>
@@ -9643,7 +9622,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:43">
       <c r="A42">
         <v>41</v>
       </c>
@@ -9774,7 +9753,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:43">
       <c r="A43">
         <v>42</v>
       </c>
@@ -9875,7 +9854,7 @@
         <v>46259</v>
       </c>
       <c r="AH43">
-        <v>8.7534246575342465</v>
+        <v>8.753424657534246</v>
       </c>
       <c r="AI43">
         <v>30</v>
@@ -9905,7 +9884,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:43">
       <c r="A44">
         <v>43</v>
       </c>
@@ -10006,7 +9985,7 @@
         <v>46259</v>
       </c>
       <c r="AH44">
-        <v>5.7534246575342456</v>
+        <v>5.753424657534246</v>
       </c>
       <c r="AI44">
         <v>21</v>
@@ -10036,7 +10015,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:43">
       <c r="A45">
         <v>44</v>
       </c>
@@ -10137,7 +10116,7 @@
         <v>46259</v>
       </c>
       <c r="AH45">
-        <v>5.7342465753424658</v>
+        <v>5.734246575342466</v>
       </c>
       <c r="AI45">
         <v>21</v>
@@ -10167,7 +10146,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:43">
       <c r="A46">
         <v>45</v>
       </c>
@@ -10268,7 +10247,7 @@
         <v>46259</v>
       </c>
       <c r="AH46">
-        <v>5.6273972602739724</v>
+        <v>5.627397260273972</v>
       </c>
       <c r="AI46">
         <v>30</v>
@@ -10298,7 +10277,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:43">
       <c r="A47">
         <v>46</v>
       </c>
@@ -10399,7 +10378,7 @@
         <v>46259</v>
       </c>
       <c r="AH47">
-        <v>4.2273972602739729</v>
+        <v>4.227397260273973</v>
       </c>
       <c r="AI47">
         <v>21</v>
@@ -10429,7 +10408,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:43">
       <c r="A48">
         <v>47</v>
       </c>
@@ -10560,7 +10539,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="49" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:43">
       <c r="A49">
         <v>48</v>
       </c>
@@ -10661,7 +10640,7 @@
         <v>46259</v>
       </c>
       <c r="AH49">
-        <v>4.1589041095890407</v>
+        <v>4.158904109589041</v>
       </c>
       <c r="AI49">
         <v>21</v>
@@ -10691,7 +10670,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="50" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:43">
       <c r="A50">
         <v>49</v>
       </c>
@@ -10792,7 +10771,7 @@
         <v>46259</v>
       </c>
       <c r="AH50">
-        <v>3.9863013698630141</v>
+        <v>3.986301369863014</v>
       </c>
       <c r="AI50">
         <v>21</v>
@@ -10822,7 +10801,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="51" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:43">
       <c r="A51">
         <v>50</v>
       </c>
@@ -10923,7 +10902,7 @@
         <v>46259</v>
       </c>
       <c r="AH51">
-        <v>3.9643835616438361</v>
+        <v>3.964383561643836</v>
       </c>
       <c r="AI51">
         <v>21</v>
@@ -10953,7 +10932,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="52" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:43">
       <c r="A52">
         <v>51</v>
       </c>
@@ -11054,7 +11033,7 @@
         <v>46259</v>
       </c>
       <c r="AH52">
-        <v>3.9643835616438361</v>
+        <v>3.964383561643836</v>
       </c>
       <c r="AI52">
         <v>21</v>
@@ -11084,7 +11063,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="53" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:43">
       <c r="A53">
         <v>52</v>
       </c>
@@ -11215,7 +11194,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="54" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:43">
       <c r="A54">
         <v>53</v>
       </c>
@@ -11316,7 +11295,7 @@
         <v>46259</v>
       </c>
       <c r="AH54">
-        <v>1.9698630136986299</v>
+        <v>1.96986301369863</v>
       </c>
       <c r="AI54">
         <v>21</v>
@@ -11346,7 +11325,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="55" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:43">
       <c r="A55">
         <v>54</v>
       </c>
@@ -11447,7 +11426,7 @@
         <v>46259</v>
       </c>
       <c r="AH55">
-        <v>0.58356164383561648</v>
+        <v>0.5835616438356165</v>
       </c>
       <c r="AI55">
         <v>21</v>
@@ -11477,7 +11456,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="56" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:43">
       <c r="A56">
         <v>55</v>
       </c>
@@ -11578,7 +11557,7 @@
         <v>46259</v>
       </c>
       <c r="AH56">
-        <v>0.58356164383561648</v>
+        <v>0.5835616438356165</v>
       </c>
       <c r="AI56">
         <v>21</v>
@@ -11608,7 +11587,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="57" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:43">
       <c r="A57">
         <v>56</v>
       </c>
@@ -11709,7 +11688,7 @@
         <v>46259</v>
       </c>
       <c r="AH57">
-        <v>7.1506849315068486</v>
+        <v>7.150684931506849</v>
       </c>
       <c r="AI57">
         <v>30</v>
@@ -11739,7 +11718,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="58" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:43">
       <c r="A58">
         <v>57</v>
       </c>
@@ -11840,7 +11819,7 @@
         <v>46259</v>
       </c>
       <c r="AH58">
-        <v>7.4821917808219176</v>
+        <v>7.482191780821918</v>
       </c>
       <c r="AI58">
         <v>30</v>
@@ -11870,7 +11849,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="59" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:43">
       <c r="A59">
         <v>58</v>
       </c>
@@ -11971,7 +11950,7 @@
         <v>46259</v>
       </c>
       <c r="AH59">
-        <v>6.575342465753424E-2</v>
+        <v>0.06575342465753424</v>
       </c>
       <c r="AI59">
         <v>21</v>
@@ -12001,7 +11980,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="60" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:43">
       <c r="A60">
         <v>59</v>
       </c>
@@ -12102,7 +12081,7 @@
         <v>46259</v>
       </c>
       <c r="AH60">
-        <v>6.575342465753424E-2</v>
+        <v>0.06575342465753424</v>
       </c>
       <c r="AI60">
         <v>21</v>
@@ -12132,7 +12111,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="61" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:43">
       <c r="A61">
         <v>58</v>
       </c>
@@ -12233,7 +12212,7 @@
         <v>46259</v>
       </c>
       <c r="AH61">
-        <v>18.263013698630139</v>
+        <v>18.26301369863014</v>
       </c>
       <c r="AI61">
         <v>30</v>
@@ -12263,7 +12242,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="62" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:43">
       <c r="A62">
         <v>59</v>
       </c>
@@ -12364,7 +12343,7 @@
         <v>46259</v>
       </c>
       <c r="AH62">
-        <v>15.076712328767121</v>
+        <v>15.07671232876712</v>
       </c>
       <c r="AI62">
         <v>30</v>
@@ -12394,7 +12373,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="63" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:43">
       <c r="A63">
         <v>60</v>
       </c>
@@ -12495,7 +12474,7 @@
         <v>46259</v>
       </c>
       <c r="AH63">
-        <v>34.049315068493151</v>
+        <v>34.04931506849315</v>
       </c>
       <c r="AI63">
         <v>30</v>
@@ -12525,7 +12504,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="64" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:43">
       <c r="A64">
         <v>61</v>
       </c>
@@ -12626,7 +12605,7 @@
         <v>46259</v>
       </c>
       <c r="AH64">
-        <v>6.1753424657534248</v>
+        <v>6.175342465753425</v>
       </c>
       <c r="AI64">
         <v>30</v>
@@ -12656,7 +12635,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="65" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:43">
       <c r="A65">
         <v>62</v>
       </c>
@@ -12757,7 +12736,7 @@
         <v>46259</v>
       </c>
       <c r="AH65">
-        <v>1.8739726027397261</v>
+        <v>1.873972602739726</v>
       </c>
       <c r="AI65">
         <v>21</v>
@@ -12787,7 +12766,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="66" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:43">
       <c r="A66">
         <v>63</v>
       </c>
@@ -12888,7 +12867,7 @@
         <v>46259</v>
       </c>
       <c r="AH66">
-        <v>5.7534246575342456</v>
+        <v>5.753424657534246</v>
       </c>
       <c r="AI66">
         <v>21</v>
@@ -12918,7 +12897,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="67" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:43">
       <c r="A67">
         <v>64</v>
       </c>
@@ -13019,7 +12998,7 @@
         <v>46259</v>
       </c>
       <c r="AH67">
-        <v>18.046575342465751</v>
+        <v>18.04657534246575</v>
       </c>
       <c r="AI67">
         <v>30</v>
@@ -13049,7 +13028,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="68" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:43">
       <c r="A68">
         <v>65</v>
       </c>
@@ -13150,7 +13129,7 @@
         <v>46259</v>
       </c>
       <c r="AH68">
-        <v>9.5315068493150683</v>
+        <v>9.531506849315068</v>
       </c>
       <c r="AI68">
         <v>30</v>
@@ -13180,7 +13159,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="69" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:43">
       <c r="A69">
         <v>66</v>
       </c>
@@ -13311,7 +13290,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="70" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:43">
       <c r="A70">
         <v>67</v>
       </c>
@@ -13412,7 +13391,7 @@
         <v>46259</v>
       </c>
       <c r="AH70">
-        <v>10.608219178082191</v>
+        <v>10.60821917808219</v>
       </c>
       <c r="AI70">
         <v>30</v>
@@ -13442,7 +13421,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="71" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:43">
       <c r="A71">
         <v>68</v>
       </c>
@@ -13543,7 +13522,7 @@
         <v>46259</v>
       </c>
       <c r="AH71">
-        <v>0.33424657534246582</v>
+        <v>0.3342465753424658</v>
       </c>
       <c r="AI71">
         <v>21</v>
@@ -13573,7 +13552,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="72" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:43">
       <c r="A72">
         <v>69</v>
       </c>
@@ -13674,7 +13653,7 @@
         <v>46259</v>
       </c>
       <c r="AH72">
-        <v>0.33424657534246582</v>
+        <v>0.3342465753424658</v>
       </c>
       <c r="AI72">
         <v>21</v>
@@ -13704,7 +13683,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="73" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:43">
       <c r="A73">
         <v>70</v>
       </c>
@@ -13805,7 +13784,7 @@
         <v>46259</v>
       </c>
       <c r="AH73">
-        <v>2.9698630136986299</v>
+        <v>2.96986301369863</v>
       </c>
       <c r="AI73">
         <v>21</v>
@@ -13835,7 +13814,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="74" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:43">
       <c r="A74">
         <v>71</v>
       </c>
@@ -13966,7 +13945,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="75" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:43">
       <c r="A75">
         <v>72</v>
       </c>
@@ -14067,7 +14046,7 @@
         <v>46259</v>
       </c>
       <c r="AH75">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="AI75">
         <v>21</v>
@@ -14097,7 +14076,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="76" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:43">
       <c r="A76">
         <v>73</v>
       </c>
@@ -14198,7 +14177,7 @@
         <v>46259</v>
       </c>
       <c r="AH76">
-        <v>4.0684931506849313</v>
+        <v>4.068493150684931</v>
       </c>
       <c r="AI76">
         <v>21</v>
@@ -14228,7 +14207,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="77" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:43">
       <c r="A77">
         <v>74</v>
       </c>
@@ -14359,7 +14338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="78" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:43">
       <c r="A78">
         <v>75</v>
       </c>
@@ -14490,7 +14469,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="79" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:43">
       <c r="A79">
         <v>76</v>
       </c>
@@ -14591,7 +14570,7 @@
         <v>46259</v>
       </c>
       <c r="AH79">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
       <c r="AI79">
         <v>21</v>
@@ -14621,7 +14600,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="80" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:43">
       <c r="A80">
         <v>77</v>
       </c>
@@ -14722,7 +14701,7 @@
         <v>46259</v>
       </c>
       <c r="AH80">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
       <c r="AI80">
         <v>21</v>
@@ -14752,7 +14731,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="81" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:43">
       <c r="A81">
         <v>78</v>
       </c>
@@ -14853,7 +14832,7 @@
         <v>46259</v>
       </c>
       <c r="AH81">
-        <v>1.8191780821917809</v>
+        <v>1.819178082191781</v>
       </c>
       <c r="AI81">
         <v>21</v>
@@ -14883,7 +14862,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="82" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:43">
       <c r="A82">
         <v>79</v>
       </c>
@@ -14984,7 +14963,7 @@
         <v>46259</v>
       </c>
       <c r="AH82">
-        <v>1.6547945205479451</v>
+        <v>1.654794520547945</v>
       </c>
       <c r="AI82">
         <v>21</v>
@@ -15014,7 +14993,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="83" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:43">
       <c r="A83">
         <v>80</v>
       </c>
@@ -15115,7 +15094,7 @@
         <v>46259</v>
       </c>
       <c r="AH83">
-        <v>15.167123287671229</v>
+        <v>15.16712328767123</v>
       </c>
       <c r="AI83">
         <v>30</v>
@@ -15145,7 +15124,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="84" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:43">
       <c r="A84">
         <v>80</v>
       </c>
@@ -15186,7 +15165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:43">
       <c r="A85">
         <v>81</v>
       </c>
@@ -15287,7 +15266,7 @@
         <v>46259</v>
       </c>
       <c r="AH85">
-        <v>8.9753424657534246</v>
+        <v>8.975342465753425</v>
       </c>
       <c r="AI85">
         <v>30</v>
@@ -15317,7 +15296,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="86" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:43">
       <c r="A86">
         <v>82</v>
       </c>
@@ -15418,7 +15397,7 @@
         <v>46259</v>
       </c>
       <c r="AH86">
-        <v>6.7095890410958896</v>
+        <v>6.70958904109589</v>
       </c>
       <c r="AI86">
         <v>30</v>
@@ -15448,7 +15427,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="87" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:43">
       <c r="A87">
         <v>83</v>
       </c>
@@ -15549,7 +15528,7 @@
         <v>46259</v>
       </c>
       <c r="AH87">
-        <v>9.3232876712328761</v>
+        <v>9.323287671232876</v>
       </c>
       <c r="AI87">
         <v>30</v>
@@ -15579,7 +15558,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="88" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:43">
       <c r="A88">
         <v>84</v>
       </c>
@@ -15680,7 +15659,7 @@
         <v>46259</v>
       </c>
       <c r="AH88">
-        <v>14.035616438356159</v>
+        <v>14.03561643835616</v>
       </c>
       <c r="AI88">
         <v>30</v>
@@ -15710,7 +15689,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="89" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:43">
       <c r="A89">
         <v>85</v>
       </c>
@@ -15811,7 +15790,7 @@
         <v>46259</v>
       </c>
       <c r="AH89">
-        <v>1.7726027397260271</v>
+        <v>1.772602739726027</v>
       </c>
       <c r="AI89">
         <v>21</v>
@@ -15841,7 +15820,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="90" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:43">
       <c r="A90">
         <v>86</v>
       </c>
@@ -15942,7 +15921,7 @@
         <v>46259</v>
       </c>
       <c r="AH90">
-        <v>8.4082191780821915</v>
+        <v>8.408219178082192</v>
       </c>
       <c r="AI90">
         <v>30</v>
@@ -15972,7 +15951,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="91" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:43">
       <c r="A91">
         <v>87</v>
       </c>
@@ -16073,7 +16052,7 @@
         <v>46259</v>
       </c>
       <c r="AH91">
-        <v>10.950684931506849</v>
+        <v>10.95068493150685</v>
       </c>
       <c r="AI91">
         <v>30</v>
@@ -16103,7 +16082,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="92" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:43">
       <c r="A92">
         <v>88</v>
       </c>
@@ -16204,7 +16183,7 @@
         <v>46259</v>
       </c>
       <c r="AH92">
-        <v>6.6821917808219178</v>
+        <v>6.682191780821918</v>
       </c>
       <c r="AI92">
         <v>21</v>
@@ -16234,7 +16213,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="93" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:43">
       <c r="A93">
         <v>89</v>
       </c>
@@ -16335,7 +16314,7 @@
         <v>46259</v>
       </c>
       <c r="AH93">
-        <v>5.6273972602739724</v>
+        <v>5.627397260273972</v>
       </c>
       <c r="AI93">
         <v>21</v>
@@ -16365,7 +16344,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="94" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:43">
       <c r="A94">
         <v>90</v>
       </c>
@@ -16466,7 +16445,7 @@
         <v>46259</v>
       </c>
       <c r="AH94">
-        <v>5.3150684931506849</v>
+        <v>5.315068493150685</v>
       </c>
       <c r="AI94">
         <v>30</v>
@@ -16496,7 +16475,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="95" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:43">
       <c r="A95">
         <v>91</v>
       </c>
@@ -16597,7 +16576,7 @@
         <v>46259</v>
       </c>
       <c r="AH95">
-        <v>5.0602739726027401</v>
+        <v>5.06027397260274</v>
       </c>
       <c r="AI95">
         <v>30</v>
@@ -16627,7 +16606,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="96" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:43">
       <c r="A96">
         <v>92</v>
       </c>
@@ -16728,7 +16707,7 @@
         <v>46259</v>
       </c>
       <c r="AH96">
-        <v>5.0602739726027401</v>
+        <v>5.06027397260274</v>
       </c>
       <c r="AI96">
         <v>21</v>
@@ -16758,7 +16737,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="97" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:43">
       <c r="A97">
         <v>93</v>
       </c>
@@ -16859,7 +16838,7 @@
         <v>46259</v>
       </c>
       <c r="AH97">
-        <v>4.7534246575342456</v>
+        <v>4.753424657534246</v>
       </c>
       <c r="AI97">
         <v>21</v>
@@ -16889,7 +16868,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="98" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:43">
       <c r="A98">
         <v>94</v>
       </c>
@@ -16990,7 +16969,7 @@
         <v>46259</v>
       </c>
       <c r="AH98">
-        <v>0.58356164383561648</v>
+        <v>0.5835616438356165</v>
       </c>
       <c r="AI98">
         <v>21</v>
@@ -17020,7 +16999,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="99" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:43">
       <c r="A99">
         <v>95</v>
       </c>
@@ -17121,7 +17100,7 @@
         <v>46259</v>
       </c>
       <c r="AH99">
-        <v>0.58356164383561648</v>
+        <v>0.5835616438356165</v>
       </c>
       <c r="AI99">
         <v>21</v>
@@ -17151,7 +17130,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="100" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:43">
       <c r="A100">
         <v>96</v>
       </c>
@@ -17252,7 +17231,7 @@
         <v>46259</v>
       </c>
       <c r="AH100">
-        <v>4.7397260273972606</v>
+        <v>4.739726027397261</v>
       </c>
       <c r="AI100">
         <v>21</v>
@@ -17282,7 +17261,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="101" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:43">
       <c r="A101">
         <v>97</v>
       </c>
@@ -17383,7 +17362,7 @@
         <v>46259</v>
       </c>
       <c r="AH101">
-        <v>4.6794520547945204</v>
+        <v>4.67945205479452</v>
       </c>
       <c r="AI101">
         <v>21</v>
@@ -17413,7 +17392,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="102" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:43">
       <c r="A102">
         <v>98</v>
       </c>
@@ -17514,7 +17493,7 @@
         <v>46259</v>
       </c>
       <c r="AH102">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="AI102">
         <v>21</v>
@@ -17544,7 +17523,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="103" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:43">
       <c r="A103">
         <v>99</v>
       </c>
@@ -17645,7 +17624,7 @@
         <v>46259</v>
       </c>
       <c r="AH103">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="AI103">
         <v>21</v>
@@ -17675,7 +17654,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="104" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:43">
       <c r="A104">
         <v>100</v>
       </c>
@@ -17776,7 +17755,7 @@
         <v>46259</v>
       </c>
       <c r="AH104">
-        <v>3.9643835616438361</v>
+        <v>3.964383561643836</v>
       </c>
       <c r="AI104">
         <v>21</v>
@@ -17806,7 +17785,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="105" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:43">
       <c r="A105">
         <v>101</v>
       </c>
@@ -17907,7 +17886,7 @@
         <v>46259</v>
       </c>
       <c r="AH105">
-        <v>7.5232876712328771</v>
+        <v>7.523287671232877</v>
       </c>
       <c r="AI105">
         <v>30</v>
@@ -17937,7 +17916,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="106" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:43">
       <c r="A106">
         <v>102</v>
       </c>
@@ -18038,7 +18017,7 @@
         <v>46259</v>
       </c>
       <c r="AH106">
-        <v>4.9726027397260273</v>
+        <v>4.972602739726027</v>
       </c>
       <c r="AI106">
         <v>21</v>
@@ -18068,7 +18047,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="107" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:43">
       <c r="A107">
         <v>103</v>
       </c>
@@ -18169,7 +18148,7 @@
         <v>46259</v>
       </c>
       <c r="AH107">
-        <v>1.9698630136986299</v>
+        <v>1.96986301369863</v>
       </c>
       <c r="AI107">
         <v>21</v>
@@ -18199,7 +18178,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="108" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:43">
       <c r="A108">
         <v>104</v>
       </c>
@@ -18300,7 +18279,7 @@
         <v>46259</v>
       </c>
       <c r="AH108">
-        <v>22.446575342465749</v>
+        <v>22.44657534246575</v>
       </c>
       <c r="AI108">
         <v>30</v>
@@ -18330,7 +18309,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="109" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:43">
       <c r="A109">
         <v>105</v>
       </c>
@@ -18431,7 +18410,7 @@
         <v>46259</v>
       </c>
       <c r="AH109">
-        <v>3.9863013698630141</v>
+        <v>3.986301369863014</v>
       </c>
       <c r="AI109">
         <v>21</v>
@@ -18461,7 +18440,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="110" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:43">
       <c r="A110">
         <v>106</v>
       </c>
@@ -18514,7 +18493,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="111" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:43">
       <c r="A111">
         <v>107</v>
       </c>
@@ -18615,7 +18594,7 @@
         <v>46259</v>
       </c>
       <c r="AH111">
-        <v>0.35890410958904112</v>
+        <v>0.3589041095890411</v>
       </c>
       <c r="AI111">
         <v>21</v>
@@ -18645,7 +18624,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="112" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:43">
       <c r="A112">
         <v>108</v>
       </c>
@@ -18746,7 +18725,7 @@
         <v>46259</v>
       </c>
       <c r="AH112">
-        <v>5.3726027397260276</v>
+        <v>5.372602739726028</v>
       </c>
       <c r="AI112">
         <v>21</v>
@@ -18776,7 +18755,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="113" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:43">
       <c r="A113">
         <v>109</v>
       </c>
@@ -18877,7 +18856,7 @@
         <v>46259</v>
       </c>
       <c r="AH113">
-        <v>4.5287671232876709</v>
+        <v>4.528767123287671</v>
       </c>
       <c r="AI113">
         <v>21</v>
@@ -18907,7 +18886,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="114" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:43">
       <c r="A114">
         <v>110</v>
       </c>
@@ -19008,7 +18987,7 @@
         <v>46259</v>
       </c>
       <c r="AH114">
-        <v>4.5835616438356164</v>
+        <v>4.583561643835616</v>
       </c>
       <c r="AI114">
         <v>21</v>
@@ -19038,7 +19017,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="115" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:43">
       <c r="A115">
         <v>111</v>
       </c>
@@ -19139,7 +19118,7 @@
         <v>46259</v>
       </c>
       <c r="AH115">
-        <v>4.5260273972602736</v>
+        <v>4.526027397260274</v>
       </c>
       <c r="AI115">
         <v>21</v>
@@ -19169,7 +19148,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="116" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:43">
       <c r="A116">
         <v>112</v>
       </c>
@@ -19270,7 +19249,7 @@
         <v>46259</v>
       </c>
       <c r="AH116">
-        <v>4.5287671232876709</v>
+        <v>4.528767123287671</v>
       </c>
       <c r="AI116">
         <v>21</v>
@@ -19300,7 +19279,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="117" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:43">
       <c r="B117">
         <v>1336</v>
       </c>
@@ -19428,7 +19407,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="118" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:43">
       <c r="A118">
         <v>113</v>
       </c>
@@ -19559,7 +19538,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="119" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:43">
       <c r="A119">
         <v>114</v>
       </c>
@@ -19660,7 +19639,7 @@
         <v>46259</v>
       </c>
       <c r="AH119">
-        <v>2.6301369863013702</v>
+        <v>2.63013698630137</v>
       </c>
       <c r="AI119">
         <v>21</v>
@@ -19690,7 +19669,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="120" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:43">
       <c r="A120">
         <v>115</v>
       </c>
@@ -19791,7 +19770,7 @@
         <v>46259</v>
       </c>
       <c r="AH120">
-        <v>2.4109589041095889</v>
+        <v>2.410958904109589</v>
       </c>
       <c r="AI120">
         <v>21</v>
@@ -19821,7 +19800,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="121" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:43">
       <c r="A121">
         <v>116</v>
       </c>
@@ -19952,7 +19931,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="122" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:43">
       <c r="A122">
         <v>117</v>
       </c>
@@ -20083,7 +20062,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="123" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:43">
       <c r="A123">
         <v>118</v>
       </c>
@@ -20214,7 +20193,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="124" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:43">
       <c r="A124">
         <v>119</v>
       </c>
@@ -20315,7 +20294,7 @@
         <v>46259</v>
       </c>
       <c r="AH124">
-        <v>2.2630136986301368</v>
+        <v>2.263013698630137</v>
       </c>
       <c r="AI124">
         <v>21</v>
@@ -20345,7 +20324,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="125" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:43">
       <c r="A125">
         <v>120</v>
       </c>
@@ -20446,7 +20425,7 @@
         <v>46259</v>
       </c>
       <c r="AH125">
-        <v>6.5863013698630137</v>
+        <v>6.586301369863014</v>
       </c>
       <c r="AI125">
         <v>30</v>
@@ -20476,7 +20455,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="126" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:43">
       <c r="A126">
         <v>120</v>
       </c>
@@ -20499,7 +20478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:43">
       <c r="A127">
         <v>121</v>
       </c>
@@ -20600,7 +20579,7 @@
         <v>46259</v>
       </c>
       <c r="AH127">
-        <v>12.265753424657531</v>
+        <v>12.26575342465753</v>
       </c>
       <c r="AI127">
         <v>30</v>
@@ -20630,7 +20609,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="128" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:43">
       <c r="A128">
         <v>122</v>
       </c>
@@ -20731,7 +20710,7 @@
         <v>46259</v>
       </c>
       <c r="AH128">
-        <v>5.9643835616438352</v>
+        <v>5.964383561643835</v>
       </c>
       <c r="AI128">
         <v>30</v>
@@ -20761,7 +20740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:43">
       <c r="A129">
         <v>123</v>
       </c>
@@ -20862,7 +20841,7 @@
         <v>46259</v>
       </c>
       <c r="AH129">
-        <v>5.7972602739726016</v>
+        <v>5.797260273972602</v>
       </c>
       <c r="AI129">
         <v>21</v>
@@ -20892,7 +20871,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="130" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:43">
       <c r="A130">
         <v>124</v>
       </c>
@@ -20993,7 +20972,7 @@
         <v>46259</v>
       </c>
       <c r="AH130">
-        <v>5.1534246575342468</v>
+        <v>5.153424657534247</v>
       </c>
       <c r="AI130">
         <v>30</v>
@@ -21023,7 +21002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:43">
       <c r="A131">
         <v>125</v>
       </c>
@@ -21124,7 +21103,7 @@
         <v>46259</v>
       </c>
       <c r="AH131">
-        <v>5.1780821917808222</v>
+        <v>5.178082191780822</v>
       </c>
       <c r="AI131">
         <v>30</v>
@@ -21154,7 +21133,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="132" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:43">
       <c r="B132">
         <v>1135</v>
       </c>
@@ -21252,7 +21231,7 @@
         <v>46259</v>
       </c>
       <c r="AH132">
-        <v>0.15068493150684931</v>
+        <v>0.1506849315068493</v>
       </c>
       <c r="AI132">
         <v>21</v>
@@ -21282,7 +21261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:43">
       <c r="A133">
         <v>126</v>
       </c>
@@ -21383,7 +21362,7 @@
         <v>46259</v>
       </c>
       <c r="AH133">
-        <v>4.2356164383561641</v>
+        <v>4.235616438356164</v>
       </c>
       <c r="AI133">
         <v>21</v>
@@ -21413,7 +21392,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="134" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:43">
       <c r="A134">
         <v>127</v>
       </c>
@@ -21514,7 +21493,7 @@
         <v>46259</v>
       </c>
       <c r="AH134">
-        <v>4.2356164383561641</v>
+        <v>4.235616438356164</v>
       </c>
       <c r="AI134">
         <v>21</v>
@@ -21544,7 +21523,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="135" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:43">
       <c r="A135">
         <v>128</v>
       </c>
@@ -21645,7 +21624,7 @@
         <v>46259</v>
       </c>
       <c r="AH135">
-        <v>4.7232876712328764</v>
+        <v>4.723287671232876</v>
       </c>
       <c r="AI135">
         <v>21</v>
@@ -21675,7 +21654,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="136" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:43">
       <c r="A136">
         <v>129</v>
       </c>
@@ -21776,7 +21755,7 @@
         <v>46259</v>
       </c>
       <c r="AH136">
-        <v>4.2904109589041104</v>
+        <v>4.29041095890411</v>
       </c>
       <c r="AI136">
         <v>21</v>
@@ -21806,7 +21785,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="137" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:43">
       <c r="A137">
         <v>130</v>
       </c>
@@ -21907,7 +21886,7 @@
         <v>46259</v>
       </c>
       <c r="AH137">
-        <v>4.5534246575342463</v>
+        <v>4.553424657534246</v>
       </c>
       <c r="AI137">
         <v>21</v>
@@ -21937,7 +21916,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="138" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:43">
       <c r="A138">
         <v>131</v>
       </c>
@@ -22038,7 +22017,7 @@
         <v>46259</v>
       </c>
       <c r="AH138">
-        <v>1.4986301369863011</v>
+        <v>1.498630136986301</v>
       </c>
       <c r="AI138">
         <v>21</v>
@@ -22068,7 +22047,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="139" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:43">
       <c r="A139">
         <v>132</v>
       </c>
@@ -22199,7 +22178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:43">
       <c r="A140">
         <v>133</v>
       </c>
@@ -22330,7 +22309,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="141" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:43">
       <c r="A141">
         <v>134</v>
       </c>
@@ -22461,7 +22440,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="142" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:43">
       <c r="A142">
         <v>135</v>
       </c>
@@ -22592,7 +22571,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="143" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:43">
       <c r="A143">
         <v>136</v>
       </c>
@@ -22693,7 +22672,7 @@
         <v>46259</v>
       </c>
       <c r="AH143">
-        <v>4.4876712328767123</v>
+        <v>4.487671232876712</v>
       </c>
       <c r="AI143">
         <v>21</v>
@@ -22723,7 +22702,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="144" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:43">
       <c r="A144">
         <v>137</v>
       </c>
@@ -22824,7 +22803,7 @@
         <v>46259</v>
       </c>
       <c r="AH144">
-        <v>4.4684931506849317</v>
+        <v>4.468493150684932</v>
       </c>
       <c r="AI144">
         <v>21</v>
@@ -22854,7 +22833,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="145" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:43">
       <c r="A145">
         <v>138</v>
       </c>
@@ -22955,7 +22934,7 @@
         <v>46259</v>
       </c>
       <c r="AH145">
-        <v>1.8575342465753419</v>
+        <v>1.857534246575342</v>
       </c>
       <c r="AI145">
         <v>21</v>
@@ -22985,7 +22964,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="146" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:43">
       <c r="A146">
         <v>139</v>
       </c>
@@ -23086,7 +23065,7 @@
         <v>46259</v>
       </c>
       <c r="AH146">
-        <v>4.3890410958904109</v>
+        <v>4.389041095890411</v>
       </c>
       <c r="AI146">
         <v>21</v>
@@ -23116,7 +23095,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="147" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:43">
       <c r="A147">
         <v>140</v>
       </c>
@@ -23217,7 +23196,7 @@
         <v>46259</v>
       </c>
       <c r="AH147">
-        <v>3.7917808219178082</v>
+        <v>3.791780821917808</v>
       </c>
       <c r="AI147">
         <v>21</v>
@@ -23247,7 +23226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:43">
       <c r="A148">
         <v>141</v>
       </c>
@@ -23348,7 +23327,7 @@
         <v>46259</v>
       </c>
       <c r="AH148">
-        <v>3.7863013698630139</v>
+        <v>3.786301369863014</v>
       </c>
       <c r="AI148">
         <v>21</v>
@@ -23378,7 +23357,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="149" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:43">
       <c r="A149">
         <v>142</v>
       </c>
@@ -23479,7 +23458,7 @@
         <v>46259</v>
       </c>
       <c r="AH149">
-        <v>3.7369863013698632</v>
+        <v>3.736986301369863</v>
       </c>
       <c r="AI149">
         <v>21</v>
@@ -23509,7 +23488,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="150" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:43">
       <c r="A150">
         <v>143</v>
       </c>
@@ -23610,7 +23589,7 @@
         <v>46259</v>
       </c>
       <c r="AH150">
-        <v>2.5452054794520551</v>
+        <v>2.545205479452055</v>
       </c>
       <c r="AI150">
         <v>21</v>
@@ -23640,7 +23619,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="151" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:43">
       <c r="A151">
         <v>144</v>
       </c>
@@ -23741,7 +23720,7 @@
         <v>46259</v>
       </c>
       <c r="AH151">
-        <v>5.9671232876712326</v>
+        <v>5.967123287671233</v>
       </c>
       <c r="AI151">
         <v>21</v>
@@ -23771,7 +23750,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="152" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:43">
       <c r="A152">
         <v>145</v>
       </c>
@@ -23872,7 +23851,7 @@
         <v>46259</v>
       </c>
       <c r="AH152">
-        <v>3.1013698630136992</v>
+        <v>3.101369863013699</v>
       </c>
       <c r="AI152">
         <v>21</v>
@@ -23902,7 +23881,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="153" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:43">
       <c r="A153">
         <v>146</v>
       </c>
@@ -24003,7 +23982,7 @@
         <v>46259</v>
       </c>
       <c r="AH153">
-        <v>5.6493150684931503</v>
+        <v>5.64931506849315</v>
       </c>
       <c r="AI153">
         <v>21</v>
@@ -24033,7 +24012,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="154" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:43">
       <c r="A154">
         <v>147</v>
       </c>
@@ -24134,7 +24113,7 @@
         <v>46259</v>
       </c>
       <c r="AH154">
-        <v>5.4027397260273968</v>
+        <v>5.402739726027397</v>
       </c>
       <c r="AI154">
         <v>21</v>
@@ -24164,7 +24143,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="155" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:43">
       <c r="A155">
         <v>148</v>
       </c>
@@ -24265,7 +24244,7 @@
         <v>46259</v>
       </c>
       <c r="AH155">
-        <v>5.3095890410958901</v>
+        <v>5.30958904109589</v>
       </c>
       <c r="AI155">
         <v>21</v>
@@ -24295,7 +24274,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="156" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:43">
       <c r="A156">
         <v>149</v>
       </c>
@@ -24396,7 +24375,7 @@
         <v>46259</v>
       </c>
       <c r="AH156">
-        <v>5.0383561643835613</v>
+        <v>5.038356164383561</v>
       </c>
       <c r="AI156">
         <v>21</v>
@@ -24426,7 +24405,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="157" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:43">
       <c r="A157">
         <v>150</v>
       </c>
@@ -24527,7 +24506,7 @@
         <v>46259</v>
       </c>
       <c r="AH157">
-        <v>5.0383561643835613</v>
+        <v>5.038356164383561</v>
       </c>
       <c r="AI157">
         <v>21</v>
@@ -24557,7 +24536,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="158" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:43">
       <c r="A158">
         <v>151</v>
       </c>
@@ -24658,7 +24637,7 @@
         <v>46259</v>
       </c>
       <c r="AH158">
-        <v>5.0383561643835613</v>
+        <v>5.038356164383561</v>
       </c>
       <c r="AI158">
         <v>21</v>
@@ -24688,7 +24667,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="159" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:43">
       <c r="A159">
         <v>152</v>
       </c>
@@ -24789,7 +24768,7 @@
         <v>46259</v>
       </c>
       <c r="AH159">
-        <v>5.0383561643835613</v>
+        <v>5.038356164383561</v>
       </c>
       <c r="AI159">
         <v>21</v>
@@ -24819,7 +24798,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="160" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:43">
       <c r="A160">
         <v>153</v>
       </c>
@@ -24920,7 +24899,7 @@
         <v>46259</v>
       </c>
       <c r="AH160">
-        <v>1.8301369863013699</v>
+        <v>1.83013698630137</v>
       </c>
       <c r="AI160">
         <v>21</v>
@@ -24950,7 +24929,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="161" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:43">
       <c r="A161">
         <v>154</v>
       </c>
@@ -25051,7 +25030,7 @@
         <v>46259</v>
       </c>
       <c r="AH161">
-        <v>4.5287671232876709</v>
+        <v>4.528767123287671</v>
       </c>
       <c r="AI161">
         <v>21</v>
@@ -25081,7 +25060,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="162" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:43">
       <c r="A162">
         <v>155</v>
       </c>
@@ -25182,7 +25161,7 @@
         <v>46259</v>
       </c>
       <c r="AH162">
-        <v>4.3890410958904109</v>
+        <v>4.389041095890411</v>
       </c>
       <c r="AI162">
         <v>21</v>
@@ -25212,7 +25191,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="163" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:43">
       <c r="A163">
         <v>156</v>
       </c>
@@ -25313,7 +25292,7 @@
         <v>46259</v>
       </c>
       <c r="AH163">
-        <v>4.3890410958904109</v>
+        <v>4.389041095890411</v>
       </c>
       <c r="AI163">
         <v>21</v>
@@ -25343,7 +25322,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="164" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:43">
       <c r="A164">
         <v>157</v>
       </c>
@@ -25474,7 +25453,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="165" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:43">
       <c r="A165">
         <v>158</v>
       </c>
@@ -25575,7 +25554,7 @@
         <v>46259</v>
       </c>
       <c r="AH165">
-        <v>3.9945205479452048</v>
+        <v>3.994520547945205</v>
       </c>
       <c r="AI165">
         <v>21</v>
@@ -25605,7 +25584,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="166" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:43">
       <c r="A166">
         <v>159</v>
       </c>
@@ -25706,7 +25685,7 @@
         <v>46259</v>
       </c>
       <c r="AH166">
-        <v>3.9643835616438361</v>
+        <v>3.964383561643836</v>
       </c>
       <c r="AI166">
         <v>21</v>
@@ -25736,7 +25715,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="167" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:43">
       <c r="A167">
         <v>161</v>
       </c>
@@ -25837,7 +25816,7 @@
         <v>46259</v>
       </c>
       <c r="AH167">
-        <v>2.3397260273972602</v>
+        <v>2.33972602739726</v>
       </c>
       <c r="AI167">
         <v>21</v>
@@ -25867,7 +25846,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="168" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:43">
       <c r="A168">
         <v>162</v>
       </c>
@@ -25968,7 +25947,7 @@
         <v>46259</v>
       </c>
       <c r="AH168">
-        <v>13.547945205479451</v>
+        <v>13.54794520547945</v>
       </c>
       <c r="AI168">
         <v>30</v>
@@ -25998,7 +25977,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="169" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:43">
       <c r="A169">
         <v>163</v>
       </c>
@@ -26099,7 +26078,7 @@
         <v>46259</v>
       </c>
       <c r="AH169">
-        <v>5.1534246575342468</v>
+        <v>5.153424657534247</v>
       </c>
       <c r="AI169">
         <v>30</v>
@@ -26129,7 +26108,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="170" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:43">
       <c r="A170">
         <v>164</v>
       </c>
@@ -26230,7 +26209,7 @@
         <v>46259</v>
       </c>
       <c r="AH170">
-        <v>5.3452054794520549</v>
+        <v>5.345205479452055</v>
       </c>
       <c r="AI170">
         <v>30</v>
@@ -26260,7 +26239,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="171" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:43">
       <c r="A171">
         <v>165</v>
       </c>
@@ -26391,7 +26370,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="172" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:43">
       <c r="A172">
         <v>166</v>
       </c>
@@ -26492,7 +26471,7 @@
         <v>46259</v>
       </c>
       <c r="AH172">
-        <v>2.8438356164383558</v>
+        <v>2.843835616438356</v>
       </c>
       <c r="AI172">
         <v>21</v>
@@ -26522,7 +26501,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="173" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:43">
       <c r="A173">
         <v>167</v>
       </c>
@@ -26653,7 +26632,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="174" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:43">
       <c r="A174">
         <v>168</v>
       </c>
@@ -26754,7 +26733,7 @@
         <v>46259</v>
       </c>
       <c r="AH174">
-        <v>1.9698630136986299</v>
+        <v>1.96986301369863</v>
       </c>
       <c r="AI174">
         <v>21</v>
@@ -26784,7 +26763,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="175" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:43">
       <c r="A175">
         <v>169</v>
       </c>
@@ -26891,13 +26870,13 @@
         <v>21</v>
       </c>
       <c r="AJ175">
-        <v>975</v>
+        <v>963</v>
       </c>
       <c r="AK175">
-        <v>375</v>
+        <v>241</v>
       </c>
       <c r="AL175">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="AM175">
         <v>0</v>
@@ -26915,7 +26894,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="176" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:43">
       <c r="A176">
         <v>170</v>
       </c>
@@ -27016,7 +26995,7 @@
         <v>46259</v>
       </c>
       <c r="AH176">
-        <v>5.8767123287671232</v>
+        <v>5.876712328767123</v>
       </c>
       <c r="AI176">
         <v>30</v>
@@ -27046,7 +27025,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="177" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:43">
       <c r="A177">
         <v>171</v>
       </c>
@@ -27177,7 +27156,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="178" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:43">
       <c r="A178">
         <v>172</v>
       </c>
@@ -27278,7 +27257,7 @@
         <v>46259</v>
       </c>
       <c r="AH178">
-        <v>2.9616438356164378</v>
+        <v>2.961643835616438</v>
       </c>
       <c r="AI178">
         <v>21</v>
@@ -27308,7 +27287,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="179" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:43">
       <c r="A179">
         <v>173</v>
       </c>
@@ -27409,7 +27388,7 @@
         <v>46259</v>
       </c>
       <c r="AH179">
-        <v>2.4684931506849321</v>
+        <v>2.468493150684932</v>
       </c>
       <c r="AI179">
         <v>21</v>
@@ -27439,7 +27418,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="180" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:43">
       <c r="A180">
         <v>174</v>
       </c>
@@ -27540,7 +27519,7 @@
         <v>46259</v>
       </c>
       <c r="AH180">
-        <v>2.2520547945205478</v>
+        <v>2.252054794520548</v>
       </c>
       <c r="AI180">
         <v>21</v>
@@ -27570,7 +27549,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="181" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:43">
       <c r="A181">
         <v>175</v>
       </c>
@@ -27701,7 +27680,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="182" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:43">
       <c r="A182">
         <v>176</v>
       </c>
@@ -27832,7 +27811,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="183" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:43">
       <c r="A183">
         <v>177</v>
       </c>
@@ -27963,7 +27942,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="184" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:43">
       <c r="A184">
         <v>178</v>
       </c>
@@ -28094,7 +28073,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="185" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:43">
       <c r="A185">
         <v>179</v>
       </c>
@@ -28225,7 +28204,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="186" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:43">
       <c r="A186">
         <v>180</v>
       </c>
@@ -28326,7 +28305,7 @@
         <v>46259</v>
       </c>
       <c r="AH186">
-        <v>1.7452054794520551</v>
+        <v>1.745205479452055</v>
       </c>
       <c r="AI186">
         <v>21</v>
@@ -28356,7 +28335,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="187" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:43">
       <c r="A187">
         <v>181</v>
       </c>
@@ -28457,7 +28436,7 @@
         <v>46259</v>
       </c>
       <c r="AH187">
-        <v>1.3890410958904109</v>
+        <v>1.389041095890411</v>
       </c>
       <c r="AI187">
         <v>21</v>
@@ -28489,7 +28468,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="S170" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="S170" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Staffdata.xlsx
+++ b/Staffdata.xlsx
@@ -1,15 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3113719057d24bf/Desktop/HR-Forms-Site/HRFORMAS/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_05E48499FC67680F1964AE368160343238AA41AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B403DCDC-E7E9-4FA3-8BB1-6D958BD53ECA}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2174,7 +2185,7 @@
     <t>-</t>
   </si>
   <si>
-    <t xml:space="preserve"> 966577040481</t>
+    <t> 966577040481</t>
   </si>
   <si>
     <t>malbatil@outlook.sa</t>
@@ -2485,10 +2496,10 @@
     <t>HAMDILLHJ038@GMAIL.COM</t>
   </si>
   <si>
-    <t xml:space="preserve"> omarzar392@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ark870725@gmail.com</t>
+    <t> omarzar392@gmail.com</t>
+  </si>
+  <si>
+    <t> ark870725@gmail.com</t>
   </si>
   <si>
     <t>waelgomaa1wg@gmail.com</t>
@@ -2561,7 +2572,7 @@
     <t>INFO2@HAIL-HOUSE.SA</t>
   </si>
   <si>
-    <t xml:space="preserve"> Sarah_elkhatib@outlook.com</t>
+    <t> Sarah_elkhatib@outlook.com</t>
   </si>
   <si>
     <t xml:space="preserve"> mohannad.fakhry00@gmail.com</t>
@@ -3905,11 +3916,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3955,18 +3966,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ارتباط تشعبي" xfId="1" builtinId="8"/>
+    <cellStyle name="عادي" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4004,7 +4023,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4038,6 +4057,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4072,9 +4092,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4247,11 +4268,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AQ187"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:43">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4382,7 +4403,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:43">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4483,7 +4504,7 @@
         <v>46259</v>
       </c>
       <c r="AH2">
-        <v>8.726027397260275</v>
+        <v>8.7260273972602747</v>
       </c>
       <c r="AI2">
         <v>30</v>
@@ -4513,7 +4534,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="3" spans="1:43">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4614,7 +4635,7 @@
         <v>46259</v>
       </c>
       <c r="AH3">
-        <v>13.63561643835616</v>
+        <v>13.635616438356161</v>
       </c>
       <c r="AI3">
         <v>30</v>
@@ -4644,7 +4665,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="4" spans="1:43">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4745,7 +4766,7 @@
         <v>46259</v>
       </c>
       <c r="AH4">
-        <v>5.890410958904109</v>
+        <v>5.8904109589041092</v>
       </c>
       <c r="AI4">
         <v>30</v>
@@ -4775,7 +4796,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="5" spans="1:43">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4876,7 +4897,7 @@
         <v>46259</v>
       </c>
       <c r="AH5">
-        <v>6.046575342465753</v>
+        <v>6.0465753424657533</v>
       </c>
       <c r="AI5">
         <v>21</v>
@@ -4906,7 +4927,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="6" spans="1:43">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5007,7 +5028,7 @@
         <v>46259</v>
       </c>
       <c r="AH6">
-        <v>6.402739726027397</v>
+        <v>6.4027397260273968</v>
       </c>
       <c r="AI6">
         <v>21</v>
@@ -5037,7 +5058,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="7" spans="1:43">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5138,7 +5159,7 @@
         <v>46259</v>
       </c>
       <c r="AH7">
-        <v>5.704109589041096</v>
+        <v>5.7041095890410958</v>
       </c>
       <c r="AI7">
         <v>30</v>
@@ -5168,7 +5189,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="8" spans="1:43">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5299,7 +5320,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="9" spans="1:43">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5430,7 +5451,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="10" spans="1:43">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5531,7 +5552,7 @@
         <v>46259</v>
       </c>
       <c r="AH10">
-        <v>6.753424657534246</v>
+        <v>6.7534246575342456</v>
       </c>
       <c r="AI10">
         <v>30</v>
@@ -5561,7 +5582,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="11" spans="1:43">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5692,7 +5713,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="12" spans="1:43">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5793,7 +5814,7 @@
         <v>46259</v>
       </c>
       <c r="AH12">
-        <v>5.750684931506849</v>
+        <v>5.7506849315068491</v>
       </c>
       <c r="AI12">
         <v>21</v>
@@ -5823,7 +5844,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="13" spans="1:43">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5954,7 +5975,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="14" spans="1:43">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6055,7 +6076,7 @@
         <v>46259</v>
       </c>
       <c r="AH14">
-        <v>0.3041095890410959</v>
+        <v>0.30410958904109592</v>
       </c>
       <c r="AI14">
         <v>21</v>
@@ -6085,7 +6106,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="15" spans="1:43">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6186,7 +6207,7 @@
         <v>46259</v>
       </c>
       <c r="AH15">
-        <v>3.983561643835616</v>
+        <v>3.9835616438356158</v>
       </c>
       <c r="AI15">
         <v>21</v>
@@ -6216,7 +6237,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="16" spans="1:43">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6317,7 +6338,7 @@
         <v>46259</v>
       </c>
       <c r="AH16">
-        <v>2.898630136986301</v>
+        <v>2.8986301369863008</v>
       </c>
       <c r="AI16">
         <v>21</v>
@@ -6347,7 +6368,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="17" spans="1:43">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -6448,7 +6469,7 @@
         <v>46259</v>
       </c>
       <c r="AH17">
-        <v>1.673972602739726</v>
+        <v>1.6739726027397259</v>
       </c>
       <c r="AI17">
         <v>21</v>
@@ -6478,7 +6499,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="18" spans="1:43">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6579,7 +6600,7 @@
         <v>46259</v>
       </c>
       <c r="AH18">
-        <v>2.049315068493151</v>
+        <v>2.0493150684931511</v>
       </c>
       <c r="AI18">
         <v>21</v>
@@ -6609,7 +6630,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="19" spans="1:43">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -6710,7 +6731,7 @@
         <v>46259</v>
       </c>
       <c r="AH19">
-        <v>2.035616438356164</v>
+        <v>2.0356164383561639</v>
       </c>
       <c r="AI19">
         <v>21</v>
@@ -6740,7 +6761,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="20" spans="1:43">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -6841,7 +6862,7 @@
         <v>46259</v>
       </c>
       <c r="AH20">
-        <v>1.512328767123288</v>
+        <v>1.5123287671232879</v>
       </c>
       <c r="AI20">
         <v>21</v>
@@ -6871,7 +6892,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="21" spans="1:43">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -6972,7 +6993,7 @@
         <v>46259</v>
       </c>
       <c r="AH21">
-        <v>2.035616438356164</v>
+        <v>2.0356164383561639</v>
       </c>
       <c r="AI21">
         <v>21</v>
@@ -7002,7 +7023,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="22" spans="1:43">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -7133,7 +7154,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="23" spans="1:43">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -7264,7 +7285,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="24" spans="1:43">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -7395,7 +7416,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="25" spans="1:43">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -7496,7 +7517,7 @@
         <v>46259</v>
       </c>
       <c r="AH25">
-        <v>0.7616438356164383</v>
+        <v>0.76164383561643834</v>
       </c>
       <c r="AI25">
         <v>21</v>
@@ -7526,7 +7547,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="26" spans="1:43">
+    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -7627,7 +7648,7 @@
         <v>46259</v>
       </c>
       <c r="AH26">
-        <v>0.7616438356164383</v>
+        <v>0.76164383561643834</v>
       </c>
       <c r="AI26">
         <v>21</v>
@@ -7657,7 +7678,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="27" spans="1:43">
+    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -7758,7 +7779,7 @@
         <v>46259</v>
       </c>
       <c r="AH27">
-        <v>6.736986301369863</v>
+        <v>6.7369863013698632</v>
       </c>
       <c r="AI27">
         <v>30</v>
@@ -7788,7 +7809,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="28" spans="1:43">
+    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -7889,7 +7910,7 @@
         <v>46259</v>
       </c>
       <c r="AH28">
-        <v>12.11232876712329</v>
+        <v>12.112328767123291</v>
       </c>
       <c r="AI28">
         <v>30</v>
@@ -7919,7 +7940,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="29" spans="1:43">
+    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -8020,7 +8041,7 @@
         <v>46259</v>
       </c>
       <c r="AH29">
-        <v>3.487671232876712</v>
+        <v>3.4876712328767119</v>
       </c>
       <c r="AI29">
         <v>21</v>
@@ -8050,7 +8071,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="30" spans="1:43">
+    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -8151,7 +8172,7 @@
         <v>46259</v>
       </c>
       <c r="AH30">
-        <v>15.07671232876712</v>
+        <v>15.076712328767121</v>
       </c>
       <c r="AI30">
         <v>30</v>
@@ -8181,7 +8202,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="31" spans="1:43">
+    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -8282,7 +8303,7 @@
         <v>46259</v>
       </c>
       <c r="AH31">
-        <v>15.07671232876712</v>
+        <v>15.076712328767121</v>
       </c>
       <c r="AI31">
         <v>30</v>
@@ -8312,7 +8333,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="32" spans="1:43">
+    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -8443,7 +8464,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="33" spans="1:43">
+    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -8544,7 +8565,7 @@
         <v>46259</v>
       </c>
       <c r="AH33">
-        <v>15.16712328767123</v>
+        <v>15.167123287671229</v>
       </c>
       <c r="AI33">
         <v>30</v>
@@ -8574,7 +8595,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="34" spans="1:43">
+    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -8675,7 +8696,7 @@
         <v>46259</v>
       </c>
       <c r="AH34">
-        <v>4.610958904109589</v>
+        <v>4.6109589041095891</v>
       </c>
       <c r="AI34">
         <v>21</v>
@@ -8705,7 +8726,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="35" spans="1:43">
+    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -8806,7 +8827,7 @@
         <v>46259</v>
       </c>
       <c r="AH35">
-        <v>4.542465753424658</v>
+        <v>4.5424657534246577</v>
       </c>
       <c r="AI35">
         <v>21</v>
@@ -8836,7 +8857,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="36" spans="1:43">
+    <row r="36" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -8937,7 +8958,7 @@
         <v>46259</v>
       </c>
       <c r="AH36">
-        <v>13.24109589041096</v>
+        <v>13.241095890410961</v>
       </c>
       <c r="AI36">
         <v>30</v>
@@ -8967,7 +8988,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="37" spans="1:43">
+    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -9098,7 +9119,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="38" spans="1:43">
+    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -9229,7 +9250,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="39" spans="1:43">
+    <row r="39" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -9330,7 +9351,7 @@
         <v>46259</v>
       </c>
       <c r="AH39">
-        <v>6.70958904109589</v>
+        <v>6.7095890410958896</v>
       </c>
       <c r="AI39">
         <v>30</v>
@@ -9360,7 +9381,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="40" spans="1:43">
+    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -9461,7 +9482,7 @@
         <v>46259</v>
       </c>
       <c r="AH40">
-        <v>6.50958904109589</v>
+        <v>6.5095890410958903</v>
       </c>
       <c r="AI40">
         <v>30</v>
@@ -9491,7 +9512,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="41" spans="1:43">
+    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -9592,7 +9613,7 @@
         <v>46259</v>
       </c>
       <c r="AH41">
-        <v>6.550684931506849</v>
+        <v>6.5506849315068489</v>
       </c>
       <c r="AI41">
         <v>21</v>
@@ -9622,7 +9643,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="42" spans="1:43">
+    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -9753,7 +9774,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="43" spans="1:43">
+    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -9854,7 +9875,7 @@
         <v>46259</v>
       </c>
       <c r="AH43">
-        <v>8.753424657534246</v>
+        <v>8.7534246575342465</v>
       </c>
       <c r="AI43">
         <v>30</v>
@@ -9884,7 +9905,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="44" spans="1:43">
+    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -9985,7 +10006,7 @@
         <v>46259</v>
       </c>
       <c r="AH44">
-        <v>5.753424657534246</v>
+        <v>5.7534246575342456</v>
       </c>
       <c r="AI44">
         <v>21</v>
@@ -10015,7 +10036,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="45" spans="1:43">
+    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -10116,7 +10137,7 @@
         <v>46259</v>
       </c>
       <c r="AH45">
-        <v>5.734246575342466</v>
+        <v>5.7342465753424658</v>
       </c>
       <c r="AI45">
         <v>21</v>
@@ -10146,7 +10167,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="46" spans="1:43">
+    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -10247,7 +10268,7 @@
         <v>46259</v>
       </c>
       <c r="AH46">
-        <v>5.627397260273972</v>
+        <v>5.6273972602739724</v>
       </c>
       <c r="AI46">
         <v>30</v>
@@ -10277,7 +10298,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="47" spans="1:43">
+    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -10378,7 +10399,7 @@
         <v>46259</v>
       </c>
       <c r="AH47">
-        <v>4.227397260273973</v>
+        <v>4.2273972602739729</v>
       </c>
       <c r="AI47">
         <v>21</v>
@@ -10408,7 +10429,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="48" spans="1:43">
+    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -10539,7 +10560,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="49" spans="1:43">
+    <row r="49" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -10640,7 +10661,7 @@
         <v>46259</v>
       </c>
       <c r="AH49">
-        <v>4.158904109589041</v>
+        <v>4.1589041095890407</v>
       </c>
       <c r="AI49">
         <v>21</v>
@@ -10670,7 +10691,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="50" spans="1:43">
+    <row r="50" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -10771,7 +10792,7 @@
         <v>46259</v>
       </c>
       <c r="AH50">
-        <v>3.986301369863014</v>
+        <v>3.9863013698630141</v>
       </c>
       <c r="AI50">
         <v>21</v>
@@ -10801,7 +10822,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="51" spans="1:43">
+    <row r="51" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -10902,7 +10923,7 @@
         <v>46259</v>
       </c>
       <c r="AH51">
-        <v>3.964383561643836</v>
+        <v>3.9643835616438361</v>
       </c>
       <c r="AI51">
         <v>21</v>
@@ -10932,7 +10953,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="52" spans="1:43">
+    <row r="52" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -11033,7 +11054,7 @@
         <v>46259</v>
       </c>
       <c r="AH52">
-        <v>3.964383561643836</v>
+        <v>3.9643835616438361</v>
       </c>
       <c r="AI52">
         <v>21</v>
@@ -11063,7 +11084,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="53" spans="1:43">
+    <row r="53" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -11194,7 +11215,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="54" spans="1:43">
+    <row r="54" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -11295,7 +11316,7 @@
         <v>46259</v>
       </c>
       <c r="AH54">
-        <v>1.96986301369863</v>
+        <v>1.9698630136986299</v>
       </c>
       <c r="AI54">
         <v>21</v>
@@ -11325,7 +11346,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="55" spans="1:43">
+    <row r="55" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -11426,7 +11447,7 @@
         <v>46259</v>
       </c>
       <c r="AH55">
-        <v>0.5835616438356165</v>
+        <v>0.58356164383561648</v>
       </c>
       <c r="AI55">
         <v>21</v>
@@ -11456,7 +11477,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="56" spans="1:43">
+    <row r="56" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -11557,7 +11578,7 @@
         <v>46259</v>
       </c>
       <c r="AH56">
-        <v>0.5835616438356165</v>
+        <v>0.58356164383561648</v>
       </c>
       <c r="AI56">
         <v>21</v>
@@ -11587,7 +11608,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="57" spans="1:43">
+    <row r="57" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -11688,7 +11709,7 @@
         <v>46259</v>
       </c>
       <c r="AH57">
-        <v>7.150684931506849</v>
+        <v>7.1506849315068486</v>
       </c>
       <c r="AI57">
         <v>30</v>
@@ -11718,7 +11739,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="58" spans="1:43">
+    <row r="58" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -11819,7 +11840,7 @@
         <v>46259</v>
       </c>
       <c r="AH58">
-        <v>7.482191780821918</v>
+        <v>7.4821917808219176</v>
       </c>
       <c r="AI58">
         <v>30</v>
@@ -11849,7 +11870,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="59" spans="1:43">
+    <row r="59" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -11950,7 +11971,7 @@
         <v>46259</v>
       </c>
       <c r="AH59">
-        <v>0.06575342465753424</v>
+        <v>6.575342465753424E-2</v>
       </c>
       <c r="AI59">
         <v>21</v>
@@ -11980,7 +12001,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="60" spans="1:43">
+    <row r="60" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -12081,7 +12102,7 @@
         <v>46259</v>
       </c>
       <c r="AH60">
-        <v>0.06575342465753424</v>
+        <v>6.575342465753424E-2</v>
       </c>
       <c r="AI60">
         <v>21</v>
@@ -12111,7 +12132,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="61" spans="1:43">
+    <row r="61" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
@@ -12212,7 +12233,7 @@
         <v>46259</v>
       </c>
       <c r="AH61">
-        <v>18.26301369863014</v>
+        <v>18.263013698630139</v>
       </c>
       <c r="AI61">
         <v>30</v>
@@ -12242,7 +12263,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="62" spans="1:43">
+    <row r="62" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
@@ -12343,7 +12364,7 @@
         <v>46259</v>
       </c>
       <c r="AH62">
-        <v>15.07671232876712</v>
+        <v>15.076712328767121</v>
       </c>
       <c r="AI62">
         <v>30</v>
@@ -12373,7 +12394,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="63" spans="1:43">
+    <row r="63" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
@@ -12474,7 +12495,7 @@
         <v>46259</v>
       </c>
       <c r="AH63">
-        <v>34.04931506849315</v>
+        <v>34.049315068493151</v>
       </c>
       <c r="AI63">
         <v>30</v>
@@ -12504,7 +12525,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="64" spans="1:43">
+    <row r="64" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
@@ -12605,7 +12626,7 @@
         <v>46259</v>
       </c>
       <c r="AH64">
-        <v>6.175342465753425</v>
+        <v>6.1753424657534248</v>
       </c>
       <c r="AI64">
         <v>30</v>
@@ -12635,7 +12656,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="65" spans="1:43">
+    <row r="65" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
@@ -12736,7 +12757,7 @@
         <v>46259</v>
       </c>
       <c r="AH65">
-        <v>1.873972602739726</v>
+        <v>1.8739726027397261</v>
       </c>
       <c r="AI65">
         <v>21</v>
@@ -12766,7 +12787,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="66" spans="1:43">
+    <row r="66" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
@@ -12867,7 +12888,7 @@
         <v>46259</v>
       </c>
       <c r="AH66">
-        <v>5.753424657534246</v>
+        <v>5.7534246575342456</v>
       </c>
       <c r="AI66">
         <v>21</v>
@@ -12897,7 +12918,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="67" spans="1:43">
+    <row r="67" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
@@ -12998,7 +13019,7 @@
         <v>46259</v>
       </c>
       <c r="AH67">
-        <v>18.04657534246575</v>
+        <v>18.046575342465751</v>
       </c>
       <c r="AI67">
         <v>30</v>
@@ -13028,7 +13049,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="68" spans="1:43">
+    <row r="68" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
@@ -13129,7 +13150,7 @@
         <v>46259</v>
       </c>
       <c r="AH68">
-        <v>9.531506849315068</v>
+        <v>9.5315068493150683</v>
       </c>
       <c r="AI68">
         <v>30</v>
@@ -13159,7 +13180,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="69" spans="1:43">
+    <row r="69" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
@@ -13290,7 +13311,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="70" spans="1:43">
+    <row r="70" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
@@ -13391,7 +13412,7 @@
         <v>46259</v>
       </c>
       <c r="AH70">
-        <v>10.60821917808219</v>
+        <v>10.608219178082191</v>
       </c>
       <c r="AI70">
         <v>30</v>
@@ -13421,7 +13442,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="71" spans="1:43">
+    <row r="71" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
@@ -13522,7 +13543,7 @@
         <v>46259</v>
       </c>
       <c r="AH71">
-        <v>0.3342465753424658</v>
+        <v>0.33424657534246582</v>
       </c>
       <c r="AI71">
         <v>21</v>
@@ -13552,7 +13573,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="72" spans="1:43">
+    <row r="72" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
@@ -13653,7 +13674,7 @@
         <v>46259</v>
       </c>
       <c r="AH72">
-        <v>0.3342465753424658</v>
+        <v>0.33424657534246582</v>
       </c>
       <c r="AI72">
         <v>21</v>
@@ -13683,7 +13704,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="73" spans="1:43">
+    <row r="73" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
@@ -13784,7 +13805,7 @@
         <v>46259</v>
       </c>
       <c r="AH73">
-        <v>2.96986301369863</v>
+        <v>2.9698630136986299</v>
       </c>
       <c r="AI73">
         <v>21</v>
@@ -13814,7 +13835,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="74" spans="1:43">
+    <row r="74" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>71</v>
       </c>
@@ -13945,7 +13966,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="75" spans="1:43">
+    <row r="75" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>72</v>
       </c>
@@ -14046,7 +14067,7 @@
         <v>46259</v>
       </c>
       <c r="AH75">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AI75">
         <v>21</v>
@@ -14076,7 +14097,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="76" spans="1:43">
+    <row r="76" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>73</v>
       </c>
@@ -14177,7 +14198,7 @@
         <v>46259</v>
       </c>
       <c r="AH76">
-        <v>4.068493150684931</v>
+        <v>4.0684931506849313</v>
       </c>
       <c r="AI76">
         <v>21</v>
@@ -14207,7 +14228,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="77" spans="1:43">
+    <row r="77" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>74</v>
       </c>
@@ -14338,7 +14359,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="78" spans="1:43">
+    <row r="78" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>75</v>
       </c>
@@ -14469,7 +14490,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="79" spans="1:43">
+    <row r="79" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>76</v>
       </c>
@@ -14570,7 +14591,7 @@
         <v>46259</v>
       </c>
       <c r="AH79">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AI79">
         <v>21</v>
@@ -14600,7 +14621,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="80" spans="1:43">
+    <row r="80" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>77</v>
       </c>
@@ -14701,7 +14722,7 @@
         <v>46259</v>
       </c>
       <c r="AH80">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AI80">
         <v>21</v>
@@ -14731,7 +14752,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="81" spans="1:43">
+    <row r="81" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>78</v>
       </c>
@@ -14832,7 +14853,7 @@
         <v>46259</v>
       </c>
       <c r="AH81">
-        <v>1.819178082191781</v>
+        <v>1.8191780821917809</v>
       </c>
       <c r="AI81">
         <v>21</v>
@@ -14862,7 +14883,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="82" spans="1:43">
+    <row r="82" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>79</v>
       </c>
@@ -14963,7 +14984,7 @@
         <v>46259</v>
       </c>
       <c r="AH82">
-        <v>1.654794520547945</v>
+        <v>1.6547945205479451</v>
       </c>
       <c r="AI82">
         <v>21</v>
@@ -14993,7 +15014,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="83" spans="1:43">
+    <row r="83" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>80</v>
       </c>
@@ -15094,7 +15115,7 @@
         <v>46259</v>
       </c>
       <c r="AH83">
-        <v>15.16712328767123</v>
+        <v>15.167123287671229</v>
       </c>
       <c r="AI83">
         <v>30</v>
@@ -15124,7 +15145,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="84" spans="1:43">
+    <row r="84" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>80</v>
       </c>
@@ -15165,7 +15186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:43">
+    <row r="85" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>81</v>
       </c>
@@ -15266,7 +15287,7 @@
         <v>46259</v>
       </c>
       <c r="AH85">
-        <v>8.975342465753425</v>
+        <v>8.9753424657534246</v>
       </c>
       <c r="AI85">
         <v>30</v>
@@ -15296,7 +15317,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="86" spans="1:43">
+    <row r="86" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>82</v>
       </c>
@@ -15397,7 +15418,7 @@
         <v>46259</v>
       </c>
       <c r="AH86">
-        <v>6.70958904109589</v>
+        <v>6.7095890410958896</v>
       </c>
       <c r="AI86">
         <v>30</v>
@@ -15427,7 +15448,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="87" spans="1:43">
+    <row r="87" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>83</v>
       </c>
@@ -15528,7 +15549,7 @@
         <v>46259</v>
       </c>
       <c r="AH87">
-        <v>9.323287671232876</v>
+        <v>9.3232876712328761</v>
       </c>
       <c r="AI87">
         <v>30</v>
@@ -15558,7 +15579,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="88" spans="1:43">
+    <row r="88" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>84</v>
       </c>
@@ -15659,7 +15680,7 @@
         <v>46259</v>
       </c>
       <c r="AH88">
-        <v>14.03561643835616</v>
+        <v>14.035616438356159</v>
       </c>
       <c r="AI88">
         <v>30</v>
@@ -15689,7 +15710,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="89" spans="1:43">
+    <row r="89" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>85</v>
       </c>
@@ -15790,7 +15811,7 @@
         <v>46259</v>
       </c>
       <c r="AH89">
-        <v>1.772602739726027</v>
+        <v>1.7726027397260271</v>
       </c>
       <c r="AI89">
         <v>21</v>
@@ -15820,7 +15841,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="90" spans="1:43">
+    <row r="90" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>86</v>
       </c>
@@ -15921,7 +15942,7 @@
         <v>46259</v>
       </c>
       <c r="AH90">
-        <v>8.408219178082192</v>
+        <v>8.4082191780821915</v>
       </c>
       <c r="AI90">
         <v>30</v>
@@ -15951,7 +15972,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="91" spans="1:43">
+    <row r="91" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>87</v>
       </c>
@@ -16052,7 +16073,7 @@
         <v>46259</v>
       </c>
       <c r="AH91">
-        <v>10.95068493150685</v>
+        <v>10.950684931506849</v>
       </c>
       <c r="AI91">
         <v>30</v>
@@ -16082,7 +16103,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="92" spans="1:43">
+    <row r="92" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>88</v>
       </c>
@@ -16183,7 +16204,7 @@
         <v>46259</v>
       </c>
       <c r="AH92">
-        <v>6.682191780821918</v>
+        <v>6.6821917808219178</v>
       </c>
       <c r="AI92">
         <v>21</v>
@@ -16213,7 +16234,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="93" spans="1:43">
+    <row r="93" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>89</v>
       </c>
@@ -16314,7 +16335,7 @@
         <v>46259</v>
       </c>
       <c r="AH93">
-        <v>5.627397260273972</v>
+        <v>5.6273972602739724</v>
       </c>
       <c r="AI93">
         <v>21</v>
@@ -16344,7 +16365,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="94" spans="1:43">
+    <row r="94" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>90</v>
       </c>
@@ -16445,7 +16466,7 @@
         <v>46259</v>
       </c>
       <c r="AH94">
-        <v>5.315068493150685</v>
+        <v>5.3150684931506849</v>
       </c>
       <c r="AI94">
         <v>30</v>
@@ -16475,7 +16496,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="95" spans="1:43">
+    <row r="95" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>91</v>
       </c>
@@ -16576,7 +16597,7 @@
         <v>46259</v>
       </c>
       <c r="AH95">
-        <v>5.06027397260274</v>
+        <v>5.0602739726027401</v>
       </c>
       <c r="AI95">
         <v>30</v>
@@ -16606,7 +16627,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="96" spans="1:43">
+    <row r="96" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>92</v>
       </c>
@@ -16707,7 +16728,7 @@
         <v>46259</v>
       </c>
       <c r="AH96">
-        <v>5.06027397260274</v>
+        <v>5.0602739726027401</v>
       </c>
       <c r="AI96">
         <v>21</v>
@@ -16737,7 +16758,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="97" spans="1:43">
+    <row r="97" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>93</v>
       </c>
@@ -16838,7 +16859,7 @@
         <v>46259</v>
       </c>
       <c r="AH97">
-        <v>4.753424657534246</v>
+        <v>4.7534246575342456</v>
       </c>
       <c r="AI97">
         <v>21</v>
@@ -16868,7 +16889,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="98" spans="1:43">
+    <row r="98" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>94</v>
       </c>
@@ -16969,7 +16990,7 @@
         <v>46259</v>
       </c>
       <c r="AH98">
-        <v>0.5835616438356165</v>
+        <v>0.58356164383561648</v>
       </c>
       <c r="AI98">
         <v>21</v>
@@ -16999,7 +17020,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="99" spans="1:43">
+    <row r="99" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>95</v>
       </c>
@@ -17100,7 +17121,7 @@
         <v>46259</v>
       </c>
       <c r="AH99">
-        <v>0.5835616438356165</v>
+        <v>0.58356164383561648</v>
       </c>
       <c r="AI99">
         <v>21</v>
@@ -17130,7 +17151,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="100" spans="1:43">
+    <row r="100" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>96</v>
       </c>
@@ -17231,7 +17252,7 @@
         <v>46259</v>
       </c>
       <c r="AH100">
-        <v>4.739726027397261</v>
+        <v>4.7397260273972606</v>
       </c>
       <c r="AI100">
         <v>21</v>
@@ -17261,7 +17282,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="101" spans="1:43">
+    <row r="101" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>97</v>
       </c>
@@ -17362,7 +17383,7 @@
         <v>46259</v>
       </c>
       <c r="AH101">
-        <v>4.67945205479452</v>
+        <v>4.6794520547945204</v>
       </c>
       <c r="AI101">
         <v>21</v>
@@ -17392,7 +17413,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="102" spans="1:43">
+    <row r="102" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>98</v>
       </c>
@@ -17493,7 +17514,7 @@
         <v>46259</v>
       </c>
       <c r="AH102">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AI102">
         <v>21</v>
@@ -17523,7 +17544,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="103" spans="1:43">
+    <row r="103" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>99</v>
       </c>
@@ -17624,7 +17645,7 @@
         <v>46259</v>
       </c>
       <c r="AH103">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AI103">
         <v>21</v>
@@ -17654,7 +17675,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="104" spans="1:43">
+    <row r="104" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>100</v>
       </c>
@@ -17755,7 +17776,7 @@
         <v>46259</v>
       </c>
       <c r="AH104">
-        <v>3.964383561643836</v>
+        <v>3.9643835616438361</v>
       </c>
       <c r="AI104">
         <v>21</v>
@@ -17785,7 +17806,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="105" spans="1:43">
+    <row r="105" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>101</v>
       </c>
@@ -17886,7 +17907,7 @@
         <v>46259</v>
       </c>
       <c r="AH105">
-        <v>7.523287671232877</v>
+        <v>7.5232876712328771</v>
       </c>
       <c r="AI105">
         <v>30</v>
@@ -17916,7 +17937,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="106" spans="1:43">
+    <row r="106" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>102</v>
       </c>
@@ -18017,7 +18038,7 @@
         <v>46259</v>
       </c>
       <c r="AH106">
-        <v>4.972602739726027</v>
+        <v>4.9726027397260273</v>
       </c>
       <c r="AI106">
         <v>21</v>
@@ -18047,7 +18068,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="107" spans="1:43">
+    <row r="107" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>103</v>
       </c>
@@ -18148,7 +18169,7 @@
         <v>46259</v>
       </c>
       <c r="AH107">
-        <v>1.96986301369863</v>
+        <v>1.9698630136986299</v>
       </c>
       <c r="AI107">
         <v>21</v>
@@ -18178,7 +18199,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="108" spans="1:43">
+    <row r="108" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>104</v>
       </c>
@@ -18279,7 +18300,7 @@
         <v>46259</v>
       </c>
       <c r="AH108">
-        <v>22.44657534246575</v>
+        <v>22.446575342465749</v>
       </c>
       <c r="AI108">
         <v>30</v>
@@ -18309,7 +18330,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="109" spans="1:43">
+    <row r="109" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>105</v>
       </c>
@@ -18410,7 +18431,7 @@
         <v>46259</v>
       </c>
       <c r="AH109">
-        <v>3.986301369863014</v>
+        <v>3.9863013698630141</v>
       </c>
       <c r="AI109">
         <v>21</v>
@@ -18440,7 +18461,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="110" spans="1:43">
+    <row r="110" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>106</v>
       </c>
@@ -18493,7 +18514,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="111" spans="1:43">
+    <row r="111" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>107</v>
       </c>
@@ -18594,7 +18615,7 @@
         <v>46259</v>
       </c>
       <c r="AH111">
-        <v>0.3589041095890411</v>
+        <v>0.35890410958904112</v>
       </c>
       <c r="AI111">
         <v>21</v>
@@ -18624,7 +18645,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="112" spans="1:43">
+    <row r="112" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>108</v>
       </c>
@@ -18725,7 +18746,7 @@
         <v>46259</v>
       </c>
       <c r="AH112">
-        <v>5.372602739726028</v>
+        <v>5.3726027397260276</v>
       </c>
       <c r="AI112">
         <v>21</v>
@@ -18755,7 +18776,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="113" spans="1:43">
+    <row r="113" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>109</v>
       </c>
@@ -18856,7 +18877,7 @@
         <v>46259</v>
       </c>
       <c r="AH113">
-        <v>4.528767123287671</v>
+        <v>4.5287671232876709</v>
       </c>
       <c r="AI113">
         <v>21</v>
@@ -18886,7 +18907,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="114" spans="1:43">
+    <row r="114" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>110</v>
       </c>
@@ -18987,7 +19008,7 @@
         <v>46259</v>
       </c>
       <c r="AH114">
-        <v>4.583561643835616</v>
+        <v>4.5835616438356164</v>
       </c>
       <c r="AI114">
         <v>21</v>
@@ -19017,7 +19038,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="115" spans="1:43">
+    <row r="115" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>111</v>
       </c>
@@ -19118,7 +19139,7 @@
         <v>46259</v>
       </c>
       <c r="AH115">
-        <v>4.526027397260274</v>
+        <v>4.5260273972602736</v>
       </c>
       <c r="AI115">
         <v>21</v>
@@ -19148,7 +19169,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="116" spans="1:43">
+    <row r="116" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>112</v>
       </c>
@@ -19249,7 +19270,7 @@
         <v>46259</v>
       </c>
       <c r="AH116">
-        <v>4.528767123287671</v>
+        <v>4.5287671232876709</v>
       </c>
       <c r="AI116">
         <v>21</v>
@@ -19279,7 +19300,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="117" spans="1:43">
+    <row r="117" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B117">
         <v>1336</v>
       </c>
@@ -19407,7 +19428,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="118" spans="1:43">
+    <row r="118" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>113</v>
       </c>
@@ -19538,7 +19559,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="119" spans="1:43">
+    <row r="119" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>114</v>
       </c>
@@ -19639,7 +19660,7 @@
         <v>46259</v>
       </c>
       <c r="AH119">
-        <v>2.63013698630137</v>
+        <v>2.6301369863013702</v>
       </c>
       <c r="AI119">
         <v>21</v>
@@ -19669,7 +19690,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="120" spans="1:43">
+    <row r="120" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>115</v>
       </c>
@@ -19770,7 +19791,7 @@
         <v>46259</v>
       </c>
       <c r="AH120">
-        <v>2.410958904109589</v>
+        <v>2.4109589041095889</v>
       </c>
       <c r="AI120">
         <v>21</v>
@@ -19800,7 +19821,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="121" spans="1:43">
+    <row r="121" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>116</v>
       </c>
@@ -19931,7 +19952,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="122" spans="1:43">
+    <row r="122" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>117</v>
       </c>
@@ -20062,7 +20083,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="123" spans="1:43">
+    <row r="123" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>118</v>
       </c>
@@ -20193,7 +20214,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="124" spans="1:43">
+    <row r="124" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>119</v>
       </c>
@@ -20294,7 +20315,7 @@
         <v>46259</v>
       </c>
       <c r="AH124">
-        <v>2.263013698630137</v>
+        <v>2.2630136986301368</v>
       </c>
       <c r="AI124">
         <v>21</v>
@@ -20324,7 +20345,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="125" spans="1:43">
+    <row r="125" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>120</v>
       </c>
@@ -20425,7 +20446,7 @@
         <v>46259</v>
       </c>
       <c r="AH125">
-        <v>6.586301369863014</v>
+        <v>6.5863013698630137</v>
       </c>
       <c r="AI125">
         <v>30</v>
@@ -20455,7 +20476,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="126" spans="1:43">
+    <row r="126" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>120</v>
       </c>
@@ -20478,7 +20499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:43">
+    <row r="127" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>121</v>
       </c>
@@ -20579,7 +20600,7 @@
         <v>46259</v>
       </c>
       <c r="AH127">
-        <v>12.26575342465753</v>
+        <v>12.265753424657531</v>
       </c>
       <c r="AI127">
         <v>30</v>
@@ -20609,7 +20630,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="128" spans="1:43">
+    <row r="128" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>122</v>
       </c>
@@ -20710,7 +20731,7 @@
         <v>46259</v>
       </c>
       <c r="AH128">
-        <v>5.964383561643835</v>
+        <v>5.9643835616438352</v>
       </c>
       <c r="AI128">
         <v>30</v>
@@ -20740,7 +20761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:43">
+    <row r="129" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>123</v>
       </c>
@@ -20841,7 +20862,7 @@
         <v>46259</v>
       </c>
       <c r="AH129">
-        <v>5.797260273972602</v>
+        <v>5.7972602739726016</v>
       </c>
       <c r="AI129">
         <v>21</v>
@@ -20871,7 +20892,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="130" spans="1:43">
+    <row r="130" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>124</v>
       </c>
@@ -20972,7 +20993,7 @@
         <v>46259</v>
       </c>
       <c r="AH130">
-        <v>5.153424657534247</v>
+        <v>5.1534246575342468</v>
       </c>
       <c r="AI130">
         <v>30</v>
@@ -21002,7 +21023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:43">
+    <row r="131" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>125</v>
       </c>
@@ -21103,7 +21124,7 @@
         <v>46259</v>
       </c>
       <c r="AH131">
-        <v>5.178082191780822</v>
+        <v>5.1780821917808222</v>
       </c>
       <c r="AI131">
         <v>30</v>
@@ -21133,7 +21154,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="132" spans="1:43">
+    <row r="132" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B132">
         <v>1135</v>
       </c>
@@ -21231,7 +21252,7 @@
         <v>46259</v>
       </c>
       <c r="AH132">
-        <v>0.1506849315068493</v>
+        <v>0.15068493150684931</v>
       </c>
       <c r="AI132">
         <v>21</v>
@@ -21261,7 +21282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:43">
+    <row r="133" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>126</v>
       </c>
@@ -21362,7 +21383,7 @@
         <v>46259</v>
       </c>
       <c r="AH133">
-        <v>4.235616438356164</v>
+        <v>4.2356164383561641</v>
       </c>
       <c r="AI133">
         <v>21</v>
@@ -21392,7 +21413,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="134" spans="1:43">
+    <row r="134" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>127</v>
       </c>
@@ -21493,7 +21514,7 @@
         <v>46259</v>
       </c>
       <c r="AH134">
-        <v>4.235616438356164</v>
+        <v>4.2356164383561641</v>
       </c>
       <c r="AI134">
         <v>21</v>
@@ -21523,7 +21544,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="135" spans="1:43">
+    <row r="135" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>128</v>
       </c>
@@ -21624,7 +21645,7 @@
         <v>46259</v>
       </c>
       <c r="AH135">
-        <v>4.723287671232876</v>
+        <v>4.7232876712328764</v>
       </c>
       <c r="AI135">
         <v>21</v>
@@ -21654,7 +21675,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="136" spans="1:43">
+    <row r="136" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>129</v>
       </c>
@@ -21755,7 +21776,7 @@
         <v>46259</v>
       </c>
       <c r="AH136">
-        <v>4.29041095890411</v>
+        <v>4.2904109589041104</v>
       </c>
       <c r="AI136">
         <v>21</v>
@@ -21785,7 +21806,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="137" spans="1:43">
+    <row r="137" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>130</v>
       </c>
@@ -21886,7 +21907,7 @@
         <v>46259</v>
       </c>
       <c r="AH137">
-        <v>4.553424657534246</v>
+        <v>4.5534246575342463</v>
       </c>
       <c r="AI137">
         <v>21</v>
@@ -21916,7 +21937,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="138" spans="1:43">
+    <row r="138" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>131</v>
       </c>
@@ -22017,7 +22038,7 @@
         <v>46259</v>
       </c>
       <c r="AH138">
-        <v>1.498630136986301</v>
+        <v>1.4986301369863011</v>
       </c>
       <c r="AI138">
         <v>21</v>
@@ -22047,7 +22068,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="139" spans="1:43">
+    <row r="139" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>132</v>
       </c>
@@ -22178,7 +22199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:43">
+    <row r="140" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>133</v>
       </c>
@@ -22309,7 +22330,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="141" spans="1:43">
+    <row r="141" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>134</v>
       </c>
@@ -22440,7 +22461,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="142" spans="1:43">
+    <row r="142" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>135</v>
       </c>
@@ -22571,7 +22592,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="143" spans="1:43">
+    <row r="143" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>136</v>
       </c>
@@ -22672,7 +22693,7 @@
         <v>46259</v>
       </c>
       <c r="AH143">
-        <v>4.487671232876712</v>
+        <v>4.4876712328767123</v>
       </c>
       <c r="AI143">
         <v>21</v>
@@ -22702,7 +22723,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="144" spans="1:43">
+    <row r="144" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>137</v>
       </c>
@@ -22803,7 +22824,7 @@
         <v>46259</v>
       </c>
       <c r="AH144">
-        <v>4.468493150684932</v>
+        <v>4.4684931506849317</v>
       </c>
       <c r="AI144">
         <v>21</v>
@@ -22833,7 +22854,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="145" spans="1:43">
+    <row r="145" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>138</v>
       </c>
@@ -22934,7 +22955,7 @@
         <v>46259</v>
       </c>
       <c r="AH145">
-        <v>1.857534246575342</v>
+        <v>1.8575342465753419</v>
       </c>
       <c r="AI145">
         <v>21</v>
@@ -22964,7 +22985,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="146" spans="1:43">
+    <row r="146" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>139</v>
       </c>
@@ -23065,7 +23086,7 @@
         <v>46259</v>
       </c>
       <c r="AH146">
-        <v>4.389041095890411</v>
+        <v>4.3890410958904109</v>
       </c>
       <c r="AI146">
         <v>21</v>
@@ -23095,7 +23116,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="147" spans="1:43">
+    <row r="147" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>140</v>
       </c>
@@ -23196,7 +23217,7 @@
         <v>46259</v>
       </c>
       <c r="AH147">
-        <v>3.791780821917808</v>
+        <v>3.7917808219178082</v>
       </c>
       <c r="AI147">
         <v>21</v>
@@ -23226,7 +23247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:43">
+    <row r="148" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>141</v>
       </c>
@@ -23327,7 +23348,7 @@
         <v>46259</v>
       </c>
       <c r="AH148">
-        <v>3.786301369863014</v>
+        <v>3.7863013698630139</v>
       </c>
       <c r="AI148">
         <v>21</v>
@@ -23357,7 +23378,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="149" spans="1:43">
+    <row r="149" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>142</v>
       </c>
@@ -23458,7 +23479,7 @@
         <v>46259</v>
       </c>
       <c r="AH149">
-        <v>3.736986301369863</v>
+        <v>3.7369863013698632</v>
       </c>
       <c r="AI149">
         <v>21</v>
@@ -23488,7 +23509,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="150" spans="1:43">
+    <row r="150" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>143</v>
       </c>
@@ -23589,7 +23610,7 @@
         <v>46259</v>
       </c>
       <c r="AH150">
-        <v>2.545205479452055</v>
+        <v>2.5452054794520551</v>
       </c>
       <c r="AI150">
         <v>21</v>
@@ -23619,7 +23640,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="151" spans="1:43">
+    <row r="151" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>144</v>
       </c>
@@ -23720,7 +23741,7 @@
         <v>46259</v>
       </c>
       <c r="AH151">
-        <v>5.967123287671233</v>
+        <v>5.9671232876712326</v>
       </c>
       <c r="AI151">
         <v>21</v>
@@ -23750,7 +23771,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="152" spans="1:43">
+    <row r="152" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>145</v>
       </c>
@@ -23851,7 +23872,7 @@
         <v>46259</v>
       </c>
       <c r="AH152">
-        <v>3.101369863013699</v>
+        <v>3.1013698630136992</v>
       </c>
       <c r="AI152">
         <v>21</v>
@@ -23881,7 +23902,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="153" spans="1:43">
+    <row r="153" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>146</v>
       </c>
@@ -23982,7 +24003,7 @@
         <v>46259</v>
       </c>
       <c r="AH153">
-        <v>5.64931506849315</v>
+        <v>5.6493150684931503</v>
       </c>
       <c r="AI153">
         <v>21</v>
@@ -24012,7 +24033,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="154" spans="1:43">
+    <row r="154" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>147</v>
       </c>
@@ -24113,7 +24134,7 @@
         <v>46259</v>
       </c>
       <c r="AH154">
-        <v>5.402739726027397</v>
+        <v>5.4027397260273968</v>
       </c>
       <c r="AI154">
         <v>21</v>
@@ -24143,7 +24164,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="155" spans="1:43">
+    <row r="155" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>148</v>
       </c>
@@ -24244,7 +24265,7 @@
         <v>46259</v>
       </c>
       <c r="AH155">
-        <v>5.30958904109589</v>
+        <v>5.3095890410958901</v>
       </c>
       <c r="AI155">
         <v>21</v>
@@ -24274,7 +24295,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="156" spans="1:43">
+    <row r="156" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>149</v>
       </c>
@@ -24375,7 +24396,7 @@
         <v>46259</v>
       </c>
       <c r="AH156">
-        <v>5.038356164383561</v>
+        <v>5.0383561643835613</v>
       </c>
       <c r="AI156">
         <v>21</v>
@@ -24405,7 +24426,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="157" spans="1:43">
+    <row r="157" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>150</v>
       </c>
@@ -24506,7 +24527,7 @@
         <v>46259</v>
       </c>
       <c r="AH157">
-        <v>5.038356164383561</v>
+        <v>5.0383561643835613</v>
       </c>
       <c r="AI157">
         <v>21</v>
@@ -24536,7 +24557,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="158" spans="1:43">
+    <row r="158" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>151</v>
       </c>
@@ -24637,7 +24658,7 @@
         <v>46259</v>
       </c>
       <c r="AH158">
-        <v>5.038356164383561</v>
+        <v>5.0383561643835613</v>
       </c>
       <c r="AI158">
         <v>21</v>
@@ -24667,7 +24688,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="159" spans="1:43">
+    <row r="159" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>152</v>
       </c>
@@ -24768,7 +24789,7 @@
         <v>46259</v>
       </c>
       <c r="AH159">
-        <v>5.038356164383561</v>
+        <v>5.0383561643835613</v>
       </c>
       <c r="AI159">
         <v>21</v>
@@ -24798,7 +24819,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="160" spans="1:43">
+    <row r="160" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>153</v>
       </c>
@@ -24899,7 +24920,7 @@
         <v>46259</v>
       </c>
       <c r="AH160">
-        <v>1.83013698630137</v>
+        <v>1.8301369863013699</v>
       </c>
       <c r="AI160">
         <v>21</v>
@@ -24929,7 +24950,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="161" spans="1:43">
+    <row r="161" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>154</v>
       </c>
@@ -25030,7 +25051,7 @@
         <v>46259</v>
       </c>
       <c r="AH161">
-        <v>4.528767123287671</v>
+        <v>4.5287671232876709</v>
       </c>
       <c r="AI161">
         <v>21</v>
@@ -25060,7 +25081,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="162" spans="1:43">
+    <row r="162" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>155</v>
       </c>
@@ -25161,7 +25182,7 @@
         <v>46259</v>
       </c>
       <c r="AH162">
-        <v>4.389041095890411</v>
+        <v>4.3890410958904109</v>
       </c>
       <c r="AI162">
         <v>21</v>
@@ -25191,7 +25212,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="163" spans="1:43">
+    <row r="163" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>156</v>
       </c>
@@ -25292,7 +25313,7 @@
         <v>46259</v>
       </c>
       <c r="AH163">
-        <v>4.389041095890411</v>
+        <v>4.3890410958904109</v>
       </c>
       <c r="AI163">
         <v>21</v>
@@ -25322,7 +25343,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="164" spans="1:43">
+    <row r="164" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>157</v>
       </c>
@@ -25453,7 +25474,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="165" spans="1:43">
+    <row r="165" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>158</v>
       </c>
@@ -25554,7 +25575,7 @@
         <v>46259</v>
       </c>
       <c r="AH165">
-        <v>3.994520547945205</v>
+        <v>3.9945205479452048</v>
       </c>
       <c r="AI165">
         <v>21</v>
@@ -25584,7 +25605,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="166" spans="1:43">
+    <row r="166" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>159</v>
       </c>
@@ -25685,7 +25706,7 @@
         <v>46259</v>
       </c>
       <c r="AH166">
-        <v>3.964383561643836</v>
+        <v>3.9643835616438361</v>
       </c>
       <c r="AI166">
         <v>21</v>
@@ -25715,7 +25736,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="167" spans="1:43">
+    <row r="167" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>161</v>
       </c>
@@ -25816,7 +25837,7 @@
         <v>46259</v>
       </c>
       <c r="AH167">
-        <v>2.33972602739726</v>
+        <v>2.3397260273972602</v>
       </c>
       <c r="AI167">
         <v>21</v>
@@ -25846,7 +25867,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="168" spans="1:43">
+    <row r="168" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>162</v>
       </c>
@@ -25947,7 +25968,7 @@
         <v>46259</v>
       </c>
       <c r="AH168">
-        <v>13.54794520547945</v>
+        <v>13.547945205479451</v>
       </c>
       <c r="AI168">
         <v>30</v>
@@ -25977,7 +25998,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="169" spans="1:43">
+    <row r="169" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>163</v>
       </c>
@@ -26078,7 +26099,7 @@
         <v>46259</v>
       </c>
       <c r="AH169">
-        <v>5.153424657534247</v>
+        <v>5.1534246575342468</v>
       </c>
       <c r="AI169">
         <v>30</v>
@@ -26108,7 +26129,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="170" spans="1:43">
+    <row r="170" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>164</v>
       </c>
@@ -26209,7 +26230,7 @@
         <v>46259</v>
       </c>
       <c r="AH170">
-        <v>5.345205479452055</v>
+        <v>5.3452054794520549</v>
       </c>
       <c r="AI170">
         <v>30</v>
@@ -26239,7 +26260,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="171" spans="1:43">
+    <row r="171" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>165</v>
       </c>
@@ -26370,7 +26391,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="172" spans="1:43">
+    <row r="172" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>166</v>
       </c>
@@ -26471,7 +26492,7 @@
         <v>46259</v>
       </c>
       <c r="AH172">
-        <v>2.843835616438356</v>
+        <v>2.8438356164383558</v>
       </c>
       <c r="AI172">
         <v>21</v>
@@ -26501,7 +26522,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="173" spans="1:43">
+    <row r="173" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>167</v>
       </c>
@@ -26632,7 +26653,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="174" spans="1:43">
+    <row r="174" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>168</v>
       </c>
@@ -26733,7 +26754,7 @@
         <v>46259</v>
       </c>
       <c r="AH174">
-        <v>1.96986301369863</v>
+        <v>1.9698630136986299</v>
       </c>
       <c r="AI174">
         <v>21</v>
@@ -26763,7 +26784,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="175" spans="1:43">
+    <row r="175" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>169</v>
       </c>
@@ -26870,13 +26891,13 @@
         <v>21</v>
       </c>
       <c r="AJ175">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="AK175">
-        <v>241</v>
+        <v>375</v>
       </c>
       <c r="AL175">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="AM175">
         <v>0</v>
@@ -26894,7 +26915,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="176" spans="1:43">
+    <row r="176" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>170</v>
       </c>
@@ -26995,7 +27016,7 @@
         <v>46259</v>
       </c>
       <c r="AH176">
-        <v>5.876712328767123</v>
+        <v>5.8767123287671232</v>
       </c>
       <c r="AI176">
         <v>30</v>
@@ -27025,7 +27046,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="177" spans="1:43">
+    <row r="177" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>171</v>
       </c>
@@ -27156,7 +27177,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="178" spans="1:43">
+    <row r="178" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>172</v>
       </c>
@@ -27257,7 +27278,7 @@
         <v>46259</v>
       </c>
       <c r="AH178">
-        <v>2.961643835616438</v>
+        <v>2.9616438356164378</v>
       </c>
       <c r="AI178">
         <v>21</v>
@@ -27287,7 +27308,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="179" spans="1:43">
+    <row r="179" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>173</v>
       </c>
@@ -27388,7 +27409,7 @@
         <v>46259</v>
       </c>
       <c r="AH179">
-        <v>2.468493150684932</v>
+        <v>2.4684931506849321</v>
       </c>
       <c r="AI179">
         <v>21</v>
@@ -27418,7 +27439,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="180" spans="1:43">
+    <row r="180" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>174</v>
       </c>
@@ -27519,7 +27540,7 @@
         <v>46259</v>
       </c>
       <c r="AH180">
-        <v>2.252054794520548</v>
+        <v>2.2520547945205478</v>
       </c>
       <c r="AI180">
         <v>21</v>
@@ -27549,7 +27570,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="181" spans="1:43">
+    <row r="181" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>175</v>
       </c>
@@ -27680,7 +27701,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="182" spans="1:43">
+    <row r="182" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>176</v>
       </c>
@@ -27811,7 +27832,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="183" spans="1:43">
+    <row r="183" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>177</v>
       </c>
@@ -27942,7 +27963,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="184" spans="1:43">
+    <row r="184" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>178</v>
       </c>
@@ -28073,7 +28094,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="185" spans="1:43">
+    <row r="185" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>179</v>
       </c>
@@ -28204,7 +28225,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="186" spans="1:43">
+    <row r="186" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>180</v>
       </c>
@@ -28305,7 +28326,7 @@
         <v>46259</v>
       </c>
       <c r="AH186">
-        <v>1.745205479452055</v>
+        <v>1.7452054794520551</v>
       </c>
       <c r="AI186">
         <v>21</v>
@@ -28335,7 +28356,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="187" spans="1:43">
+    <row r="187" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>181</v>
       </c>
@@ -28436,7 +28457,7 @@
         <v>46259</v>
       </c>
       <c r="AH187">
-        <v>1.389041095890411</v>
+        <v>1.3890410958904109</v>
       </c>
       <c r="AI187">
         <v>21</v>
@@ -28468,7 +28489,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="S170" r:id="rId1"/>
+    <hyperlink ref="S170" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Staffdata.xlsx
+++ b/Staffdata.xlsx
@@ -1,26 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3113719057d24bf/Desktop/HR-Forms-Site/HRFORMAS/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_05E48499FC67680F1964AE368160343238AA41AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B403DCDC-E7E9-4FA3-8BB1-6D958BD53ECA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -2185,7 +2174,7 @@
     <t>-</t>
   </si>
   <si>
-    <t> 966577040481</t>
+    <t xml:space="preserve"> 966577040481</t>
   </si>
   <si>
     <t>malbatil@outlook.sa</t>
@@ -2496,10 +2485,10 @@
     <t>HAMDILLHJ038@GMAIL.COM</t>
   </si>
   <si>
-    <t> omarzar392@gmail.com</t>
-  </si>
-  <si>
-    <t> ark870725@gmail.com</t>
+    <t xml:space="preserve"> omarzar392@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ark870725@gmail.com</t>
   </si>
   <si>
     <t>waelgomaa1wg@gmail.com</t>
@@ -2572,7 +2561,7 @@
     <t>INFO2@HAIL-HOUSE.SA</t>
   </si>
   <si>
-    <t> Sarah_elkhatib@outlook.com</t>
+    <t xml:space="preserve"> Sarah_elkhatib@outlook.com</t>
   </si>
   <si>
     <t xml:space="preserve"> mohannad.fakhry00@gmail.com</t>
@@ -3916,11 +3905,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3966,26 +3955,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="ارتباط تشعبي" xfId="1" builtinId="8"/>
-    <cellStyle name="عادي" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4023,7 +4004,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4057,7 +4038,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4092,10 +4072,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4268,11 +4247,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AQ187"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4403,7 +4382,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4504,7 +4483,7 @@
         <v>46259</v>
       </c>
       <c r="AH2">
-        <v>8.7260273972602747</v>
+        <v>8.726027397260275</v>
       </c>
       <c r="AI2">
         <v>30</v>
@@ -4534,7 +4513,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4635,7 +4614,7 @@
         <v>46259</v>
       </c>
       <c r="AH3">
-        <v>13.635616438356161</v>
+        <v>13.63561643835616</v>
       </c>
       <c r="AI3">
         <v>30</v>
@@ -4665,7 +4644,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4766,7 +4745,7 @@
         <v>46259</v>
       </c>
       <c r="AH4">
-        <v>5.8904109589041092</v>
+        <v>5.890410958904109</v>
       </c>
       <c r="AI4">
         <v>30</v>
@@ -4796,7 +4775,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4897,7 +4876,7 @@
         <v>46259</v>
       </c>
       <c r="AH5">
-        <v>6.0465753424657533</v>
+        <v>6.046575342465753</v>
       </c>
       <c r="AI5">
         <v>21</v>
@@ -4927,7 +4906,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5028,7 +5007,7 @@
         <v>46259</v>
       </c>
       <c r="AH6">
-        <v>6.4027397260273968</v>
+        <v>6.402739726027397</v>
       </c>
       <c r="AI6">
         <v>21</v>
@@ -5058,7 +5037,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5159,7 +5138,7 @@
         <v>46259</v>
       </c>
       <c r="AH7">
-        <v>5.7041095890410958</v>
+        <v>5.704109589041096</v>
       </c>
       <c r="AI7">
         <v>30</v>
@@ -5189,7 +5168,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5320,7 +5299,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5451,7 +5430,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5552,7 +5531,7 @@
         <v>46259</v>
       </c>
       <c r="AH10">
-        <v>6.7534246575342456</v>
+        <v>6.753424657534246</v>
       </c>
       <c r="AI10">
         <v>30</v>
@@ -5582,7 +5561,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5713,7 +5692,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5814,7 +5793,7 @@
         <v>46259</v>
       </c>
       <c r="AH12">
-        <v>5.7506849315068491</v>
+        <v>5.750684931506849</v>
       </c>
       <c r="AI12">
         <v>21</v>
@@ -5844,7 +5823,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5975,7 +5954,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6076,7 +6055,7 @@
         <v>46259</v>
       </c>
       <c r="AH14">
-        <v>0.30410958904109592</v>
+        <v>0.3041095890410959</v>
       </c>
       <c r="AI14">
         <v>21</v>
@@ -6106,7 +6085,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6207,7 +6186,7 @@
         <v>46259</v>
       </c>
       <c r="AH15">
-        <v>3.9835616438356158</v>
+        <v>3.983561643835616</v>
       </c>
       <c r="AI15">
         <v>21</v>
@@ -6237,7 +6216,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6338,7 +6317,7 @@
         <v>46259</v>
       </c>
       <c r="AH16">
-        <v>2.8986301369863008</v>
+        <v>2.898630136986301</v>
       </c>
       <c r="AI16">
         <v>21</v>
@@ -6368,7 +6347,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:43">
       <c r="A17">
         <v>16</v>
       </c>
@@ -6469,7 +6448,7 @@
         <v>46259</v>
       </c>
       <c r="AH17">
-        <v>1.6739726027397259</v>
+        <v>1.673972602739726</v>
       </c>
       <c r="AI17">
         <v>21</v>
@@ -6499,7 +6478,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:43">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6600,7 +6579,7 @@
         <v>46259</v>
       </c>
       <c r="AH18">
-        <v>2.0493150684931511</v>
+        <v>2.049315068493151</v>
       </c>
       <c r="AI18">
         <v>21</v>
@@ -6630,7 +6609,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:43">
       <c r="A19">
         <v>18</v>
       </c>
@@ -6731,7 +6710,7 @@
         <v>46259</v>
       </c>
       <c r="AH19">
-        <v>2.0356164383561639</v>
+        <v>2.035616438356164</v>
       </c>
       <c r="AI19">
         <v>21</v>
@@ -6761,7 +6740,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43">
       <c r="A20">
         <v>19</v>
       </c>
@@ -6862,7 +6841,7 @@
         <v>46259</v>
       </c>
       <c r="AH20">
-        <v>1.5123287671232879</v>
+        <v>1.512328767123288</v>
       </c>
       <c r="AI20">
         <v>21</v>
@@ -6892,7 +6871,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:43">
       <c r="A21">
         <v>20</v>
       </c>
@@ -6993,7 +6972,7 @@
         <v>46259</v>
       </c>
       <c r="AH21">
-        <v>2.0356164383561639</v>
+        <v>2.035616438356164</v>
       </c>
       <c r="AI21">
         <v>21</v>
@@ -7023,7 +7002,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43">
       <c r="A22">
         <v>21</v>
       </c>
@@ -7154,7 +7133,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:43">
       <c r="A23">
         <v>22</v>
       </c>
@@ -7285,7 +7264,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:43">
       <c r="A24">
         <v>23</v>
       </c>
@@ -7416,7 +7395,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:43">
       <c r="A25">
         <v>24</v>
       </c>
@@ -7517,7 +7496,7 @@
         <v>46259</v>
       </c>
       <c r="AH25">
-        <v>0.76164383561643834</v>
+        <v>0.7616438356164383</v>
       </c>
       <c r="AI25">
         <v>21</v>
@@ -7547,7 +7526,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:43">
       <c r="A26">
         <v>25</v>
       </c>
@@ -7648,7 +7627,7 @@
         <v>46259</v>
       </c>
       <c r="AH26">
-        <v>0.76164383561643834</v>
+        <v>0.7616438356164383</v>
       </c>
       <c r="AI26">
         <v>21</v>
@@ -7678,7 +7657,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:43">
       <c r="A27">
         <v>26</v>
       </c>
@@ -7779,7 +7758,7 @@
         <v>46259</v>
       </c>
       <c r="AH27">
-        <v>6.7369863013698632</v>
+        <v>6.736986301369863</v>
       </c>
       <c r="AI27">
         <v>30</v>
@@ -7809,7 +7788,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:43">
       <c r="A28">
         <v>27</v>
       </c>
@@ -7910,7 +7889,7 @@
         <v>46259</v>
       </c>
       <c r="AH28">
-        <v>12.112328767123291</v>
+        <v>12.11232876712329</v>
       </c>
       <c r="AI28">
         <v>30</v>
@@ -7940,7 +7919,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:43">
       <c r="A29">
         <v>28</v>
       </c>
@@ -8041,7 +8020,7 @@
         <v>46259</v>
       </c>
       <c r="AH29">
-        <v>3.4876712328767119</v>
+        <v>3.487671232876712</v>
       </c>
       <c r="AI29">
         <v>21</v>
@@ -8071,7 +8050,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:43">
       <c r="A30">
         <v>29</v>
       </c>
@@ -8172,7 +8151,7 @@
         <v>46259</v>
       </c>
       <c r="AH30">
-        <v>15.076712328767121</v>
+        <v>15.07671232876712</v>
       </c>
       <c r="AI30">
         <v>30</v>
@@ -8202,7 +8181,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:43">
       <c r="A31">
         <v>30</v>
       </c>
@@ -8303,7 +8282,7 @@
         <v>46259</v>
       </c>
       <c r="AH31">
-        <v>15.076712328767121</v>
+        <v>15.07671232876712</v>
       </c>
       <c r="AI31">
         <v>30</v>
@@ -8333,7 +8312,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:43">
       <c r="A32">
         <v>31</v>
       </c>
@@ -8464,7 +8443,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:43">
       <c r="A33">
         <v>32</v>
       </c>
@@ -8565,7 +8544,7 @@
         <v>46259</v>
       </c>
       <c r="AH33">
-        <v>15.167123287671229</v>
+        <v>15.16712328767123</v>
       </c>
       <c r="AI33">
         <v>30</v>
@@ -8595,7 +8574,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:43">
       <c r="A34">
         <v>33</v>
       </c>
@@ -8696,7 +8675,7 @@
         <v>46259</v>
       </c>
       <c r="AH34">
-        <v>4.6109589041095891</v>
+        <v>4.610958904109589</v>
       </c>
       <c r="AI34">
         <v>21</v>
@@ -8726,7 +8705,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:43">
       <c r="A35">
         <v>34</v>
       </c>
@@ -8827,7 +8806,7 @@
         <v>46259</v>
       </c>
       <c r="AH35">
-        <v>4.5424657534246577</v>
+        <v>4.542465753424658</v>
       </c>
       <c r="AI35">
         <v>21</v>
@@ -8857,7 +8836,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="36" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:43">
       <c r="A36">
         <v>35</v>
       </c>
@@ -8958,7 +8937,7 @@
         <v>46259</v>
       </c>
       <c r="AH36">
-        <v>13.241095890410961</v>
+        <v>13.24109589041096</v>
       </c>
       <c r="AI36">
         <v>30</v>
@@ -8988,7 +8967,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:43">
       <c r="A37">
         <v>36</v>
       </c>
@@ -9119,7 +9098,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:43">
       <c r="A38">
         <v>37</v>
       </c>
@@ -9250,7 +9229,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="39" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:43">
       <c r="A39">
         <v>38</v>
       </c>
@@ -9351,7 +9330,7 @@
         <v>46259</v>
       </c>
       <c r="AH39">
-        <v>6.7095890410958896</v>
+        <v>6.70958904109589</v>
       </c>
       <c r="AI39">
         <v>30</v>
@@ -9381,7 +9360,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:43">
       <c r="A40">
         <v>39</v>
       </c>
@@ -9482,7 +9461,7 @@
         <v>46259</v>
       </c>
       <c r="AH40">
-        <v>6.5095890410958903</v>
+        <v>6.50958904109589</v>
       </c>
       <c r="AI40">
         <v>30</v>
@@ -9512,7 +9491,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:43">
       <c r="A41">
         <v>40</v>
       </c>
@@ -9613,7 +9592,7 @@
         <v>46259</v>
       </c>
       <c r="AH41">
-        <v>6.5506849315068489</v>
+        <v>6.550684931506849</v>
       </c>
       <c r="AI41">
         <v>21</v>
@@ -9643,7 +9622,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:43">
       <c r="A42">
         <v>41</v>
       </c>
@@ -9774,7 +9753,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:43">
       <c r="A43">
         <v>42</v>
       </c>
@@ -9875,7 +9854,7 @@
         <v>46259</v>
       </c>
       <c r="AH43">
-        <v>8.7534246575342465</v>
+        <v>8.753424657534246</v>
       </c>
       <c r="AI43">
         <v>30</v>
@@ -9905,7 +9884,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:43">
       <c r="A44">
         <v>43</v>
       </c>
@@ -10006,7 +9985,7 @@
         <v>46259</v>
       </c>
       <c r="AH44">
-        <v>5.7534246575342456</v>
+        <v>5.753424657534246</v>
       </c>
       <c r="AI44">
         <v>21</v>
@@ -10036,7 +10015,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:43">
       <c r="A45">
         <v>44</v>
       </c>
@@ -10137,7 +10116,7 @@
         <v>46259</v>
       </c>
       <c r="AH45">
-        <v>5.7342465753424658</v>
+        <v>5.734246575342466</v>
       </c>
       <c r="AI45">
         <v>21</v>
@@ -10167,7 +10146,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:43">
       <c r="A46">
         <v>45</v>
       </c>
@@ -10268,7 +10247,7 @@
         <v>46259</v>
       </c>
       <c r="AH46">
-        <v>5.6273972602739724</v>
+        <v>5.627397260273972</v>
       </c>
       <c r="AI46">
         <v>30</v>
@@ -10298,7 +10277,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:43">
       <c r="A47">
         <v>46</v>
       </c>
@@ -10399,7 +10378,7 @@
         <v>46259</v>
       </c>
       <c r="AH47">
-        <v>4.2273972602739729</v>
+        <v>4.227397260273973</v>
       </c>
       <c r="AI47">
         <v>21</v>
@@ -10429,7 +10408,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:43">
       <c r="A48">
         <v>47</v>
       </c>
@@ -10560,7 +10539,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="49" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:43">
       <c r="A49">
         <v>48</v>
       </c>
@@ -10661,7 +10640,7 @@
         <v>46259</v>
       </c>
       <c r="AH49">
-        <v>4.1589041095890407</v>
+        <v>4.158904109589041</v>
       </c>
       <c r="AI49">
         <v>21</v>
@@ -10691,7 +10670,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="50" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:43">
       <c r="A50">
         <v>49</v>
       </c>
@@ -10792,7 +10771,7 @@
         <v>46259</v>
       </c>
       <c r="AH50">
-        <v>3.9863013698630141</v>
+        <v>3.986301369863014</v>
       </c>
       <c r="AI50">
         <v>21</v>
@@ -10822,7 +10801,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="51" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:43">
       <c r="A51">
         <v>50</v>
       </c>
@@ -10923,7 +10902,7 @@
         <v>46259</v>
       </c>
       <c r="AH51">
-        <v>3.9643835616438361</v>
+        <v>3.964383561643836</v>
       </c>
       <c r="AI51">
         <v>21</v>
@@ -10953,7 +10932,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="52" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:43">
       <c r="A52">
         <v>51</v>
       </c>
@@ -11054,7 +11033,7 @@
         <v>46259</v>
       </c>
       <c r="AH52">
-        <v>3.9643835616438361</v>
+        <v>3.964383561643836</v>
       </c>
       <c r="AI52">
         <v>21</v>
@@ -11084,7 +11063,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="53" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:43">
       <c r="A53">
         <v>52</v>
       </c>
@@ -11215,7 +11194,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="54" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:43">
       <c r="A54">
         <v>53</v>
       </c>
@@ -11316,7 +11295,7 @@
         <v>46259</v>
       </c>
       <c r="AH54">
-        <v>1.9698630136986299</v>
+        <v>1.96986301369863</v>
       </c>
       <c r="AI54">
         <v>21</v>
@@ -11346,7 +11325,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="55" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:43">
       <c r="A55">
         <v>54</v>
       </c>
@@ -11447,7 +11426,7 @@
         <v>46259</v>
       </c>
       <c r="AH55">
-        <v>0.58356164383561648</v>
+        <v>0.5835616438356165</v>
       </c>
       <c r="AI55">
         <v>21</v>
@@ -11477,7 +11456,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="56" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:43">
       <c r="A56">
         <v>55</v>
       </c>
@@ -11578,7 +11557,7 @@
         <v>46259</v>
       </c>
       <c r="AH56">
-        <v>0.58356164383561648</v>
+        <v>0.5835616438356165</v>
       </c>
       <c r="AI56">
         <v>21</v>
@@ -11608,7 +11587,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="57" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:43">
       <c r="A57">
         <v>56</v>
       </c>
@@ -11709,7 +11688,7 @@
         <v>46259</v>
       </c>
       <c r="AH57">
-        <v>7.1506849315068486</v>
+        <v>7.150684931506849</v>
       </c>
       <c r="AI57">
         <v>30</v>
@@ -11739,7 +11718,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="58" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:43">
       <c r="A58">
         <v>57</v>
       </c>
@@ -11840,7 +11819,7 @@
         <v>46259</v>
       </c>
       <c r="AH58">
-        <v>7.4821917808219176</v>
+        <v>7.482191780821918</v>
       </c>
       <c r="AI58">
         <v>30</v>
@@ -11870,7 +11849,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="59" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:43">
       <c r="A59">
         <v>58</v>
       </c>
@@ -11971,7 +11950,7 @@
         <v>46259</v>
       </c>
       <c r="AH59">
-        <v>6.575342465753424E-2</v>
+        <v>0.06575342465753424</v>
       </c>
       <c r="AI59">
         <v>21</v>
@@ -12001,7 +11980,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="60" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:43">
       <c r="A60">
         <v>59</v>
       </c>
@@ -12102,7 +12081,7 @@
         <v>46259</v>
       </c>
       <c r="AH60">
-        <v>6.575342465753424E-2</v>
+        <v>0.06575342465753424</v>
       </c>
       <c r="AI60">
         <v>21</v>
@@ -12132,7 +12111,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="61" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:43">
       <c r="A61">
         <v>58</v>
       </c>
@@ -12233,7 +12212,7 @@
         <v>46259</v>
       </c>
       <c r="AH61">
-        <v>18.263013698630139</v>
+        <v>18.26301369863014</v>
       </c>
       <c r="AI61">
         <v>30</v>
@@ -12263,7 +12242,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="62" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:43">
       <c r="A62">
         <v>59</v>
       </c>
@@ -12364,7 +12343,7 @@
         <v>46259</v>
       </c>
       <c r="AH62">
-        <v>15.076712328767121</v>
+        <v>15.07671232876712</v>
       </c>
       <c r="AI62">
         <v>30</v>
@@ -12394,7 +12373,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="63" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:43">
       <c r="A63">
         <v>60</v>
       </c>
@@ -12495,7 +12474,7 @@
         <v>46259</v>
       </c>
       <c r="AH63">
-        <v>34.049315068493151</v>
+        <v>34.04931506849315</v>
       </c>
       <c r="AI63">
         <v>30</v>
@@ -12525,7 +12504,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="64" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:43">
       <c r="A64">
         <v>61</v>
       </c>
@@ -12626,7 +12605,7 @@
         <v>46259</v>
       </c>
       <c r="AH64">
-        <v>6.1753424657534248</v>
+        <v>6.175342465753425</v>
       </c>
       <c r="AI64">
         <v>30</v>
@@ -12656,7 +12635,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="65" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:43">
       <c r="A65">
         <v>62</v>
       </c>
@@ -12757,7 +12736,7 @@
         <v>46259</v>
       </c>
       <c r="AH65">
-        <v>1.8739726027397261</v>
+        <v>1.873972602739726</v>
       </c>
       <c r="AI65">
         <v>21</v>
@@ -12787,7 +12766,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="66" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:43">
       <c r="A66">
         <v>63</v>
       </c>
@@ -12888,7 +12867,7 @@
         <v>46259</v>
       </c>
       <c r="AH66">
-        <v>5.7534246575342456</v>
+        <v>5.753424657534246</v>
       </c>
       <c r="AI66">
         <v>21</v>
@@ -12918,7 +12897,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="67" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:43">
       <c r="A67">
         <v>64</v>
       </c>
@@ -13019,7 +12998,7 @@
         <v>46259</v>
       </c>
       <c r="AH67">
-        <v>18.046575342465751</v>
+        <v>18.04657534246575</v>
       </c>
       <c r="AI67">
         <v>30</v>
@@ -13049,7 +13028,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="68" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:43">
       <c r="A68">
         <v>65</v>
       </c>
@@ -13150,7 +13129,7 @@
         <v>46259</v>
       </c>
       <c r="AH68">
-        <v>9.5315068493150683</v>
+        <v>9.531506849315068</v>
       </c>
       <c r="AI68">
         <v>30</v>
@@ -13180,7 +13159,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="69" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:43">
       <c r="A69">
         <v>66</v>
       </c>
@@ -13311,7 +13290,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="70" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:43">
       <c r="A70">
         <v>67</v>
       </c>
@@ -13412,7 +13391,7 @@
         <v>46259</v>
       </c>
       <c r="AH70">
-        <v>10.608219178082191</v>
+        <v>10.60821917808219</v>
       </c>
       <c r="AI70">
         <v>30</v>
@@ -13442,7 +13421,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="71" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:43">
       <c r="A71">
         <v>68</v>
       </c>
@@ -13543,7 +13522,7 @@
         <v>46259</v>
       </c>
       <c r="AH71">
-        <v>0.33424657534246582</v>
+        <v>0.3342465753424658</v>
       </c>
       <c r="AI71">
         <v>21</v>
@@ -13573,7 +13552,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="72" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:43">
       <c r="A72">
         <v>69</v>
       </c>
@@ -13674,7 +13653,7 @@
         <v>46259</v>
       </c>
       <c r="AH72">
-        <v>0.33424657534246582</v>
+        <v>0.3342465753424658</v>
       </c>
       <c r="AI72">
         <v>21</v>
@@ -13704,7 +13683,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="73" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:43">
       <c r="A73">
         <v>70</v>
       </c>
@@ -13805,7 +13784,7 @@
         <v>46259</v>
       </c>
       <c r="AH73">
-        <v>2.9698630136986299</v>
+        <v>2.96986301369863</v>
       </c>
       <c r="AI73">
         <v>21</v>
@@ -13835,7 +13814,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="74" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:43">
       <c r="A74">
         <v>71</v>
       </c>
@@ -13966,7 +13945,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="75" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:43">
       <c r="A75">
         <v>72</v>
       </c>
@@ -14067,7 +14046,7 @@
         <v>46259</v>
       </c>
       <c r="AH75">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="AI75">
         <v>21</v>
@@ -14097,7 +14076,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="76" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:43">
       <c r="A76">
         <v>73</v>
       </c>
@@ -14198,7 +14177,7 @@
         <v>46259</v>
       </c>
       <c r="AH76">
-        <v>4.0684931506849313</v>
+        <v>4.068493150684931</v>
       </c>
       <c r="AI76">
         <v>21</v>
@@ -14228,7 +14207,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="77" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:43">
       <c r="A77">
         <v>74</v>
       </c>
@@ -14359,7 +14338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="78" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:43">
       <c r="A78">
         <v>75</v>
       </c>
@@ -14490,7 +14469,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="79" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:43">
       <c r="A79">
         <v>76</v>
       </c>
@@ -14591,7 +14570,7 @@
         <v>46259</v>
       </c>
       <c r="AH79">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
       <c r="AI79">
         <v>21</v>
@@ -14621,7 +14600,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="80" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:43">
       <c r="A80">
         <v>77</v>
       </c>
@@ -14722,7 +14701,7 @@
         <v>46259</v>
       </c>
       <c r="AH80">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
       <c r="AI80">
         <v>21</v>
@@ -14752,7 +14731,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="81" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:43">
       <c r="A81">
         <v>78</v>
       </c>
@@ -14853,7 +14832,7 @@
         <v>46259</v>
       </c>
       <c r="AH81">
-        <v>1.8191780821917809</v>
+        <v>1.819178082191781</v>
       </c>
       <c r="AI81">
         <v>21</v>
@@ -14883,7 +14862,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="82" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:43">
       <c r="A82">
         <v>79</v>
       </c>
@@ -14984,7 +14963,7 @@
         <v>46259</v>
       </c>
       <c r="AH82">
-        <v>1.6547945205479451</v>
+        <v>1.654794520547945</v>
       </c>
       <c r="AI82">
         <v>21</v>
@@ -15014,7 +14993,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="83" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:43">
       <c r="A83">
         <v>80</v>
       </c>
@@ -15115,7 +15094,7 @@
         <v>46259</v>
       </c>
       <c r="AH83">
-        <v>15.167123287671229</v>
+        <v>15.16712328767123</v>
       </c>
       <c r="AI83">
         <v>30</v>
@@ -15145,7 +15124,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="84" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:43">
       <c r="A84">
         <v>80</v>
       </c>
@@ -15186,7 +15165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:43">
       <c r="A85">
         <v>81</v>
       </c>
@@ -15287,7 +15266,7 @@
         <v>46259</v>
       </c>
       <c r="AH85">
-        <v>8.9753424657534246</v>
+        <v>8.975342465753425</v>
       </c>
       <c r="AI85">
         <v>30</v>
@@ -15317,7 +15296,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="86" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:43">
       <c r="A86">
         <v>82</v>
       </c>
@@ -15418,7 +15397,7 @@
         <v>46259</v>
       </c>
       <c r="AH86">
-        <v>6.7095890410958896</v>
+        <v>6.70958904109589</v>
       </c>
       <c r="AI86">
         <v>30</v>
@@ -15448,7 +15427,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="87" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:43">
       <c r="A87">
         <v>83</v>
       </c>
@@ -15549,7 +15528,7 @@
         <v>46259</v>
       </c>
       <c r="AH87">
-        <v>9.3232876712328761</v>
+        <v>9.323287671232876</v>
       </c>
       <c r="AI87">
         <v>30</v>
@@ -15579,7 +15558,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="88" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:43">
       <c r="A88">
         <v>84</v>
       </c>
@@ -15680,7 +15659,7 @@
         <v>46259</v>
       </c>
       <c r="AH88">
-        <v>14.035616438356159</v>
+        <v>14.03561643835616</v>
       </c>
       <c r="AI88">
         <v>30</v>
@@ -15710,7 +15689,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="89" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:43">
       <c r="A89">
         <v>85</v>
       </c>
@@ -15811,7 +15790,7 @@
         <v>46259</v>
       </c>
       <c r="AH89">
-        <v>1.7726027397260271</v>
+        <v>1.772602739726027</v>
       </c>
       <c r="AI89">
         <v>21</v>
@@ -15841,7 +15820,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="90" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:43">
       <c r="A90">
         <v>86</v>
       </c>
@@ -15942,7 +15921,7 @@
         <v>46259</v>
       </c>
       <c r="AH90">
-        <v>8.4082191780821915</v>
+        <v>8.408219178082192</v>
       </c>
       <c r="AI90">
         <v>30</v>
@@ -15972,7 +15951,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="91" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:43">
       <c r="A91">
         <v>87</v>
       </c>
@@ -16073,7 +16052,7 @@
         <v>46259</v>
       </c>
       <c r="AH91">
-        <v>10.950684931506849</v>
+        <v>10.95068493150685</v>
       </c>
       <c r="AI91">
         <v>30</v>
@@ -16103,7 +16082,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="92" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:43">
       <c r="A92">
         <v>88</v>
       </c>
@@ -16204,7 +16183,7 @@
         <v>46259</v>
       </c>
       <c r="AH92">
-        <v>6.6821917808219178</v>
+        <v>6.682191780821918</v>
       </c>
       <c r="AI92">
         <v>21</v>
@@ -16234,7 +16213,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="93" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:43">
       <c r="A93">
         <v>89</v>
       </c>
@@ -16335,7 +16314,7 @@
         <v>46259</v>
       </c>
       <c r="AH93">
-        <v>5.6273972602739724</v>
+        <v>5.627397260273972</v>
       </c>
       <c r="AI93">
         <v>21</v>
@@ -16365,7 +16344,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="94" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:43">
       <c r="A94">
         <v>90</v>
       </c>
@@ -16466,7 +16445,7 @@
         <v>46259</v>
       </c>
       <c r="AH94">
-        <v>5.3150684931506849</v>
+        <v>5.315068493150685</v>
       </c>
       <c r="AI94">
         <v>30</v>
@@ -16496,7 +16475,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="95" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:43">
       <c r="A95">
         <v>91</v>
       </c>
@@ -16597,7 +16576,7 @@
         <v>46259</v>
       </c>
       <c r="AH95">
-        <v>5.0602739726027401</v>
+        <v>5.06027397260274</v>
       </c>
       <c r="AI95">
         <v>30</v>
@@ -16627,7 +16606,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="96" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:43">
       <c r="A96">
         <v>92</v>
       </c>
@@ -16728,7 +16707,7 @@
         <v>46259</v>
       </c>
       <c r="AH96">
-        <v>5.0602739726027401</v>
+        <v>5.06027397260274</v>
       </c>
       <c r="AI96">
         <v>21</v>
@@ -16758,7 +16737,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="97" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:43">
       <c r="A97">
         <v>93</v>
       </c>
@@ -16859,7 +16838,7 @@
         <v>46259</v>
       </c>
       <c r="AH97">
-        <v>4.7534246575342456</v>
+        <v>4.753424657534246</v>
       </c>
       <c r="AI97">
         <v>21</v>
@@ -16889,7 +16868,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="98" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:43">
       <c r="A98">
         <v>94</v>
       </c>
@@ -16990,7 +16969,7 @@
         <v>46259</v>
       </c>
       <c r="AH98">
-        <v>0.58356164383561648</v>
+        <v>0.5835616438356165</v>
       </c>
       <c r="AI98">
         <v>21</v>
@@ -17020,7 +16999,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="99" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:43">
       <c r="A99">
         <v>95</v>
       </c>
@@ -17121,7 +17100,7 @@
         <v>46259</v>
       </c>
       <c r="AH99">
-        <v>0.58356164383561648</v>
+        <v>0.5835616438356165</v>
       </c>
       <c r="AI99">
         <v>21</v>
@@ -17151,7 +17130,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="100" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:43">
       <c r="A100">
         <v>96</v>
       </c>
@@ -17252,7 +17231,7 @@
         <v>46259</v>
       </c>
       <c r="AH100">
-        <v>4.7397260273972606</v>
+        <v>4.739726027397261</v>
       </c>
       <c r="AI100">
         <v>21</v>
@@ -17282,7 +17261,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="101" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:43">
       <c r="A101">
         <v>97</v>
       </c>
@@ -17383,7 +17362,7 @@
         <v>46259</v>
       </c>
       <c r="AH101">
-        <v>4.6794520547945204</v>
+        <v>4.67945205479452</v>
       </c>
       <c r="AI101">
         <v>21</v>
@@ -17413,7 +17392,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="102" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:43">
       <c r="A102">
         <v>98</v>
       </c>
@@ -17514,7 +17493,7 @@
         <v>46259</v>
       </c>
       <c r="AH102">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="AI102">
         <v>21</v>
@@ -17544,7 +17523,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="103" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:43">
       <c r="A103">
         <v>99</v>
       </c>
@@ -17645,7 +17624,7 @@
         <v>46259</v>
       </c>
       <c r="AH103">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="AI103">
         <v>21</v>
@@ -17675,7 +17654,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="104" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:43">
       <c r="A104">
         <v>100</v>
       </c>
@@ -17776,7 +17755,7 @@
         <v>46259</v>
       </c>
       <c r="AH104">
-        <v>3.9643835616438361</v>
+        <v>3.964383561643836</v>
       </c>
       <c r="AI104">
         <v>21</v>
@@ -17806,7 +17785,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="105" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:43">
       <c r="A105">
         <v>101</v>
       </c>
@@ -17907,7 +17886,7 @@
         <v>46259</v>
       </c>
       <c r="AH105">
-        <v>7.5232876712328771</v>
+        <v>7.523287671232877</v>
       </c>
       <c r="AI105">
         <v>30</v>
@@ -17937,7 +17916,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="106" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:43">
       <c r="A106">
         <v>102</v>
       </c>
@@ -18038,7 +18017,7 @@
         <v>46259</v>
       </c>
       <c r="AH106">
-        <v>4.9726027397260273</v>
+        <v>4.972602739726027</v>
       </c>
       <c r="AI106">
         <v>21</v>
@@ -18068,7 +18047,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="107" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:43">
       <c r="A107">
         <v>103</v>
       </c>
@@ -18169,7 +18148,7 @@
         <v>46259</v>
       </c>
       <c r="AH107">
-        <v>1.9698630136986299</v>
+        <v>1.96986301369863</v>
       </c>
       <c r="AI107">
         <v>21</v>
@@ -18199,7 +18178,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="108" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:43">
       <c r="A108">
         <v>104</v>
       </c>
@@ -18300,7 +18279,7 @@
         <v>46259</v>
       </c>
       <c r="AH108">
-        <v>22.446575342465749</v>
+        <v>22.44657534246575</v>
       </c>
       <c r="AI108">
         <v>30</v>
@@ -18330,7 +18309,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="109" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:43">
       <c r="A109">
         <v>105</v>
       </c>
@@ -18431,7 +18410,7 @@
         <v>46259</v>
       </c>
       <c r="AH109">
-        <v>3.9863013698630141</v>
+        <v>3.986301369863014</v>
       </c>
       <c r="AI109">
         <v>21</v>
@@ -18461,7 +18440,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="110" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:43">
       <c r="A110">
         <v>106</v>
       </c>
@@ -18514,7 +18493,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="111" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:43">
       <c r="A111">
         <v>107</v>
       </c>
@@ -18615,7 +18594,7 @@
         <v>46259</v>
       </c>
       <c r="AH111">
-        <v>0.35890410958904112</v>
+        <v>0.3589041095890411</v>
       </c>
       <c r="AI111">
         <v>21</v>
@@ -18645,7 +18624,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="112" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:43">
       <c r="A112">
         <v>108</v>
       </c>
@@ -18746,7 +18725,7 @@
         <v>46259</v>
       </c>
       <c r="AH112">
-        <v>5.3726027397260276</v>
+        <v>5.372602739726028</v>
       </c>
       <c r="AI112">
         <v>21</v>
@@ -18776,7 +18755,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="113" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:43">
       <c r="A113">
         <v>109</v>
       </c>
@@ -18877,7 +18856,7 @@
         <v>46259</v>
       </c>
       <c r="AH113">
-        <v>4.5287671232876709</v>
+        <v>4.528767123287671</v>
       </c>
       <c r="AI113">
         <v>21</v>
@@ -18907,7 +18886,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="114" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:43">
       <c r="A114">
         <v>110</v>
       </c>
@@ -19008,7 +18987,7 @@
         <v>46259</v>
       </c>
       <c r="AH114">
-        <v>4.5835616438356164</v>
+        <v>4.583561643835616</v>
       </c>
       <c r="AI114">
         <v>21</v>
@@ -19038,7 +19017,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="115" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:43">
       <c r="A115">
         <v>111</v>
       </c>
@@ -19139,7 +19118,7 @@
         <v>46259</v>
       </c>
       <c r="AH115">
-        <v>4.5260273972602736</v>
+        <v>4.526027397260274</v>
       </c>
       <c r="AI115">
         <v>21</v>
@@ -19169,7 +19148,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="116" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:43">
       <c r="A116">
         <v>112</v>
       </c>
@@ -19270,7 +19249,7 @@
         <v>46259</v>
       </c>
       <c r="AH116">
-        <v>4.5287671232876709</v>
+        <v>4.528767123287671</v>
       </c>
       <c r="AI116">
         <v>21</v>
@@ -19300,7 +19279,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="117" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:43">
       <c r="B117">
         <v>1336</v>
       </c>
@@ -19428,7 +19407,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="118" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:43">
       <c r="A118">
         <v>113</v>
       </c>
@@ -19559,7 +19538,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="119" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:43">
       <c r="A119">
         <v>114</v>
       </c>
@@ -19660,7 +19639,7 @@
         <v>46259</v>
       </c>
       <c r="AH119">
-        <v>2.6301369863013702</v>
+        <v>2.63013698630137</v>
       </c>
       <c r="AI119">
         <v>21</v>
@@ -19690,7 +19669,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="120" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:43">
       <c r="A120">
         <v>115</v>
       </c>
@@ -19791,7 +19770,7 @@
         <v>46259</v>
       </c>
       <c r="AH120">
-        <v>2.4109589041095889</v>
+        <v>2.410958904109589</v>
       </c>
       <c r="AI120">
         <v>21</v>
@@ -19821,7 +19800,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="121" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:43">
       <c r="A121">
         <v>116</v>
       </c>
@@ -19952,7 +19931,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="122" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:43">
       <c r="A122">
         <v>117</v>
       </c>
@@ -20083,7 +20062,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="123" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:43">
       <c r="A123">
         <v>118</v>
       </c>
@@ -20214,7 +20193,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="124" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:43">
       <c r="A124">
         <v>119</v>
       </c>
@@ -20315,7 +20294,7 @@
         <v>46259</v>
       </c>
       <c r="AH124">
-        <v>2.2630136986301368</v>
+        <v>2.263013698630137</v>
       </c>
       <c r="AI124">
         <v>21</v>
@@ -20345,7 +20324,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="125" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:43">
       <c r="A125">
         <v>120</v>
       </c>
@@ -20446,7 +20425,7 @@
         <v>46259</v>
       </c>
       <c r="AH125">
-        <v>6.5863013698630137</v>
+        <v>6.586301369863014</v>
       </c>
       <c r="AI125">
         <v>30</v>
@@ -20476,7 +20455,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="126" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:43">
       <c r="A126">
         <v>120</v>
       </c>
@@ -20499,7 +20478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:43">
       <c r="A127">
         <v>121</v>
       </c>
@@ -20600,7 +20579,7 @@
         <v>46259</v>
       </c>
       <c r="AH127">
-        <v>12.265753424657531</v>
+        <v>12.26575342465753</v>
       </c>
       <c r="AI127">
         <v>30</v>
@@ -20630,7 +20609,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="128" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:43">
       <c r="A128">
         <v>122</v>
       </c>
@@ -20731,7 +20710,7 @@
         <v>46259</v>
       </c>
       <c r="AH128">
-        <v>5.9643835616438352</v>
+        <v>5.964383561643835</v>
       </c>
       <c r="AI128">
         <v>30</v>
@@ -20761,7 +20740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:43">
       <c r="A129">
         <v>123</v>
       </c>
@@ -20862,7 +20841,7 @@
         <v>46259</v>
       </c>
       <c r="AH129">
-        <v>5.7972602739726016</v>
+        <v>5.797260273972602</v>
       </c>
       <c r="AI129">
         <v>21</v>
@@ -20892,7 +20871,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="130" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:43">
       <c r="A130">
         <v>124</v>
       </c>
@@ -20993,7 +20972,7 @@
         <v>46259</v>
       </c>
       <c r="AH130">
-        <v>5.1534246575342468</v>
+        <v>5.153424657534247</v>
       </c>
       <c r="AI130">
         <v>30</v>
@@ -21023,7 +21002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:43">
       <c r="A131">
         <v>125</v>
       </c>
@@ -21124,7 +21103,7 @@
         <v>46259</v>
       </c>
       <c r="AH131">
-        <v>5.1780821917808222</v>
+        <v>5.178082191780822</v>
       </c>
       <c r="AI131">
         <v>30</v>
@@ -21154,7 +21133,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="132" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:43">
       <c r="B132">
         <v>1135</v>
       </c>
@@ -21252,7 +21231,7 @@
         <v>46259</v>
       </c>
       <c r="AH132">
-        <v>0.15068493150684931</v>
+        <v>0.1506849315068493</v>
       </c>
       <c r="AI132">
         <v>21</v>
@@ -21282,7 +21261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:43">
       <c r="A133">
         <v>126</v>
       </c>
@@ -21383,7 +21362,7 @@
         <v>46259</v>
       </c>
       <c r="AH133">
-        <v>4.2356164383561641</v>
+        <v>4.235616438356164</v>
       </c>
       <c r="AI133">
         <v>21</v>
@@ -21413,7 +21392,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="134" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:43">
       <c r="A134">
         <v>127</v>
       </c>
@@ -21514,7 +21493,7 @@
         <v>46259</v>
       </c>
       <c r="AH134">
-        <v>4.2356164383561641</v>
+        <v>4.235616438356164</v>
       </c>
       <c r="AI134">
         <v>21</v>
@@ -21544,7 +21523,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="135" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:43">
       <c r="A135">
         <v>128</v>
       </c>
@@ -21645,7 +21624,7 @@
         <v>46259</v>
       </c>
       <c r="AH135">
-        <v>4.7232876712328764</v>
+        <v>4.723287671232876</v>
       </c>
       <c r="AI135">
         <v>21</v>
@@ -21675,7 +21654,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="136" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:43">
       <c r="A136">
         <v>129</v>
       </c>
@@ -21776,7 +21755,7 @@
         <v>46259</v>
       </c>
       <c r="AH136">
-        <v>4.2904109589041104</v>
+        <v>4.29041095890411</v>
       </c>
       <c r="AI136">
         <v>21</v>
@@ -21806,7 +21785,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="137" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:43">
       <c r="A137">
         <v>130</v>
       </c>
@@ -21907,7 +21886,7 @@
         <v>46259</v>
       </c>
       <c r="AH137">
-        <v>4.5534246575342463</v>
+        <v>4.553424657534246</v>
       </c>
       <c r="AI137">
         <v>21</v>
@@ -21937,7 +21916,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="138" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:43">
       <c r="A138">
         <v>131</v>
       </c>
@@ -22038,7 +22017,7 @@
         <v>46259</v>
       </c>
       <c r="AH138">
-        <v>1.4986301369863011</v>
+        <v>1.498630136986301</v>
       </c>
       <c r="AI138">
         <v>21</v>
@@ -22068,7 +22047,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="139" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:43">
       <c r="A139">
         <v>132</v>
       </c>
@@ -22199,7 +22178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:43">
       <c r="A140">
         <v>133</v>
       </c>
@@ -22330,7 +22309,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="141" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:43">
       <c r="A141">
         <v>134</v>
       </c>
@@ -22461,7 +22440,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="142" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:43">
       <c r="A142">
         <v>135</v>
       </c>
@@ -22592,7 +22571,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="143" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:43">
       <c r="A143">
         <v>136</v>
       </c>
@@ -22693,7 +22672,7 @@
         <v>46259</v>
       </c>
       <c r="AH143">
-        <v>4.4876712328767123</v>
+        <v>4.487671232876712</v>
       </c>
       <c r="AI143">
         <v>21</v>
@@ -22723,7 +22702,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="144" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:43">
       <c r="A144">
         <v>137</v>
       </c>
@@ -22824,7 +22803,7 @@
         <v>46259</v>
       </c>
       <c r="AH144">
-        <v>4.4684931506849317</v>
+        <v>4.468493150684932</v>
       </c>
       <c r="AI144">
         <v>21</v>
@@ -22854,7 +22833,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="145" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:43">
       <c r="A145">
         <v>138</v>
       </c>
@@ -22955,7 +22934,7 @@
         <v>46259</v>
       </c>
       <c r="AH145">
-        <v>1.8575342465753419</v>
+        <v>1.857534246575342</v>
       </c>
       <c r="AI145">
         <v>21</v>
@@ -22985,7 +22964,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="146" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:43">
       <c r="A146">
         <v>139</v>
       </c>
@@ -23086,7 +23065,7 @@
         <v>46259</v>
       </c>
       <c r="AH146">
-        <v>4.3890410958904109</v>
+        <v>4.389041095890411</v>
       </c>
       <c r="AI146">
         <v>21</v>
@@ -23116,7 +23095,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="147" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:43">
       <c r="A147">
         <v>140</v>
       </c>
@@ -23217,7 +23196,7 @@
         <v>46259</v>
       </c>
       <c r="AH147">
-        <v>3.7917808219178082</v>
+        <v>3.791780821917808</v>
       </c>
       <c r="AI147">
         <v>21</v>
@@ -23247,7 +23226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:43">
       <c r="A148">
         <v>141</v>
       </c>
@@ -23348,7 +23327,7 @@
         <v>46259</v>
       </c>
       <c r="AH148">
-        <v>3.7863013698630139</v>
+        <v>3.786301369863014</v>
       </c>
       <c r="AI148">
         <v>21</v>
@@ -23378,7 +23357,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="149" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:43">
       <c r="A149">
         <v>142</v>
       </c>
@@ -23479,7 +23458,7 @@
         <v>46259</v>
       </c>
       <c r="AH149">
-        <v>3.7369863013698632</v>
+        <v>3.736986301369863</v>
       </c>
       <c r="AI149">
         <v>21</v>
@@ -23509,7 +23488,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="150" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:43">
       <c r="A150">
         <v>143</v>
       </c>
@@ -23610,7 +23589,7 @@
         <v>46259</v>
       </c>
       <c r="AH150">
-        <v>2.5452054794520551</v>
+        <v>2.545205479452055</v>
       </c>
       <c r="AI150">
         <v>21</v>
@@ -23640,7 +23619,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="151" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:43">
       <c r="A151">
         <v>144</v>
       </c>
@@ -23741,7 +23720,7 @@
         <v>46259</v>
       </c>
       <c r="AH151">
-        <v>5.9671232876712326</v>
+        <v>5.967123287671233</v>
       </c>
       <c r="AI151">
         <v>21</v>
@@ -23771,7 +23750,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="152" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:43">
       <c r="A152">
         <v>145</v>
       </c>
@@ -23872,7 +23851,7 @@
         <v>46259</v>
       </c>
       <c r="AH152">
-        <v>3.1013698630136992</v>
+        <v>3.101369863013699</v>
       </c>
       <c r="AI152">
         <v>21</v>
@@ -23902,7 +23881,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="153" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:43">
       <c r="A153">
         <v>146</v>
       </c>
@@ -24003,7 +23982,7 @@
         <v>46259</v>
       </c>
       <c r="AH153">
-        <v>5.6493150684931503</v>
+        <v>5.64931506849315</v>
       </c>
       <c r="AI153">
         <v>21</v>
@@ -24033,7 +24012,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="154" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:43">
       <c r="A154">
         <v>147</v>
       </c>
@@ -24134,7 +24113,7 @@
         <v>46259</v>
       </c>
       <c r="AH154">
-        <v>5.4027397260273968</v>
+        <v>5.402739726027397</v>
       </c>
       <c r="AI154">
         <v>21</v>
@@ -24164,7 +24143,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="155" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:43">
       <c r="A155">
         <v>148</v>
       </c>
@@ -24265,7 +24244,7 @@
         <v>46259</v>
       </c>
       <c r="AH155">
-        <v>5.3095890410958901</v>
+        <v>5.30958904109589</v>
       </c>
       <c r="AI155">
         <v>21</v>
@@ -24295,7 +24274,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="156" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:43">
       <c r="A156">
         <v>149</v>
       </c>
@@ -24396,7 +24375,7 @@
         <v>46259</v>
       </c>
       <c r="AH156">
-        <v>5.0383561643835613</v>
+        <v>5.038356164383561</v>
       </c>
       <c r="AI156">
         <v>21</v>
@@ -24426,7 +24405,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="157" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:43">
       <c r="A157">
         <v>150</v>
       </c>
@@ -24527,7 +24506,7 @@
         <v>46259</v>
       </c>
       <c r="AH157">
-        <v>5.0383561643835613</v>
+        <v>5.038356164383561</v>
       </c>
       <c r="AI157">
         <v>21</v>
@@ -24557,7 +24536,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="158" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:43">
       <c r="A158">
         <v>151</v>
       </c>
@@ -24658,7 +24637,7 @@
         <v>46259</v>
       </c>
       <c r="AH158">
-        <v>5.0383561643835613</v>
+        <v>5.038356164383561</v>
       </c>
       <c r="AI158">
         <v>21</v>
@@ -24688,7 +24667,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="159" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:43">
       <c r="A159">
         <v>152</v>
       </c>
@@ -24789,7 +24768,7 @@
         <v>46259</v>
       </c>
       <c r="AH159">
-        <v>5.0383561643835613</v>
+        <v>5.038356164383561</v>
       </c>
       <c r="AI159">
         <v>21</v>
@@ -24819,7 +24798,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="160" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:43">
       <c r="A160">
         <v>153</v>
       </c>
@@ -24920,7 +24899,7 @@
         <v>46259</v>
       </c>
       <c r="AH160">
-        <v>1.8301369863013699</v>
+        <v>1.83013698630137</v>
       </c>
       <c r="AI160">
         <v>21</v>
@@ -24950,7 +24929,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="161" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:43">
       <c r="A161">
         <v>154</v>
       </c>
@@ -25051,7 +25030,7 @@
         <v>46259</v>
       </c>
       <c r="AH161">
-        <v>4.5287671232876709</v>
+        <v>4.528767123287671</v>
       </c>
       <c r="AI161">
         <v>21</v>
@@ -25081,7 +25060,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="162" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:43">
       <c r="A162">
         <v>155</v>
       </c>
@@ -25182,7 +25161,7 @@
         <v>46259</v>
       </c>
       <c r="AH162">
-        <v>4.3890410958904109</v>
+        <v>4.389041095890411</v>
       </c>
       <c r="AI162">
         <v>21</v>
@@ -25212,7 +25191,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="163" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:43">
       <c r="A163">
         <v>156</v>
       </c>
@@ -25313,7 +25292,7 @@
         <v>46259</v>
       </c>
       <c r="AH163">
-        <v>4.3890410958904109</v>
+        <v>4.389041095890411</v>
       </c>
       <c r="AI163">
         <v>21</v>
@@ -25343,7 +25322,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="164" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:43">
       <c r="A164">
         <v>157</v>
       </c>
@@ -25474,7 +25453,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="165" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:43">
       <c r="A165">
         <v>158</v>
       </c>
@@ -25575,7 +25554,7 @@
         <v>46259</v>
       </c>
       <c r="AH165">
-        <v>3.9945205479452048</v>
+        <v>3.994520547945205</v>
       </c>
       <c r="AI165">
         <v>21</v>
@@ -25605,7 +25584,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="166" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:43">
       <c r="A166">
         <v>159</v>
       </c>
@@ -25706,7 +25685,7 @@
         <v>46259</v>
       </c>
       <c r="AH166">
-        <v>3.9643835616438361</v>
+        <v>3.964383561643836</v>
       </c>
       <c r="AI166">
         <v>21</v>
@@ -25736,7 +25715,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="167" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:43">
       <c r="A167">
         <v>161</v>
       </c>
@@ -25837,7 +25816,7 @@
         <v>46259</v>
       </c>
       <c r="AH167">
-        <v>2.3397260273972602</v>
+        <v>2.33972602739726</v>
       </c>
       <c r="AI167">
         <v>21</v>
@@ -25867,7 +25846,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="168" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:43">
       <c r="A168">
         <v>162</v>
       </c>
@@ -25968,7 +25947,7 @@
         <v>46259</v>
       </c>
       <c r="AH168">
-        <v>13.547945205479451</v>
+        <v>13.54794520547945</v>
       </c>
       <c r="AI168">
         <v>30</v>
@@ -25998,7 +25977,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="169" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:43">
       <c r="A169">
         <v>163</v>
       </c>
@@ -26099,7 +26078,7 @@
         <v>46259</v>
       </c>
       <c r="AH169">
-        <v>5.1534246575342468</v>
+        <v>5.153424657534247</v>
       </c>
       <c r="AI169">
         <v>30</v>
@@ -26129,7 +26108,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="170" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:43">
       <c r="A170">
         <v>164</v>
       </c>
@@ -26230,7 +26209,7 @@
         <v>46259</v>
       </c>
       <c r="AH170">
-        <v>5.3452054794520549</v>
+        <v>5.345205479452055</v>
       </c>
       <c r="AI170">
         <v>30</v>
@@ -26260,7 +26239,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="171" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:43">
       <c r="A171">
         <v>165</v>
       </c>
@@ -26391,7 +26370,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="172" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:43">
       <c r="A172">
         <v>166</v>
       </c>
@@ -26492,7 +26471,7 @@
         <v>46259</v>
       </c>
       <c r="AH172">
-        <v>2.8438356164383558</v>
+        <v>2.843835616438356</v>
       </c>
       <c r="AI172">
         <v>21</v>
@@ -26522,7 +26501,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="173" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:43">
       <c r="A173">
         <v>167</v>
       </c>
@@ -26653,7 +26632,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="174" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:43">
       <c r="A174">
         <v>168</v>
       </c>
@@ -26754,7 +26733,7 @@
         <v>46259</v>
       </c>
       <c r="AH174">
-        <v>1.9698630136986299</v>
+        <v>1.96986301369863</v>
       </c>
       <c r="AI174">
         <v>21</v>
@@ -26784,7 +26763,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="175" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:43">
       <c r="A175">
         <v>169</v>
       </c>
@@ -26891,13 +26870,13 @@
         <v>21</v>
       </c>
       <c r="AJ175">
-        <v>975</v>
+        <v>963</v>
       </c>
       <c r="AK175">
-        <v>375</v>
+        <v>241</v>
       </c>
       <c r="AL175">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="AM175">
         <v>0</v>
@@ -26915,7 +26894,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="176" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:43">
       <c r="A176">
         <v>170</v>
       </c>
@@ -27016,7 +26995,7 @@
         <v>46259</v>
       </c>
       <c r="AH176">
-        <v>5.8767123287671232</v>
+        <v>5.876712328767123</v>
       </c>
       <c r="AI176">
         <v>30</v>
@@ -27046,7 +27025,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="177" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:43">
       <c r="A177">
         <v>171</v>
       </c>
@@ -27177,7 +27156,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="178" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:43">
       <c r="A178">
         <v>172</v>
       </c>
@@ -27278,7 +27257,7 @@
         <v>46259</v>
       </c>
       <c r="AH178">
-        <v>2.9616438356164378</v>
+        <v>2.961643835616438</v>
       </c>
       <c r="AI178">
         <v>21</v>
@@ -27308,7 +27287,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="179" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:43">
       <c r="A179">
         <v>173</v>
       </c>
@@ -27409,7 +27388,7 @@
         <v>46259</v>
       </c>
       <c r="AH179">
-        <v>2.4684931506849321</v>
+        <v>2.468493150684932</v>
       </c>
       <c r="AI179">
         <v>21</v>
@@ -27439,7 +27418,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="180" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:43">
       <c r="A180">
         <v>174</v>
       </c>
@@ -27540,7 +27519,7 @@
         <v>46259</v>
       </c>
       <c r="AH180">
-        <v>2.2520547945205478</v>
+        <v>2.252054794520548</v>
       </c>
       <c r="AI180">
         <v>21</v>
@@ -27570,7 +27549,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="181" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:43">
       <c r="A181">
         <v>175</v>
       </c>
@@ -27701,7 +27680,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="182" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:43">
       <c r="A182">
         <v>176</v>
       </c>
@@ -27832,7 +27811,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="183" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:43">
       <c r="A183">
         <v>177</v>
       </c>
@@ -27963,7 +27942,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="184" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:43">
       <c r="A184">
         <v>178</v>
       </c>
@@ -28094,7 +28073,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="185" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:43">
       <c r="A185">
         <v>179</v>
       </c>
@@ -28225,7 +28204,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="186" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:43">
       <c r="A186">
         <v>180</v>
       </c>
@@ -28326,7 +28305,7 @@
         <v>46259</v>
       </c>
       <c r="AH186">
-        <v>1.7452054794520551</v>
+        <v>1.745205479452055</v>
       </c>
       <c r="AI186">
         <v>21</v>
@@ -28356,7 +28335,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="187" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:43">
       <c r="A187">
         <v>181</v>
       </c>
@@ -28457,7 +28436,7 @@
         <v>46259</v>
       </c>
       <c r="AH187">
-        <v>1.3890410958904109</v>
+        <v>1.389041095890411</v>
       </c>
       <c r="AI187">
         <v>21</v>
@@ -28489,7 +28468,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="S170" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="S170" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Staffdata.xlsx
+++ b/Staffdata.xlsx
@@ -1,15 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3113719057d24bf/Desktop/HR-Forms-Site/HRFORMAS/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_05E48499FC67680F1964AE368160343238AA41AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF2605B4-16ED-446A-80C3-78523540B582}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2174,7 +2185,7 @@
     <t>-</t>
   </si>
   <si>
-    <t xml:space="preserve"> 966577040481</t>
+    <t> 966577040481</t>
   </si>
   <si>
     <t>malbatil@outlook.sa</t>
@@ -2485,10 +2496,10 @@
     <t>HAMDILLHJ038@GMAIL.COM</t>
   </si>
   <si>
-    <t xml:space="preserve"> omarzar392@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ark870725@gmail.com</t>
+    <t> omarzar392@gmail.com</t>
+  </si>
+  <si>
+    <t> ark870725@gmail.com</t>
   </si>
   <si>
     <t>waelgomaa1wg@gmail.com</t>
@@ -2561,7 +2572,7 @@
     <t>INFO2@HAIL-HOUSE.SA</t>
   </si>
   <si>
-    <t xml:space="preserve"> Sarah_elkhatib@outlook.com</t>
+    <t> Sarah_elkhatib@outlook.com</t>
   </si>
   <si>
     <t xml:space="preserve"> mohannad.fakhry00@gmail.com</t>
@@ -3905,11 +3916,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3955,18 +3966,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ارتباط تشعبي" xfId="1" builtinId="8"/>
+    <cellStyle name="عادي" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4004,7 +4023,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4038,6 +4057,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4072,9 +4092,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4247,11 +4268,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AQ187"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:43">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4382,7 +4403,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:43">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4483,7 +4504,7 @@
         <v>46259</v>
       </c>
       <c r="AH2">
-        <v>8.726027397260275</v>
+        <v>8.7260273972602747</v>
       </c>
       <c r="AI2">
         <v>30</v>
@@ -4513,7 +4534,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="3" spans="1:43">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4614,7 +4635,7 @@
         <v>46259</v>
       </c>
       <c r="AH3">
-        <v>13.63561643835616</v>
+        <v>13.635616438356161</v>
       </c>
       <c r="AI3">
         <v>30</v>
@@ -4644,7 +4665,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="4" spans="1:43">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4745,7 +4766,7 @@
         <v>46259</v>
       </c>
       <c r="AH4">
-        <v>5.890410958904109</v>
+        <v>5.8904109589041092</v>
       </c>
       <c r="AI4">
         <v>30</v>
@@ -4775,7 +4796,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="5" spans="1:43">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4876,7 +4897,7 @@
         <v>46259</v>
       </c>
       <c r="AH5">
-        <v>6.046575342465753</v>
+        <v>6.0465753424657533</v>
       </c>
       <c r="AI5">
         <v>21</v>
@@ -4906,7 +4927,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="6" spans="1:43">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5007,7 +5028,7 @@
         <v>46259</v>
       </c>
       <c r="AH6">
-        <v>6.402739726027397</v>
+        <v>6.4027397260273968</v>
       </c>
       <c r="AI6">
         <v>21</v>
@@ -5037,7 +5058,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="7" spans="1:43">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5138,7 +5159,7 @@
         <v>46259</v>
       </c>
       <c r="AH7">
-        <v>5.704109589041096</v>
+        <v>5.7041095890410958</v>
       </c>
       <c r="AI7">
         <v>30</v>
@@ -5168,7 +5189,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="8" spans="1:43">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5299,7 +5320,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="9" spans="1:43">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5430,7 +5451,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="10" spans="1:43">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5531,7 +5552,7 @@
         <v>46259</v>
       </c>
       <c r="AH10">
-        <v>6.753424657534246</v>
+        <v>6.7534246575342456</v>
       </c>
       <c r="AI10">
         <v>30</v>
@@ -5561,7 +5582,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="11" spans="1:43">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5692,7 +5713,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="12" spans="1:43">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5793,7 +5814,7 @@
         <v>46259</v>
       </c>
       <c r="AH12">
-        <v>5.750684931506849</v>
+        <v>5.7506849315068491</v>
       </c>
       <c r="AI12">
         <v>21</v>
@@ -5823,7 +5844,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="13" spans="1:43">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5954,7 +5975,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="14" spans="1:43">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6055,7 +6076,7 @@
         <v>46259</v>
       </c>
       <c r="AH14">
-        <v>0.3041095890410959</v>
+        <v>0.30410958904109592</v>
       </c>
       <c r="AI14">
         <v>21</v>
@@ -6085,7 +6106,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="15" spans="1:43">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6186,7 +6207,7 @@
         <v>46259</v>
       </c>
       <c r="AH15">
-        <v>3.983561643835616</v>
+        <v>3.9835616438356158</v>
       </c>
       <c r="AI15">
         <v>21</v>
@@ -6216,7 +6237,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="16" spans="1:43">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6317,7 +6338,7 @@
         <v>46259</v>
       </c>
       <c r="AH16">
-        <v>2.898630136986301</v>
+        <v>2.8986301369863008</v>
       </c>
       <c r="AI16">
         <v>21</v>
@@ -6347,7 +6368,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="17" spans="1:43">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -6448,7 +6469,7 @@
         <v>46259</v>
       </c>
       <c r="AH17">
-        <v>1.673972602739726</v>
+        <v>1.6739726027397259</v>
       </c>
       <c r="AI17">
         <v>21</v>
@@ -6478,7 +6499,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="18" spans="1:43">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6579,7 +6600,7 @@
         <v>46259</v>
       </c>
       <c r="AH18">
-        <v>2.049315068493151</v>
+        <v>2.0493150684931511</v>
       </c>
       <c r="AI18">
         <v>21</v>
@@ -6609,7 +6630,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="19" spans="1:43">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -6710,7 +6731,7 @@
         <v>46259</v>
       </c>
       <c r="AH19">
-        <v>2.035616438356164</v>
+        <v>2.0356164383561639</v>
       </c>
       <c r="AI19">
         <v>21</v>
@@ -6740,7 +6761,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="20" spans="1:43">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -6841,7 +6862,7 @@
         <v>46259</v>
       </c>
       <c r="AH20">
-        <v>1.512328767123288</v>
+        <v>1.5123287671232879</v>
       </c>
       <c r="AI20">
         <v>21</v>
@@ -6871,7 +6892,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="21" spans="1:43">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -6972,7 +6993,7 @@
         <v>46259</v>
       </c>
       <c r="AH21">
-        <v>2.035616438356164</v>
+        <v>2.0356164383561639</v>
       </c>
       <c r="AI21">
         <v>21</v>
@@ -7002,7 +7023,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="22" spans="1:43">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -7133,7 +7154,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="23" spans="1:43">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -7264,7 +7285,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="24" spans="1:43">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -7395,7 +7416,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="25" spans="1:43">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -7496,7 +7517,7 @@
         <v>46259</v>
       </c>
       <c r="AH25">
-        <v>0.7616438356164383</v>
+        <v>0.76164383561643834</v>
       </c>
       <c r="AI25">
         <v>21</v>
@@ -7526,7 +7547,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="26" spans="1:43">
+    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -7627,7 +7648,7 @@
         <v>46259</v>
       </c>
       <c r="AH26">
-        <v>0.7616438356164383</v>
+        <v>0.76164383561643834</v>
       </c>
       <c r="AI26">
         <v>21</v>
@@ -7657,7 +7678,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="27" spans="1:43">
+    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -7758,7 +7779,7 @@
         <v>46259</v>
       </c>
       <c r="AH27">
-        <v>6.736986301369863</v>
+        <v>6.7369863013698632</v>
       </c>
       <c r="AI27">
         <v>30</v>
@@ -7788,7 +7809,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="28" spans="1:43">
+    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -7889,7 +7910,7 @@
         <v>46259</v>
       </c>
       <c r="AH28">
-        <v>12.11232876712329</v>
+        <v>12.112328767123291</v>
       </c>
       <c r="AI28">
         <v>30</v>
@@ -7919,7 +7940,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="29" spans="1:43">
+    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -8020,7 +8041,7 @@
         <v>46259</v>
       </c>
       <c r="AH29">
-        <v>3.487671232876712</v>
+        <v>3.4876712328767119</v>
       </c>
       <c r="AI29">
         <v>21</v>
@@ -8050,7 +8071,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="30" spans="1:43">
+    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -8151,7 +8172,7 @@
         <v>46259</v>
       </c>
       <c r="AH30">
-        <v>15.07671232876712</v>
+        <v>15.076712328767121</v>
       </c>
       <c r="AI30">
         <v>30</v>
@@ -8181,7 +8202,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="31" spans="1:43">
+    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -8282,7 +8303,7 @@
         <v>46259</v>
       </c>
       <c r="AH31">
-        <v>15.07671232876712</v>
+        <v>15.076712328767121</v>
       </c>
       <c r="AI31">
         <v>30</v>
@@ -8312,7 +8333,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="32" spans="1:43">
+    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -8443,7 +8464,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="33" spans="1:43">
+    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -8544,7 +8565,7 @@
         <v>46259</v>
       </c>
       <c r="AH33">
-        <v>15.16712328767123</v>
+        <v>15.167123287671229</v>
       </c>
       <c r="AI33">
         <v>30</v>
@@ -8574,7 +8595,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="34" spans="1:43">
+    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -8675,7 +8696,7 @@
         <v>46259</v>
       </c>
       <c r="AH34">
-        <v>4.610958904109589</v>
+        <v>4.6109589041095891</v>
       </c>
       <c r="AI34">
         <v>21</v>
@@ -8705,7 +8726,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="35" spans="1:43">
+    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -8806,7 +8827,7 @@
         <v>46259</v>
       </c>
       <c r="AH35">
-        <v>4.542465753424658</v>
+        <v>4.5424657534246577</v>
       </c>
       <c r="AI35">
         <v>21</v>
@@ -8836,7 +8857,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="36" spans="1:43">
+    <row r="36" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -8937,7 +8958,7 @@
         <v>46259</v>
       </c>
       <c r="AH36">
-        <v>13.24109589041096</v>
+        <v>13.241095890410961</v>
       </c>
       <c r="AI36">
         <v>30</v>
@@ -8967,7 +8988,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="37" spans="1:43">
+    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -9098,7 +9119,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="38" spans="1:43">
+    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -9229,7 +9250,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="39" spans="1:43">
+    <row r="39" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -9330,7 +9351,7 @@
         <v>46259</v>
       </c>
       <c r="AH39">
-        <v>6.70958904109589</v>
+        <v>6.7095890410958896</v>
       </c>
       <c r="AI39">
         <v>30</v>
@@ -9360,7 +9381,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="40" spans="1:43">
+    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -9461,7 +9482,7 @@
         <v>46259</v>
       </c>
       <c r="AH40">
-        <v>6.50958904109589</v>
+        <v>6.5095890410958903</v>
       </c>
       <c r="AI40">
         <v>30</v>
@@ -9491,7 +9512,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="41" spans="1:43">
+    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -9592,7 +9613,7 @@
         <v>46259</v>
       </c>
       <c r="AH41">
-        <v>6.550684931506849</v>
+        <v>6.5506849315068489</v>
       </c>
       <c r="AI41">
         <v>21</v>
@@ -9622,7 +9643,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="42" spans="1:43">
+    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -9753,7 +9774,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="43" spans="1:43">
+    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -9854,7 +9875,7 @@
         <v>46259</v>
       </c>
       <c r="AH43">
-        <v>8.753424657534246</v>
+        <v>8.7534246575342465</v>
       </c>
       <c r="AI43">
         <v>30</v>
@@ -9884,7 +9905,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="44" spans="1:43">
+    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -9985,7 +10006,7 @@
         <v>46259</v>
       </c>
       <c r="AH44">
-        <v>5.753424657534246</v>
+        <v>5.7534246575342456</v>
       </c>
       <c r="AI44">
         <v>21</v>
@@ -10015,7 +10036,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="45" spans="1:43">
+    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -10116,7 +10137,7 @@
         <v>46259</v>
       </c>
       <c r="AH45">
-        <v>5.734246575342466</v>
+        <v>5.7342465753424658</v>
       </c>
       <c r="AI45">
         <v>21</v>
@@ -10146,7 +10167,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="46" spans="1:43">
+    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -10247,7 +10268,7 @@
         <v>46259</v>
       </c>
       <c r="AH46">
-        <v>5.627397260273972</v>
+        <v>5.6273972602739724</v>
       </c>
       <c r="AI46">
         <v>30</v>
@@ -10277,7 +10298,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="47" spans="1:43">
+    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -10378,7 +10399,7 @@
         <v>46259</v>
       </c>
       <c r="AH47">
-        <v>4.227397260273973</v>
+        <v>4.2273972602739729</v>
       </c>
       <c r="AI47">
         <v>21</v>
@@ -10408,7 +10429,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="48" spans="1:43">
+    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -10539,7 +10560,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="49" spans="1:43">
+    <row r="49" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -10640,7 +10661,7 @@
         <v>46259</v>
       </c>
       <c r="AH49">
-        <v>4.158904109589041</v>
+        <v>4.1589041095890407</v>
       </c>
       <c r="AI49">
         <v>21</v>
@@ -10670,7 +10691,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="50" spans="1:43">
+    <row r="50" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -10771,7 +10792,7 @@
         <v>46259</v>
       </c>
       <c r="AH50">
-        <v>3.986301369863014</v>
+        <v>3.9863013698630141</v>
       </c>
       <c r="AI50">
         <v>21</v>
@@ -10801,7 +10822,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="51" spans="1:43">
+    <row r="51" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -10902,7 +10923,7 @@
         <v>46259</v>
       </c>
       <c r="AH51">
-        <v>3.964383561643836</v>
+        <v>3.9643835616438361</v>
       </c>
       <c r="AI51">
         <v>21</v>
@@ -10932,7 +10953,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="52" spans="1:43">
+    <row r="52" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -11033,7 +11054,7 @@
         <v>46259</v>
       </c>
       <c r="AH52">
-        <v>3.964383561643836</v>
+        <v>3.9643835616438361</v>
       </c>
       <c r="AI52">
         <v>21</v>
@@ -11063,7 +11084,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="53" spans="1:43">
+    <row r="53" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -11194,7 +11215,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="54" spans="1:43">
+    <row r="54" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -11295,7 +11316,7 @@
         <v>46259</v>
       </c>
       <c r="AH54">
-        <v>1.96986301369863</v>
+        <v>1.9698630136986299</v>
       </c>
       <c r="AI54">
         <v>21</v>
@@ -11325,7 +11346,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="55" spans="1:43">
+    <row r="55" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -11426,7 +11447,7 @@
         <v>46259</v>
       </c>
       <c r="AH55">
-        <v>0.5835616438356165</v>
+        <v>0.58356164383561648</v>
       </c>
       <c r="AI55">
         <v>21</v>
@@ -11456,7 +11477,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="56" spans="1:43">
+    <row r="56" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -11557,7 +11578,7 @@
         <v>46259</v>
       </c>
       <c r="AH56">
-        <v>0.5835616438356165</v>
+        <v>0.58356164383561648</v>
       </c>
       <c r="AI56">
         <v>21</v>
@@ -11587,7 +11608,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="57" spans="1:43">
+    <row r="57" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -11688,7 +11709,7 @@
         <v>46259</v>
       </c>
       <c r="AH57">
-        <v>7.150684931506849</v>
+        <v>7.1506849315068486</v>
       </c>
       <c r="AI57">
         <v>30</v>
@@ -11718,7 +11739,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="58" spans="1:43">
+    <row r="58" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -11819,7 +11840,7 @@
         <v>46259</v>
       </c>
       <c r="AH58">
-        <v>7.482191780821918</v>
+        <v>7.4821917808219176</v>
       </c>
       <c r="AI58">
         <v>30</v>
@@ -11849,7 +11870,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="59" spans="1:43">
+    <row r="59" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -11950,7 +11971,7 @@
         <v>46259</v>
       </c>
       <c r="AH59">
-        <v>0.06575342465753424</v>
+        <v>6.575342465753424E-2</v>
       </c>
       <c r="AI59">
         <v>21</v>
@@ -11980,7 +12001,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="60" spans="1:43">
+    <row r="60" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -12081,7 +12102,7 @@
         <v>46259</v>
       </c>
       <c r="AH60">
-        <v>0.06575342465753424</v>
+        <v>6.575342465753424E-2</v>
       </c>
       <c r="AI60">
         <v>21</v>
@@ -12111,7 +12132,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="61" spans="1:43">
+    <row r="61" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
@@ -12212,7 +12233,7 @@
         <v>46259</v>
       </c>
       <c r="AH61">
-        <v>18.26301369863014</v>
+        <v>18.263013698630139</v>
       </c>
       <c r="AI61">
         <v>30</v>
@@ -12242,7 +12263,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="62" spans="1:43">
+    <row r="62" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
@@ -12343,7 +12364,7 @@
         <v>46259</v>
       </c>
       <c r="AH62">
-        <v>15.07671232876712</v>
+        <v>15.076712328767121</v>
       </c>
       <c r="AI62">
         <v>30</v>
@@ -12373,7 +12394,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="63" spans="1:43">
+    <row r="63" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
@@ -12474,7 +12495,7 @@
         <v>46259</v>
       </c>
       <c r="AH63">
-        <v>34.04931506849315</v>
+        <v>34.049315068493151</v>
       </c>
       <c r="AI63">
         <v>30</v>
@@ -12504,7 +12525,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="64" spans="1:43">
+    <row r="64" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
@@ -12605,7 +12626,7 @@
         <v>46259</v>
       </c>
       <c r="AH64">
-        <v>6.175342465753425</v>
+        <v>6.1753424657534248</v>
       </c>
       <c r="AI64">
         <v>30</v>
@@ -12635,7 +12656,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="65" spans="1:43">
+    <row r="65" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
@@ -12736,7 +12757,7 @@
         <v>46259</v>
       </c>
       <c r="AH65">
-        <v>1.873972602739726</v>
+        <v>1.8739726027397261</v>
       </c>
       <c r="AI65">
         <v>21</v>
@@ -12766,7 +12787,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="66" spans="1:43">
+    <row r="66" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
@@ -12867,7 +12888,7 @@
         <v>46259</v>
       </c>
       <c r="AH66">
-        <v>5.753424657534246</v>
+        <v>5.7534246575342456</v>
       </c>
       <c r="AI66">
         <v>21</v>
@@ -12897,7 +12918,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="67" spans="1:43">
+    <row r="67" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
@@ -12998,7 +13019,7 @@
         <v>46259</v>
       </c>
       <c r="AH67">
-        <v>18.04657534246575</v>
+        <v>18.046575342465751</v>
       </c>
       <c r="AI67">
         <v>30</v>
@@ -13028,7 +13049,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="68" spans="1:43">
+    <row r="68" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
@@ -13129,7 +13150,7 @@
         <v>46259</v>
       </c>
       <c r="AH68">
-        <v>9.531506849315068</v>
+        <v>9.5315068493150683</v>
       </c>
       <c r="AI68">
         <v>30</v>
@@ -13159,7 +13180,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="69" spans="1:43">
+    <row r="69" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
@@ -13290,7 +13311,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="70" spans="1:43">
+    <row r="70" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
@@ -13391,7 +13412,7 @@
         <v>46259</v>
       </c>
       <c r="AH70">
-        <v>10.60821917808219</v>
+        <v>10.608219178082191</v>
       </c>
       <c r="AI70">
         <v>30</v>
@@ -13421,7 +13442,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="71" spans="1:43">
+    <row r="71" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
@@ -13522,7 +13543,7 @@
         <v>46259</v>
       </c>
       <c r="AH71">
-        <v>0.3342465753424658</v>
+        <v>0.33424657534246582</v>
       </c>
       <c r="AI71">
         <v>21</v>
@@ -13552,7 +13573,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="72" spans="1:43">
+    <row r="72" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
@@ -13653,7 +13674,7 @@
         <v>46259</v>
       </c>
       <c r="AH72">
-        <v>0.3342465753424658</v>
+        <v>0.33424657534246582</v>
       </c>
       <c r="AI72">
         <v>21</v>
@@ -13683,7 +13704,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="73" spans="1:43">
+    <row r="73" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
@@ -13784,7 +13805,7 @@
         <v>46259</v>
       </c>
       <c r="AH73">
-        <v>2.96986301369863</v>
+        <v>2.9698630136986299</v>
       </c>
       <c r="AI73">
         <v>21</v>
@@ -13814,7 +13835,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="74" spans="1:43">
+    <row r="74" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>71</v>
       </c>
@@ -13945,7 +13966,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="75" spans="1:43">
+    <row r="75" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>72</v>
       </c>
@@ -14046,7 +14067,7 @@
         <v>46259</v>
       </c>
       <c r="AH75">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AI75">
         <v>21</v>
@@ -14076,7 +14097,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="76" spans="1:43">
+    <row r="76" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>73</v>
       </c>
@@ -14177,7 +14198,7 @@
         <v>46259</v>
       </c>
       <c r="AH76">
-        <v>4.068493150684931</v>
+        <v>4.0684931506849313</v>
       </c>
       <c r="AI76">
         <v>21</v>
@@ -14207,7 +14228,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="77" spans="1:43">
+    <row r="77" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>74</v>
       </c>
@@ -14338,7 +14359,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="78" spans="1:43">
+    <row r="78" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>75</v>
       </c>
@@ -14469,7 +14490,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="79" spans="1:43">
+    <row r="79" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>76</v>
       </c>
@@ -14570,7 +14591,7 @@
         <v>46259</v>
       </c>
       <c r="AH79">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AI79">
         <v>21</v>
@@ -14600,7 +14621,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="80" spans="1:43">
+    <row r="80" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>77</v>
       </c>
@@ -14701,7 +14722,7 @@
         <v>46259</v>
       </c>
       <c r="AH80">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AI80">
         <v>21</v>
@@ -14731,7 +14752,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="81" spans="1:43">
+    <row r="81" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>78</v>
       </c>
@@ -14832,7 +14853,7 @@
         <v>46259</v>
       </c>
       <c r="AH81">
-        <v>1.819178082191781</v>
+        <v>1.8191780821917809</v>
       </c>
       <c r="AI81">
         <v>21</v>
@@ -14862,7 +14883,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="82" spans="1:43">
+    <row r="82" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>79</v>
       </c>
@@ -14963,7 +14984,7 @@
         <v>46259</v>
       </c>
       <c r="AH82">
-        <v>1.654794520547945</v>
+        <v>1.6547945205479451</v>
       </c>
       <c r="AI82">
         <v>21</v>
@@ -14993,7 +15014,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="83" spans="1:43">
+    <row r="83" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>80</v>
       </c>
@@ -15094,7 +15115,7 @@
         <v>46259</v>
       </c>
       <c r="AH83">
-        <v>15.16712328767123</v>
+        <v>15.167123287671229</v>
       </c>
       <c r="AI83">
         <v>30</v>
@@ -15124,7 +15145,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="84" spans="1:43">
+    <row r="84" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>80</v>
       </c>
@@ -15165,7 +15186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:43">
+    <row r="85" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>81</v>
       </c>
@@ -15266,7 +15287,7 @@
         <v>46259</v>
       </c>
       <c r="AH85">
-        <v>8.975342465753425</v>
+        <v>8.9753424657534246</v>
       </c>
       <c r="AI85">
         <v>30</v>
@@ -15296,7 +15317,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="86" spans="1:43">
+    <row r="86" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>82</v>
       </c>
@@ -15397,7 +15418,7 @@
         <v>46259</v>
       </c>
       <c r="AH86">
-        <v>6.70958904109589</v>
+        <v>6.7095890410958896</v>
       </c>
       <c r="AI86">
         <v>30</v>
@@ -15427,7 +15448,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="87" spans="1:43">
+    <row r="87" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>83</v>
       </c>
@@ -15528,7 +15549,7 @@
         <v>46259</v>
       </c>
       <c r="AH87">
-        <v>9.323287671232876</v>
+        <v>9.3232876712328761</v>
       </c>
       <c r="AI87">
         <v>30</v>
@@ -15558,7 +15579,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="88" spans="1:43">
+    <row r="88" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>84</v>
       </c>
@@ -15659,7 +15680,7 @@
         <v>46259</v>
       </c>
       <c r="AH88">
-        <v>14.03561643835616</v>
+        <v>14.035616438356159</v>
       </c>
       <c r="AI88">
         <v>30</v>
@@ -15689,7 +15710,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="89" spans="1:43">
+    <row r="89" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>85</v>
       </c>
@@ -15790,7 +15811,7 @@
         <v>46259</v>
       </c>
       <c r="AH89">
-        <v>1.772602739726027</v>
+        <v>1.7726027397260271</v>
       </c>
       <c r="AI89">
         <v>21</v>
@@ -15820,7 +15841,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="90" spans="1:43">
+    <row r="90" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>86</v>
       </c>
@@ -15921,7 +15942,7 @@
         <v>46259</v>
       </c>
       <c r="AH90">
-        <v>8.408219178082192</v>
+        <v>8.4082191780821915</v>
       </c>
       <c r="AI90">
         <v>30</v>
@@ -15951,7 +15972,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="91" spans="1:43">
+    <row r="91" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>87</v>
       </c>
@@ -16052,7 +16073,7 @@
         <v>46259</v>
       </c>
       <c r="AH91">
-        <v>10.95068493150685</v>
+        <v>10.950684931506849</v>
       </c>
       <c r="AI91">
         <v>30</v>
@@ -16082,7 +16103,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="92" spans="1:43">
+    <row r="92" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>88</v>
       </c>
@@ -16183,7 +16204,7 @@
         <v>46259</v>
       </c>
       <c r="AH92">
-        <v>6.682191780821918</v>
+        <v>6.6821917808219178</v>
       </c>
       <c r="AI92">
         <v>21</v>
@@ -16213,7 +16234,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="93" spans="1:43">
+    <row r="93" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>89</v>
       </c>
@@ -16314,7 +16335,7 @@
         <v>46259</v>
       </c>
       <c r="AH93">
-        <v>5.627397260273972</v>
+        <v>5.6273972602739724</v>
       </c>
       <c r="AI93">
         <v>21</v>
@@ -16344,7 +16365,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="94" spans="1:43">
+    <row r="94" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>90</v>
       </c>
@@ -16445,7 +16466,7 @@
         <v>46259</v>
       </c>
       <c r="AH94">
-        <v>5.315068493150685</v>
+        <v>5.3150684931506849</v>
       </c>
       <c r="AI94">
         <v>30</v>
@@ -16475,7 +16496,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="95" spans="1:43">
+    <row r="95" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>91</v>
       </c>
@@ -16576,7 +16597,7 @@
         <v>46259</v>
       </c>
       <c r="AH95">
-        <v>5.06027397260274</v>
+        <v>5.0602739726027401</v>
       </c>
       <c r="AI95">
         <v>30</v>
@@ -16606,7 +16627,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="96" spans="1:43">
+    <row r="96" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>92</v>
       </c>
@@ -16707,7 +16728,7 @@
         <v>46259</v>
       </c>
       <c r="AH96">
-        <v>5.06027397260274</v>
+        <v>5.0602739726027401</v>
       </c>
       <c r="AI96">
         <v>21</v>
@@ -16737,7 +16758,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="97" spans="1:43">
+    <row r="97" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>93</v>
       </c>
@@ -16838,7 +16859,7 @@
         <v>46259</v>
       </c>
       <c r="AH97">
-        <v>4.753424657534246</v>
+        <v>4.7534246575342456</v>
       </c>
       <c r="AI97">
         <v>21</v>
@@ -16868,7 +16889,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="98" spans="1:43">
+    <row r="98" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>94</v>
       </c>
@@ -16969,7 +16990,7 @@
         <v>46259</v>
       </c>
       <c r="AH98">
-        <v>0.5835616438356165</v>
+        <v>0.58356164383561648</v>
       </c>
       <c r="AI98">
         <v>21</v>
@@ -16999,7 +17020,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="99" spans="1:43">
+    <row r="99" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>95</v>
       </c>
@@ -17100,7 +17121,7 @@
         <v>46259</v>
       </c>
       <c r="AH99">
-        <v>0.5835616438356165</v>
+        <v>0.58356164383561648</v>
       </c>
       <c r="AI99">
         <v>21</v>
@@ -17130,7 +17151,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="100" spans="1:43">
+    <row r="100" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>96</v>
       </c>
@@ -17231,7 +17252,7 @@
         <v>46259</v>
       </c>
       <c r="AH100">
-        <v>4.739726027397261</v>
+        <v>4.7397260273972606</v>
       </c>
       <c r="AI100">
         <v>21</v>
@@ -17261,7 +17282,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="101" spans="1:43">
+    <row r="101" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>97</v>
       </c>
@@ -17362,7 +17383,7 @@
         <v>46259</v>
       </c>
       <c r="AH101">
-        <v>4.67945205479452</v>
+        <v>4.6794520547945204</v>
       </c>
       <c r="AI101">
         <v>21</v>
@@ -17392,7 +17413,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="102" spans="1:43">
+    <row r="102" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>98</v>
       </c>
@@ -17493,7 +17514,7 @@
         <v>46259</v>
       </c>
       <c r="AH102">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AI102">
         <v>21</v>
@@ -17523,7 +17544,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="103" spans="1:43">
+    <row r="103" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>99</v>
       </c>
@@ -17624,7 +17645,7 @@
         <v>46259</v>
       </c>
       <c r="AH103">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AI103">
         <v>21</v>
@@ -17654,7 +17675,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="104" spans="1:43">
+    <row r="104" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>100</v>
       </c>
@@ -17755,7 +17776,7 @@
         <v>46259</v>
       </c>
       <c r="AH104">
-        <v>3.964383561643836</v>
+        <v>3.9643835616438361</v>
       </c>
       <c r="AI104">
         <v>21</v>
@@ -17785,7 +17806,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="105" spans="1:43">
+    <row r="105" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>101</v>
       </c>
@@ -17886,7 +17907,7 @@
         <v>46259</v>
       </c>
       <c r="AH105">
-        <v>7.523287671232877</v>
+        <v>7.5232876712328771</v>
       </c>
       <c r="AI105">
         <v>30</v>
@@ -17916,7 +17937,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="106" spans="1:43">
+    <row r="106" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>102</v>
       </c>
@@ -18017,7 +18038,7 @@
         <v>46259</v>
       </c>
       <c r="AH106">
-        <v>4.972602739726027</v>
+        <v>4.9726027397260273</v>
       </c>
       <c r="AI106">
         <v>21</v>
@@ -18047,7 +18068,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="107" spans="1:43">
+    <row r="107" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>103</v>
       </c>
@@ -18148,7 +18169,7 @@
         <v>46259</v>
       </c>
       <c r="AH107">
-        <v>1.96986301369863</v>
+        <v>1.9698630136986299</v>
       </c>
       <c r="AI107">
         <v>21</v>
@@ -18178,7 +18199,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="108" spans="1:43">
+    <row r="108" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>104</v>
       </c>
@@ -18279,7 +18300,7 @@
         <v>46259</v>
       </c>
       <c r="AH108">
-        <v>22.44657534246575</v>
+        <v>22.446575342465749</v>
       </c>
       <c r="AI108">
         <v>30</v>
@@ -18309,7 +18330,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="109" spans="1:43">
+    <row r="109" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>105</v>
       </c>
@@ -18410,7 +18431,7 @@
         <v>46259</v>
       </c>
       <c r="AH109">
-        <v>3.986301369863014</v>
+        <v>3.9863013698630141</v>
       </c>
       <c r="AI109">
         <v>21</v>
@@ -18440,7 +18461,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="110" spans="1:43">
+    <row r="110" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>106</v>
       </c>
@@ -18493,7 +18514,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="111" spans="1:43">
+    <row r="111" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>107</v>
       </c>
@@ -18594,7 +18615,7 @@
         <v>46259</v>
       </c>
       <c r="AH111">
-        <v>0.3589041095890411</v>
+        <v>0.35890410958904112</v>
       </c>
       <c r="AI111">
         <v>21</v>
@@ -18624,7 +18645,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="112" spans="1:43">
+    <row r="112" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>108</v>
       </c>
@@ -18725,7 +18746,7 @@
         <v>46259</v>
       </c>
       <c r="AH112">
-        <v>5.372602739726028</v>
+        <v>5.3726027397260276</v>
       </c>
       <c r="AI112">
         <v>21</v>
@@ -18755,7 +18776,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="113" spans="1:43">
+    <row r="113" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>109</v>
       </c>
@@ -18856,7 +18877,7 @@
         <v>46259</v>
       </c>
       <c r="AH113">
-        <v>4.528767123287671</v>
+        <v>4.5287671232876709</v>
       </c>
       <c r="AI113">
         <v>21</v>
@@ -18886,7 +18907,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="114" spans="1:43">
+    <row r="114" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>110</v>
       </c>
@@ -18987,7 +19008,7 @@
         <v>46259</v>
       </c>
       <c r="AH114">
-        <v>4.583561643835616</v>
+        <v>4.5835616438356164</v>
       </c>
       <c r="AI114">
         <v>21</v>
@@ -19017,7 +19038,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="115" spans="1:43">
+    <row r="115" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>111</v>
       </c>
@@ -19118,7 +19139,7 @@
         <v>46259</v>
       </c>
       <c r="AH115">
-        <v>4.526027397260274</v>
+        <v>4.5260273972602736</v>
       </c>
       <c r="AI115">
         <v>21</v>
@@ -19148,7 +19169,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="116" spans="1:43">
+    <row r="116" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>112</v>
       </c>
@@ -19249,7 +19270,7 @@
         <v>46259</v>
       </c>
       <c r="AH116">
-        <v>4.528767123287671</v>
+        <v>4.5287671232876709</v>
       </c>
       <c r="AI116">
         <v>21</v>
@@ -19279,7 +19300,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="117" spans="1:43">
+    <row r="117" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B117">
         <v>1336</v>
       </c>
@@ -19407,7 +19428,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="118" spans="1:43">
+    <row r="118" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>113</v>
       </c>
@@ -19538,7 +19559,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="119" spans="1:43">
+    <row r="119" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>114</v>
       </c>
@@ -19639,7 +19660,7 @@
         <v>46259</v>
       </c>
       <c r="AH119">
-        <v>2.63013698630137</v>
+        <v>2.6301369863013702</v>
       </c>
       <c r="AI119">
         <v>21</v>
@@ -19669,7 +19690,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="120" spans="1:43">
+    <row r="120" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>115</v>
       </c>
@@ -19770,7 +19791,7 @@
         <v>46259</v>
       </c>
       <c r="AH120">
-        <v>2.410958904109589</v>
+        <v>2.4109589041095889</v>
       </c>
       <c r="AI120">
         <v>21</v>
@@ -19800,7 +19821,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="121" spans="1:43">
+    <row r="121" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>116</v>
       </c>
@@ -19931,7 +19952,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="122" spans="1:43">
+    <row r="122" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>117</v>
       </c>
@@ -20062,7 +20083,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="123" spans="1:43">
+    <row r="123" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>118</v>
       </c>
@@ -20193,7 +20214,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="124" spans="1:43">
+    <row r="124" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>119</v>
       </c>
@@ -20294,7 +20315,7 @@
         <v>46259</v>
       </c>
       <c r="AH124">
-        <v>2.263013698630137</v>
+        <v>2.2630136986301368</v>
       </c>
       <c r="AI124">
         <v>21</v>
@@ -20324,7 +20345,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="125" spans="1:43">
+    <row r="125" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>120</v>
       </c>
@@ -20425,7 +20446,7 @@
         <v>46259</v>
       </c>
       <c r="AH125">
-        <v>6.586301369863014</v>
+        <v>6.5863013698630137</v>
       </c>
       <c r="AI125">
         <v>30</v>
@@ -20455,7 +20476,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="126" spans="1:43">
+    <row r="126" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>120</v>
       </c>
@@ -20478,7 +20499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:43">
+    <row r="127" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>121</v>
       </c>
@@ -20579,7 +20600,7 @@
         <v>46259</v>
       </c>
       <c r="AH127">
-        <v>12.26575342465753</v>
+        <v>12.265753424657531</v>
       </c>
       <c r="AI127">
         <v>30</v>
@@ -20609,7 +20630,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="128" spans="1:43">
+    <row r="128" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>122</v>
       </c>
@@ -20710,7 +20731,7 @@
         <v>46259</v>
       </c>
       <c r="AH128">
-        <v>5.964383561643835</v>
+        <v>5.9643835616438352</v>
       </c>
       <c r="AI128">
         <v>30</v>
@@ -20740,7 +20761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:43">
+    <row r="129" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>123</v>
       </c>
@@ -20841,7 +20862,7 @@
         <v>46259</v>
       </c>
       <c r="AH129">
-        <v>5.797260273972602</v>
+        <v>5.7972602739726016</v>
       </c>
       <c r="AI129">
         <v>21</v>
@@ -20871,7 +20892,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="130" spans="1:43">
+    <row r="130" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>124</v>
       </c>
@@ -20972,7 +20993,7 @@
         <v>46259</v>
       </c>
       <c r="AH130">
-        <v>5.153424657534247</v>
+        <v>5.1534246575342468</v>
       </c>
       <c r="AI130">
         <v>30</v>
@@ -21002,7 +21023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:43">
+    <row r="131" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>125</v>
       </c>
@@ -21103,7 +21124,7 @@
         <v>46259</v>
       </c>
       <c r="AH131">
-        <v>5.178082191780822</v>
+        <v>5.1780821917808222</v>
       </c>
       <c r="AI131">
         <v>30</v>
@@ -21133,7 +21154,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="132" spans="1:43">
+    <row r="132" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B132">
         <v>1135</v>
       </c>
@@ -21231,7 +21252,7 @@
         <v>46259</v>
       </c>
       <c r="AH132">
-        <v>0.1506849315068493</v>
+        <v>0.15068493150684931</v>
       </c>
       <c r="AI132">
         <v>21</v>
@@ -21261,7 +21282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:43">
+    <row r="133" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>126</v>
       </c>
@@ -21362,7 +21383,7 @@
         <v>46259</v>
       </c>
       <c r="AH133">
-        <v>4.235616438356164</v>
+        <v>4.2356164383561641</v>
       </c>
       <c r="AI133">
         <v>21</v>
@@ -21392,7 +21413,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="134" spans="1:43">
+    <row r="134" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>127</v>
       </c>
@@ -21493,7 +21514,7 @@
         <v>46259</v>
       </c>
       <c r="AH134">
-        <v>4.235616438356164</v>
+        <v>4.2356164383561641</v>
       </c>
       <c r="AI134">
         <v>21</v>
@@ -21523,7 +21544,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="135" spans="1:43">
+    <row r="135" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>128</v>
       </c>
@@ -21624,7 +21645,7 @@
         <v>46259</v>
       </c>
       <c r="AH135">
-        <v>4.723287671232876</v>
+        <v>4.7232876712328764</v>
       </c>
       <c r="AI135">
         <v>21</v>
@@ -21654,7 +21675,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="136" spans="1:43">
+    <row r="136" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>129</v>
       </c>
@@ -21755,7 +21776,7 @@
         <v>46259</v>
       </c>
       <c r="AH136">
-        <v>4.29041095890411</v>
+        <v>4.2904109589041104</v>
       </c>
       <c r="AI136">
         <v>21</v>
@@ -21785,7 +21806,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="137" spans="1:43">
+    <row r="137" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>130</v>
       </c>
@@ -21886,7 +21907,7 @@
         <v>46259</v>
       </c>
       <c r="AH137">
-        <v>4.553424657534246</v>
+        <v>4.5534246575342463</v>
       </c>
       <c r="AI137">
         <v>21</v>
@@ -21916,7 +21937,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="138" spans="1:43">
+    <row r="138" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>131</v>
       </c>
@@ -22017,7 +22038,7 @@
         <v>46259</v>
       </c>
       <c r="AH138">
-        <v>1.498630136986301</v>
+        <v>1.4986301369863011</v>
       </c>
       <c r="AI138">
         <v>21</v>
@@ -22047,7 +22068,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="139" spans="1:43">
+    <row r="139" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>132</v>
       </c>
@@ -22178,7 +22199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:43">
+    <row r="140" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>133</v>
       </c>
@@ -22309,7 +22330,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="141" spans="1:43">
+    <row r="141" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>134</v>
       </c>
@@ -22440,7 +22461,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="142" spans="1:43">
+    <row r="142" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>135</v>
       </c>
@@ -22571,7 +22592,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="143" spans="1:43">
+    <row r="143" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>136</v>
       </c>
@@ -22672,7 +22693,7 @@
         <v>46259</v>
       </c>
       <c r="AH143">
-        <v>4.487671232876712</v>
+        <v>4.4876712328767123</v>
       </c>
       <c r="AI143">
         <v>21</v>
@@ -22702,7 +22723,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="144" spans="1:43">
+    <row r="144" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>137</v>
       </c>
@@ -22803,7 +22824,7 @@
         <v>46259</v>
       </c>
       <c r="AH144">
-        <v>4.468493150684932</v>
+        <v>4.4684931506849317</v>
       </c>
       <c r="AI144">
         <v>21</v>
@@ -22833,7 +22854,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="145" spans="1:43">
+    <row r="145" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>138</v>
       </c>
@@ -22934,7 +22955,7 @@
         <v>46259</v>
       </c>
       <c r="AH145">
-        <v>1.857534246575342</v>
+        <v>1.8575342465753419</v>
       </c>
       <c r="AI145">
         <v>21</v>
@@ -22964,7 +22985,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="146" spans="1:43">
+    <row r="146" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>139</v>
       </c>
@@ -23065,7 +23086,7 @@
         <v>46259</v>
       </c>
       <c r="AH146">
-        <v>4.389041095890411</v>
+        <v>4.3890410958904109</v>
       </c>
       <c r="AI146">
         <v>21</v>
@@ -23095,7 +23116,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="147" spans="1:43">
+    <row r="147" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>140</v>
       </c>
@@ -23196,7 +23217,7 @@
         <v>46259</v>
       </c>
       <c r="AH147">
-        <v>3.791780821917808</v>
+        <v>3.7917808219178082</v>
       </c>
       <c r="AI147">
         <v>21</v>
@@ -23226,7 +23247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:43">
+    <row r="148" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>141</v>
       </c>
@@ -23327,7 +23348,7 @@
         <v>46259</v>
       </c>
       <c r="AH148">
-        <v>3.786301369863014</v>
+        <v>3.7863013698630139</v>
       </c>
       <c r="AI148">
         <v>21</v>
@@ -23357,7 +23378,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="149" spans="1:43">
+    <row r="149" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>142</v>
       </c>
@@ -23458,7 +23479,7 @@
         <v>46259</v>
       </c>
       <c r="AH149">
-        <v>3.736986301369863</v>
+        <v>3.7369863013698632</v>
       </c>
       <c r="AI149">
         <v>21</v>
@@ -23488,7 +23509,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="150" spans="1:43">
+    <row r="150" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>143</v>
       </c>
@@ -23589,7 +23610,7 @@
         <v>46259</v>
       </c>
       <c r="AH150">
-        <v>2.545205479452055</v>
+        <v>2.5452054794520551</v>
       </c>
       <c r="AI150">
         <v>21</v>
@@ -23619,7 +23640,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="151" spans="1:43">
+    <row r="151" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>144</v>
       </c>
@@ -23720,7 +23741,7 @@
         <v>46259</v>
       </c>
       <c r="AH151">
-        <v>5.967123287671233</v>
+        <v>5.9671232876712326</v>
       </c>
       <c r="AI151">
         <v>21</v>
@@ -23750,7 +23771,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="152" spans="1:43">
+    <row r="152" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>145</v>
       </c>
@@ -23851,7 +23872,7 @@
         <v>46259</v>
       </c>
       <c r="AH152">
-        <v>3.101369863013699</v>
+        <v>3.1013698630136992</v>
       </c>
       <c r="AI152">
         <v>21</v>
@@ -23881,7 +23902,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="153" spans="1:43">
+    <row r="153" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>146</v>
       </c>
@@ -23982,7 +24003,7 @@
         <v>46259</v>
       </c>
       <c r="AH153">
-        <v>5.64931506849315</v>
+        <v>5.6493150684931503</v>
       </c>
       <c r="AI153">
         <v>21</v>
@@ -24012,7 +24033,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="154" spans="1:43">
+    <row r="154" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>147</v>
       </c>
@@ -24113,7 +24134,7 @@
         <v>46259</v>
       </c>
       <c r="AH154">
-        <v>5.402739726027397</v>
+        <v>5.4027397260273968</v>
       </c>
       <c r="AI154">
         <v>21</v>
@@ -24143,7 +24164,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="155" spans="1:43">
+    <row r="155" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>148</v>
       </c>
@@ -24244,7 +24265,7 @@
         <v>46259</v>
       </c>
       <c r="AH155">
-        <v>5.30958904109589</v>
+        <v>5.3095890410958901</v>
       </c>
       <c r="AI155">
         <v>21</v>
@@ -24274,7 +24295,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="156" spans="1:43">
+    <row r="156" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>149</v>
       </c>
@@ -24375,7 +24396,7 @@
         <v>46259</v>
       </c>
       <c r="AH156">
-        <v>5.038356164383561</v>
+        <v>5.0383561643835613</v>
       </c>
       <c r="AI156">
         <v>21</v>
@@ -24405,7 +24426,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="157" spans="1:43">
+    <row r="157" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>150</v>
       </c>
@@ -24506,7 +24527,7 @@
         <v>46259</v>
       </c>
       <c r="AH157">
-        <v>5.038356164383561</v>
+        <v>5.0383561643835613</v>
       </c>
       <c r="AI157">
         <v>21</v>
@@ -24536,7 +24557,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="158" spans="1:43">
+    <row r="158" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>151</v>
       </c>
@@ -24637,7 +24658,7 @@
         <v>46259</v>
       </c>
       <c r="AH158">
-        <v>5.038356164383561</v>
+        <v>5.0383561643835613</v>
       </c>
       <c r="AI158">
         <v>21</v>
@@ -24667,7 +24688,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="159" spans="1:43">
+    <row r="159" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>152</v>
       </c>
@@ -24768,7 +24789,7 @@
         <v>46259</v>
       </c>
       <c r="AH159">
-        <v>5.038356164383561</v>
+        <v>5.0383561643835613</v>
       </c>
       <c r="AI159">
         <v>21</v>
@@ -24798,7 +24819,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="160" spans="1:43">
+    <row r="160" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>153</v>
       </c>
@@ -24899,7 +24920,7 @@
         <v>46259</v>
       </c>
       <c r="AH160">
-        <v>1.83013698630137</v>
+        <v>1.8301369863013699</v>
       </c>
       <c r="AI160">
         <v>21</v>
@@ -24929,7 +24950,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="161" spans="1:43">
+    <row r="161" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>154</v>
       </c>
@@ -25030,7 +25051,7 @@
         <v>46259</v>
       </c>
       <c r="AH161">
-        <v>4.528767123287671</v>
+        <v>4.5287671232876709</v>
       </c>
       <c r="AI161">
         <v>21</v>
@@ -25060,7 +25081,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="162" spans="1:43">
+    <row r="162" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>155</v>
       </c>
@@ -25161,7 +25182,7 @@
         <v>46259</v>
       </c>
       <c r="AH162">
-        <v>4.389041095890411</v>
+        <v>4.3890410958904109</v>
       </c>
       <c r="AI162">
         <v>21</v>
@@ -25191,7 +25212,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="163" spans="1:43">
+    <row r="163" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>156</v>
       </c>
@@ -25292,7 +25313,7 @@
         <v>46259</v>
       </c>
       <c r="AH163">
-        <v>4.389041095890411</v>
+        <v>4.3890410958904109</v>
       </c>
       <c r="AI163">
         <v>21</v>
@@ -25322,7 +25343,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="164" spans="1:43">
+    <row r="164" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>157</v>
       </c>
@@ -25453,7 +25474,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="165" spans="1:43">
+    <row r="165" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>158</v>
       </c>
@@ -25554,7 +25575,7 @@
         <v>46259</v>
       </c>
       <c r="AH165">
-        <v>3.994520547945205</v>
+        <v>3.9945205479452048</v>
       </c>
       <c r="AI165">
         <v>21</v>
@@ -25584,7 +25605,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="166" spans="1:43">
+    <row r="166" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>159</v>
       </c>
@@ -25685,7 +25706,7 @@
         <v>46259</v>
       </c>
       <c r="AH166">
-        <v>3.964383561643836</v>
+        <v>3.9643835616438361</v>
       </c>
       <c r="AI166">
         <v>21</v>
@@ -25715,7 +25736,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="167" spans="1:43">
+    <row r="167" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>161</v>
       </c>
@@ -25816,7 +25837,7 @@
         <v>46259</v>
       </c>
       <c r="AH167">
-        <v>2.33972602739726</v>
+        <v>2.3397260273972602</v>
       </c>
       <c r="AI167">
         <v>21</v>
@@ -25846,7 +25867,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="168" spans="1:43">
+    <row r="168" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>162</v>
       </c>
@@ -25947,7 +25968,7 @@
         <v>46259</v>
       </c>
       <c r="AH168">
-        <v>13.54794520547945</v>
+        <v>13.547945205479451</v>
       </c>
       <c r="AI168">
         <v>30</v>
@@ -25977,7 +25998,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="169" spans="1:43">
+    <row r="169" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>163</v>
       </c>
@@ -26078,7 +26099,7 @@
         <v>46259</v>
       </c>
       <c r="AH169">
-        <v>5.153424657534247</v>
+        <v>5.1534246575342468</v>
       </c>
       <c r="AI169">
         <v>30</v>
@@ -26108,7 +26129,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="170" spans="1:43">
+    <row r="170" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>164</v>
       </c>
@@ -26209,7 +26230,7 @@
         <v>46259</v>
       </c>
       <c r="AH170">
-        <v>5.345205479452055</v>
+        <v>5.3452054794520549</v>
       </c>
       <c r="AI170">
         <v>30</v>
@@ -26239,7 +26260,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="171" spans="1:43">
+    <row r="171" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>165</v>
       </c>
@@ -26370,7 +26391,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="172" spans="1:43">
+    <row r="172" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>166</v>
       </c>
@@ -26471,7 +26492,7 @@
         <v>46259</v>
       </c>
       <c r="AH172">
-        <v>2.843835616438356</v>
+        <v>2.8438356164383558</v>
       </c>
       <c r="AI172">
         <v>21</v>
@@ -26501,7 +26522,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="173" spans="1:43">
+    <row r="173" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>167</v>
       </c>
@@ -26632,7 +26653,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="174" spans="1:43">
+    <row r="174" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>168</v>
       </c>
@@ -26733,7 +26754,7 @@
         <v>46259</v>
       </c>
       <c r="AH174">
-        <v>1.96986301369863</v>
+        <v>1.9698630136986299</v>
       </c>
       <c r="AI174">
         <v>21</v>
@@ -26763,7 +26784,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="175" spans="1:43">
+    <row r="175" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>169</v>
       </c>
@@ -26870,19 +26891,19 @@
         <v>21</v>
       </c>
       <c r="AJ175">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="AK175">
-        <v>241</v>
+        <v>375</v>
       </c>
       <c r="AL175">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="AM175">
         <v>0</v>
       </c>
       <c r="AN175">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="AO175" t="s">
         <v>1113</v>
@@ -26894,7 +26915,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="176" spans="1:43">
+    <row r="176" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>170</v>
       </c>
@@ -26995,7 +27016,7 @@
         <v>46259</v>
       </c>
       <c r="AH176">
-        <v>5.876712328767123</v>
+        <v>5.8767123287671232</v>
       </c>
       <c r="AI176">
         <v>30</v>
@@ -27025,7 +27046,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="177" spans="1:43">
+    <row r="177" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>171</v>
       </c>
@@ -27156,7 +27177,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="178" spans="1:43">
+    <row r="178" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>172</v>
       </c>
@@ -27257,7 +27278,7 @@
         <v>46259</v>
       </c>
       <c r="AH178">
-        <v>2.961643835616438</v>
+        <v>2.9616438356164378</v>
       </c>
       <c r="AI178">
         <v>21</v>
@@ -27287,7 +27308,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="179" spans="1:43">
+    <row r="179" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>173</v>
       </c>
@@ -27388,7 +27409,7 @@
         <v>46259</v>
       </c>
       <c r="AH179">
-        <v>2.468493150684932</v>
+        <v>2.4684931506849321</v>
       </c>
       <c r="AI179">
         <v>21</v>
@@ -27418,7 +27439,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="180" spans="1:43">
+    <row r="180" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>174</v>
       </c>
@@ -27519,7 +27540,7 @@
         <v>46259</v>
       </c>
       <c r="AH180">
-        <v>2.252054794520548</v>
+        <v>2.2520547945205478</v>
       </c>
       <c r="AI180">
         <v>21</v>
@@ -27549,7 +27570,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="181" spans="1:43">
+    <row r="181" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>175</v>
       </c>
@@ -27680,7 +27701,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="182" spans="1:43">
+    <row r="182" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>176</v>
       </c>
@@ -27811,7 +27832,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="183" spans="1:43">
+    <row r="183" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>177</v>
       </c>
@@ -27942,7 +27963,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="184" spans="1:43">
+    <row r="184" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>178</v>
       </c>
@@ -28073,7 +28094,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="185" spans="1:43">
+    <row r="185" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>179</v>
       </c>
@@ -28204,7 +28225,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="186" spans="1:43">
+    <row r="186" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>180</v>
       </c>
@@ -28305,7 +28326,7 @@
         <v>46259</v>
       </c>
       <c r="AH186">
-        <v>1.745205479452055</v>
+        <v>1.7452054794520551</v>
       </c>
       <c r="AI186">
         <v>21</v>
@@ -28335,7 +28356,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="187" spans="1:43">
+    <row r="187" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>181</v>
       </c>
@@ -28436,7 +28457,7 @@
         <v>46259</v>
       </c>
       <c r="AH187">
-        <v>1.389041095890411</v>
+        <v>1.3890410958904109</v>
       </c>
       <c r="AI187">
         <v>21</v>
@@ -28468,7 +28489,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="S170" r:id="rId1"/>
+    <hyperlink ref="S170" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Staffdata.xlsx
+++ b/Staffdata.xlsx
@@ -1,26 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3113719057d24bf/Desktop/HR-Forms-Site/HRFORMAS/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_05E48499FC67680F1964AE368160343238AA41AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF2605B4-16ED-446A-80C3-78523540B582}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -2185,7 +2174,7 @@
     <t>-</t>
   </si>
   <si>
-    <t> 966577040481</t>
+    <t xml:space="preserve"> 966577040481</t>
   </si>
   <si>
     <t>malbatil@outlook.sa</t>
@@ -2496,10 +2485,10 @@
     <t>HAMDILLHJ038@GMAIL.COM</t>
   </si>
   <si>
-    <t> omarzar392@gmail.com</t>
-  </si>
-  <si>
-    <t> ark870725@gmail.com</t>
+    <t xml:space="preserve"> omarzar392@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ark870725@gmail.com</t>
   </si>
   <si>
     <t>waelgomaa1wg@gmail.com</t>
@@ -2572,7 +2561,7 @@
     <t>INFO2@HAIL-HOUSE.SA</t>
   </si>
   <si>
-    <t> Sarah_elkhatib@outlook.com</t>
+    <t xml:space="preserve"> Sarah_elkhatib@outlook.com</t>
   </si>
   <si>
     <t xml:space="preserve"> mohannad.fakhry00@gmail.com</t>
@@ -3916,11 +3905,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3966,26 +3955,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="ارتباط تشعبي" xfId="1" builtinId="8"/>
-    <cellStyle name="عادي" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4023,7 +4004,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4057,7 +4038,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4092,10 +4072,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4268,11 +4247,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AQ187"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4403,7 +4382,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4504,7 +4483,7 @@
         <v>46259</v>
       </c>
       <c r="AH2">
-        <v>8.7260273972602747</v>
+        <v>8.726027397260275</v>
       </c>
       <c r="AI2">
         <v>30</v>
@@ -4534,7 +4513,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4635,7 +4614,7 @@
         <v>46259</v>
       </c>
       <c r="AH3">
-        <v>13.635616438356161</v>
+        <v>13.63561643835616</v>
       </c>
       <c r="AI3">
         <v>30</v>
@@ -4665,7 +4644,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4766,7 +4745,7 @@
         <v>46259</v>
       </c>
       <c r="AH4">
-        <v>5.8904109589041092</v>
+        <v>5.890410958904109</v>
       </c>
       <c r="AI4">
         <v>30</v>
@@ -4796,7 +4775,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4897,7 +4876,7 @@
         <v>46259</v>
       </c>
       <c r="AH5">
-        <v>6.0465753424657533</v>
+        <v>6.046575342465753</v>
       </c>
       <c r="AI5">
         <v>21</v>
@@ -4927,7 +4906,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5028,7 +5007,7 @@
         <v>46259</v>
       </c>
       <c r="AH6">
-        <v>6.4027397260273968</v>
+        <v>6.402739726027397</v>
       </c>
       <c r="AI6">
         <v>21</v>
@@ -5058,7 +5037,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5159,7 +5138,7 @@
         <v>46259</v>
       </c>
       <c r="AH7">
-        <v>5.7041095890410958</v>
+        <v>5.704109589041096</v>
       </c>
       <c r="AI7">
         <v>30</v>
@@ -5189,7 +5168,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5320,7 +5299,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5451,7 +5430,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5552,7 +5531,7 @@
         <v>46259</v>
       </c>
       <c r="AH10">
-        <v>6.7534246575342456</v>
+        <v>6.753424657534246</v>
       </c>
       <c r="AI10">
         <v>30</v>
@@ -5582,7 +5561,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5713,7 +5692,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5814,7 +5793,7 @@
         <v>46259</v>
       </c>
       <c r="AH12">
-        <v>5.7506849315068491</v>
+        <v>5.750684931506849</v>
       </c>
       <c r="AI12">
         <v>21</v>
@@ -5844,7 +5823,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5975,7 +5954,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6076,7 +6055,7 @@
         <v>46259</v>
       </c>
       <c r="AH14">
-        <v>0.30410958904109592</v>
+        <v>0.3041095890410959</v>
       </c>
       <c r="AI14">
         <v>21</v>
@@ -6106,7 +6085,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6207,7 +6186,7 @@
         <v>46259</v>
       </c>
       <c r="AH15">
-        <v>3.9835616438356158</v>
+        <v>3.983561643835616</v>
       </c>
       <c r="AI15">
         <v>21</v>
@@ -6237,7 +6216,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6338,7 +6317,7 @@
         <v>46259</v>
       </c>
       <c r="AH16">
-        <v>2.8986301369863008</v>
+        <v>2.898630136986301</v>
       </c>
       <c r="AI16">
         <v>21</v>
@@ -6368,7 +6347,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:43">
       <c r="A17">
         <v>16</v>
       </c>
@@ -6469,7 +6448,7 @@
         <v>46259</v>
       </c>
       <c r="AH17">
-        <v>1.6739726027397259</v>
+        <v>1.673972602739726</v>
       </c>
       <c r="AI17">
         <v>21</v>
@@ -6499,7 +6478,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:43">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6600,7 +6579,7 @@
         <v>46259</v>
       </c>
       <c r="AH18">
-        <v>2.0493150684931511</v>
+        <v>2.049315068493151</v>
       </c>
       <c r="AI18">
         <v>21</v>
@@ -6630,7 +6609,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:43">
       <c r="A19">
         <v>18</v>
       </c>
@@ -6731,7 +6710,7 @@
         <v>46259</v>
       </c>
       <c r="AH19">
-        <v>2.0356164383561639</v>
+        <v>2.035616438356164</v>
       </c>
       <c r="AI19">
         <v>21</v>
@@ -6761,7 +6740,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43">
       <c r="A20">
         <v>19</v>
       </c>
@@ -6862,7 +6841,7 @@
         <v>46259</v>
       </c>
       <c r="AH20">
-        <v>1.5123287671232879</v>
+        <v>1.512328767123288</v>
       </c>
       <c r="AI20">
         <v>21</v>
@@ -6892,7 +6871,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:43">
       <c r="A21">
         <v>20</v>
       </c>
@@ -6993,7 +6972,7 @@
         <v>46259</v>
       </c>
       <c r="AH21">
-        <v>2.0356164383561639</v>
+        <v>2.035616438356164</v>
       </c>
       <c r="AI21">
         <v>21</v>
@@ -7023,7 +7002,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43">
       <c r="A22">
         <v>21</v>
       </c>
@@ -7154,7 +7133,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:43">
       <c r="A23">
         <v>22</v>
       </c>
@@ -7285,7 +7264,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:43">
       <c r="A24">
         <v>23</v>
       </c>
@@ -7416,7 +7395,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:43">
       <c r="A25">
         <v>24</v>
       </c>
@@ -7517,7 +7496,7 @@
         <v>46259</v>
       </c>
       <c r="AH25">
-        <v>0.76164383561643834</v>
+        <v>0.7616438356164383</v>
       </c>
       <c r="AI25">
         <v>21</v>
@@ -7547,7 +7526,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:43">
       <c r="A26">
         <v>25</v>
       </c>
@@ -7648,7 +7627,7 @@
         <v>46259</v>
       </c>
       <c r="AH26">
-        <v>0.76164383561643834</v>
+        <v>0.7616438356164383</v>
       </c>
       <c r="AI26">
         <v>21</v>
@@ -7678,7 +7657,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:43">
       <c r="A27">
         <v>26</v>
       </c>
@@ -7779,7 +7758,7 @@
         <v>46259</v>
       </c>
       <c r="AH27">
-        <v>6.7369863013698632</v>
+        <v>6.736986301369863</v>
       </c>
       <c r="AI27">
         <v>30</v>
@@ -7809,7 +7788,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:43">
       <c r="A28">
         <v>27</v>
       </c>
@@ -7910,7 +7889,7 @@
         <v>46259</v>
       </c>
       <c r="AH28">
-        <v>12.112328767123291</v>
+        <v>12.11232876712329</v>
       </c>
       <c r="AI28">
         <v>30</v>
@@ -7940,7 +7919,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:43">
       <c r="A29">
         <v>28</v>
       </c>
@@ -8041,7 +8020,7 @@
         <v>46259</v>
       </c>
       <c r="AH29">
-        <v>3.4876712328767119</v>
+        <v>3.487671232876712</v>
       </c>
       <c r="AI29">
         <v>21</v>
@@ -8071,7 +8050,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:43">
       <c r="A30">
         <v>29</v>
       </c>
@@ -8172,7 +8151,7 @@
         <v>46259</v>
       </c>
       <c r="AH30">
-        <v>15.076712328767121</v>
+        <v>15.07671232876712</v>
       </c>
       <c r="AI30">
         <v>30</v>
@@ -8202,7 +8181,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:43">
       <c r="A31">
         <v>30</v>
       </c>
@@ -8303,7 +8282,7 @@
         <v>46259</v>
       </c>
       <c r="AH31">
-        <v>15.076712328767121</v>
+        <v>15.07671232876712</v>
       </c>
       <c r="AI31">
         <v>30</v>
@@ -8333,7 +8312,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:43">
       <c r="A32">
         <v>31</v>
       </c>
@@ -8464,7 +8443,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:43">
       <c r="A33">
         <v>32</v>
       </c>
@@ -8565,7 +8544,7 @@
         <v>46259</v>
       </c>
       <c r="AH33">
-        <v>15.167123287671229</v>
+        <v>15.16712328767123</v>
       </c>
       <c r="AI33">
         <v>30</v>
@@ -8595,7 +8574,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:43">
       <c r="A34">
         <v>33</v>
       </c>
@@ -8696,7 +8675,7 @@
         <v>46259</v>
       </c>
       <c r="AH34">
-        <v>4.6109589041095891</v>
+        <v>4.610958904109589</v>
       </c>
       <c r="AI34">
         <v>21</v>
@@ -8726,7 +8705,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:43">
       <c r="A35">
         <v>34</v>
       </c>
@@ -8827,7 +8806,7 @@
         <v>46259</v>
       </c>
       <c r="AH35">
-        <v>4.5424657534246577</v>
+        <v>4.542465753424658</v>
       </c>
       <c r="AI35">
         <v>21</v>
@@ -8857,7 +8836,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="36" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:43">
       <c r="A36">
         <v>35</v>
       </c>
@@ -8958,7 +8937,7 @@
         <v>46259</v>
       </c>
       <c r="AH36">
-        <v>13.241095890410961</v>
+        <v>13.24109589041096</v>
       </c>
       <c r="AI36">
         <v>30</v>
@@ -8988,7 +8967,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:43">
       <c r="A37">
         <v>36</v>
       </c>
@@ -9119,7 +9098,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:43">
       <c r="A38">
         <v>37</v>
       </c>
@@ -9250,7 +9229,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="39" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:43">
       <c r="A39">
         <v>38</v>
       </c>
@@ -9351,7 +9330,7 @@
         <v>46259</v>
       </c>
       <c r="AH39">
-        <v>6.7095890410958896</v>
+        <v>6.70958904109589</v>
       </c>
       <c r="AI39">
         <v>30</v>
@@ -9381,7 +9360,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:43">
       <c r="A40">
         <v>39</v>
       </c>
@@ -9482,7 +9461,7 @@
         <v>46259</v>
       </c>
       <c r="AH40">
-        <v>6.5095890410958903</v>
+        <v>6.50958904109589</v>
       </c>
       <c r="AI40">
         <v>30</v>
@@ -9512,7 +9491,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:43">
       <c r="A41">
         <v>40</v>
       </c>
@@ -9613,7 +9592,7 @@
         <v>46259</v>
       </c>
       <c r="AH41">
-        <v>6.5506849315068489</v>
+        <v>6.550684931506849</v>
       </c>
       <c r="AI41">
         <v>21</v>
@@ -9643,7 +9622,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:43">
       <c r="A42">
         <v>41</v>
       </c>
@@ -9774,7 +9753,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:43">
       <c r="A43">
         <v>42</v>
       </c>
@@ -9875,7 +9854,7 @@
         <v>46259</v>
       </c>
       <c r="AH43">
-        <v>8.7534246575342465</v>
+        <v>8.753424657534246</v>
       </c>
       <c r="AI43">
         <v>30</v>
@@ -9905,7 +9884,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:43">
       <c r="A44">
         <v>43</v>
       </c>
@@ -10006,7 +9985,7 @@
         <v>46259</v>
       </c>
       <c r="AH44">
-        <v>5.7534246575342456</v>
+        <v>5.753424657534246</v>
       </c>
       <c r="AI44">
         <v>21</v>
@@ -10036,7 +10015,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:43">
       <c r="A45">
         <v>44</v>
       </c>
@@ -10137,7 +10116,7 @@
         <v>46259</v>
       </c>
       <c r="AH45">
-        <v>5.7342465753424658</v>
+        <v>5.734246575342466</v>
       </c>
       <c r="AI45">
         <v>21</v>
@@ -10167,7 +10146,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:43">
       <c r="A46">
         <v>45</v>
       </c>
@@ -10268,7 +10247,7 @@
         <v>46259</v>
       </c>
       <c r="AH46">
-        <v>5.6273972602739724</v>
+        <v>5.627397260273972</v>
       </c>
       <c r="AI46">
         <v>30</v>
@@ -10298,7 +10277,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:43">
       <c r="A47">
         <v>46</v>
       </c>
@@ -10399,7 +10378,7 @@
         <v>46259</v>
       </c>
       <c r="AH47">
-        <v>4.2273972602739729</v>
+        <v>4.227397260273973</v>
       </c>
       <c r="AI47">
         <v>21</v>
@@ -10429,7 +10408,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:43">
       <c r="A48">
         <v>47</v>
       </c>
@@ -10560,7 +10539,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="49" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:43">
       <c r="A49">
         <v>48</v>
       </c>
@@ -10661,7 +10640,7 @@
         <v>46259</v>
       </c>
       <c r="AH49">
-        <v>4.1589041095890407</v>
+        <v>4.158904109589041</v>
       </c>
       <c r="AI49">
         <v>21</v>
@@ -10691,7 +10670,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="50" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:43">
       <c r="A50">
         <v>49</v>
       </c>
@@ -10792,7 +10771,7 @@
         <v>46259</v>
       </c>
       <c r="AH50">
-        <v>3.9863013698630141</v>
+        <v>3.986301369863014</v>
       </c>
       <c r="AI50">
         <v>21</v>
@@ -10822,7 +10801,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="51" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:43">
       <c r="A51">
         <v>50</v>
       </c>
@@ -10923,7 +10902,7 @@
         <v>46259</v>
       </c>
       <c r="AH51">
-        <v>3.9643835616438361</v>
+        <v>3.964383561643836</v>
       </c>
       <c r="AI51">
         <v>21</v>
@@ -10953,7 +10932,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="52" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:43">
       <c r="A52">
         <v>51</v>
       </c>
@@ -11054,7 +11033,7 @@
         <v>46259</v>
       </c>
       <c r="AH52">
-        <v>3.9643835616438361</v>
+        <v>3.964383561643836</v>
       </c>
       <c r="AI52">
         <v>21</v>
@@ -11084,7 +11063,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="53" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:43">
       <c r="A53">
         <v>52</v>
       </c>
@@ -11215,7 +11194,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="54" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:43">
       <c r="A54">
         <v>53</v>
       </c>
@@ -11316,7 +11295,7 @@
         <v>46259</v>
       </c>
       <c r="AH54">
-        <v>1.9698630136986299</v>
+        <v>1.96986301369863</v>
       </c>
       <c r="AI54">
         <v>21</v>
@@ -11346,7 +11325,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="55" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:43">
       <c r="A55">
         <v>54</v>
       </c>
@@ -11447,7 +11426,7 @@
         <v>46259</v>
       </c>
       <c r="AH55">
-        <v>0.58356164383561648</v>
+        <v>0.5835616438356165</v>
       </c>
       <c r="AI55">
         <v>21</v>
@@ -11477,7 +11456,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="56" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:43">
       <c r="A56">
         <v>55</v>
       </c>
@@ -11578,7 +11557,7 @@
         <v>46259</v>
       </c>
       <c r="AH56">
-        <v>0.58356164383561648</v>
+        <v>0.5835616438356165</v>
       </c>
       <c r="AI56">
         <v>21</v>
@@ -11608,7 +11587,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="57" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:43">
       <c r="A57">
         <v>56</v>
       </c>
@@ -11709,7 +11688,7 @@
         <v>46259</v>
       </c>
       <c r="AH57">
-        <v>7.1506849315068486</v>
+        <v>7.150684931506849</v>
       </c>
       <c r="AI57">
         <v>30</v>
@@ -11739,7 +11718,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="58" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:43">
       <c r="A58">
         <v>57</v>
       </c>
@@ -11840,7 +11819,7 @@
         <v>46259</v>
       </c>
       <c r="AH58">
-        <v>7.4821917808219176</v>
+        <v>7.482191780821918</v>
       </c>
       <c r="AI58">
         <v>30</v>
@@ -11870,7 +11849,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="59" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:43">
       <c r="A59">
         <v>58</v>
       </c>
@@ -11971,7 +11950,7 @@
         <v>46259</v>
       </c>
       <c r="AH59">
-        <v>6.575342465753424E-2</v>
+        <v>0.06575342465753424</v>
       </c>
       <c r="AI59">
         <v>21</v>
@@ -12001,7 +11980,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="60" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:43">
       <c r="A60">
         <v>59</v>
       </c>
@@ -12102,7 +12081,7 @@
         <v>46259</v>
       </c>
       <c r="AH60">
-        <v>6.575342465753424E-2</v>
+        <v>0.06575342465753424</v>
       </c>
       <c r="AI60">
         <v>21</v>
@@ -12132,7 +12111,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="61" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:43">
       <c r="A61">
         <v>58</v>
       </c>
@@ -12233,7 +12212,7 @@
         <v>46259</v>
       </c>
       <c r="AH61">
-        <v>18.263013698630139</v>
+        <v>18.26301369863014</v>
       </c>
       <c r="AI61">
         <v>30</v>
@@ -12263,7 +12242,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="62" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:43">
       <c r="A62">
         <v>59</v>
       </c>
@@ -12364,7 +12343,7 @@
         <v>46259</v>
       </c>
       <c r="AH62">
-        <v>15.076712328767121</v>
+        <v>15.07671232876712</v>
       </c>
       <c r="AI62">
         <v>30</v>
@@ -12394,7 +12373,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="63" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:43">
       <c r="A63">
         <v>60</v>
       </c>
@@ -12495,7 +12474,7 @@
         <v>46259</v>
       </c>
       <c r="AH63">
-        <v>34.049315068493151</v>
+        <v>34.04931506849315</v>
       </c>
       <c r="AI63">
         <v>30</v>
@@ -12525,7 +12504,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="64" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:43">
       <c r="A64">
         <v>61</v>
       </c>
@@ -12626,7 +12605,7 @@
         <v>46259</v>
       </c>
       <c r="AH64">
-        <v>6.1753424657534248</v>
+        <v>6.175342465753425</v>
       </c>
       <c r="AI64">
         <v>30</v>
@@ -12656,7 +12635,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="65" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:43">
       <c r="A65">
         <v>62</v>
       </c>
@@ -12757,7 +12736,7 @@
         <v>46259</v>
       </c>
       <c r="AH65">
-        <v>1.8739726027397261</v>
+        <v>1.873972602739726</v>
       </c>
       <c r="AI65">
         <v>21</v>
@@ -12787,7 +12766,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="66" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:43">
       <c r="A66">
         <v>63</v>
       </c>
@@ -12888,7 +12867,7 @@
         <v>46259</v>
       </c>
       <c r="AH66">
-        <v>5.7534246575342456</v>
+        <v>5.753424657534246</v>
       </c>
       <c r="AI66">
         <v>21</v>
@@ -12918,7 +12897,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="67" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:43">
       <c r="A67">
         <v>64</v>
       </c>
@@ -13019,7 +12998,7 @@
         <v>46259</v>
       </c>
       <c r="AH67">
-        <v>18.046575342465751</v>
+        <v>18.04657534246575</v>
       </c>
       <c r="AI67">
         <v>30</v>
@@ -13049,7 +13028,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="68" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:43">
       <c r="A68">
         <v>65</v>
       </c>
@@ -13150,7 +13129,7 @@
         <v>46259</v>
       </c>
       <c r="AH68">
-        <v>9.5315068493150683</v>
+        <v>9.531506849315068</v>
       </c>
       <c r="AI68">
         <v>30</v>
@@ -13180,7 +13159,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="69" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:43">
       <c r="A69">
         <v>66</v>
       </c>
@@ -13311,7 +13290,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="70" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:43">
       <c r="A70">
         <v>67</v>
       </c>
@@ -13412,7 +13391,7 @@
         <v>46259</v>
       </c>
       <c r="AH70">
-        <v>10.608219178082191</v>
+        <v>10.60821917808219</v>
       </c>
       <c r="AI70">
         <v>30</v>
@@ -13442,7 +13421,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="71" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:43">
       <c r="A71">
         <v>68</v>
       </c>
@@ -13543,7 +13522,7 @@
         <v>46259</v>
       </c>
       <c r="AH71">
-        <v>0.33424657534246582</v>
+        <v>0.3342465753424658</v>
       </c>
       <c r="AI71">
         <v>21</v>
@@ -13573,7 +13552,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="72" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:43">
       <c r="A72">
         <v>69</v>
       </c>
@@ -13674,7 +13653,7 @@
         <v>46259</v>
       </c>
       <c r="AH72">
-        <v>0.33424657534246582</v>
+        <v>0.3342465753424658</v>
       </c>
       <c r="AI72">
         <v>21</v>
@@ -13704,7 +13683,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="73" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:43">
       <c r="A73">
         <v>70</v>
       </c>
@@ -13805,7 +13784,7 @@
         <v>46259</v>
       </c>
       <c r="AH73">
-        <v>2.9698630136986299</v>
+        <v>2.96986301369863</v>
       </c>
       <c r="AI73">
         <v>21</v>
@@ -13835,7 +13814,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="74" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:43">
       <c r="A74">
         <v>71</v>
       </c>
@@ -13966,7 +13945,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="75" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:43">
       <c r="A75">
         <v>72</v>
       </c>
@@ -14067,7 +14046,7 @@
         <v>46259</v>
       </c>
       <c r="AH75">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="AI75">
         <v>21</v>
@@ -14097,7 +14076,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="76" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:43">
       <c r="A76">
         <v>73</v>
       </c>
@@ -14198,7 +14177,7 @@
         <v>46259</v>
       </c>
       <c r="AH76">
-        <v>4.0684931506849313</v>
+        <v>4.068493150684931</v>
       </c>
       <c r="AI76">
         <v>21</v>
@@ -14228,7 +14207,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="77" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:43">
       <c r="A77">
         <v>74</v>
       </c>
@@ -14359,7 +14338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="78" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:43">
       <c r="A78">
         <v>75</v>
       </c>
@@ -14490,7 +14469,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="79" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:43">
       <c r="A79">
         <v>76</v>
       </c>
@@ -14591,7 +14570,7 @@
         <v>46259</v>
       </c>
       <c r="AH79">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
       <c r="AI79">
         <v>21</v>
@@ -14621,7 +14600,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="80" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:43">
       <c r="A80">
         <v>77</v>
       </c>
@@ -14722,7 +14701,7 @@
         <v>46259</v>
       </c>
       <c r="AH80">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
       <c r="AI80">
         <v>21</v>
@@ -14752,7 +14731,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="81" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:43">
       <c r="A81">
         <v>78</v>
       </c>
@@ -14853,7 +14832,7 @@
         <v>46259</v>
       </c>
       <c r="AH81">
-        <v>1.8191780821917809</v>
+        <v>1.819178082191781</v>
       </c>
       <c r="AI81">
         <v>21</v>
@@ -14883,7 +14862,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="82" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:43">
       <c r="A82">
         <v>79</v>
       </c>
@@ -14984,7 +14963,7 @@
         <v>46259</v>
       </c>
       <c r="AH82">
-        <v>1.6547945205479451</v>
+        <v>1.654794520547945</v>
       </c>
       <c r="AI82">
         <v>21</v>
@@ -15014,7 +14993,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="83" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:43">
       <c r="A83">
         <v>80</v>
       </c>
@@ -15115,7 +15094,7 @@
         <v>46259</v>
       </c>
       <c r="AH83">
-        <v>15.167123287671229</v>
+        <v>15.16712328767123</v>
       </c>
       <c r="AI83">
         <v>30</v>
@@ -15145,7 +15124,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="84" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:43">
       <c r="A84">
         <v>80</v>
       </c>
@@ -15186,7 +15165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:43">
       <c r="A85">
         <v>81</v>
       </c>
@@ -15287,7 +15266,7 @@
         <v>46259</v>
       </c>
       <c r="AH85">
-        <v>8.9753424657534246</v>
+        <v>8.975342465753425</v>
       </c>
       <c r="AI85">
         <v>30</v>
@@ -15317,7 +15296,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="86" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:43">
       <c r="A86">
         <v>82</v>
       </c>
@@ -15418,7 +15397,7 @@
         <v>46259</v>
       </c>
       <c r="AH86">
-        <v>6.7095890410958896</v>
+        <v>6.70958904109589</v>
       </c>
       <c r="AI86">
         <v>30</v>
@@ -15448,7 +15427,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="87" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:43">
       <c r="A87">
         <v>83</v>
       </c>
@@ -15549,7 +15528,7 @@
         <v>46259</v>
       </c>
       <c r="AH87">
-        <v>9.3232876712328761</v>
+        <v>9.323287671232876</v>
       </c>
       <c r="AI87">
         <v>30</v>
@@ -15579,7 +15558,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="88" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:43">
       <c r="A88">
         <v>84</v>
       </c>
@@ -15680,7 +15659,7 @@
         <v>46259</v>
       </c>
       <c r="AH88">
-        <v>14.035616438356159</v>
+        <v>14.03561643835616</v>
       </c>
       <c r="AI88">
         <v>30</v>
@@ -15710,7 +15689,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="89" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:43">
       <c r="A89">
         <v>85</v>
       </c>
@@ -15811,7 +15790,7 @@
         <v>46259</v>
       </c>
       <c r="AH89">
-        <v>1.7726027397260271</v>
+        <v>1.772602739726027</v>
       </c>
       <c r="AI89">
         <v>21</v>
@@ -15841,7 +15820,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="90" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:43">
       <c r="A90">
         <v>86</v>
       </c>
@@ -15942,7 +15921,7 @@
         <v>46259</v>
       </c>
       <c r="AH90">
-        <v>8.4082191780821915</v>
+        <v>8.408219178082192</v>
       </c>
       <c r="AI90">
         <v>30</v>
@@ -15972,7 +15951,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="91" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:43">
       <c r="A91">
         <v>87</v>
       </c>
@@ -16073,7 +16052,7 @@
         <v>46259</v>
       </c>
       <c r="AH91">
-        <v>10.950684931506849</v>
+        <v>10.95068493150685</v>
       </c>
       <c r="AI91">
         <v>30</v>
@@ -16103,7 +16082,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="92" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:43">
       <c r="A92">
         <v>88</v>
       </c>
@@ -16204,7 +16183,7 @@
         <v>46259</v>
       </c>
       <c r="AH92">
-        <v>6.6821917808219178</v>
+        <v>6.682191780821918</v>
       </c>
       <c r="AI92">
         <v>21</v>
@@ -16234,7 +16213,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="93" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:43">
       <c r="A93">
         <v>89</v>
       </c>
@@ -16335,7 +16314,7 @@
         <v>46259</v>
       </c>
       <c r="AH93">
-        <v>5.6273972602739724</v>
+        <v>5.627397260273972</v>
       </c>
       <c r="AI93">
         <v>21</v>
@@ -16365,7 +16344,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="94" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:43">
       <c r="A94">
         <v>90</v>
       </c>
@@ -16466,7 +16445,7 @@
         <v>46259</v>
       </c>
       <c r="AH94">
-        <v>5.3150684931506849</v>
+        <v>5.315068493150685</v>
       </c>
       <c r="AI94">
         <v>30</v>
@@ -16496,7 +16475,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="95" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:43">
       <c r="A95">
         <v>91</v>
       </c>
@@ -16597,7 +16576,7 @@
         <v>46259</v>
       </c>
       <c r="AH95">
-        <v>5.0602739726027401</v>
+        <v>5.06027397260274</v>
       </c>
       <c r="AI95">
         <v>30</v>
@@ -16627,7 +16606,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="96" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:43">
       <c r="A96">
         <v>92</v>
       </c>
@@ -16728,7 +16707,7 @@
         <v>46259</v>
       </c>
       <c r="AH96">
-        <v>5.0602739726027401</v>
+        <v>5.06027397260274</v>
       </c>
       <c r="AI96">
         <v>21</v>
@@ -16758,7 +16737,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="97" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:43">
       <c r="A97">
         <v>93</v>
       </c>
@@ -16859,7 +16838,7 @@
         <v>46259</v>
       </c>
       <c r="AH97">
-        <v>4.7534246575342456</v>
+        <v>4.753424657534246</v>
       </c>
       <c r="AI97">
         <v>21</v>
@@ -16889,7 +16868,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="98" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:43">
       <c r="A98">
         <v>94</v>
       </c>
@@ -16990,7 +16969,7 @@
         <v>46259</v>
       </c>
       <c r="AH98">
-        <v>0.58356164383561648</v>
+        <v>0.5835616438356165</v>
       </c>
       <c r="AI98">
         <v>21</v>
@@ -17020,7 +16999,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="99" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:43">
       <c r="A99">
         <v>95</v>
       </c>
@@ -17121,7 +17100,7 @@
         <v>46259</v>
       </c>
       <c r="AH99">
-        <v>0.58356164383561648</v>
+        <v>0.5835616438356165</v>
       </c>
       <c r="AI99">
         <v>21</v>
@@ -17151,7 +17130,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="100" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:43">
       <c r="A100">
         <v>96</v>
       </c>
@@ -17252,7 +17231,7 @@
         <v>46259</v>
       </c>
       <c r="AH100">
-        <v>4.7397260273972606</v>
+        <v>4.739726027397261</v>
       </c>
       <c r="AI100">
         <v>21</v>
@@ -17282,7 +17261,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="101" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:43">
       <c r="A101">
         <v>97</v>
       </c>
@@ -17383,7 +17362,7 @@
         <v>46259</v>
       </c>
       <c r="AH101">
-        <v>4.6794520547945204</v>
+        <v>4.67945205479452</v>
       </c>
       <c r="AI101">
         <v>21</v>
@@ -17413,7 +17392,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="102" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:43">
       <c r="A102">
         <v>98</v>
       </c>
@@ -17514,7 +17493,7 @@
         <v>46259</v>
       </c>
       <c r="AH102">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="AI102">
         <v>21</v>
@@ -17544,7 +17523,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="103" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:43">
       <c r="A103">
         <v>99</v>
       </c>
@@ -17645,7 +17624,7 @@
         <v>46259</v>
       </c>
       <c r="AH103">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="AI103">
         <v>21</v>
@@ -17675,7 +17654,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="104" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:43">
       <c r="A104">
         <v>100</v>
       </c>
@@ -17776,7 +17755,7 @@
         <v>46259</v>
       </c>
       <c r="AH104">
-        <v>3.9643835616438361</v>
+        <v>3.964383561643836</v>
       </c>
       <c r="AI104">
         <v>21</v>
@@ -17806,7 +17785,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="105" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:43">
       <c r="A105">
         <v>101</v>
       </c>
@@ -17907,7 +17886,7 @@
         <v>46259</v>
       </c>
       <c r="AH105">
-        <v>7.5232876712328771</v>
+        <v>7.523287671232877</v>
       </c>
       <c r="AI105">
         <v>30</v>
@@ -17937,7 +17916,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="106" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:43">
       <c r="A106">
         <v>102</v>
       </c>
@@ -18038,7 +18017,7 @@
         <v>46259</v>
       </c>
       <c r="AH106">
-        <v>4.9726027397260273</v>
+        <v>4.972602739726027</v>
       </c>
       <c r="AI106">
         <v>21</v>
@@ -18068,7 +18047,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="107" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:43">
       <c r="A107">
         <v>103</v>
       </c>
@@ -18169,7 +18148,7 @@
         <v>46259</v>
       </c>
       <c r="AH107">
-        <v>1.9698630136986299</v>
+        <v>1.96986301369863</v>
       </c>
       <c r="AI107">
         <v>21</v>
@@ -18199,7 +18178,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="108" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:43">
       <c r="A108">
         <v>104</v>
       </c>
@@ -18300,7 +18279,7 @@
         <v>46259</v>
       </c>
       <c r="AH108">
-        <v>22.446575342465749</v>
+        <v>22.44657534246575</v>
       </c>
       <c r="AI108">
         <v>30</v>
@@ -18330,7 +18309,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="109" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:43">
       <c r="A109">
         <v>105</v>
       </c>
@@ -18431,7 +18410,7 @@
         <v>46259</v>
       </c>
       <c r="AH109">
-        <v>3.9863013698630141</v>
+        <v>3.986301369863014</v>
       </c>
       <c r="AI109">
         <v>21</v>
@@ -18461,7 +18440,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="110" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:43">
       <c r="A110">
         <v>106</v>
       </c>
@@ -18514,7 +18493,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="111" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:43">
       <c r="A111">
         <v>107</v>
       </c>
@@ -18615,7 +18594,7 @@
         <v>46259</v>
       </c>
       <c r="AH111">
-        <v>0.35890410958904112</v>
+        <v>0.3589041095890411</v>
       </c>
       <c r="AI111">
         <v>21</v>
@@ -18645,7 +18624,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="112" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:43">
       <c r="A112">
         <v>108</v>
       </c>
@@ -18746,7 +18725,7 @@
         <v>46259</v>
       </c>
       <c r="AH112">
-        <v>5.3726027397260276</v>
+        <v>5.372602739726028</v>
       </c>
       <c r="AI112">
         <v>21</v>
@@ -18776,7 +18755,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="113" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:43">
       <c r="A113">
         <v>109</v>
       </c>
@@ -18877,7 +18856,7 @@
         <v>46259</v>
       </c>
       <c r="AH113">
-        <v>4.5287671232876709</v>
+        <v>4.528767123287671</v>
       </c>
       <c r="AI113">
         <v>21</v>
@@ -18907,7 +18886,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="114" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:43">
       <c r="A114">
         <v>110</v>
       </c>
@@ -19008,7 +18987,7 @@
         <v>46259</v>
       </c>
       <c r="AH114">
-        <v>4.5835616438356164</v>
+        <v>4.583561643835616</v>
       </c>
       <c r="AI114">
         <v>21</v>
@@ -19038,7 +19017,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="115" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:43">
       <c r="A115">
         <v>111</v>
       </c>
@@ -19139,7 +19118,7 @@
         <v>46259</v>
       </c>
       <c r="AH115">
-        <v>4.5260273972602736</v>
+        <v>4.526027397260274</v>
       </c>
       <c r="AI115">
         <v>21</v>
@@ -19169,7 +19148,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="116" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:43">
       <c r="A116">
         <v>112</v>
       </c>
@@ -19270,7 +19249,7 @@
         <v>46259</v>
       </c>
       <c r="AH116">
-        <v>4.5287671232876709</v>
+        <v>4.528767123287671</v>
       </c>
       <c r="AI116">
         <v>21</v>
@@ -19300,7 +19279,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="117" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:43">
       <c r="B117">
         <v>1336</v>
       </c>
@@ -19428,7 +19407,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="118" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:43">
       <c r="A118">
         <v>113</v>
       </c>
@@ -19559,7 +19538,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="119" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:43">
       <c r="A119">
         <v>114</v>
       </c>
@@ -19660,7 +19639,7 @@
         <v>46259</v>
       </c>
       <c r="AH119">
-        <v>2.6301369863013702</v>
+        <v>2.63013698630137</v>
       </c>
       <c r="AI119">
         <v>21</v>
@@ -19690,7 +19669,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="120" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:43">
       <c r="A120">
         <v>115</v>
       </c>
@@ -19791,7 +19770,7 @@
         <v>46259</v>
       </c>
       <c r="AH120">
-        <v>2.4109589041095889</v>
+        <v>2.410958904109589</v>
       </c>
       <c r="AI120">
         <v>21</v>
@@ -19821,7 +19800,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="121" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:43">
       <c r="A121">
         <v>116</v>
       </c>
@@ -19952,7 +19931,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="122" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:43">
       <c r="A122">
         <v>117</v>
       </c>
@@ -20083,7 +20062,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="123" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:43">
       <c r="A123">
         <v>118</v>
       </c>
@@ -20214,7 +20193,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="124" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:43">
       <c r="A124">
         <v>119</v>
       </c>
@@ -20315,7 +20294,7 @@
         <v>46259</v>
       </c>
       <c r="AH124">
-        <v>2.2630136986301368</v>
+        <v>2.263013698630137</v>
       </c>
       <c r="AI124">
         <v>21</v>
@@ -20345,7 +20324,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="125" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:43">
       <c r="A125">
         <v>120</v>
       </c>
@@ -20446,7 +20425,7 @@
         <v>46259</v>
       </c>
       <c r="AH125">
-        <v>6.5863013698630137</v>
+        <v>6.586301369863014</v>
       </c>
       <c r="AI125">
         <v>30</v>
@@ -20476,7 +20455,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="126" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:43">
       <c r="A126">
         <v>120</v>
       </c>
@@ -20499,7 +20478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:43">
       <c r="A127">
         <v>121</v>
       </c>
@@ -20600,7 +20579,7 @@
         <v>46259</v>
       </c>
       <c r="AH127">
-        <v>12.265753424657531</v>
+        <v>12.26575342465753</v>
       </c>
       <c r="AI127">
         <v>30</v>
@@ -20630,7 +20609,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="128" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:43">
       <c r="A128">
         <v>122</v>
       </c>
@@ -20731,7 +20710,7 @@
         <v>46259</v>
       </c>
       <c r="AH128">
-        <v>5.9643835616438352</v>
+        <v>5.964383561643835</v>
       </c>
       <c r="AI128">
         <v>30</v>
@@ -20761,7 +20740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:43">
       <c r="A129">
         <v>123</v>
       </c>
@@ -20862,7 +20841,7 @@
         <v>46259</v>
       </c>
       <c r="AH129">
-        <v>5.7972602739726016</v>
+        <v>5.797260273972602</v>
       </c>
       <c r="AI129">
         <v>21</v>
@@ -20892,7 +20871,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="130" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:43">
       <c r="A130">
         <v>124</v>
       </c>
@@ -20993,7 +20972,7 @@
         <v>46259</v>
       </c>
       <c r="AH130">
-        <v>5.1534246575342468</v>
+        <v>5.153424657534247</v>
       </c>
       <c r="AI130">
         <v>30</v>
@@ -21023,7 +21002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:43">
       <c r="A131">
         <v>125</v>
       </c>
@@ -21124,7 +21103,7 @@
         <v>46259</v>
       </c>
       <c r="AH131">
-        <v>5.1780821917808222</v>
+        <v>5.178082191780822</v>
       </c>
       <c r="AI131">
         <v>30</v>
@@ -21154,7 +21133,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="132" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:43">
       <c r="B132">
         <v>1135</v>
       </c>
@@ -21252,7 +21231,7 @@
         <v>46259</v>
       </c>
       <c r="AH132">
-        <v>0.15068493150684931</v>
+        <v>0.1506849315068493</v>
       </c>
       <c r="AI132">
         <v>21</v>
@@ -21282,7 +21261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:43">
       <c r="A133">
         <v>126</v>
       </c>
@@ -21383,7 +21362,7 @@
         <v>46259</v>
       </c>
       <c r="AH133">
-        <v>4.2356164383561641</v>
+        <v>4.235616438356164</v>
       </c>
       <c r="AI133">
         <v>21</v>
@@ -21413,7 +21392,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="134" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:43">
       <c r="A134">
         <v>127</v>
       </c>
@@ -21514,7 +21493,7 @@
         <v>46259</v>
       </c>
       <c r="AH134">
-        <v>4.2356164383561641</v>
+        <v>4.235616438356164</v>
       </c>
       <c r="AI134">
         <v>21</v>
@@ -21544,7 +21523,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="135" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:43">
       <c r="A135">
         <v>128</v>
       </c>
@@ -21645,7 +21624,7 @@
         <v>46259</v>
       </c>
       <c r="AH135">
-        <v>4.7232876712328764</v>
+        <v>4.723287671232876</v>
       </c>
       <c r="AI135">
         <v>21</v>
@@ -21675,7 +21654,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="136" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:43">
       <c r="A136">
         <v>129</v>
       </c>
@@ -21776,7 +21755,7 @@
         <v>46259</v>
       </c>
       <c r="AH136">
-        <v>4.2904109589041104</v>
+        <v>4.29041095890411</v>
       </c>
       <c r="AI136">
         <v>21</v>
@@ -21806,7 +21785,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="137" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:43">
       <c r="A137">
         <v>130</v>
       </c>
@@ -21907,7 +21886,7 @@
         <v>46259</v>
       </c>
       <c r="AH137">
-        <v>4.5534246575342463</v>
+        <v>4.553424657534246</v>
       </c>
       <c r="AI137">
         <v>21</v>
@@ -21937,7 +21916,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="138" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:43">
       <c r="A138">
         <v>131</v>
       </c>
@@ -22038,7 +22017,7 @@
         <v>46259</v>
       </c>
       <c r="AH138">
-        <v>1.4986301369863011</v>
+        <v>1.498630136986301</v>
       </c>
       <c r="AI138">
         <v>21</v>
@@ -22068,7 +22047,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="139" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:43">
       <c r="A139">
         <v>132</v>
       </c>
@@ -22199,7 +22178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:43">
       <c r="A140">
         <v>133</v>
       </c>
@@ -22330,7 +22309,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="141" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:43">
       <c r="A141">
         <v>134</v>
       </c>
@@ -22461,7 +22440,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="142" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:43">
       <c r="A142">
         <v>135</v>
       </c>
@@ -22592,7 +22571,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="143" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:43">
       <c r="A143">
         <v>136</v>
       </c>
@@ -22693,7 +22672,7 @@
         <v>46259</v>
       </c>
       <c r="AH143">
-        <v>4.4876712328767123</v>
+        <v>4.487671232876712</v>
       </c>
       <c r="AI143">
         <v>21</v>
@@ -22723,7 +22702,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="144" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:43">
       <c r="A144">
         <v>137</v>
       </c>
@@ -22824,7 +22803,7 @@
         <v>46259</v>
       </c>
       <c r="AH144">
-        <v>4.4684931506849317</v>
+        <v>4.468493150684932</v>
       </c>
       <c r="AI144">
         <v>21</v>
@@ -22854,7 +22833,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="145" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:43">
       <c r="A145">
         <v>138</v>
       </c>
@@ -22955,7 +22934,7 @@
         <v>46259</v>
       </c>
       <c r="AH145">
-        <v>1.8575342465753419</v>
+        <v>1.857534246575342</v>
       </c>
       <c r="AI145">
         <v>21</v>
@@ -22985,7 +22964,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="146" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:43">
       <c r="A146">
         <v>139</v>
       </c>
@@ -23086,7 +23065,7 @@
         <v>46259</v>
       </c>
       <c r="AH146">
-        <v>4.3890410958904109</v>
+        <v>4.389041095890411</v>
       </c>
       <c r="AI146">
         <v>21</v>
@@ -23116,7 +23095,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="147" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:43">
       <c r="A147">
         <v>140</v>
       </c>
@@ -23217,7 +23196,7 @@
         <v>46259</v>
       </c>
       <c r="AH147">
-        <v>3.7917808219178082</v>
+        <v>3.791780821917808</v>
       </c>
       <c r="AI147">
         <v>21</v>
@@ -23247,7 +23226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:43">
       <c r="A148">
         <v>141</v>
       </c>
@@ -23348,7 +23327,7 @@
         <v>46259</v>
       </c>
       <c r="AH148">
-        <v>3.7863013698630139</v>
+        <v>3.786301369863014</v>
       </c>
       <c r="AI148">
         <v>21</v>
@@ -23378,7 +23357,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="149" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:43">
       <c r="A149">
         <v>142</v>
       </c>
@@ -23479,7 +23458,7 @@
         <v>46259</v>
       </c>
       <c r="AH149">
-        <v>3.7369863013698632</v>
+        <v>3.736986301369863</v>
       </c>
       <c r="AI149">
         <v>21</v>
@@ -23509,7 +23488,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="150" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:43">
       <c r="A150">
         <v>143</v>
       </c>
@@ -23610,7 +23589,7 @@
         <v>46259</v>
       </c>
       <c r="AH150">
-        <v>2.5452054794520551</v>
+        <v>2.545205479452055</v>
       </c>
       <c r="AI150">
         <v>21</v>
@@ -23640,7 +23619,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="151" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:43">
       <c r="A151">
         <v>144</v>
       </c>
@@ -23741,7 +23720,7 @@
         <v>46259</v>
       </c>
       <c r="AH151">
-        <v>5.9671232876712326</v>
+        <v>5.967123287671233</v>
       </c>
       <c r="AI151">
         <v>21</v>
@@ -23771,7 +23750,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="152" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:43">
       <c r="A152">
         <v>145</v>
       </c>
@@ -23872,7 +23851,7 @@
         <v>46259</v>
       </c>
       <c r="AH152">
-        <v>3.1013698630136992</v>
+        <v>3.101369863013699</v>
       </c>
       <c r="AI152">
         <v>21</v>
@@ -23902,7 +23881,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="153" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:43">
       <c r="A153">
         <v>146</v>
       </c>
@@ -24003,7 +23982,7 @@
         <v>46259</v>
       </c>
       <c r="AH153">
-        <v>5.6493150684931503</v>
+        <v>5.64931506849315</v>
       </c>
       <c r="AI153">
         <v>21</v>
@@ -24033,7 +24012,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="154" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:43">
       <c r="A154">
         <v>147</v>
       </c>
@@ -24134,7 +24113,7 @@
         <v>46259</v>
       </c>
       <c r="AH154">
-        <v>5.4027397260273968</v>
+        <v>5.402739726027397</v>
       </c>
       <c r="AI154">
         <v>21</v>
@@ -24164,7 +24143,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="155" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:43">
       <c r="A155">
         <v>148</v>
       </c>
@@ -24265,7 +24244,7 @@
         <v>46259</v>
       </c>
       <c r="AH155">
-        <v>5.3095890410958901</v>
+        <v>5.30958904109589</v>
       </c>
       <c r="AI155">
         <v>21</v>
@@ -24295,7 +24274,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="156" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:43">
       <c r="A156">
         <v>149</v>
       </c>
@@ -24396,7 +24375,7 @@
         <v>46259</v>
       </c>
       <c r="AH156">
-        <v>5.0383561643835613</v>
+        <v>5.038356164383561</v>
       </c>
       <c r="AI156">
         <v>21</v>
@@ -24426,7 +24405,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="157" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:43">
       <c r="A157">
         <v>150</v>
       </c>
@@ -24527,7 +24506,7 @@
         <v>46259</v>
       </c>
       <c r="AH157">
-        <v>5.0383561643835613</v>
+        <v>5.038356164383561</v>
       </c>
       <c r="AI157">
         <v>21</v>
@@ -24557,7 +24536,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="158" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:43">
       <c r="A158">
         <v>151</v>
       </c>
@@ -24658,7 +24637,7 @@
         <v>46259</v>
       </c>
       <c r="AH158">
-        <v>5.0383561643835613</v>
+        <v>5.038356164383561</v>
       </c>
       <c r="AI158">
         <v>21</v>
@@ -24688,7 +24667,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="159" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:43">
       <c r="A159">
         <v>152</v>
       </c>
@@ -24789,7 +24768,7 @@
         <v>46259</v>
       </c>
       <c r="AH159">
-        <v>5.0383561643835613</v>
+        <v>5.038356164383561</v>
       </c>
       <c r="AI159">
         <v>21</v>
@@ -24819,7 +24798,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="160" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:43">
       <c r="A160">
         <v>153</v>
       </c>
@@ -24920,7 +24899,7 @@
         <v>46259</v>
       </c>
       <c r="AH160">
-        <v>1.8301369863013699</v>
+        <v>1.83013698630137</v>
       </c>
       <c r="AI160">
         <v>21</v>
@@ -24950,7 +24929,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="161" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:43">
       <c r="A161">
         <v>154</v>
       </c>
@@ -25051,7 +25030,7 @@
         <v>46259</v>
       </c>
       <c r="AH161">
-        <v>4.5287671232876709</v>
+        <v>4.528767123287671</v>
       </c>
       <c r="AI161">
         <v>21</v>
@@ -25081,7 +25060,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="162" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:43">
       <c r="A162">
         <v>155</v>
       </c>
@@ -25182,7 +25161,7 @@
         <v>46259</v>
       </c>
       <c r="AH162">
-        <v>4.3890410958904109</v>
+        <v>4.389041095890411</v>
       </c>
       <c r="AI162">
         <v>21</v>
@@ -25212,7 +25191,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="163" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:43">
       <c r="A163">
         <v>156</v>
       </c>
@@ -25313,7 +25292,7 @@
         <v>46259</v>
       </c>
       <c r="AH163">
-        <v>4.3890410958904109</v>
+        <v>4.389041095890411</v>
       </c>
       <c r="AI163">
         <v>21</v>
@@ -25343,7 +25322,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="164" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:43">
       <c r="A164">
         <v>157</v>
       </c>
@@ -25474,7 +25453,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="165" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:43">
       <c r="A165">
         <v>158</v>
       </c>
@@ -25575,7 +25554,7 @@
         <v>46259</v>
       </c>
       <c r="AH165">
-        <v>3.9945205479452048</v>
+        <v>3.994520547945205</v>
       </c>
       <c r="AI165">
         <v>21</v>
@@ -25605,7 +25584,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="166" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:43">
       <c r="A166">
         <v>159</v>
       </c>
@@ -25706,7 +25685,7 @@
         <v>46259</v>
       </c>
       <c r="AH166">
-        <v>3.9643835616438361</v>
+        <v>3.964383561643836</v>
       </c>
       <c r="AI166">
         <v>21</v>
@@ -25736,7 +25715,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="167" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:43">
       <c r="A167">
         <v>161</v>
       </c>
@@ -25837,7 +25816,7 @@
         <v>46259</v>
       </c>
       <c r="AH167">
-        <v>2.3397260273972602</v>
+        <v>2.33972602739726</v>
       </c>
       <c r="AI167">
         <v>21</v>
@@ -25867,7 +25846,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="168" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:43">
       <c r="A168">
         <v>162</v>
       </c>
@@ -25968,7 +25947,7 @@
         <v>46259</v>
       </c>
       <c r="AH168">
-        <v>13.547945205479451</v>
+        <v>13.54794520547945</v>
       </c>
       <c r="AI168">
         <v>30</v>
@@ -25998,7 +25977,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="169" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:43">
       <c r="A169">
         <v>163</v>
       </c>
@@ -26099,7 +26078,7 @@
         <v>46259</v>
       </c>
       <c r="AH169">
-        <v>5.1534246575342468</v>
+        <v>5.153424657534247</v>
       </c>
       <c r="AI169">
         <v>30</v>
@@ -26129,7 +26108,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="170" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:43">
       <c r="A170">
         <v>164</v>
       </c>
@@ -26230,7 +26209,7 @@
         <v>46259</v>
       </c>
       <c r="AH170">
-        <v>5.3452054794520549</v>
+        <v>5.345205479452055</v>
       </c>
       <c r="AI170">
         <v>30</v>
@@ -26260,7 +26239,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="171" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:43">
       <c r="A171">
         <v>165</v>
       </c>
@@ -26391,7 +26370,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="172" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:43">
       <c r="A172">
         <v>166</v>
       </c>
@@ -26492,7 +26471,7 @@
         <v>46259</v>
       </c>
       <c r="AH172">
-        <v>2.8438356164383558</v>
+        <v>2.843835616438356</v>
       </c>
       <c r="AI172">
         <v>21</v>
@@ -26522,7 +26501,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="173" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:43">
       <c r="A173">
         <v>167</v>
       </c>
@@ -26653,7 +26632,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="174" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:43">
       <c r="A174">
         <v>168</v>
       </c>
@@ -26754,7 +26733,7 @@
         <v>46259</v>
       </c>
       <c r="AH174">
-        <v>1.9698630136986299</v>
+        <v>1.96986301369863</v>
       </c>
       <c r="AI174">
         <v>21</v>
@@ -26784,7 +26763,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="175" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:43">
       <c r="A175">
         <v>169</v>
       </c>
@@ -26891,19 +26870,19 @@
         <v>21</v>
       </c>
       <c r="AJ175">
-        <v>975</v>
+        <v>963</v>
       </c>
       <c r="AK175">
-        <v>375</v>
+        <v>241</v>
       </c>
       <c r="AL175">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="AM175">
         <v>0</v>
       </c>
       <c r="AN175">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="AO175" t="s">
         <v>1113</v>
@@ -26915,7 +26894,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="176" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:43">
       <c r="A176">
         <v>170</v>
       </c>
@@ -27016,7 +26995,7 @@
         <v>46259</v>
       </c>
       <c r="AH176">
-        <v>5.8767123287671232</v>
+        <v>5.876712328767123</v>
       </c>
       <c r="AI176">
         <v>30</v>
@@ -27046,7 +27025,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="177" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:43">
       <c r="A177">
         <v>171</v>
       </c>
@@ -27177,7 +27156,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="178" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:43">
       <c r="A178">
         <v>172</v>
       </c>
@@ -27278,7 +27257,7 @@
         <v>46259</v>
       </c>
       <c r="AH178">
-        <v>2.9616438356164378</v>
+        <v>2.961643835616438</v>
       </c>
       <c r="AI178">
         <v>21</v>
@@ -27308,7 +27287,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="179" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:43">
       <c r="A179">
         <v>173</v>
       </c>
@@ -27409,7 +27388,7 @@
         <v>46259</v>
       </c>
       <c r="AH179">
-        <v>2.4684931506849321</v>
+        <v>2.468493150684932</v>
       </c>
       <c r="AI179">
         <v>21</v>
@@ -27439,7 +27418,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="180" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:43">
       <c r="A180">
         <v>174</v>
       </c>
@@ -27540,7 +27519,7 @@
         <v>46259</v>
       </c>
       <c r="AH180">
-        <v>2.2520547945205478</v>
+        <v>2.252054794520548</v>
       </c>
       <c r="AI180">
         <v>21</v>
@@ -27570,7 +27549,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="181" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:43">
       <c r="A181">
         <v>175</v>
       </c>
@@ -27701,7 +27680,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="182" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:43">
       <c r="A182">
         <v>176</v>
       </c>
@@ -27832,7 +27811,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="183" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:43">
       <c r="A183">
         <v>177</v>
       </c>
@@ -27963,7 +27942,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="184" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:43">
       <c r="A184">
         <v>178</v>
       </c>
@@ -28094,7 +28073,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="185" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:43">
       <c r="A185">
         <v>179</v>
       </c>
@@ -28225,7 +28204,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="186" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:43">
       <c r="A186">
         <v>180</v>
       </c>
@@ -28326,7 +28305,7 @@
         <v>46259</v>
       </c>
       <c r="AH186">
-        <v>1.7452054794520551</v>
+        <v>1.745205479452055</v>
       </c>
       <c r="AI186">
         <v>21</v>
@@ -28356,7 +28335,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="187" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:43">
       <c r="A187">
         <v>181</v>
       </c>
@@ -28457,7 +28436,7 @@
         <v>46259</v>
       </c>
       <c r="AH187">
-        <v>1.3890410958904109</v>
+        <v>1.389041095890411</v>
       </c>
       <c r="AI187">
         <v>21</v>
@@ -28489,7 +28468,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="S170" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="S170" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Staffdata.xlsx
+++ b/Staffdata.xlsx
@@ -1,15 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3113719057d24bf/Desktop/HR-Forms-Site/HRFORMAS/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_05E48499FC67680F1964AE368160343238AA41AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29250F51-42FE-41D0-8FB2-FFCF09498050}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2174,7 +2185,7 @@
     <t>-</t>
   </si>
   <si>
-    <t xml:space="preserve"> 966577040481</t>
+    <t> 966577040481</t>
   </si>
   <si>
     <t>malbatil@outlook.sa</t>
@@ -2485,10 +2496,10 @@
     <t>HAMDILLHJ038@GMAIL.COM</t>
   </si>
   <si>
-    <t xml:space="preserve"> omarzar392@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ark870725@gmail.com</t>
+    <t> omarzar392@gmail.com</t>
+  </si>
+  <si>
+    <t> ark870725@gmail.com</t>
   </si>
   <si>
     <t>waelgomaa1wg@gmail.com</t>
@@ -2561,7 +2572,7 @@
     <t>INFO2@HAIL-HOUSE.SA</t>
   </si>
   <si>
-    <t xml:space="preserve"> Sarah_elkhatib@outlook.com</t>
+    <t> Sarah_elkhatib@outlook.com</t>
   </si>
   <si>
     <t xml:space="preserve"> mohannad.fakhry00@gmail.com</t>
@@ -3905,11 +3916,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3955,18 +3966,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ارتباط تشعبي" xfId="1" builtinId="8"/>
+    <cellStyle name="عادي" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4004,7 +4023,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4038,6 +4057,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4072,9 +4092,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4247,11 +4268,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AQ187"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="30" max="33" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:43">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4382,7 +4406,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:43">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4483,7 +4507,7 @@
         <v>46259</v>
       </c>
       <c r="AH2">
-        <v>8.726027397260275</v>
+        <v>8.7260273972602747</v>
       </c>
       <c r="AI2">
         <v>30</v>
@@ -4513,7 +4537,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="3" spans="1:43">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4614,7 +4638,7 @@
         <v>46259</v>
       </c>
       <c r="AH3">
-        <v>13.63561643835616</v>
+        <v>13.635616438356161</v>
       </c>
       <c r="AI3">
         <v>30</v>
@@ -4644,7 +4668,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="4" spans="1:43">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4745,7 +4769,7 @@
         <v>46259</v>
       </c>
       <c r="AH4">
-        <v>5.890410958904109</v>
+        <v>5.8904109589041092</v>
       </c>
       <c r="AI4">
         <v>30</v>
@@ -4775,7 +4799,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="5" spans="1:43">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4876,7 +4900,7 @@
         <v>46259</v>
       </c>
       <c r="AH5">
-        <v>6.046575342465753</v>
+        <v>6.0465753424657533</v>
       </c>
       <c r="AI5">
         <v>21</v>
@@ -4906,7 +4930,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="6" spans="1:43">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5007,7 +5031,7 @@
         <v>46259</v>
       </c>
       <c r="AH6">
-        <v>6.402739726027397</v>
+        <v>6.4027397260273968</v>
       </c>
       <c r="AI6">
         <v>21</v>
@@ -5037,7 +5061,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="7" spans="1:43">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5138,7 +5162,7 @@
         <v>46259</v>
       </c>
       <c r="AH7">
-        <v>5.704109589041096</v>
+        <v>5.7041095890410958</v>
       </c>
       <c r="AI7">
         <v>30</v>
@@ -5168,7 +5192,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="8" spans="1:43">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5299,7 +5323,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="9" spans="1:43">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5430,7 +5454,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="10" spans="1:43">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5531,7 +5555,7 @@
         <v>46259</v>
       </c>
       <c r="AH10">
-        <v>6.753424657534246</v>
+        <v>6.7534246575342456</v>
       </c>
       <c r="AI10">
         <v>30</v>
@@ -5561,7 +5585,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="11" spans="1:43">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5692,7 +5716,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="12" spans="1:43">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5793,7 +5817,7 @@
         <v>46259</v>
       </c>
       <c r="AH12">
-        <v>5.750684931506849</v>
+        <v>5.7506849315068491</v>
       </c>
       <c r="AI12">
         <v>21</v>
@@ -5823,7 +5847,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="13" spans="1:43">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5954,7 +5978,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="14" spans="1:43">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6055,7 +6079,7 @@
         <v>46259</v>
       </c>
       <c r="AH14">
-        <v>0.3041095890410959</v>
+        <v>0.30410958904109592</v>
       </c>
       <c r="AI14">
         <v>21</v>
@@ -6085,7 +6109,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="15" spans="1:43">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6186,7 +6210,7 @@
         <v>46259</v>
       </c>
       <c r="AH15">
-        <v>3.983561643835616</v>
+        <v>3.9835616438356158</v>
       </c>
       <c r="AI15">
         <v>21</v>
@@ -6216,7 +6240,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="16" spans="1:43">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6317,7 +6341,7 @@
         <v>46259</v>
       </c>
       <c r="AH16">
-        <v>2.898630136986301</v>
+        <v>2.8986301369863008</v>
       </c>
       <c r="AI16">
         <v>21</v>
@@ -6347,7 +6371,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="17" spans="1:43">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -6448,7 +6472,7 @@
         <v>46259</v>
       </c>
       <c r="AH17">
-        <v>1.673972602739726</v>
+        <v>1.6739726027397259</v>
       </c>
       <c r="AI17">
         <v>21</v>
@@ -6478,7 +6502,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="18" spans="1:43">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6579,7 +6603,7 @@
         <v>46259</v>
       </c>
       <c r="AH18">
-        <v>2.049315068493151</v>
+        <v>2.0493150684931511</v>
       </c>
       <c r="AI18">
         <v>21</v>
@@ -6609,7 +6633,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="19" spans="1:43">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -6710,7 +6734,7 @@
         <v>46259</v>
       </c>
       <c r="AH19">
-        <v>2.035616438356164</v>
+        <v>2.0356164383561639</v>
       </c>
       <c r="AI19">
         <v>21</v>
@@ -6740,7 +6764,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="20" spans="1:43">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -6841,7 +6865,7 @@
         <v>46259</v>
       </c>
       <c r="AH20">
-        <v>1.512328767123288</v>
+        <v>1.5123287671232879</v>
       </c>
       <c r="AI20">
         <v>21</v>
@@ -6871,7 +6895,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="21" spans="1:43">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -6972,7 +6996,7 @@
         <v>46259</v>
       </c>
       <c r="AH21">
-        <v>2.035616438356164</v>
+        <v>2.0356164383561639</v>
       </c>
       <c r="AI21">
         <v>21</v>
@@ -7002,7 +7026,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="22" spans="1:43">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -7133,7 +7157,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="23" spans="1:43">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -7264,7 +7288,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="24" spans="1:43">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -7395,7 +7419,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="25" spans="1:43">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -7496,7 +7520,7 @@
         <v>46259</v>
       </c>
       <c r="AH25">
-        <v>0.7616438356164383</v>
+        <v>0.76164383561643834</v>
       </c>
       <c r="AI25">
         <v>21</v>
@@ -7526,7 +7550,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="26" spans="1:43">
+    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -7627,7 +7651,7 @@
         <v>46259</v>
       </c>
       <c r="AH26">
-        <v>0.7616438356164383</v>
+        <v>0.76164383561643834</v>
       </c>
       <c r="AI26">
         <v>21</v>
@@ -7657,7 +7681,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="27" spans="1:43">
+    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -7758,7 +7782,7 @@
         <v>46259</v>
       </c>
       <c r="AH27">
-        <v>6.736986301369863</v>
+        <v>6.7369863013698632</v>
       </c>
       <c r="AI27">
         <v>30</v>
@@ -7788,7 +7812,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="28" spans="1:43">
+    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -7889,7 +7913,7 @@
         <v>46259</v>
       </c>
       <c r="AH28">
-        <v>12.11232876712329</v>
+        <v>12.112328767123291</v>
       </c>
       <c r="AI28">
         <v>30</v>
@@ -7919,7 +7943,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="29" spans="1:43">
+    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -8020,7 +8044,7 @@
         <v>46259</v>
       </c>
       <c r="AH29">
-        <v>3.487671232876712</v>
+        <v>3.4876712328767119</v>
       </c>
       <c r="AI29">
         <v>21</v>
@@ -8050,7 +8074,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="30" spans="1:43">
+    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -8151,7 +8175,7 @@
         <v>46259</v>
       </c>
       <c r="AH30">
-        <v>15.07671232876712</v>
+        <v>15.076712328767121</v>
       </c>
       <c r="AI30">
         <v>30</v>
@@ -8181,7 +8205,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="31" spans="1:43">
+    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -8282,7 +8306,7 @@
         <v>46259</v>
       </c>
       <c r="AH31">
-        <v>15.07671232876712</v>
+        <v>15.076712328767121</v>
       </c>
       <c r="AI31">
         <v>30</v>
@@ -8312,7 +8336,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="32" spans="1:43">
+    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -8443,7 +8467,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="33" spans="1:43">
+    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -8544,7 +8568,7 @@
         <v>46259</v>
       </c>
       <c r="AH33">
-        <v>15.16712328767123</v>
+        <v>15.167123287671229</v>
       </c>
       <c r="AI33">
         <v>30</v>
@@ -8574,7 +8598,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="34" spans="1:43">
+    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -8675,7 +8699,7 @@
         <v>46259</v>
       </c>
       <c r="AH34">
-        <v>4.610958904109589</v>
+        <v>4.6109589041095891</v>
       </c>
       <c r="AI34">
         <v>21</v>
@@ -8705,7 +8729,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="35" spans="1:43">
+    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -8806,7 +8830,7 @@
         <v>46259</v>
       </c>
       <c r="AH35">
-        <v>4.542465753424658</v>
+        <v>4.5424657534246577</v>
       </c>
       <c r="AI35">
         <v>21</v>
@@ -8836,7 +8860,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="36" spans="1:43">
+    <row r="36" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -8937,7 +8961,7 @@
         <v>46259</v>
       </c>
       <c r="AH36">
-        <v>13.24109589041096</v>
+        <v>13.241095890410961</v>
       </c>
       <c r="AI36">
         <v>30</v>
@@ -8967,7 +8991,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="37" spans="1:43">
+    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -9098,7 +9122,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="38" spans="1:43">
+    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -9229,7 +9253,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="39" spans="1:43">
+    <row r="39" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -9330,7 +9354,7 @@
         <v>46259</v>
       </c>
       <c r="AH39">
-        <v>6.70958904109589</v>
+        <v>6.7095890410958896</v>
       </c>
       <c r="AI39">
         <v>30</v>
@@ -9360,7 +9384,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="40" spans="1:43">
+    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -9461,7 +9485,7 @@
         <v>46259</v>
       </c>
       <c r="AH40">
-        <v>6.50958904109589</v>
+        <v>6.5095890410958903</v>
       </c>
       <c r="AI40">
         <v>30</v>
@@ -9491,7 +9515,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="41" spans="1:43">
+    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -9592,7 +9616,7 @@
         <v>46259</v>
       </c>
       <c r="AH41">
-        <v>6.550684931506849</v>
+        <v>6.5506849315068489</v>
       </c>
       <c r="AI41">
         <v>21</v>
@@ -9622,7 +9646,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="42" spans="1:43">
+    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -9753,7 +9777,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="43" spans="1:43">
+    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -9854,7 +9878,7 @@
         <v>46259</v>
       </c>
       <c r="AH43">
-        <v>8.753424657534246</v>
+        <v>8.7534246575342465</v>
       </c>
       <c r="AI43">
         <v>30</v>
@@ -9884,7 +9908,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="44" spans="1:43">
+    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -9985,7 +10009,7 @@
         <v>46259</v>
       </c>
       <c r="AH44">
-        <v>5.753424657534246</v>
+        <v>5.7534246575342456</v>
       </c>
       <c r="AI44">
         <v>21</v>
@@ -10015,7 +10039,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="45" spans="1:43">
+    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -10116,7 +10140,7 @@
         <v>46259</v>
       </c>
       <c r="AH45">
-        <v>5.734246575342466</v>
+        <v>5.7342465753424658</v>
       </c>
       <c r="AI45">
         <v>21</v>
@@ -10146,7 +10170,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="46" spans="1:43">
+    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -10247,7 +10271,7 @@
         <v>46259</v>
       </c>
       <c r="AH46">
-        <v>5.627397260273972</v>
+        <v>5.6273972602739724</v>
       </c>
       <c r="AI46">
         <v>30</v>
@@ -10277,7 +10301,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="47" spans="1:43">
+    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -10378,7 +10402,7 @@
         <v>46259</v>
       </c>
       <c r="AH47">
-        <v>4.227397260273973</v>
+        <v>4.2273972602739729</v>
       </c>
       <c r="AI47">
         <v>21</v>
@@ -10408,7 +10432,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="48" spans="1:43">
+    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -10539,7 +10563,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="49" spans="1:43">
+    <row r="49" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -10640,7 +10664,7 @@
         <v>46259</v>
       </c>
       <c r="AH49">
-        <v>4.158904109589041</v>
+        <v>4.1589041095890407</v>
       </c>
       <c r="AI49">
         <v>21</v>
@@ -10670,7 +10694,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="50" spans="1:43">
+    <row r="50" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -10771,7 +10795,7 @@
         <v>46259</v>
       </c>
       <c r="AH50">
-        <v>3.986301369863014</v>
+        <v>3.9863013698630141</v>
       </c>
       <c r="AI50">
         <v>21</v>
@@ -10801,7 +10825,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="51" spans="1:43">
+    <row r="51" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -10902,7 +10926,7 @@
         <v>46259</v>
       </c>
       <c r="AH51">
-        <v>3.964383561643836</v>
+        <v>3.9643835616438361</v>
       </c>
       <c r="AI51">
         <v>21</v>
@@ -10932,7 +10956,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="52" spans="1:43">
+    <row r="52" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -11033,7 +11057,7 @@
         <v>46259</v>
       </c>
       <c r="AH52">
-        <v>3.964383561643836</v>
+        <v>3.9643835616438361</v>
       </c>
       <c r="AI52">
         <v>21</v>
@@ -11063,7 +11087,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="53" spans="1:43">
+    <row r="53" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -11194,7 +11218,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="54" spans="1:43">
+    <row r="54" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -11295,7 +11319,7 @@
         <v>46259</v>
       </c>
       <c r="AH54">
-        <v>1.96986301369863</v>
+        <v>1.9698630136986299</v>
       </c>
       <c r="AI54">
         <v>21</v>
@@ -11325,7 +11349,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="55" spans="1:43">
+    <row r="55" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -11426,7 +11450,7 @@
         <v>46259</v>
       </c>
       <c r="AH55">
-        <v>0.5835616438356165</v>
+        <v>0.58356164383561648</v>
       </c>
       <c r="AI55">
         <v>21</v>
@@ -11456,7 +11480,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="56" spans="1:43">
+    <row r="56" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -11557,7 +11581,7 @@
         <v>46259</v>
       </c>
       <c r="AH56">
-        <v>0.5835616438356165</v>
+        <v>0.58356164383561648</v>
       </c>
       <c r="AI56">
         <v>21</v>
@@ -11587,7 +11611,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="57" spans="1:43">
+    <row r="57" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -11688,7 +11712,7 @@
         <v>46259</v>
       </c>
       <c r="AH57">
-        <v>7.150684931506849</v>
+        <v>7.1506849315068486</v>
       </c>
       <c r="AI57">
         <v>30</v>
@@ -11718,7 +11742,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="58" spans="1:43">
+    <row r="58" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -11819,7 +11843,7 @@
         <v>46259</v>
       </c>
       <c r="AH58">
-        <v>7.482191780821918</v>
+        <v>7.4821917808219176</v>
       </c>
       <c r="AI58">
         <v>30</v>
@@ -11849,7 +11873,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="59" spans="1:43">
+    <row r="59" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -11950,7 +11974,7 @@
         <v>46259</v>
       </c>
       <c r="AH59">
-        <v>0.06575342465753424</v>
+        <v>6.575342465753424E-2</v>
       </c>
       <c r="AI59">
         <v>21</v>
@@ -11980,7 +12004,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="60" spans="1:43">
+    <row r="60" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -12081,7 +12105,7 @@
         <v>46259</v>
       </c>
       <c r="AH60">
-        <v>0.06575342465753424</v>
+        <v>6.575342465753424E-2</v>
       </c>
       <c r="AI60">
         <v>21</v>
@@ -12111,7 +12135,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="61" spans="1:43">
+    <row r="61" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
@@ -12212,7 +12236,7 @@
         <v>46259</v>
       </c>
       <c r="AH61">
-        <v>18.26301369863014</v>
+        <v>18.263013698630139</v>
       </c>
       <c r="AI61">
         <v>30</v>
@@ -12242,7 +12266,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="62" spans="1:43">
+    <row r="62" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
@@ -12343,7 +12367,7 @@
         <v>46259</v>
       </c>
       <c r="AH62">
-        <v>15.07671232876712</v>
+        <v>15.076712328767121</v>
       </c>
       <c r="AI62">
         <v>30</v>
@@ -12373,7 +12397,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="63" spans="1:43">
+    <row r="63" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
@@ -12474,7 +12498,7 @@
         <v>46259</v>
       </c>
       <c r="AH63">
-        <v>34.04931506849315</v>
+        <v>34.049315068493151</v>
       </c>
       <c r="AI63">
         <v>30</v>
@@ -12504,7 +12528,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="64" spans="1:43">
+    <row r="64" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
@@ -12605,7 +12629,7 @@
         <v>46259</v>
       </c>
       <c r="AH64">
-        <v>6.175342465753425</v>
+        <v>6.1753424657534248</v>
       </c>
       <c r="AI64">
         <v>30</v>
@@ -12635,7 +12659,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="65" spans="1:43">
+    <row r="65" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
@@ -12736,7 +12760,7 @@
         <v>46259</v>
       </c>
       <c r="AH65">
-        <v>1.873972602739726</v>
+        <v>1.8739726027397261</v>
       </c>
       <c r="AI65">
         <v>21</v>
@@ -12766,7 +12790,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="66" spans="1:43">
+    <row r="66" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
@@ -12867,7 +12891,7 @@
         <v>46259</v>
       </c>
       <c r="AH66">
-        <v>5.753424657534246</v>
+        <v>5.7534246575342456</v>
       </c>
       <c r="AI66">
         <v>21</v>
@@ -12897,7 +12921,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="67" spans="1:43">
+    <row r="67" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
@@ -12998,7 +13022,7 @@
         <v>46259</v>
       </c>
       <c r="AH67">
-        <v>18.04657534246575</v>
+        <v>18.046575342465751</v>
       </c>
       <c r="AI67">
         <v>30</v>
@@ -13028,7 +13052,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="68" spans="1:43">
+    <row r="68" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
@@ -13129,7 +13153,7 @@
         <v>46259</v>
       </c>
       <c r="AH68">
-        <v>9.531506849315068</v>
+        <v>9.5315068493150683</v>
       </c>
       <c r="AI68">
         <v>30</v>
@@ -13159,7 +13183,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="69" spans="1:43">
+    <row r="69" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
@@ -13290,7 +13314,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="70" spans="1:43">
+    <row r="70" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
@@ -13391,7 +13415,7 @@
         <v>46259</v>
       </c>
       <c r="AH70">
-        <v>10.60821917808219</v>
+        <v>10.608219178082191</v>
       </c>
       <c r="AI70">
         <v>30</v>
@@ -13421,7 +13445,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="71" spans="1:43">
+    <row r="71" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
@@ -13522,7 +13546,7 @@
         <v>46259</v>
       </c>
       <c r="AH71">
-        <v>0.3342465753424658</v>
+        <v>0.33424657534246582</v>
       </c>
       <c r="AI71">
         <v>21</v>
@@ -13552,7 +13576,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="72" spans="1:43">
+    <row r="72" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
@@ -13653,7 +13677,7 @@
         <v>46259</v>
       </c>
       <c r="AH72">
-        <v>0.3342465753424658</v>
+        <v>0.33424657534246582</v>
       </c>
       <c r="AI72">
         <v>21</v>
@@ -13683,7 +13707,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="73" spans="1:43">
+    <row r="73" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
@@ -13784,7 +13808,7 @@
         <v>46259</v>
       </c>
       <c r="AH73">
-        <v>2.96986301369863</v>
+        <v>2.9698630136986299</v>
       </c>
       <c r="AI73">
         <v>21</v>
@@ -13814,7 +13838,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="74" spans="1:43">
+    <row r="74" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>71</v>
       </c>
@@ -13945,7 +13969,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="75" spans="1:43">
+    <row r="75" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>72</v>
       </c>
@@ -14046,7 +14070,7 @@
         <v>46259</v>
       </c>
       <c r="AH75">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AI75">
         <v>21</v>
@@ -14076,7 +14100,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="76" spans="1:43">
+    <row r="76" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>73</v>
       </c>
@@ -14177,7 +14201,7 @@
         <v>46259</v>
       </c>
       <c r="AH76">
-        <v>4.068493150684931</v>
+        <v>4.0684931506849313</v>
       </c>
       <c r="AI76">
         <v>21</v>
@@ -14207,7 +14231,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="77" spans="1:43">
+    <row r="77" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>74</v>
       </c>
@@ -14338,7 +14362,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="78" spans="1:43">
+    <row r="78" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>75</v>
       </c>
@@ -14469,7 +14493,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="79" spans="1:43">
+    <row r="79" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>76</v>
       </c>
@@ -14570,7 +14594,7 @@
         <v>46259</v>
       </c>
       <c r="AH79">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AI79">
         <v>21</v>
@@ -14600,7 +14624,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="80" spans="1:43">
+    <row r="80" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>77</v>
       </c>
@@ -14701,7 +14725,7 @@
         <v>46259</v>
       </c>
       <c r="AH80">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AI80">
         <v>21</v>
@@ -14731,7 +14755,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="81" spans="1:43">
+    <row r="81" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>78</v>
       </c>
@@ -14832,7 +14856,7 @@
         <v>46259</v>
       </c>
       <c r="AH81">
-        <v>1.819178082191781</v>
+        <v>1.8191780821917809</v>
       </c>
       <c r="AI81">
         <v>21</v>
@@ -14862,7 +14886,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="82" spans="1:43">
+    <row r="82" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>79</v>
       </c>
@@ -14963,7 +14987,7 @@
         <v>46259</v>
       </c>
       <c r="AH82">
-        <v>1.654794520547945</v>
+        <v>1.6547945205479451</v>
       </c>
       <c r="AI82">
         <v>21</v>
@@ -14993,7 +15017,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="83" spans="1:43">
+    <row r="83" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>80</v>
       </c>
@@ -15094,7 +15118,7 @@
         <v>46259</v>
       </c>
       <c r="AH83">
-        <v>15.16712328767123</v>
+        <v>15.167123287671229</v>
       </c>
       <c r="AI83">
         <v>30</v>
@@ -15124,7 +15148,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="84" spans="1:43">
+    <row r="84" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>80</v>
       </c>
@@ -15165,7 +15189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:43">
+    <row r="85" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>81</v>
       </c>
@@ -15266,7 +15290,7 @@
         <v>46259</v>
       </c>
       <c r="AH85">
-        <v>8.975342465753425</v>
+        <v>8.9753424657534246</v>
       </c>
       <c r="AI85">
         <v>30</v>
@@ -15296,7 +15320,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="86" spans="1:43">
+    <row r="86" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>82</v>
       </c>
@@ -15397,7 +15421,7 @@
         <v>46259</v>
       </c>
       <c r="AH86">
-        <v>6.70958904109589</v>
+        <v>6.7095890410958896</v>
       </c>
       <c r="AI86">
         <v>30</v>
@@ -15427,7 +15451,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="87" spans="1:43">
+    <row r="87" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>83</v>
       </c>
@@ -15528,7 +15552,7 @@
         <v>46259</v>
       </c>
       <c r="AH87">
-        <v>9.323287671232876</v>
+        <v>9.3232876712328761</v>
       </c>
       <c r="AI87">
         <v>30</v>
@@ -15558,7 +15582,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="88" spans="1:43">
+    <row r="88" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>84</v>
       </c>
@@ -15659,7 +15683,7 @@
         <v>46259</v>
       </c>
       <c r="AH88">
-        <v>14.03561643835616</v>
+        <v>14.035616438356159</v>
       </c>
       <c r="AI88">
         <v>30</v>
@@ -15689,7 +15713,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="89" spans="1:43">
+    <row r="89" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>85</v>
       </c>
@@ -15790,7 +15814,7 @@
         <v>46259</v>
       </c>
       <c r="AH89">
-        <v>1.772602739726027</v>
+        <v>1.7726027397260271</v>
       </c>
       <c r="AI89">
         <v>21</v>
@@ -15820,7 +15844,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="90" spans="1:43">
+    <row r="90" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>86</v>
       </c>
@@ -15921,7 +15945,7 @@
         <v>46259</v>
       </c>
       <c r="AH90">
-        <v>8.408219178082192</v>
+        <v>8.4082191780821915</v>
       </c>
       <c r="AI90">
         <v>30</v>
@@ -15951,7 +15975,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="91" spans="1:43">
+    <row r="91" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>87</v>
       </c>
@@ -16052,7 +16076,7 @@
         <v>46259</v>
       </c>
       <c r="AH91">
-        <v>10.95068493150685</v>
+        <v>10.950684931506849</v>
       </c>
       <c r="AI91">
         <v>30</v>
@@ -16082,7 +16106,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="92" spans="1:43">
+    <row r="92" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>88</v>
       </c>
@@ -16183,7 +16207,7 @@
         <v>46259</v>
       </c>
       <c r="AH92">
-        <v>6.682191780821918</v>
+        <v>6.6821917808219178</v>
       </c>
       <c r="AI92">
         <v>21</v>
@@ -16213,7 +16237,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="93" spans="1:43">
+    <row r="93" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>89</v>
       </c>
@@ -16314,7 +16338,7 @@
         <v>46259</v>
       </c>
       <c r="AH93">
-        <v>5.627397260273972</v>
+        <v>5.6273972602739724</v>
       </c>
       <c r="AI93">
         <v>21</v>
@@ -16344,7 +16368,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="94" spans="1:43">
+    <row r="94" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>90</v>
       </c>
@@ -16445,7 +16469,7 @@
         <v>46259</v>
       </c>
       <c r="AH94">
-        <v>5.315068493150685</v>
+        <v>5.3150684931506849</v>
       </c>
       <c r="AI94">
         <v>30</v>
@@ -16475,7 +16499,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="95" spans="1:43">
+    <row r="95" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>91</v>
       </c>
@@ -16576,7 +16600,7 @@
         <v>46259</v>
       </c>
       <c r="AH95">
-        <v>5.06027397260274</v>
+        <v>5.0602739726027401</v>
       </c>
       <c r="AI95">
         <v>30</v>
@@ -16606,7 +16630,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="96" spans="1:43">
+    <row r="96" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>92</v>
       </c>
@@ -16707,7 +16731,7 @@
         <v>46259</v>
       </c>
       <c r="AH96">
-        <v>5.06027397260274</v>
+        <v>5.0602739726027401</v>
       </c>
       <c r="AI96">
         <v>21</v>
@@ -16737,7 +16761,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="97" spans="1:43">
+    <row r="97" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>93</v>
       </c>
@@ -16838,7 +16862,7 @@
         <v>46259</v>
       </c>
       <c r="AH97">
-        <v>4.753424657534246</v>
+        <v>4.7534246575342456</v>
       </c>
       <c r="AI97">
         <v>21</v>
@@ -16868,7 +16892,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="98" spans="1:43">
+    <row r="98" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>94</v>
       </c>
@@ -16969,7 +16993,7 @@
         <v>46259</v>
       </c>
       <c r="AH98">
-        <v>0.5835616438356165</v>
+        <v>0.58356164383561648</v>
       </c>
       <c r="AI98">
         <v>21</v>
@@ -16999,7 +17023,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="99" spans="1:43">
+    <row r="99" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>95</v>
       </c>
@@ -17100,7 +17124,7 @@
         <v>46259</v>
       </c>
       <c r="AH99">
-        <v>0.5835616438356165</v>
+        <v>0.58356164383561648</v>
       </c>
       <c r="AI99">
         <v>21</v>
@@ -17130,7 +17154,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="100" spans="1:43">
+    <row r="100" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>96</v>
       </c>
@@ -17231,7 +17255,7 @@
         <v>46259</v>
       </c>
       <c r="AH100">
-        <v>4.739726027397261</v>
+        <v>4.7397260273972606</v>
       </c>
       <c r="AI100">
         <v>21</v>
@@ -17261,7 +17285,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="101" spans="1:43">
+    <row r="101" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>97</v>
       </c>
@@ -17362,7 +17386,7 @@
         <v>46259</v>
       </c>
       <c r="AH101">
-        <v>4.67945205479452</v>
+        <v>4.6794520547945204</v>
       </c>
       <c r="AI101">
         <v>21</v>
@@ -17392,7 +17416,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="102" spans="1:43">
+    <row r="102" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>98</v>
       </c>
@@ -17493,7 +17517,7 @@
         <v>46259</v>
       </c>
       <c r="AH102">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AI102">
         <v>21</v>
@@ -17523,7 +17547,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="103" spans="1:43">
+    <row r="103" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>99</v>
       </c>
@@ -17624,7 +17648,7 @@
         <v>46259</v>
       </c>
       <c r="AH103">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AI103">
         <v>21</v>
@@ -17654,7 +17678,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="104" spans="1:43">
+    <row r="104" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>100</v>
       </c>
@@ -17755,7 +17779,7 @@
         <v>46259</v>
       </c>
       <c r="AH104">
-        <v>3.964383561643836</v>
+        <v>3.9643835616438361</v>
       </c>
       <c r="AI104">
         <v>21</v>
@@ -17785,7 +17809,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="105" spans="1:43">
+    <row r="105" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>101</v>
       </c>
@@ -17886,7 +17910,7 @@
         <v>46259</v>
       </c>
       <c r="AH105">
-        <v>7.523287671232877</v>
+        <v>7.5232876712328771</v>
       </c>
       <c r="AI105">
         <v>30</v>
@@ -17916,7 +17940,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="106" spans="1:43">
+    <row r="106" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>102</v>
       </c>
@@ -18017,7 +18041,7 @@
         <v>46259</v>
       </c>
       <c r="AH106">
-        <v>4.972602739726027</v>
+        <v>4.9726027397260273</v>
       </c>
       <c r="AI106">
         <v>21</v>
@@ -18047,7 +18071,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="107" spans="1:43">
+    <row r="107" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>103</v>
       </c>
@@ -18148,7 +18172,7 @@
         <v>46259</v>
       </c>
       <c r="AH107">
-        <v>1.96986301369863</v>
+        <v>1.9698630136986299</v>
       </c>
       <c r="AI107">
         <v>21</v>
@@ -18178,7 +18202,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="108" spans="1:43">
+    <row r="108" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>104</v>
       </c>
@@ -18279,7 +18303,7 @@
         <v>46259</v>
       </c>
       <c r="AH108">
-        <v>22.44657534246575</v>
+        <v>22.446575342465749</v>
       </c>
       <c r="AI108">
         <v>30</v>
@@ -18309,7 +18333,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="109" spans="1:43">
+    <row r="109" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>105</v>
       </c>
@@ -18410,7 +18434,7 @@
         <v>46259</v>
       </c>
       <c r="AH109">
-        <v>3.986301369863014</v>
+        <v>3.9863013698630141</v>
       </c>
       <c r="AI109">
         <v>21</v>
@@ -18440,7 +18464,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="110" spans="1:43">
+    <row r="110" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>106</v>
       </c>
@@ -18493,7 +18517,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="111" spans="1:43">
+    <row r="111" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>107</v>
       </c>
@@ -18594,7 +18618,7 @@
         <v>46259</v>
       </c>
       <c r="AH111">
-        <v>0.3589041095890411</v>
+        <v>0.35890410958904112</v>
       </c>
       <c r="AI111">
         <v>21</v>
@@ -18624,7 +18648,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="112" spans="1:43">
+    <row r="112" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>108</v>
       </c>
@@ -18725,7 +18749,7 @@
         <v>46259</v>
       </c>
       <c r="AH112">
-        <v>5.372602739726028</v>
+        <v>5.3726027397260276</v>
       </c>
       <c r="AI112">
         <v>21</v>
@@ -18755,7 +18779,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="113" spans="1:43">
+    <row r="113" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>109</v>
       </c>
@@ -18856,7 +18880,7 @@
         <v>46259</v>
       </c>
       <c r="AH113">
-        <v>4.528767123287671</v>
+        <v>4.5287671232876709</v>
       </c>
       <c r="AI113">
         <v>21</v>
@@ -18886,7 +18910,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="114" spans="1:43">
+    <row r="114" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>110</v>
       </c>
@@ -18987,7 +19011,7 @@
         <v>46259</v>
       </c>
       <c r="AH114">
-        <v>4.583561643835616</v>
+        <v>4.5835616438356164</v>
       </c>
       <c r="AI114">
         <v>21</v>
@@ -19017,7 +19041,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="115" spans="1:43">
+    <row r="115" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>111</v>
       </c>
@@ -19118,7 +19142,7 @@
         <v>46259</v>
       </c>
       <c r="AH115">
-        <v>4.526027397260274</v>
+        <v>4.5260273972602736</v>
       </c>
       <c r="AI115">
         <v>21</v>
@@ -19148,7 +19172,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="116" spans="1:43">
+    <row r="116" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>112</v>
       </c>
@@ -19249,7 +19273,7 @@
         <v>46259</v>
       </c>
       <c r="AH116">
-        <v>4.528767123287671</v>
+        <v>4.5287671232876709</v>
       </c>
       <c r="AI116">
         <v>21</v>
@@ -19279,7 +19303,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="117" spans="1:43">
+    <row r="117" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B117">
         <v>1336</v>
       </c>
@@ -19407,7 +19431,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="118" spans="1:43">
+    <row r="118" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>113</v>
       </c>
@@ -19538,7 +19562,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="119" spans="1:43">
+    <row r="119" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>114</v>
       </c>
@@ -19639,7 +19663,7 @@
         <v>46259</v>
       </c>
       <c r="AH119">
-        <v>2.63013698630137</v>
+        <v>2.6301369863013702</v>
       </c>
       <c r="AI119">
         <v>21</v>
@@ -19669,7 +19693,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="120" spans="1:43">
+    <row r="120" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>115</v>
       </c>
@@ -19770,7 +19794,7 @@
         <v>46259</v>
       </c>
       <c r="AH120">
-        <v>2.410958904109589</v>
+        <v>2.4109589041095889</v>
       </c>
       <c r="AI120">
         <v>21</v>
@@ -19800,7 +19824,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="121" spans="1:43">
+    <row r="121" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>116</v>
       </c>
@@ -19931,7 +19955,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="122" spans="1:43">
+    <row r="122" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>117</v>
       </c>
@@ -20062,7 +20086,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="123" spans="1:43">
+    <row r="123" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>118</v>
       </c>
@@ -20193,7 +20217,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="124" spans="1:43">
+    <row r="124" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>119</v>
       </c>
@@ -20294,7 +20318,7 @@
         <v>46259</v>
       </c>
       <c r="AH124">
-        <v>2.263013698630137</v>
+        <v>2.2630136986301368</v>
       </c>
       <c r="AI124">
         <v>21</v>
@@ -20324,7 +20348,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="125" spans="1:43">
+    <row r="125" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>120</v>
       </c>
@@ -20425,7 +20449,7 @@
         <v>46259</v>
       </c>
       <c r="AH125">
-        <v>6.586301369863014</v>
+        <v>6.5863013698630137</v>
       </c>
       <c r="AI125">
         <v>30</v>
@@ -20455,7 +20479,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="126" spans="1:43">
+    <row r="126" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>120</v>
       </c>
@@ -20478,7 +20502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:43">
+    <row r="127" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>121</v>
       </c>
@@ -20579,7 +20603,7 @@
         <v>46259</v>
       </c>
       <c r="AH127">
-        <v>12.26575342465753</v>
+        <v>12.265753424657531</v>
       </c>
       <c r="AI127">
         <v>30</v>
@@ -20609,7 +20633,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="128" spans="1:43">
+    <row r="128" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>122</v>
       </c>
@@ -20710,7 +20734,7 @@
         <v>46259</v>
       </c>
       <c r="AH128">
-        <v>5.964383561643835</v>
+        <v>5.9643835616438352</v>
       </c>
       <c r="AI128">
         <v>30</v>
@@ -20740,7 +20764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:43">
+    <row r="129" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>123</v>
       </c>
@@ -20841,7 +20865,7 @@
         <v>46259</v>
       </c>
       <c r="AH129">
-        <v>5.797260273972602</v>
+        <v>5.7972602739726016</v>
       </c>
       <c r="AI129">
         <v>21</v>
@@ -20871,7 +20895,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="130" spans="1:43">
+    <row r="130" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>124</v>
       </c>
@@ -20972,7 +20996,7 @@
         <v>46259</v>
       </c>
       <c r="AH130">
-        <v>5.153424657534247</v>
+        <v>5.1534246575342468</v>
       </c>
       <c r="AI130">
         <v>30</v>
@@ -21002,7 +21026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:43">
+    <row r="131" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>125</v>
       </c>
@@ -21103,7 +21127,7 @@
         <v>46259</v>
       </c>
       <c r="AH131">
-        <v>5.178082191780822</v>
+        <v>5.1780821917808222</v>
       </c>
       <c r="AI131">
         <v>30</v>
@@ -21133,7 +21157,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="132" spans="1:43">
+    <row r="132" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B132">
         <v>1135</v>
       </c>
@@ -21231,7 +21255,7 @@
         <v>46259</v>
       </c>
       <c r="AH132">
-        <v>0.1506849315068493</v>
+        <v>0.15068493150684931</v>
       </c>
       <c r="AI132">
         <v>21</v>
@@ -21261,7 +21285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:43">
+    <row r="133" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>126</v>
       </c>
@@ -21362,7 +21386,7 @@
         <v>46259</v>
       </c>
       <c r="AH133">
-        <v>4.235616438356164</v>
+        <v>4.2356164383561641</v>
       </c>
       <c r="AI133">
         <v>21</v>
@@ -21392,7 +21416,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="134" spans="1:43">
+    <row r="134" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>127</v>
       </c>
@@ -21493,7 +21517,7 @@
         <v>46259</v>
       </c>
       <c r="AH134">
-        <v>4.235616438356164</v>
+        <v>4.2356164383561641</v>
       </c>
       <c r="AI134">
         <v>21</v>
@@ -21523,7 +21547,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="135" spans="1:43">
+    <row r="135" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>128</v>
       </c>
@@ -21624,7 +21648,7 @@
         <v>46259</v>
       </c>
       <c r="AH135">
-        <v>4.723287671232876</v>
+        <v>4.7232876712328764</v>
       </c>
       <c r="AI135">
         <v>21</v>
@@ -21654,7 +21678,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="136" spans="1:43">
+    <row r="136" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>129</v>
       </c>
@@ -21755,7 +21779,7 @@
         <v>46259</v>
       </c>
       <c r="AH136">
-        <v>4.29041095890411</v>
+        <v>4.2904109589041104</v>
       </c>
       <c r="AI136">
         <v>21</v>
@@ -21785,7 +21809,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="137" spans="1:43">
+    <row r="137" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>130</v>
       </c>
@@ -21886,7 +21910,7 @@
         <v>46259</v>
       </c>
       <c r="AH137">
-        <v>4.553424657534246</v>
+        <v>4.5534246575342463</v>
       </c>
       <c r="AI137">
         <v>21</v>
@@ -21916,7 +21940,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="138" spans="1:43">
+    <row r="138" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>131</v>
       </c>
@@ -22017,7 +22041,7 @@
         <v>46259</v>
       </c>
       <c r="AH138">
-        <v>1.498630136986301</v>
+        <v>1.4986301369863011</v>
       </c>
       <c r="AI138">
         <v>21</v>
@@ -22047,7 +22071,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="139" spans="1:43">
+    <row r="139" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>132</v>
       </c>
@@ -22178,7 +22202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:43">
+    <row r="140" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>133</v>
       </c>
@@ -22309,7 +22333,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="141" spans="1:43">
+    <row r="141" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>134</v>
       </c>
@@ -22440,7 +22464,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="142" spans="1:43">
+    <row r="142" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>135</v>
       </c>
@@ -22571,7 +22595,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="143" spans="1:43">
+    <row r="143" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>136</v>
       </c>
@@ -22672,7 +22696,7 @@
         <v>46259</v>
       </c>
       <c r="AH143">
-        <v>4.487671232876712</v>
+        <v>4.4876712328767123</v>
       </c>
       <c r="AI143">
         <v>21</v>
@@ -22702,7 +22726,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="144" spans="1:43">
+    <row r="144" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>137</v>
       </c>
@@ -22803,7 +22827,7 @@
         <v>46259</v>
       </c>
       <c r="AH144">
-        <v>4.468493150684932</v>
+        <v>4.4684931506849317</v>
       </c>
       <c r="AI144">
         <v>21</v>
@@ -22833,7 +22857,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="145" spans="1:43">
+    <row r="145" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>138</v>
       </c>
@@ -22934,7 +22958,7 @@
         <v>46259</v>
       </c>
       <c r="AH145">
-        <v>1.857534246575342</v>
+        <v>1.8575342465753419</v>
       </c>
       <c r="AI145">
         <v>21</v>
@@ -22964,7 +22988,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="146" spans="1:43">
+    <row r="146" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>139</v>
       </c>
@@ -23065,7 +23089,7 @@
         <v>46259</v>
       </c>
       <c r="AH146">
-        <v>4.389041095890411</v>
+        <v>4.3890410958904109</v>
       </c>
       <c r="AI146">
         <v>21</v>
@@ -23095,7 +23119,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="147" spans="1:43">
+    <row r="147" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>140</v>
       </c>
@@ -23196,7 +23220,7 @@
         <v>46259</v>
       </c>
       <c r="AH147">
-        <v>3.791780821917808</v>
+        <v>3.7917808219178082</v>
       </c>
       <c r="AI147">
         <v>21</v>
@@ -23226,7 +23250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:43">
+    <row r="148" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>141</v>
       </c>
@@ -23327,7 +23351,7 @@
         <v>46259</v>
       </c>
       <c r="AH148">
-        <v>3.786301369863014</v>
+        <v>3.7863013698630139</v>
       </c>
       <c r="AI148">
         <v>21</v>
@@ -23357,7 +23381,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="149" spans="1:43">
+    <row r="149" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>142</v>
       </c>
@@ -23458,7 +23482,7 @@
         <v>46259</v>
       </c>
       <c r="AH149">
-        <v>3.736986301369863</v>
+        <v>3.7369863013698632</v>
       </c>
       <c r="AI149">
         <v>21</v>
@@ -23488,7 +23512,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="150" spans="1:43">
+    <row r="150" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>143</v>
       </c>
@@ -23589,7 +23613,7 @@
         <v>46259</v>
       </c>
       <c r="AH150">
-        <v>2.545205479452055</v>
+        <v>2.5452054794520551</v>
       </c>
       <c r="AI150">
         <v>21</v>
@@ -23619,7 +23643,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="151" spans="1:43">
+    <row r="151" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>144</v>
       </c>
@@ -23720,7 +23744,7 @@
         <v>46259</v>
       </c>
       <c r="AH151">
-        <v>5.967123287671233</v>
+        <v>5.9671232876712326</v>
       </c>
       <c r="AI151">
         <v>21</v>
@@ -23750,7 +23774,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="152" spans="1:43">
+    <row r="152" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>145</v>
       </c>
@@ -23851,7 +23875,7 @@
         <v>46259</v>
       </c>
       <c r="AH152">
-        <v>3.101369863013699</v>
+        <v>3.1013698630136992</v>
       </c>
       <c r="AI152">
         <v>21</v>
@@ -23881,7 +23905,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="153" spans="1:43">
+    <row r="153" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>146</v>
       </c>
@@ -23982,7 +24006,7 @@
         <v>46259</v>
       </c>
       <c r="AH153">
-        <v>5.64931506849315</v>
+        <v>5.6493150684931503</v>
       </c>
       <c r="AI153">
         <v>21</v>
@@ -24012,7 +24036,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="154" spans="1:43">
+    <row r="154" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>147</v>
       </c>
@@ -24113,7 +24137,7 @@
         <v>46259</v>
       </c>
       <c r="AH154">
-        <v>5.402739726027397</v>
+        <v>5.4027397260273968</v>
       </c>
       <c r="AI154">
         <v>21</v>
@@ -24143,7 +24167,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="155" spans="1:43">
+    <row r="155" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>148</v>
       </c>
@@ -24244,7 +24268,7 @@
         <v>46259</v>
       </c>
       <c r="AH155">
-        <v>5.30958904109589</v>
+        <v>5.3095890410958901</v>
       </c>
       <c r="AI155">
         <v>21</v>
@@ -24274,7 +24298,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="156" spans="1:43">
+    <row r="156" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>149</v>
       </c>
@@ -24375,7 +24399,7 @@
         <v>46259</v>
       </c>
       <c r="AH156">
-        <v>5.038356164383561</v>
+        <v>5.0383561643835613</v>
       </c>
       <c r="AI156">
         <v>21</v>
@@ -24405,7 +24429,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="157" spans="1:43">
+    <row r="157" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>150</v>
       </c>
@@ -24506,7 +24530,7 @@
         <v>46259</v>
       </c>
       <c r="AH157">
-        <v>5.038356164383561</v>
+        <v>5.0383561643835613</v>
       </c>
       <c r="AI157">
         <v>21</v>
@@ -24536,7 +24560,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="158" spans="1:43">
+    <row r="158" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>151</v>
       </c>
@@ -24637,7 +24661,7 @@
         <v>46259</v>
       </c>
       <c r="AH158">
-        <v>5.038356164383561</v>
+        <v>5.0383561643835613</v>
       </c>
       <c r="AI158">
         <v>21</v>
@@ -24667,7 +24691,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="159" spans="1:43">
+    <row r="159" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>152</v>
       </c>
@@ -24768,7 +24792,7 @@
         <v>46259</v>
       </c>
       <c r="AH159">
-        <v>5.038356164383561</v>
+        <v>5.0383561643835613</v>
       </c>
       <c r="AI159">
         <v>21</v>
@@ -24798,7 +24822,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="160" spans="1:43">
+    <row r="160" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>153</v>
       </c>
@@ -24899,7 +24923,7 @@
         <v>46259</v>
       </c>
       <c r="AH160">
-        <v>1.83013698630137</v>
+        <v>1.8301369863013699</v>
       </c>
       <c r="AI160">
         <v>21</v>
@@ -24929,7 +24953,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="161" spans="1:43">
+    <row r="161" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>154</v>
       </c>
@@ -25030,7 +25054,7 @@
         <v>46259</v>
       </c>
       <c r="AH161">
-        <v>4.528767123287671</v>
+        <v>4.5287671232876709</v>
       </c>
       <c r="AI161">
         <v>21</v>
@@ -25060,7 +25084,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="162" spans="1:43">
+    <row r="162" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>155</v>
       </c>
@@ -25161,7 +25185,7 @@
         <v>46259</v>
       </c>
       <c r="AH162">
-        <v>4.389041095890411</v>
+        <v>4.3890410958904109</v>
       </c>
       <c r="AI162">
         <v>21</v>
@@ -25191,7 +25215,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="163" spans="1:43">
+    <row r="163" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>156</v>
       </c>
@@ -25292,7 +25316,7 @@
         <v>46259</v>
       </c>
       <c r="AH163">
-        <v>4.389041095890411</v>
+        <v>4.3890410958904109</v>
       </c>
       <c r="AI163">
         <v>21</v>
@@ -25322,7 +25346,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="164" spans="1:43">
+    <row r="164" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>157</v>
       </c>
@@ -25453,7 +25477,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="165" spans="1:43">
+    <row r="165" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>158</v>
       </c>
@@ -25554,7 +25578,7 @@
         <v>46259</v>
       </c>
       <c r="AH165">
-        <v>3.994520547945205</v>
+        <v>3.9945205479452048</v>
       </c>
       <c r="AI165">
         <v>21</v>
@@ -25584,7 +25608,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="166" spans="1:43">
+    <row r="166" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>159</v>
       </c>
@@ -25685,7 +25709,7 @@
         <v>46259</v>
       </c>
       <c r="AH166">
-        <v>3.964383561643836</v>
+        <v>3.9643835616438361</v>
       </c>
       <c r="AI166">
         <v>21</v>
@@ -25715,7 +25739,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="167" spans="1:43">
+    <row r="167" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>161</v>
       </c>
@@ -25816,7 +25840,7 @@
         <v>46259</v>
       </c>
       <c r="AH167">
-        <v>2.33972602739726</v>
+        <v>2.3397260273972602</v>
       </c>
       <c r="AI167">
         <v>21</v>
@@ -25846,7 +25870,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="168" spans="1:43">
+    <row r="168" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>162</v>
       </c>
@@ -25947,7 +25971,7 @@
         <v>46259</v>
       </c>
       <c r="AH168">
-        <v>13.54794520547945</v>
+        <v>13.547945205479451</v>
       </c>
       <c r="AI168">
         <v>30</v>
@@ -25977,7 +26001,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="169" spans="1:43">
+    <row r="169" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>163</v>
       </c>
@@ -26078,7 +26102,7 @@
         <v>46259</v>
       </c>
       <c r="AH169">
-        <v>5.153424657534247</v>
+        <v>5.1534246575342468</v>
       </c>
       <c r="AI169">
         <v>30</v>
@@ -26108,7 +26132,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="170" spans="1:43">
+    <row r="170" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>164</v>
       </c>
@@ -26209,7 +26233,7 @@
         <v>46259</v>
       </c>
       <c r="AH170">
-        <v>5.345205479452055</v>
+        <v>5.3452054794520549</v>
       </c>
       <c r="AI170">
         <v>30</v>
@@ -26239,7 +26263,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="171" spans="1:43">
+    <row r="171" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>165</v>
       </c>
@@ -26370,7 +26394,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="172" spans="1:43">
+    <row r="172" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>166</v>
       </c>
@@ -26471,7 +26495,7 @@
         <v>46259</v>
       </c>
       <c r="AH172">
-        <v>2.843835616438356</v>
+        <v>2.8438356164383558</v>
       </c>
       <c r="AI172">
         <v>21</v>
@@ -26501,7 +26525,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="173" spans="1:43">
+    <row r="173" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>167</v>
       </c>
@@ -26632,7 +26656,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="174" spans="1:43">
+    <row r="174" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>168</v>
       </c>
@@ -26733,7 +26757,7 @@
         <v>46259</v>
       </c>
       <c r="AH174">
-        <v>1.96986301369863</v>
+        <v>1.9698630136986299</v>
       </c>
       <c r="AI174">
         <v>21</v>
@@ -26763,7 +26787,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="175" spans="1:43">
+    <row r="175" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>169</v>
       </c>
@@ -26894,7 +26918,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="176" spans="1:43">
+    <row r="176" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>170</v>
       </c>
@@ -26995,7 +27019,7 @@
         <v>46259</v>
       </c>
       <c r="AH176">
-        <v>5.876712328767123</v>
+        <v>5.8767123287671232</v>
       </c>
       <c r="AI176">
         <v>30</v>
@@ -27025,7 +27049,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="177" spans="1:43">
+    <row r="177" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>171</v>
       </c>
@@ -27156,7 +27180,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="178" spans="1:43">
+    <row r="178" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>172</v>
       </c>
@@ -27257,7 +27281,7 @@
         <v>46259</v>
       </c>
       <c r="AH178">
-        <v>2.961643835616438</v>
+        <v>2.9616438356164378</v>
       </c>
       <c r="AI178">
         <v>21</v>
@@ -27287,7 +27311,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="179" spans="1:43">
+    <row r="179" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>173</v>
       </c>
@@ -27388,7 +27412,7 @@
         <v>46259</v>
       </c>
       <c r="AH179">
-        <v>2.468493150684932</v>
+        <v>2.4684931506849321</v>
       </c>
       <c r="AI179">
         <v>21</v>
@@ -27418,7 +27442,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="180" spans="1:43">
+    <row r="180" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>174</v>
       </c>
@@ -27519,7 +27543,7 @@
         <v>46259</v>
       </c>
       <c r="AH180">
-        <v>2.252054794520548</v>
+        <v>2.2520547945205478</v>
       </c>
       <c r="AI180">
         <v>21</v>
@@ -27549,7 +27573,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="181" spans="1:43">
+    <row r="181" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>175</v>
       </c>
@@ -27680,7 +27704,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="182" spans="1:43">
+    <row r="182" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>176</v>
       </c>
@@ -27811,7 +27835,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="183" spans="1:43">
+    <row r="183" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>177</v>
       </c>
@@ -27942,7 +27966,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="184" spans="1:43">
+    <row r="184" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>178</v>
       </c>
@@ -28073,7 +28097,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="185" spans="1:43">
+    <row r="185" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>179</v>
       </c>
@@ -28204,7 +28228,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="186" spans="1:43">
+    <row r="186" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>180</v>
       </c>
@@ -28305,7 +28329,7 @@
         <v>46259</v>
       </c>
       <c r="AH186">
-        <v>1.745205479452055</v>
+        <v>1.7452054794520551</v>
       </c>
       <c r="AI186">
         <v>21</v>
@@ -28335,7 +28359,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="187" spans="1:43">
+    <row r="187" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>181</v>
       </c>
@@ -28436,7 +28460,7 @@
         <v>46259</v>
       </c>
       <c r="AH187">
-        <v>1.389041095890411</v>
+        <v>1.3890410958904109</v>
       </c>
       <c r="AI187">
         <v>21</v>
@@ -28468,7 +28492,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="S170" r:id="rId1"/>
+    <hyperlink ref="S170" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Staffdata.xlsx
+++ b/Staffdata.xlsx
@@ -1,26 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3113719057d24bf/Desktop/HR-Forms-Site/HRFORMAS/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_05E48499FC67680F1964AE368160343238AA41AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29250F51-42FE-41D0-8FB2-FFCF09498050}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -2185,7 +2174,7 @@
     <t>-</t>
   </si>
   <si>
-    <t> 966577040481</t>
+    <t xml:space="preserve"> 966577040481</t>
   </si>
   <si>
     <t>malbatil@outlook.sa</t>
@@ -2496,10 +2485,10 @@
     <t>HAMDILLHJ038@GMAIL.COM</t>
   </si>
   <si>
-    <t> omarzar392@gmail.com</t>
-  </si>
-  <si>
-    <t> ark870725@gmail.com</t>
+    <t xml:space="preserve"> omarzar392@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ark870725@gmail.com</t>
   </si>
   <si>
     <t>waelgomaa1wg@gmail.com</t>
@@ -2572,7 +2561,7 @@
     <t>INFO2@HAIL-HOUSE.SA</t>
   </si>
   <si>
-    <t> Sarah_elkhatib@outlook.com</t>
+    <t xml:space="preserve"> Sarah_elkhatib@outlook.com</t>
   </si>
   <si>
     <t xml:space="preserve"> mohannad.fakhry00@gmail.com</t>
@@ -3916,11 +3905,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3966,26 +3955,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="ارتباط تشعبي" xfId="1" builtinId="8"/>
-    <cellStyle name="عادي" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4023,7 +4004,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4057,7 +4038,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4092,10 +4072,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4268,14 +4247,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AQ187"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="30" max="33" width="18.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4406,7 +4382,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4507,7 +4483,7 @@
         <v>46259</v>
       </c>
       <c r="AH2">
-        <v>8.7260273972602747</v>
+        <v>8.726027397260275</v>
       </c>
       <c r="AI2">
         <v>30</v>
@@ -4537,7 +4513,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4638,7 +4614,7 @@
         <v>46259</v>
       </c>
       <c r="AH3">
-        <v>13.635616438356161</v>
+        <v>13.63561643835616</v>
       </c>
       <c r="AI3">
         <v>30</v>
@@ -4668,7 +4644,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4769,7 +4745,7 @@
         <v>46259</v>
       </c>
       <c r="AH4">
-        <v>5.8904109589041092</v>
+        <v>5.890410958904109</v>
       </c>
       <c r="AI4">
         <v>30</v>
@@ -4799,7 +4775,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4900,7 +4876,7 @@
         <v>46259</v>
       </c>
       <c r="AH5">
-        <v>6.0465753424657533</v>
+        <v>6.046575342465753</v>
       </c>
       <c r="AI5">
         <v>21</v>
@@ -4930,7 +4906,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5031,7 +5007,7 @@
         <v>46259</v>
       </c>
       <c r="AH6">
-        <v>6.4027397260273968</v>
+        <v>6.402739726027397</v>
       </c>
       <c r="AI6">
         <v>21</v>
@@ -5061,7 +5037,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5162,7 +5138,7 @@
         <v>46259</v>
       </c>
       <c r="AH7">
-        <v>5.7041095890410958</v>
+        <v>5.704109589041096</v>
       </c>
       <c r="AI7">
         <v>30</v>
@@ -5192,7 +5168,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5323,7 +5299,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5454,7 +5430,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5555,7 +5531,7 @@
         <v>46259</v>
       </c>
       <c r="AH10">
-        <v>6.7534246575342456</v>
+        <v>6.753424657534246</v>
       </c>
       <c r="AI10">
         <v>30</v>
@@ -5585,7 +5561,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5716,7 +5692,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5817,7 +5793,7 @@
         <v>46259</v>
       </c>
       <c r="AH12">
-        <v>5.7506849315068491</v>
+        <v>5.750684931506849</v>
       </c>
       <c r="AI12">
         <v>21</v>
@@ -5847,7 +5823,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5978,7 +5954,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6079,7 +6055,7 @@
         <v>46259</v>
       </c>
       <c r="AH14">
-        <v>0.30410958904109592</v>
+        <v>0.3041095890410959</v>
       </c>
       <c r="AI14">
         <v>21</v>
@@ -6109,7 +6085,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6210,7 +6186,7 @@
         <v>46259</v>
       </c>
       <c r="AH15">
-        <v>3.9835616438356158</v>
+        <v>3.983561643835616</v>
       </c>
       <c r="AI15">
         <v>21</v>
@@ -6240,7 +6216,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6341,7 +6317,7 @@
         <v>46259</v>
       </c>
       <c r="AH16">
-        <v>2.8986301369863008</v>
+        <v>2.898630136986301</v>
       </c>
       <c r="AI16">
         <v>21</v>
@@ -6371,7 +6347,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:43">
       <c r="A17">
         <v>16</v>
       </c>
@@ -6472,7 +6448,7 @@
         <v>46259</v>
       </c>
       <c r="AH17">
-        <v>1.6739726027397259</v>
+        <v>1.673972602739726</v>
       </c>
       <c r="AI17">
         <v>21</v>
@@ -6502,7 +6478,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:43">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6603,7 +6579,7 @@
         <v>46259</v>
       </c>
       <c r="AH18">
-        <v>2.0493150684931511</v>
+        <v>2.049315068493151</v>
       </c>
       <c r="AI18">
         <v>21</v>
@@ -6633,7 +6609,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:43">
       <c r="A19">
         <v>18</v>
       </c>
@@ -6734,7 +6710,7 @@
         <v>46259</v>
       </c>
       <c r="AH19">
-        <v>2.0356164383561639</v>
+        <v>2.035616438356164</v>
       </c>
       <c r="AI19">
         <v>21</v>
@@ -6764,7 +6740,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43">
       <c r="A20">
         <v>19</v>
       </c>
@@ -6865,7 +6841,7 @@
         <v>46259</v>
       </c>
       <c r="AH20">
-        <v>1.5123287671232879</v>
+        <v>1.512328767123288</v>
       </c>
       <c r="AI20">
         <v>21</v>
@@ -6895,7 +6871,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:43">
       <c r="A21">
         <v>20</v>
       </c>
@@ -6996,7 +6972,7 @@
         <v>46259</v>
       </c>
       <c r="AH21">
-        <v>2.0356164383561639</v>
+        <v>2.035616438356164</v>
       </c>
       <c r="AI21">
         <v>21</v>
@@ -7026,7 +7002,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43">
       <c r="A22">
         <v>21</v>
       </c>
@@ -7157,7 +7133,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:43">
       <c r="A23">
         <v>22</v>
       </c>
@@ -7288,7 +7264,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:43">
       <c r="A24">
         <v>23</v>
       </c>
@@ -7419,7 +7395,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:43">
       <c r="A25">
         <v>24</v>
       </c>
@@ -7520,7 +7496,7 @@
         <v>46259</v>
       </c>
       <c r="AH25">
-        <v>0.76164383561643834</v>
+        <v>0.7616438356164383</v>
       </c>
       <c r="AI25">
         <v>21</v>
@@ -7550,7 +7526,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:43">
       <c r="A26">
         <v>25</v>
       </c>
@@ -7651,7 +7627,7 @@
         <v>46259</v>
       </c>
       <c r="AH26">
-        <v>0.76164383561643834</v>
+        <v>0.7616438356164383</v>
       </c>
       <c r="AI26">
         <v>21</v>
@@ -7681,7 +7657,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:43">
       <c r="A27">
         <v>26</v>
       </c>
@@ -7782,7 +7758,7 @@
         <v>46259</v>
       </c>
       <c r="AH27">
-        <v>6.7369863013698632</v>
+        <v>6.736986301369863</v>
       </c>
       <c r="AI27">
         <v>30</v>
@@ -7812,7 +7788,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:43">
       <c r="A28">
         <v>27</v>
       </c>
@@ -7913,7 +7889,7 @@
         <v>46259</v>
       </c>
       <c r="AH28">
-        <v>12.112328767123291</v>
+        <v>12.11232876712329</v>
       </c>
       <c r="AI28">
         <v>30</v>
@@ -7943,7 +7919,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:43">
       <c r="A29">
         <v>28</v>
       </c>
@@ -8044,7 +8020,7 @@
         <v>46259</v>
       </c>
       <c r="AH29">
-        <v>3.4876712328767119</v>
+        <v>3.487671232876712</v>
       </c>
       <c r="AI29">
         <v>21</v>
@@ -8074,7 +8050,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:43">
       <c r="A30">
         <v>29</v>
       </c>
@@ -8175,7 +8151,7 @@
         <v>46259</v>
       </c>
       <c r="AH30">
-        <v>15.076712328767121</v>
+        <v>15.07671232876712</v>
       </c>
       <c r="AI30">
         <v>30</v>
@@ -8205,7 +8181,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:43">
       <c r="A31">
         <v>30</v>
       </c>
@@ -8306,7 +8282,7 @@
         <v>46259</v>
       </c>
       <c r="AH31">
-        <v>15.076712328767121</v>
+        <v>15.07671232876712</v>
       </c>
       <c r="AI31">
         <v>30</v>
@@ -8336,7 +8312,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:43">
       <c r="A32">
         <v>31</v>
       </c>
@@ -8467,7 +8443,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:43">
       <c r="A33">
         <v>32</v>
       </c>
@@ -8568,7 +8544,7 @@
         <v>46259</v>
       </c>
       <c r="AH33">
-        <v>15.167123287671229</v>
+        <v>15.16712328767123</v>
       </c>
       <c r="AI33">
         <v>30</v>
@@ -8598,7 +8574,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:43">
       <c r="A34">
         <v>33</v>
       </c>
@@ -8699,7 +8675,7 @@
         <v>46259</v>
       </c>
       <c r="AH34">
-        <v>4.6109589041095891</v>
+        <v>4.610958904109589</v>
       </c>
       <c r="AI34">
         <v>21</v>
@@ -8729,7 +8705,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:43">
       <c r="A35">
         <v>34</v>
       </c>
@@ -8830,7 +8806,7 @@
         <v>46259</v>
       </c>
       <c r="AH35">
-        <v>4.5424657534246577</v>
+        <v>4.542465753424658</v>
       </c>
       <c r="AI35">
         <v>21</v>
@@ -8860,7 +8836,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="36" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:43">
       <c r="A36">
         <v>35</v>
       </c>
@@ -8961,7 +8937,7 @@
         <v>46259</v>
       </c>
       <c r="AH36">
-        <v>13.241095890410961</v>
+        <v>13.24109589041096</v>
       </c>
       <c r="AI36">
         <v>30</v>
@@ -8991,7 +8967,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:43">
       <c r="A37">
         <v>36</v>
       </c>
@@ -9122,7 +9098,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:43">
       <c r="A38">
         <v>37</v>
       </c>
@@ -9253,7 +9229,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="39" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:43">
       <c r="A39">
         <v>38</v>
       </c>
@@ -9354,7 +9330,7 @@
         <v>46259</v>
       </c>
       <c r="AH39">
-        <v>6.7095890410958896</v>
+        <v>6.70958904109589</v>
       </c>
       <c r="AI39">
         <v>30</v>
@@ -9384,7 +9360,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:43">
       <c r="A40">
         <v>39</v>
       </c>
@@ -9485,7 +9461,7 @@
         <v>46259</v>
       </c>
       <c r="AH40">
-        <v>6.5095890410958903</v>
+        <v>6.50958904109589</v>
       </c>
       <c r="AI40">
         <v>30</v>
@@ -9515,7 +9491,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:43">
       <c r="A41">
         <v>40</v>
       </c>
@@ -9616,7 +9592,7 @@
         <v>46259</v>
       </c>
       <c r="AH41">
-        <v>6.5506849315068489</v>
+        <v>6.550684931506849</v>
       </c>
       <c r="AI41">
         <v>21</v>
@@ -9646,7 +9622,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:43">
       <c r="A42">
         <v>41</v>
       </c>
@@ -9777,7 +9753,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:43">
       <c r="A43">
         <v>42</v>
       </c>
@@ -9878,7 +9854,7 @@
         <v>46259</v>
       </c>
       <c r="AH43">
-        <v>8.7534246575342465</v>
+        <v>8.753424657534246</v>
       </c>
       <c r="AI43">
         <v>30</v>
@@ -9908,7 +9884,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:43">
       <c r="A44">
         <v>43</v>
       </c>
@@ -10009,7 +9985,7 @@
         <v>46259</v>
       </c>
       <c r="AH44">
-        <v>5.7534246575342456</v>
+        <v>5.753424657534246</v>
       </c>
       <c r="AI44">
         <v>21</v>
@@ -10039,7 +10015,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:43">
       <c r="A45">
         <v>44</v>
       </c>
@@ -10140,7 +10116,7 @@
         <v>46259</v>
       </c>
       <c r="AH45">
-        <v>5.7342465753424658</v>
+        <v>5.734246575342466</v>
       </c>
       <c r="AI45">
         <v>21</v>
@@ -10170,7 +10146,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:43">
       <c r="A46">
         <v>45</v>
       </c>
@@ -10271,7 +10247,7 @@
         <v>46259</v>
       </c>
       <c r="AH46">
-        <v>5.6273972602739724</v>
+        <v>5.627397260273972</v>
       </c>
       <c r="AI46">
         <v>30</v>
@@ -10301,7 +10277,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:43">
       <c r="A47">
         <v>46</v>
       </c>
@@ -10402,7 +10378,7 @@
         <v>46259</v>
       </c>
       <c r="AH47">
-        <v>4.2273972602739729</v>
+        <v>4.227397260273973</v>
       </c>
       <c r="AI47">
         <v>21</v>
@@ -10432,7 +10408,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:43">
       <c r="A48">
         <v>47</v>
       </c>
@@ -10563,7 +10539,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="49" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:43">
       <c r="A49">
         <v>48</v>
       </c>
@@ -10664,7 +10640,7 @@
         <v>46259</v>
       </c>
       <c r="AH49">
-        <v>4.1589041095890407</v>
+        <v>4.158904109589041</v>
       </c>
       <c r="AI49">
         <v>21</v>
@@ -10694,7 +10670,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="50" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:43">
       <c r="A50">
         <v>49</v>
       </c>
@@ -10795,7 +10771,7 @@
         <v>46259</v>
       </c>
       <c r="AH50">
-        <v>3.9863013698630141</v>
+        <v>3.986301369863014</v>
       </c>
       <c r="AI50">
         <v>21</v>
@@ -10825,7 +10801,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="51" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:43">
       <c r="A51">
         <v>50</v>
       </c>
@@ -10926,7 +10902,7 @@
         <v>46259</v>
       </c>
       <c r="AH51">
-        <v>3.9643835616438361</v>
+        <v>3.964383561643836</v>
       </c>
       <c r="AI51">
         <v>21</v>
@@ -10956,7 +10932,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="52" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:43">
       <c r="A52">
         <v>51</v>
       </c>
@@ -11057,7 +11033,7 @@
         <v>46259</v>
       </c>
       <c r="AH52">
-        <v>3.9643835616438361</v>
+        <v>3.964383561643836</v>
       </c>
       <c r="AI52">
         <v>21</v>
@@ -11087,7 +11063,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="53" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:43">
       <c r="A53">
         <v>52</v>
       </c>
@@ -11218,7 +11194,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="54" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:43">
       <c r="A54">
         <v>53</v>
       </c>
@@ -11319,7 +11295,7 @@
         <v>46259</v>
       </c>
       <c r="AH54">
-        <v>1.9698630136986299</v>
+        <v>1.96986301369863</v>
       </c>
       <c r="AI54">
         <v>21</v>
@@ -11349,7 +11325,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="55" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:43">
       <c r="A55">
         <v>54</v>
       </c>
@@ -11450,7 +11426,7 @@
         <v>46259</v>
       </c>
       <c r="AH55">
-        <v>0.58356164383561648</v>
+        <v>0.5835616438356165</v>
       </c>
       <c r="AI55">
         <v>21</v>
@@ -11480,7 +11456,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="56" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:43">
       <c r="A56">
         <v>55</v>
       </c>
@@ -11581,7 +11557,7 @@
         <v>46259</v>
       </c>
       <c r="AH56">
-        <v>0.58356164383561648</v>
+        <v>0.5835616438356165</v>
       </c>
       <c r="AI56">
         <v>21</v>
@@ -11611,7 +11587,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="57" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:43">
       <c r="A57">
         <v>56</v>
       </c>
@@ -11712,7 +11688,7 @@
         <v>46259</v>
       </c>
       <c r="AH57">
-        <v>7.1506849315068486</v>
+        <v>7.150684931506849</v>
       </c>
       <c r="AI57">
         <v>30</v>
@@ -11742,7 +11718,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="58" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:43">
       <c r="A58">
         <v>57</v>
       </c>
@@ -11843,7 +11819,7 @@
         <v>46259</v>
       </c>
       <c r="AH58">
-        <v>7.4821917808219176</v>
+        <v>7.482191780821918</v>
       </c>
       <c r="AI58">
         <v>30</v>
@@ -11873,7 +11849,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="59" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:43">
       <c r="A59">
         <v>58</v>
       </c>
@@ -11974,7 +11950,7 @@
         <v>46259</v>
       </c>
       <c r="AH59">
-        <v>6.575342465753424E-2</v>
+        <v>0.06575342465753424</v>
       </c>
       <c r="AI59">
         <v>21</v>
@@ -12004,7 +11980,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="60" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:43">
       <c r="A60">
         <v>59</v>
       </c>
@@ -12105,7 +12081,7 @@
         <v>46259</v>
       </c>
       <c r="AH60">
-        <v>6.575342465753424E-2</v>
+        <v>0.06575342465753424</v>
       </c>
       <c r="AI60">
         <v>21</v>
@@ -12135,7 +12111,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="61" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:43">
       <c r="A61">
         <v>58</v>
       </c>
@@ -12236,7 +12212,7 @@
         <v>46259</v>
       </c>
       <c r="AH61">
-        <v>18.263013698630139</v>
+        <v>18.26301369863014</v>
       </c>
       <c r="AI61">
         <v>30</v>
@@ -12266,7 +12242,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="62" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:43">
       <c r="A62">
         <v>59</v>
       </c>
@@ -12367,7 +12343,7 @@
         <v>46259</v>
       </c>
       <c r="AH62">
-        <v>15.076712328767121</v>
+        <v>15.07671232876712</v>
       </c>
       <c r="AI62">
         <v>30</v>
@@ -12397,7 +12373,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="63" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:43">
       <c r="A63">
         <v>60</v>
       </c>
@@ -12498,7 +12474,7 @@
         <v>46259</v>
       </c>
       <c r="AH63">
-        <v>34.049315068493151</v>
+        <v>34.04931506849315</v>
       </c>
       <c r="AI63">
         <v>30</v>
@@ -12528,7 +12504,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="64" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:43">
       <c r="A64">
         <v>61</v>
       </c>
@@ -12629,7 +12605,7 @@
         <v>46259</v>
       </c>
       <c r="AH64">
-        <v>6.1753424657534248</v>
+        <v>6.175342465753425</v>
       </c>
       <c r="AI64">
         <v>30</v>
@@ -12659,7 +12635,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="65" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:43">
       <c r="A65">
         <v>62</v>
       </c>
@@ -12760,7 +12736,7 @@
         <v>46259</v>
       </c>
       <c r="AH65">
-        <v>1.8739726027397261</v>
+        <v>1.873972602739726</v>
       </c>
       <c r="AI65">
         <v>21</v>
@@ -12790,7 +12766,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="66" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:43">
       <c r="A66">
         <v>63</v>
       </c>
@@ -12891,7 +12867,7 @@
         <v>46259</v>
       </c>
       <c r="AH66">
-        <v>5.7534246575342456</v>
+        <v>5.753424657534246</v>
       </c>
       <c r="AI66">
         <v>21</v>
@@ -12921,7 +12897,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="67" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:43">
       <c r="A67">
         <v>64</v>
       </c>
@@ -13022,7 +12998,7 @@
         <v>46259</v>
       </c>
       <c r="AH67">
-        <v>18.046575342465751</v>
+        <v>18.04657534246575</v>
       </c>
       <c r="AI67">
         <v>30</v>
@@ -13052,7 +13028,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="68" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:43">
       <c r="A68">
         <v>65</v>
       </c>
@@ -13153,7 +13129,7 @@
         <v>46259</v>
       </c>
       <c r="AH68">
-        <v>9.5315068493150683</v>
+        <v>9.531506849315068</v>
       </c>
       <c r="AI68">
         <v>30</v>
@@ -13183,7 +13159,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="69" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:43">
       <c r="A69">
         <v>66</v>
       </c>
@@ -13314,7 +13290,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="70" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:43">
       <c r="A70">
         <v>67</v>
       </c>
@@ -13415,7 +13391,7 @@
         <v>46259</v>
       </c>
       <c r="AH70">
-        <v>10.608219178082191</v>
+        <v>10.60821917808219</v>
       </c>
       <c r="AI70">
         <v>30</v>
@@ -13445,7 +13421,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="71" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:43">
       <c r="A71">
         <v>68</v>
       </c>
@@ -13546,7 +13522,7 @@
         <v>46259</v>
       </c>
       <c r="AH71">
-        <v>0.33424657534246582</v>
+        <v>0.3342465753424658</v>
       </c>
       <c r="AI71">
         <v>21</v>
@@ -13576,7 +13552,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="72" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:43">
       <c r="A72">
         <v>69</v>
       </c>
@@ -13677,7 +13653,7 @@
         <v>46259</v>
       </c>
       <c r="AH72">
-        <v>0.33424657534246582</v>
+        <v>0.3342465753424658</v>
       </c>
       <c r="AI72">
         <v>21</v>
@@ -13707,7 +13683,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="73" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:43">
       <c r="A73">
         <v>70</v>
       </c>
@@ -13808,7 +13784,7 @@
         <v>46259</v>
       </c>
       <c r="AH73">
-        <v>2.9698630136986299</v>
+        <v>2.96986301369863</v>
       </c>
       <c r="AI73">
         <v>21</v>
@@ -13838,7 +13814,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="74" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:43">
       <c r="A74">
         <v>71</v>
       </c>
@@ -13969,7 +13945,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="75" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:43">
       <c r="A75">
         <v>72</v>
       </c>
@@ -14070,7 +14046,7 @@
         <v>46259</v>
       </c>
       <c r="AH75">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="AI75">
         <v>21</v>
@@ -14100,7 +14076,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="76" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:43">
       <c r="A76">
         <v>73</v>
       </c>
@@ -14201,7 +14177,7 @@
         <v>46259</v>
       </c>
       <c r="AH76">
-        <v>4.0684931506849313</v>
+        <v>4.068493150684931</v>
       </c>
       <c r="AI76">
         <v>21</v>
@@ -14231,7 +14207,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="77" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:43">
       <c r="A77">
         <v>74</v>
       </c>
@@ -14362,7 +14338,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="78" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:43">
       <c r="A78">
         <v>75</v>
       </c>
@@ -14493,7 +14469,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="79" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:43">
       <c r="A79">
         <v>76</v>
       </c>
@@ -14594,7 +14570,7 @@
         <v>46259</v>
       </c>
       <c r="AH79">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
       <c r="AI79">
         <v>21</v>
@@ -14624,7 +14600,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="80" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:43">
       <c r="A80">
         <v>77</v>
       </c>
@@ -14725,7 +14701,7 @@
         <v>46259</v>
       </c>
       <c r="AH80">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
       <c r="AI80">
         <v>21</v>
@@ -14755,7 +14731,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="81" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:43">
       <c r="A81">
         <v>78</v>
       </c>
@@ -14856,7 +14832,7 @@
         <v>46259</v>
       </c>
       <c r="AH81">
-        <v>1.8191780821917809</v>
+        <v>1.819178082191781</v>
       </c>
       <c r="AI81">
         <v>21</v>
@@ -14886,7 +14862,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="82" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:43">
       <c r="A82">
         <v>79</v>
       </c>
@@ -14987,7 +14963,7 @@
         <v>46259</v>
       </c>
       <c r="AH82">
-        <v>1.6547945205479451</v>
+        <v>1.654794520547945</v>
       </c>
       <c r="AI82">
         <v>21</v>
@@ -15017,7 +14993,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="83" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:43">
       <c r="A83">
         <v>80</v>
       </c>
@@ -15118,7 +15094,7 @@
         <v>46259</v>
       </c>
       <c r="AH83">
-        <v>15.167123287671229</v>
+        <v>15.16712328767123</v>
       </c>
       <c r="AI83">
         <v>30</v>
@@ -15148,7 +15124,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="84" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:43">
       <c r="A84">
         <v>80</v>
       </c>
@@ -15189,7 +15165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:43">
       <c r="A85">
         <v>81</v>
       </c>
@@ -15290,7 +15266,7 @@
         <v>46259</v>
       </c>
       <c r="AH85">
-        <v>8.9753424657534246</v>
+        <v>8.975342465753425</v>
       </c>
       <c r="AI85">
         <v>30</v>
@@ -15320,7 +15296,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="86" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:43">
       <c r="A86">
         <v>82</v>
       </c>
@@ -15421,7 +15397,7 @@
         <v>46259</v>
       </c>
       <c r="AH86">
-        <v>6.7095890410958896</v>
+        <v>6.70958904109589</v>
       </c>
       <c r="AI86">
         <v>30</v>
@@ -15451,7 +15427,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="87" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:43">
       <c r="A87">
         <v>83</v>
       </c>
@@ -15552,7 +15528,7 @@
         <v>46259</v>
       </c>
       <c r="AH87">
-        <v>9.3232876712328761</v>
+        <v>9.323287671232876</v>
       </c>
       <c r="AI87">
         <v>30</v>
@@ -15582,7 +15558,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="88" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:43">
       <c r="A88">
         <v>84</v>
       </c>
@@ -15683,7 +15659,7 @@
         <v>46259</v>
       </c>
       <c r="AH88">
-        <v>14.035616438356159</v>
+        <v>14.03561643835616</v>
       </c>
       <c r="AI88">
         <v>30</v>
@@ -15713,7 +15689,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="89" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:43">
       <c r="A89">
         <v>85</v>
       </c>
@@ -15814,7 +15790,7 @@
         <v>46259</v>
       </c>
       <c r="AH89">
-        <v>1.7726027397260271</v>
+        <v>1.772602739726027</v>
       </c>
       <c r="AI89">
         <v>21</v>
@@ -15844,7 +15820,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="90" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:43">
       <c r="A90">
         <v>86</v>
       </c>
@@ -15945,7 +15921,7 @@
         <v>46259</v>
       </c>
       <c r="AH90">
-        <v>8.4082191780821915</v>
+        <v>8.408219178082192</v>
       </c>
       <c r="AI90">
         <v>30</v>
@@ -15975,7 +15951,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="91" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:43">
       <c r="A91">
         <v>87</v>
       </c>
@@ -16076,7 +16052,7 @@
         <v>46259</v>
       </c>
       <c r="AH91">
-        <v>10.950684931506849</v>
+        <v>10.95068493150685</v>
       </c>
       <c r="AI91">
         <v>30</v>
@@ -16106,7 +16082,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="92" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:43">
       <c r="A92">
         <v>88</v>
       </c>
@@ -16207,7 +16183,7 @@
         <v>46259</v>
       </c>
       <c r="AH92">
-        <v>6.6821917808219178</v>
+        <v>6.682191780821918</v>
       </c>
       <c r="AI92">
         <v>21</v>
@@ -16237,7 +16213,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="93" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:43">
       <c r="A93">
         <v>89</v>
       </c>
@@ -16338,7 +16314,7 @@
         <v>46259</v>
       </c>
       <c r="AH93">
-        <v>5.6273972602739724</v>
+        <v>5.627397260273972</v>
       </c>
       <c r="AI93">
         <v>21</v>
@@ -16368,7 +16344,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="94" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:43">
       <c r="A94">
         <v>90</v>
       </c>
@@ -16469,7 +16445,7 @@
         <v>46259</v>
       </c>
       <c r="AH94">
-        <v>5.3150684931506849</v>
+        <v>5.315068493150685</v>
       </c>
       <c r="AI94">
         <v>30</v>
@@ -16499,7 +16475,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="95" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:43">
       <c r="A95">
         <v>91</v>
       </c>
@@ -16600,7 +16576,7 @@
         <v>46259</v>
       </c>
       <c r="AH95">
-        <v>5.0602739726027401</v>
+        <v>5.06027397260274</v>
       </c>
       <c r="AI95">
         <v>30</v>
@@ -16630,7 +16606,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="96" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:43">
       <c r="A96">
         <v>92</v>
       </c>
@@ -16731,7 +16707,7 @@
         <v>46259</v>
       </c>
       <c r="AH96">
-        <v>5.0602739726027401</v>
+        <v>5.06027397260274</v>
       </c>
       <c r="AI96">
         <v>21</v>
@@ -16761,7 +16737,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="97" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:43">
       <c r="A97">
         <v>93</v>
       </c>
@@ -16862,7 +16838,7 @@
         <v>46259</v>
       </c>
       <c r="AH97">
-        <v>4.7534246575342456</v>
+        <v>4.753424657534246</v>
       </c>
       <c r="AI97">
         <v>21</v>
@@ -16892,7 +16868,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="98" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:43">
       <c r="A98">
         <v>94</v>
       </c>
@@ -16993,7 +16969,7 @@
         <v>46259</v>
       </c>
       <c r="AH98">
-        <v>0.58356164383561648</v>
+        <v>0.5835616438356165</v>
       </c>
       <c r="AI98">
         <v>21</v>
@@ -17023,7 +16999,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="99" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:43">
       <c r="A99">
         <v>95</v>
       </c>
@@ -17124,7 +17100,7 @@
         <v>46259</v>
       </c>
       <c r="AH99">
-        <v>0.58356164383561648</v>
+        <v>0.5835616438356165</v>
       </c>
       <c r="AI99">
         <v>21</v>
@@ -17154,7 +17130,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="100" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:43">
       <c r="A100">
         <v>96</v>
       </c>
@@ -17255,7 +17231,7 @@
         <v>46259</v>
       </c>
       <c r="AH100">
-        <v>4.7397260273972606</v>
+        <v>4.739726027397261</v>
       </c>
       <c r="AI100">
         <v>21</v>
@@ -17285,7 +17261,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="101" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:43">
       <c r="A101">
         <v>97</v>
       </c>
@@ -17386,7 +17362,7 @@
         <v>46259</v>
       </c>
       <c r="AH101">
-        <v>4.6794520547945204</v>
+        <v>4.67945205479452</v>
       </c>
       <c r="AI101">
         <v>21</v>
@@ -17416,7 +17392,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="102" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:43">
       <c r="A102">
         <v>98</v>
       </c>
@@ -17517,7 +17493,7 @@
         <v>46259</v>
       </c>
       <c r="AH102">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="AI102">
         <v>21</v>
@@ -17547,7 +17523,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="103" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:43">
       <c r="A103">
         <v>99</v>
       </c>
@@ -17648,7 +17624,7 @@
         <v>46259</v>
       </c>
       <c r="AH103">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="AI103">
         <v>21</v>
@@ -17678,7 +17654,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="104" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:43">
       <c r="A104">
         <v>100</v>
       </c>
@@ -17779,7 +17755,7 @@
         <v>46259</v>
       </c>
       <c r="AH104">
-        <v>3.9643835616438361</v>
+        <v>3.964383561643836</v>
       </c>
       <c r="AI104">
         <v>21</v>
@@ -17809,7 +17785,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="105" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:43">
       <c r="A105">
         <v>101</v>
       </c>
@@ -17910,7 +17886,7 @@
         <v>46259</v>
       </c>
       <c r="AH105">
-        <v>7.5232876712328771</v>
+        <v>7.523287671232877</v>
       </c>
       <c r="AI105">
         <v>30</v>
@@ -17940,7 +17916,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="106" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:43">
       <c r="A106">
         <v>102</v>
       </c>
@@ -18041,7 +18017,7 @@
         <v>46259</v>
       </c>
       <c r="AH106">
-        <v>4.9726027397260273</v>
+        <v>4.972602739726027</v>
       </c>
       <c r="AI106">
         <v>21</v>
@@ -18071,7 +18047,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="107" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:43">
       <c r="A107">
         <v>103</v>
       </c>
@@ -18172,7 +18148,7 @@
         <v>46259</v>
       </c>
       <c r="AH107">
-        <v>1.9698630136986299</v>
+        <v>1.96986301369863</v>
       </c>
       <c r="AI107">
         <v>21</v>
@@ -18202,7 +18178,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="108" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:43">
       <c r="A108">
         <v>104</v>
       </c>
@@ -18303,7 +18279,7 @@
         <v>46259</v>
       </c>
       <c r="AH108">
-        <v>22.446575342465749</v>
+        <v>22.44657534246575</v>
       </c>
       <c r="AI108">
         <v>30</v>
@@ -18333,7 +18309,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="109" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:43">
       <c r="A109">
         <v>105</v>
       </c>
@@ -18434,7 +18410,7 @@
         <v>46259</v>
       </c>
       <c r="AH109">
-        <v>3.9863013698630141</v>
+        <v>3.986301369863014</v>
       </c>
       <c r="AI109">
         <v>21</v>
@@ -18464,7 +18440,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="110" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:43">
       <c r="A110">
         <v>106</v>
       </c>
@@ -18517,7 +18493,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="111" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:43">
       <c r="A111">
         <v>107</v>
       </c>
@@ -18618,7 +18594,7 @@
         <v>46259</v>
       </c>
       <c r="AH111">
-        <v>0.35890410958904112</v>
+        <v>0.3589041095890411</v>
       </c>
       <c r="AI111">
         <v>21</v>
@@ -18648,7 +18624,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="112" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:43">
       <c r="A112">
         <v>108</v>
       </c>
@@ -18749,7 +18725,7 @@
         <v>46259</v>
       </c>
       <c r="AH112">
-        <v>5.3726027397260276</v>
+        <v>5.372602739726028</v>
       </c>
       <c r="AI112">
         <v>21</v>
@@ -18779,7 +18755,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="113" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:43">
       <c r="A113">
         <v>109</v>
       </c>
@@ -18880,7 +18856,7 @@
         <v>46259</v>
       </c>
       <c r="AH113">
-        <v>4.5287671232876709</v>
+        <v>4.528767123287671</v>
       </c>
       <c r="AI113">
         <v>21</v>
@@ -18910,7 +18886,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="114" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:43">
       <c r="A114">
         <v>110</v>
       </c>
@@ -19011,7 +18987,7 @@
         <v>46259</v>
       </c>
       <c r="AH114">
-        <v>4.5835616438356164</v>
+        <v>4.583561643835616</v>
       </c>
       <c r="AI114">
         <v>21</v>
@@ -19041,7 +19017,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="115" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:43">
       <c r="A115">
         <v>111</v>
       </c>
@@ -19142,7 +19118,7 @@
         <v>46259</v>
       </c>
       <c r="AH115">
-        <v>4.5260273972602736</v>
+        <v>4.526027397260274</v>
       </c>
       <c r="AI115">
         <v>21</v>
@@ -19172,7 +19148,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="116" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:43">
       <c r="A116">
         <v>112</v>
       </c>
@@ -19273,7 +19249,7 @@
         <v>46259</v>
       </c>
       <c r="AH116">
-        <v>4.5287671232876709</v>
+        <v>4.528767123287671</v>
       </c>
       <c r="AI116">
         <v>21</v>
@@ -19303,7 +19279,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="117" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:43">
       <c r="B117">
         <v>1336</v>
       </c>
@@ -19431,7 +19407,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="118" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:43">
       <c r="A118">
         <v>113</v>
       </c>
@@ -19562,7 +19538,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="119" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:43">
       <c r="A119">
         <v>114</v>
       </c>
@@ -19663,7 +19639,7 @@
         <v>46259</v>
       </c>
       <c r="AH119">
-        <v>2.6301369863013702</v>
+        <v>2.63013698630137</v>
       </c>
       <c r="AI119">
         <v>21</v>
@@ -19693,7 +19669,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="120" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:43">
       <c r="A120">
         <v>115</v>
       </c>
@@ -19794,7 +19770,7 @@
         <v>46259</v>
       </c>
       <c r="AH120">
-        <v>2.4109589041095889</v>
+        <v>2.410958904109589</v>
       </c>
       <c r="AI120">
         <v>21</v>
@@ -19824,7 +19800,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="121" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:43">
       <c r="A121">
         <v>116</v>
       </c>
@@ -19955,7 +19931,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="122" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:43">
       <c r="A122">
         <v>117</v>
       </c>
@@ -20086,7 +20062,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="123" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:43">
       <c r="A123">
         <v>118</v>
       </c>
@@ -20217,7 +20193,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="124" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:43">
       <c r="A124">
         <v>119</v>
       </c>
@@ -20318,7 +20294,7 @@
         <v>46259</v>
       </c>
       <c r="AH124">
-        <v>2.2630136986301368</v>
+        <v>2.263013698630137</v>
       </c>
       <c r="AI124">
         <v>21</v>
@@ -20348,7 +20324,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="125" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:43">
       <c r="A125">
         <v>120</v>
       </c>
@@ -20449,7 +20425,7 @@
         <v>46259</v>
       </c>
       <c r="AH125">
-        <v>6.5863013698630137</v>
+        <v>6.586301369863014</v>
       </c>
       <c r="AI125">
         <v>30</v>
@@ -20479,7 +20455,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="126" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:43">
       <c r="A126">
         <v>120</v>
       </c>
@@ -20502,7 +20478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:43">
       <c r="A127">
         <v>121</v>
       </c>
@@ -20603,7 +20579,7 @@
         <v>46259</v>
       </c>
       <c r="AH127">
-        <v>12.265753424657531</v>
+        <v>12.26575342465753</v>
       </c>
       <c r="AI127">
         <v>30</v>
@@ -20633,7 +20609,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="128" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:43">
       <c r="A128">
         <v>122</v>
       </c>
@@ -20734,7 +20710,7 @@
         <v>46259</v>
       </c>
       <c r="AH128">
-        <v>5.9643835616438352</v>
+        <v>5.964383561643835</v>
       </c>
       <c r="AI128">
         <v>30</v>
@@ -20764,7 +20740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:43">
       <c r="A129">
         <v>123</v>
       </c>
@@ -20865,7 +20841,7 @@
         <v>46259</v>
       </c>
       <c r="AH129">
-        <v>5.7972602739726016</v>
+        <v>5.797260273972602</v>
       </c>
       <c r="AI129">
         <v>21</v>
@@ -20895,7 +20871,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="130" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:43">
       <c r="A130">
         <v>124</v>
       </c>
@@ -20996,7 +20972,7 @@
         <v>46259</v>
       </c>
       <c r="AH130">
-        <v>5.1534246575342468</v>
+        <v>5.153424657534247</v>
       </c>
       <c r="AI130">
         <v>30</v>
@@ -21026,7 +21002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:43">
       <c r="A131">
         <v>125</v>
       </c>
@@ -21127,7 +21103,7 @@
         <v>46259</v>
       </c>
       <c r="AH131">
-        <v>5.1780821917808222</v>
+        <v>5.178082191780822</v>
       </c>
       <c r="AI131">
         <v>30</v>
@@ -21157,7 +21133,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="132" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:43">
       <c r="B132">
         <v>1135</v>
       </c>
@@ -21255,7 +21231,7 @@
         <v>46259</v>
       </c>
       <c r="AH132">
-        <v>0.15068493150684931</v>
+        <v>0.1506849315068493</v>
       </c>
       <c r="AI132">
         <v>21</v>
@@ -21285,7 +21261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:43">
       <c r="A133">
         <v>126</v>
       </c>
@@ -21386,7 +21362,7 @@
         <v>46259</v>
       </c>
       <c r="AH133">
-        <v>4.2356164383561641</v>
+        <v>4.235616438356164</v>
       </c>
       <c r="AI133">
         <v>21</v>
@@ -21416,7 +21392,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="134" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:43">
       <c r="A134">
         <v>127</v>
       </c>
@@ -21517,7 +21493,7 @@
         <v>46259</v>
       </c>
       <c r="AH134">
-        <v>4.2356164383561641</v>
+        <v>4.235616438356164</v>
       </c>
       <c r="AI134">
         <v>21</v>
@@ -21547,7 +21523,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="135" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:43">
       <c r="A135">
         <v>128</v>
       </c>
@@ -21648,7 +21624,7 @@
         <v>46259</v>
       </c>
       <c r="AH135">
-        <v>4.7232876712328764</v>
+        <v>4.723287671232876</v>
       </c>
       <c r="AI135">
         <v>21</v>
@@ -21678,7 +21654,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="136" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:43">
       <c r="A136">
         <v>129</v>
       </c>
@@ -21779,7 +21755,7 @@
         <v>46259</v>
       </c>
       <c r="AH136">
-        <v>4.2904109589041104</v>
+        <v>4.29041095890411</v>
       </c>
       <c r="AI136">
         <v>21</v>
@@ -21809,7 +21785,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="137" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:43">
       <c r="A137">
         <v>130</v>
       </c>
@@ -21910,7 +21886,7 @@
         <v>46259</v>
       </c>
       <c r="AH137">
-        <v>4.5534246575342463</v>
+        <v>4.553424657534246</v>
       </c>
       <c r="AI137">
         <v>21</v>
@@ -21940,7 +21916,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="138" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:43">
       <c r="A138">
         <v>131</v>
       </c>
@@ -22041,7 +22017,7 @@
         <v>46259</v>
       </c>
       <c r="AH138">
-        <v>1.4986301369863011</v>
+        <v>1.498630136986301</v>
       </c>
       <c r="AI138">
         <v>21</v>
@@ -22071,7 +22047,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="139" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:43">
       <c r="A139">
         <v>132</v>
       </c>
@@ -22202,7 +22178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:43">
       <c r="A140">
         <v>133</v>
       </c>
@@ -22333,7 +22309,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="141" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:43">
       <c r="A141">
         <v>134</v>
       </c>
@@ -22464,7 +22440,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="142" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:43">
       <c r="A142">
         <v>135</v>
       </c>
@@ -22595,7 +22571,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="143" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:43">
       <c r="A143">
         <v>136</v>
       </c>
@@ -22696,7 +22672,7 @@
         <v>46259</v>
       </c>
       <c r="AH143">
-        <v>4.4876712328767123</v>
+        <v>4.487671232876712</v>
       </c>
       <c r="AI143">
         <v>21</v>
@@ -22726,7 +22702,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="144" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:43">
       <c r="A144">
         <v>137</v>
       </c>
@@ -22827,7 +22803,7 @@
         <v>46259</v>
       </c>
       <c r="AH144">
-        <v>4.4684931506849317</v>
+        <v>4.468493150684932</v>
       </c>
       <c r="AI144">
         <v>21</v>
@@ -22857,7 +22833,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="145" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:43">
       <c r="A145">
         <v>138</v>
       </c>
@@ -22958,7 +22934,7 @@
         <v>46259</v>
       </c>
       <c r="AH145">
-        <v>1.8575342465753419</v>
+        <v>1.857534246575342</v>
       </c>
       <c r="AI145">
         <v>21</v>
@@ -22988,7 +22964,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="146" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:43">
       <c r="A146">
         <v>139</v>
       </c>
@@ -23089,7 +23065,7 @@
         <v>46259</v>
       </c>
       <c r="AH146">
-        <v>4.3890410958904109</v>
+        <v>4.389041095890411</v>
       </c>
       <c r="AI146">
         <v>21</v>
@@ -23119,7 +23095,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="147" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:43">
       <c r="A147">
         <v>140</v>
       </c>
@@ -23220,7 +23196,7 @@
         <v>46259</v>
       </c>
       <c r="AH147">
-        <v>3.7917808219178082</v>
+        <v>3.791780821917808</v>
       </c>
       <c r="AI147">
         <v>21</v>
@@ -23250,7 +23226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:43">
       <c r="A148">
         <v>141</v>
       </c>
@@ -23351,7 +23327,7 @@
         <v>46259</v>
       </c>
       <c r="AH148">
-        <v>3.7863013698630139</v>
+        <v>3.786301369863014</v>
       </c>
       <c r="AI148">
         <v>21</v>
@@ -23381,7 +23357,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="149" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:43">
       <c r="A149">
         <v>142</v>
       </c>
@@ -23482,7 +23458,7 @@
         <v>46259</v>
       </c>
       <c r="AH149">
-        <v>3.7369863013698632</v>
+        <v>3.736986301369863</v>
       </c>
       <c r="AI149">
         <v>21</v>
@@ -23512,7 +23488,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="150" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:43">
       <c r="A150">
         <v>143</v>
       </c>
@@ -23613,7 +23589,7 @@
         <v>46259</v>
       </c>
       <c r="AH150">
-        <v>2.5452054794520551</v>
+        <v>2.545205479452055</v>
       </c>
       <c r="AI150">
         <v>21</v>
@@ -23643,7 +23619,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="151" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:43">
       <c r="A151">
         <v>144</v>
       </c>
@@ -23744,7 +23720,7 @@
         <v>46259</v>
       </c>
       <c r="AH151">
-        <v>5.9671232876712326</v>
+        <v>5.967123287671233</v>
       </c>
       <c r="AI151">
         <v>21</v>
@@ -23774,7 +23750,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="152" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:43">
       <c r="A152">
         <v>145</v>
       </c>
@@ -23875,7 +23851,7 @@
         <v>46259</v>
       </c>
       <c r="AH152">
-        <v>3.1013698630136992</v>
+        <v>3.101369863013699</v>
       </c>
       <c r="AI152">
         <v>21</v>
@@ -23905,7 +23881,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="153" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:43">
       <c r="A153">
         <v>146</v>
       </c>
@@ -24006,7 +23982,7 @@
         <v>46259</v>
       </c>
       <c r="AH153">
-        <v>5.6493150684931503</v>
+        <v>5.64931506849315</v>
       </c>
       <c r="AI153">
         <v>21</v>
@@ -24036,7 +24012,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="154" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:43">
       <c r="A154">
         <v>147</v>
       </c>
@@ -24137,7 +24113,7 @@
         <v>46259</v>
       </c>
       <c r="AH154">
-        <v>5.4027397260273968</v>
+        <v>5.402739726027397</v>
       </c>
       <c r="AI154">
         <v>21</v>
@@ -24167,7 +24143,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="155" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:43">
       <c r="A155">
         <v>148</v>
       </c>
@@ -24268,7 +24244,7 @@
         <v>46259</v>
       </c>
       <c r="AH155">
-        <v>5.3095890410958901</v>
+        <v>5.30958904109589</v>
       </c>
       <c r="AI155">
         <v>21</v>
@@ -24298,7 +24274,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="156" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:43">
       <c r="A156">
         <v>149</v>
       </c>
@@ -24399,7 +24375,7 @@
         <v>46259</v>
       </c>
       <c r="AH156">
-        <v>5.0383561643835613</v>
+        <v>5.038356164383561</v>
       </c>
       <c r="AI156">
         <v>21</v>
@@ -24429,7 +24405,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="157" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:43">
       <c r="A157">
         <v>150</v>
       </c>
@@ -24530,7 +24506,7 @@
         <v>46259</v>
       </c>
       <c r="AH157">
-        <v>5.0383561643835613</v>
+        <v>5.038356164383561</v>
       </c>
       <c r="AI157">
         <v>21</v>
@@ -24560,7 +24536,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="158" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:43">
       <c r="A158">
         <v>151</v>
       </c>
@@ -24661,7 +24637,7 @@
         <v>46259</v>
       </c>
       <c r="AH158">
-        <v>5.0383561643835613</v>
+        <v>5.038356164383561</v>
       </c>
       <c r="AI158">
         <v>21</v>
@@ -24691,7 +24667,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="159" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:43">
       <c r="A159">
         <v>152</v>
       </c>
@@ -24792,7 +24768,7 @@
         <v>46259</v>
       </c>
       <c r="AH159">
-        <v>5.0383561643835613</v>
+        <v>5.038356164383561</v>
       </c>
       <c r="AI159">
         <v>21</v>
@@ -24822,7 +24798,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="160" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:43">
       <c r="A160">
         <v>153</v>
       </c>
@@ -24923,7 +24899,7 @@
         <v>46259</v>
       </c>
       <c r="AH160">
-        <v>1.8301369863013699</v>
+        <v>1.83013698630137</v>
       </c>
       <c r="AI160">
         <v>21</v>
@@ -24953,7 +24929,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="161" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:43">
       <c r="A161">
         <v>154</v>
       </c>
@@ -25054,7 +25030,7 @@
         <v>46259</v>
       </c>
       <c r="AH161">
-        <v>4.5287671232876709</v>
+        <v>4.528767123287671</v>
       </c>
       <c r="AI161">
         <v>21</v>
@@ -25084,7 +25060,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="162" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:43">
       <c r="A162">
         <v>155</v>
       </c>
@@ -25185,7 +25161,7 @@
         <v>46259</v>
       </c>
       <c r="AH162">
-        <v>4.3890410958904109</v>
+        <v>4.389041095890411</v>
       </c>
       <c r="AI162">
         <v>21</v>
@@ -25215,7 +25191,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="163" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:43">
       <c r="A163">
         <v>156</v>
       </c>
@@ -25316,7 +25292,7 @@
         <v>46259</v>
       </c>
       <c r="AH163">
-        <v>4.3890410958904109</v>
+        <v>4.389041095890411</v>
       </c>
       <c r="AI163">
         <v>21</v>
@@ -25346,7 +25322,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="164" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:43">
       <c r="A164">
         <v>157</v>
       </c>
@@ -25477,7 +25453,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="165" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:43">
       <c r="A165">
         <v>158</v>
       </c>
@@ -25578,7 +25554,7 @@
         <v>46259</v>
       </c>
       <c r="AH165">
-        <v>3.9945205479452048</v>
+        <v>3.994520547945205</v>
       </c>
       <c r="AI165">
         <v>21</v>
@@ -25608,7 +25584,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="166" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:43">
       <c r="A166">
         <v>159</v>
       </c>
@@ -25709,7 +25685,7 @@
         <v>46259</v>
       </c>
       <c r="AH166">
-        <v>3.9643835616438361</v>
+        <v>3.964383561643836</v>
       </c>
       <c r="AI166">
         <v>21</v>
@@ -25739,7 +25715,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="167" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:43">
       <c r="A167">
         <v>161</v>
       </c>
@@ -25840,7 +25816,7 @@
         <v>46259</v>
       </c>
       <c r="AH167">
-        <v>2.3397260273972602</v>
+        <v>2.33972602739726</v>
       </c>
       <c r="AI167">
         <v>21</v>
@@ -25870,7 +25846,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="168" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:43">
       <c r="A168">
         <v>162</v>
       </c>
@@ -25971,7 +25947,7 @@
         <v>46259</v>
       </c>
       <c r="AH168">
-        <v>13.547945205479451</v>
+        <v>13.54794520547945</v>
       </c>
       <c r="AI168">
         <v>30</v>
@@ -26001,7 +25977,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="169" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:43">
       <c r="A169">
         <v>163</v>
       </c>
@@ -26102,7 +26078,7 @@
         <v>46259</v>
       </c>
       <c r="AH169">
-        <v>5.1534246575342468</v>
+        <v>5.153424657534247</v>
       </c>
       <c r="AI169">
         <v>30</v>
@@ -26132,7 +26108,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="170" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:43">
       <c r="A170">
         <v>164</v>
       </c>
@@ -26233,7 +26209,7 @@
         <v>46259</v>
       </c>
       <c r="AH170">
-        <v>5.3452054794520549</v>
+        <v>5.345205479452055</v>
       </c>
       <c r="AI170">
         <v>30</v>
@@ -26263,7 +26239,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="171" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:43">
       <c r="A171">
         <v>165</v>
       </c>
@@ -26394,7 +26370,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="172" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:43">
       <c r="A172">
         <v>166</v>
       </c>
@@ -26495,7 +26471,7 @@
         <v>46259</v>
       </c>
       <c r="AH172">
-        <v>2.8438356164383558</v>
+        <v>2.843835616438356</v>
       </c>
       <c r="AI172">
         <v>21</v>
@@ -26525,7 +26501,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="173" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:43">
       <c r="A173">
         <v>167</v>
       </c>
@@ -26656,7 +26632,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="174" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:43">
       <c r="A174">
         <v>168</v>
       </c>
@@ -26757,7 +26733,7 @@
         <v>46259</v>
       </c>
       <c r="AH174">
-        <v>1.9698630136986299</v>
+        <v>1.96986301369863</v>
       </c>
       <c r="AI174">
         <v>21</v>
@@ -26787,7 +26763,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="175" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:43">
       <c r="A175">
         <v>169</v>
       </c>
@@ -26918,7 +26894,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="176" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:43">
       <c r="A176">
         <v>170</v>
       </c>
@@ -27019,7 +26995,7 @@
         <v>46259</v>
       </c>
       <c r="AH176">
-        <v>5.8767123287671232</v>
+        <v>5.876712328767123</v>
       </c>
       <c r="AI176">
         <v>30</v>
@@ -27049,7 +27025,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="177" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:43">
       <c r="A177">
         <v>171</v>
       </c>
@@ -27180,7 +27156,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="178" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:43">
       <c r="A178">
         <v>172</v>
       </c>
@@ -27281,7 +27257,7 @@
         <v>46259</v>
       </c>
       <c r="AH178">
-        <v>2.9616438356164378</v>
+        <v>2.961643835616438</v>
       </c>
       <c r="AI178">
         <v>21</v>
@@ -27311,7 +27287,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="179" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:43">
       <c r="A179">
         <v>173</v>
       </c>
@@ -27412,7 +27388,7 @@
         <v>46259</v>
       </c>
       <c r="AH179">
-        <v>2.4684931506849321</v>
+        <v>2.468493150684932</v>
       </c>
       <c r="AI179">
         <v>21</v>
@@ -27442,7 +27418,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="180" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:43">
       <c r="A180">
         <v>174</v>
       </c>
@@ -27543,7 +27519,7 @@
         <v>46259</v>
       </c>
       <c r="AH180">
-        <v>2.2520547945205478</v>
+        <v>2.252054794520548</v>
       </c>
       <c r="AI180">
         <v>21</v>
@@ -27573,7 +27549,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="181" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:43">
       <c r="A181">
         <v>175</v>
       </c>
@@ -27704,7 +27680,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="182" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:43">
       <c r="A182">
         <v>176</v>
       </c>
@@ -27835,7 +27811,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="183" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:43">
       <c r="A183">
         <v>177</v>
       </c>
@@ -27966,7 +27942,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="184" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:43">
       <c r="A184">
         <v>178</v>
       </c>
@@ -28097,7 +28073,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="185" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:43">
       <c r="A185">
         <v>179</v>
       </c>
@@ -28228,7 +28204,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="186" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:43">
       <c r="A186">
         <v>180</v>
       </c>
@@ -28329,7 +28305,7 @@
         <v>46259</v>
       </c>
       <c r="AH186">
-        <v>1.7452054794520551</v>
+        <v>1.745205479452055</v>
       </c>
       <c r="AI186">
         <v>21</v>
@@ -28359,7 +28335,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="187" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:43">
       <c r="A187">
         <v>181</v>
       </c>
@@ -28460,7 +28436,7 @@
         <v>46259</v>
       </c>
       <c r="AH187">
-        <v>1.3890410958904109</v>
+        <v>1.389041095890411</v>
       </c>
       <c r="AI187">
         <v>21</v>
@@ -28492,7 +28468,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="S170" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="S170" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Staffdata.xlsx
+++ b/Staffdata.xlsx
@@ -1,15 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3113719057d24bf/Desktop/HR-Forms-Site/HRFORMAS/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_05E48499FC67680F1964AE368160343238AA41AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91AF1319-B794-4D52-BCC5-584C93E2EB2B}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2174,7 +2185,7 @@
     <t>-</t>
   </si>
   <si>
-    <t xml:space="preserve"> 966577040481</t>
+    <t> 966577040481</t>
   </si>
   <si>
     <t>malbatil@outlook.sa</t>
@@ -2485,10 +2496,10 @@
     <t>HAMDILLHJ038@GMAIL.COM</t>
   </si>
   <si>
-    <t xml:space="preserve"> omarzar392@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ark870725@gmail.com</t>
+    <t> omarzar392@gmail.com</t>
+  </si>
+  <si>
+    <t> ark870725@gmail.com</t>
   </si>
   <si>
     <t>waelgomaa1wg@gmail.com</t>
@@ -2561,7 +2572,7 @@
     <t>INFO2@HAIL-HOUSE.SA</t>
   </si>
   <si>
-    <t xml:space="preserve"> Sarah_elkhatib@outlook.com</t>
+    <t> Sarah_elkhatib@outlook.com</t>
   </si>
   <si>
     <t xml:space="preserve"> mohannad.fakhry00@gmail.com</t>
@@ -3905,11 +3916,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3955,18 +3966,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ارتباط تشعبي" xfId="1" builtinId="8"/>
+    <cellStyle name="عادي" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4004,7 +4023,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4038,6 +4057,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4072,9 +4092,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4247,11 +4268,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AQ187"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:43">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4382,7 +4407,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:43">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4483,7 +4508,7 @@
         <v>46259</v>
       </c>
       <c r="AH2">
-        <v>8.726027397260275</v>
+        <v>8.7260273972602747</v>
       </c>
       <c r="AI2">
         <v>30</v>
@@ -4513,7 +4538,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="3" spans="1:43">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4614,7 +4639,7 @@
         <v>46259</v>
       </c>
       <c r="AH3">
-        <v>13.63561643835616</v>
+        <v>13.635616438356161</v>
       </c>
       <c r="AI3">
         <v>30</v>
@@ -4644,7 +4669,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="4" spans="1:43">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4745,7 +4770,7 @@
         <v>46259</v>
       </c>
       <c r="AH4">
-        <v>5.890410958904109</v>
+        <v>5.8904109589041092</v>
       </c>
       <c r="AI4">
         <v>30</v>
@@ -4775,7 +4800,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="5" spans="1:43">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4876,7 +4901,7 @@
         <v>46259</v>
       </c>
       <c r="AH5">
-        <v>6.046575342465753</v>
+        <v>6.0465753424657533</v>
       </c>
       <c r="AI5">
         <v>21</v>
@@ -4906,7 +4931,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="6" spans="1:43">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5007,7 +5032,7 @@
         <v>46259</v>
       </c>
       <c r="AH6">
-        <v>6.402739726027397</v>
+        <v>6.4027397260273968</v>
       </c>
       <c r="AI6">
         <v>21</v>
@@ -5037,7 +5062,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="7" spans="1:43">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5138,7 +5163,7 @@
         <v>46259</v>
       </c>
       <c r="AH7">
-        <v>5.704109589041096</v>
+        <v>5.7041095890410958</v>
       </c>
       <c r="AI7">
         <v>30</v>
@@ -5168,7 +5193,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="8" spans="1:43">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5299,7 +5324,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="9" spans="1:43">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5430,7 +5455,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="10" spans="1:43">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5531,7 +5556,7 @@
         <v>46259</v>
       </c>
       <c r="AH10">
-        <v>6.753424657534246</v>
+        <v>6.7534246575342456</v>
       </c>
       <c r="AI10">
         <v>30</v>
@@ -5561,7 +5586,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="11" spans="1:43">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5692,7 +5717,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="12" spans="1:43">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5793,7 +5818,7 @@
         <v>46259</v>
       </c>
       <c r="AH12">
-        <v>5.750684931506849</v>
+        <v>5.7506849315068491</v>
       </c>
       <c r="AI12">
         <v>21</v>
@@ -5823,7 +5848,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="13" spans="1:43">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5954,7 +5979,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="14" spans="1:43">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6055,7 +6080,7 @@
         <v>46259</v>
       </c>
       <c r="AH14">
-        <v>0.3041095890410959</v>
+        <v>0.30410958904109592</v>
       </c>
       <c r="AI14">
         <v>21</v>
@@ -6085,7 +6110,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="15" spans="1:43">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6186,7 +6211,7 @@
         <v>46259</v>
       </c>
       <c r="AH15">
-        <v>3.983561643835616</v>
+        <v>3.9835616438356158</v>
       </c>
       <c r="AI15">
         <v>21</v>
@@ -6216,7 +6241,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="16" spans="1:43">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6317,7 +6342,7 @@
         <v>46259</v>
       </c>
       <c r="AH16">
-        <v>2.898630136986301</v>
+        <v>2.8986301369863008</v>
       </c>
       <c r="AI16">
         <v>21</v>
@@ -6347,7 +6372,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="17" spans="1:43">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -6448,7 +6473,7 @@
         <v>46259</v>
       </c>
       <c r="AH17">
-        <v>1.673972602739726</v>
+        <v>1.6739726027397259</v>
       </c>
       <c r="AI17">
         <v>21</v>
@@ -6478,7 +6503,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="18" spans="1:43">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6579,7 +6604,7 @@
         <v>46259</v>
       </c>
       <c r="AH18">
-        <v>2.049315068493151</v>
+        <v>2.0493150684931511</v>
       </c>
       <c r="AI18">
         <v>21</v>
@@ -6609,7 +6634,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="19" spans="1:43">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -6710,7 +6735,7 @@
         <v>46259</v>
       </c>
       <c r="AH19">
-        <v>2.035616438356164</v>
+        <v>2.0356164383561639</v>
       </c>
       <c r="AI19">
         <v>21</v>
@@ -6740,7 +6765,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="20" spans="1:43">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -6841,7 +6866,7 @@
         <v>46259</v>
       </c>
       <c r="AH20">
-        <v>1.512328767123288</v>
+        <v>1.5123287671232879</v>
       </c>
       <c r="AI20">
         <v>21</v>
@@ -6871,7 +6896,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="21" spans="1:43">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -6972,7 +6997,7 @@
         <v>46259</v>
       </c>
       <c r="AH21">
-        <v>2.035616438356164</v>
+        <v>2.0356164383561639</v>
       </c>
       <c r="AI21">
         <v>21</v>
@@ -7002,7 +7027,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="22" spans="1:43">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -7133,7 +7158,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="23" spans="1:43">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -7264,7 +7289,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="24" spans="1:43">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -7395,7 +7420,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="25" spans="1:43">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -7496,7 +7521,7 @@
         <v>46259</v>
       </c>
       <c r="AH25">
-        <v>0.7616438356164383</v>
+        <v>0.76164383561643834</v>
       </c>
       <c r="AI25">
         <v>21</v>
@@ -7526,7 +7551,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="26" spans="1:43">
+    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -7627,7 +7652,7 @@
         <v>46259</v>
       </c>
       <c r="AH26">
-        <v>0.7616438356164383</v>
+        <v>0.76164383561643834</v>
       </c>
       <c r="AI26">
         <v>21</v>
@@ -7657,7 +7682,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="27" spans="1:43">
+    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -7758,7 +7783,7 @@
         <v>46259</v>
       </c>
       <c r="AH27">
-        <v>6.736986301369863</v>
+        <v>6.7369863013698632</v>
       </c>
       <c r="AI27">
         <v>30</v>
@@ -7788,7 +7813,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="28" spans="1:43">
+    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -7889,7 +7914,7 @@
         <v>46259</v>
       </c>
       <c r="AH28">
-        <v>12.11232876712329</v>
+        <v>12.112328767123291</v>
       </c>
       <c r="AI28">
         <v>30</v>
@@ -7919,7 +7944,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="29" spans="1:43">
+    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -8020,7 +8045,7 @@
         <v>46259</v>
       </c>
       <c r="AH29">
-        <v>3.487671232876712</v>
+        <v>3.4876712328767119</v>
       </c>
       <c r="AI29">
         <v>21</v>
@@ -8050,7 +8075,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="30" spans="1:43">
+    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -8151,7 +8176,7 @@
         <v>46259</v>
       </c>
       <c r="AH30">
-        <v>15.07671232876712</v>
+        <v>15.076712328767121</v>
       </c>
       <c r="AI30">
         <v>30</v>
@@ -8181,7 +8206,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="31" spans="1:43">
+    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -8282,7 +8307,7 @@
         <v>46259</v>
       </c>
       <c r="AH31">
-        <v>15.07671232876712</v>
+        <v>15.076712328767121</v>
       </c>
       <c r="AI31">
         <v>30</v>
@@ -8312,7 +8337,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="32" spans="1:43">
+    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -8443,7 +8468,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="33" spans="1:43">
+    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -8544,7 +8569,7 @@
         <v>46259</v>
       </c>
       <c r="AH33">
-        <v>15.16712328767123</v>
+        <v>15.167123287671229</v>
       </c>
       <c r="AI33">
         <v>30</v>
@@ -8574,7 +8599,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="34" spans="1:43">
+    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -8675,7 +8700,7 @@
         <v>46259</v>
       </c>
       <c r="AH34">
-        <v>4.610958904109589</v>
+        <v>4.6109589041095891</v>
       </c>
       <c r="AI34">
         <v>21</v>
@@ -8705,7 +8730,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="35" spans="1:43">
+    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -8806,7 +8831,7 @@
         <v>46259</v>
       </c>
       <c r="AH35">
-        <v>4.542465753424658</v>
+        <v>4.5424657534246577</v>
       </c>
       <c r="AI35">
         <v>21</v>
@@ -8836,7 +8861,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="36" spans="1:43">
+    <row r="36" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -8937,7 +8962,7 @@
         <v>46259</v>
       </c>
       <c r="AH36">
-        <v>13.24109589041096</v>
+        <v>13.241095890410961</v>
       </c>
       <c r="AI36">
         <v>30</v>
@@ -8967,7 +8992,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="37" spans="1:43">
+    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -9098,7 +9123,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="38" spans="1:43">
+    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -9229,7 +9254,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="39" spans="1:43">
+    <row r="39" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -9330,7 +9355,7 @@
         <v>46259</v>
       </c>
       <c r="AH39">
-        <v>6.70958904109589</v>
+        <v>6.7095890410958896</v>
       </c>
       <c r="AI39">
         <v>30</v>
@@ -9360,7 +9385,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="40" spans="1:43">
+    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -9461,7 +9486,7 @@
         <v>46259</v>
       </c>
       <c r="AH40">
-        <v>6.50958904109589</v>
+        <v>6.5095890410958903</v>
       </c>
       <c r="AI40">
         <v>30</v>
@@ -9491,7 +9516,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="41" spans="1:43">
+    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -9592,7 +9617,7 @@
         <v>46259</v>
       </c>
       <c r="AH41">
-        <v>6.550684931506849</v>
+        <v>6.5506849315068489</v>
       </c>
       <c r="AI41">
         <v>21</v>
@@ -9622,7 +9647,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="42" spans="1:43">
+    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -9753,7 +9778,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="43" spans="1:43">
+    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -9854,7 +9879,7 @@
         <v>46259</v>
       </c>
       <c r="AH43">
-        <v>8.753424657534246</v>
+        <v>8.7534246575342465</v>
       </c>
       <c r="AI43">
         <v>30</v>
@@ -9884,7 +9909,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="44" spans="1:43">
+    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -9985,7 +10010,7 @@
         <v>46259</v>
       </c>
       <c r="AH44">
-        <v>5.753424657534246</v>
+        <v>5.7534246575342456</v>
       </c>
       <c r="AI44">
         <v>21</v>
@@ -10015,7 +10040,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="45" spans="1:43">
+    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -10116,7 +10141,7 @@
         <v>46259</v>
       </c>
       <c r="AH45">
-        <v>5.734246575342466</v>
+        <v>5.7342465753424658</v>
       </c>
       <c r="AI45">
         <v>21</v>
@@ -10146,7 +10171,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="46" spans="1:43">
+    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -10247,7 +10272,7 @@
         <v>46259</v>
       </c>
       <c r="AH46">
-        <v>5.627397260273972</v>
+        <v>5.6273972602739724</v>
       </c>
       <c r="AI46">
         <v>30</v>
@@ -10277,7 +10302,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="47" spans="1:43">
+    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -10378,7 +10403,7 @@
         <v>46259</v>
       </c>
       <c r="AH47">
-        <v>4.227397260273973</v>
+        <v>4.2273972602739729</v>
       </c>
       <c r="AI47">
         <v>21</v>
@@ -10408,7 +10433,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="48" spans="1:43">
+    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -10539,7 +10564,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="49" spans="1:43">
+    <row r="49" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -10640,7 +10665,7 @@
         <v>46259</v>
       </c>
       <c r="AH49">
-        <v>4.158904109589041</v>
+        <v>4.1589041095890407</v>
       </c>
       <c r="AI49">
         <v>21</v>
@@ -10670,7 +10695,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="50" spans="1:43">
+    <row r="50" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -10771,7 +10796,7 @@
         <v>46259</v>
       </c>
       <c r="AH50">
-        <v>3.986301369863014</v>
+        <v>3.9863013698630141</v>
       </c>
       <c r="AI50">
         <v>21</v>
@@ -10801,7 +10826,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="51" spans="1:43">
+    <row r="51" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -10902,7 +10927,7 @@
         <v>46259</v>
       </c>
       <c r="AH51">
-        <v>3.964383561643836</v>
+        <v>3.9643835616438361</v>
       </c>
       <c r="AI51">
         <v>21</v>
@@ -10932,7 +10957,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="52" spans="1:43">
+    <row r="52" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -11033,7 +11058,7 @@
         <v>46259</v>
       </c>
       <c r="AH52">
-        <v>3.964383561643836</v>
+        <v>3.9643835616438361</v>
       </c>
       <c r="AI52">
         <v>21</v>
@@ -11063,7 +11088,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="53" spans="1:43">
+    <row r="53" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -11194,7 +11219,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="54" spans="1:43">
+    <row r="54" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -11295,7 +11320,7 @@
         <v>46259</v>
       </c>
       <c r="AH54">
-        <v>1.96986301369863</v>
+        <v>1.9698630136986299</v>
       </c>
       <c r="AI54">
         <v>21</v>
@@ -11325,7 +11350,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="55" spans="1:43">
+    <row r="55" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -11426,7 +11451,7 @@
         <v>46259</v>
       </c>
       <c r="AH55">
-        <v>0.5835616438356165</v>
+        <v>0.58356164383561648</v>
       </c>
       <c r="AI55">
         <v>21</v>
@@ -11456,7 +11481,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="56" spans="1:43">
+    <row r="56" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -11557,7 +11582,7 @@
         <v>46259</v>
       </c>
       <c r="AH56">
-        <v>0.5835616438356165</v>
+        <v>0.58356164383561648</v>
       </c>
       <c r="AI56">
         <v>21</v>
@@ -11587,7 +11612,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="57" spans="1:43">
+    <row r="57" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -11688,7 +11713,7 @@
         <v>46259</v>
       </c>
       <c r="AH57">
-        <v>7.150684931506849</v>
+        <v>7.1506849315068486</v>
       </c>
       <c r="AI57">
         <v>30</v>
@@ -11718,7 +11743,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="58" spans="1:43">
+    <row r="58" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -11819,7 +11844,7 @@
         <v>46259</v>
       </c>
       <c r="AH58">
-        <v>7.482191780821918</v>
+        <v>7.4821917808219176</v>
       </c>
       <c r="AI58">
         <v>30</v>
@@ -11849,7 +11874,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="59" spans="1:43">
+    <row r="59" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -11950,7 +11975,7 @@
         <v>46259</v>
       </c>
       <c r="AH59">
-        <v>0.06575342465753424</v>
+        <v>6.575342465753424E-2</v>
       </c>
       <c r="AI59">
         <v>21</v>
@@ -11980,7 +12005,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="60" spans="1:43">
+    <row r="60" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -12081,7 +12106,7 @@
         <v>46259</v>
       </c>
       <c r="AH60">
-        <v>0.06575342465753424</v>
+        <v>6.575342465753424E-2</v>
       </c>
       <c r="AI60">
         <v>21</v>
@@ -12111,7 +12136,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="61" spans="1:43">
+    <row r="61" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>58</v>
       </c>
@@ -12212,7 +12237,7 @@
         <v>46259</v>
       </c>
       <c r="AH61">
-        <v>18.26301369863014</v>
+        <v>18.263013698630139</v>
       </c>
       <c r="AI61">
         <v>30</v>
@@ -12242,7 +12267,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="62" spans="1:43">
+    <row r="62" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>59</v>
       </c>
@@ -12343,7 +12368,7 @@
         <v>46259</v>
       </c>
       <c r="AH62">
-        <v>15.07671232876712</v>
+        <v>15.076712328767121</v>
       </c>
       <c r="AI62">
         <v>30</v>
@@ -12373,7 +12398,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="63" spans="1:43">
+    <row r="63" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>60</v>
       </c>
@@ -12474,7 +12499,7 @@
         <v>46259</v>
       </c>
       <c r="AH63">
-        <v>34.04931506849315</v>
+        <v>34.049315068493151</v>
       </c>
       <c r="AI63">
         <v>30</v>
@@ -12504,7 +12529,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="64" spans="1:43">
+    <row r="64" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>61</v>
       </c>
@@ -12605,7 +12630,7 @@
         <v>46259</v>
       </c>
       <c r="AH64">
-        <v>6.175342465753425</v>
+        <v>6.1753424657534248</v>
       </c>
       <c r="AI64">
         <v>30</v>
@@ -12635,7 +12660,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="65" spans="1:43">
+    <row r="65" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>62</v>
       </c>
@@ -12736,7 +12761,7 @@
         <v>46259</v>
       </c>
       <c r="AH65">
-        <v>1.873972602739726</v>
+        <v>1.8739726027397261</v>
       </c>
       <c r="AI65">
         <v>21</v>
@@ -12766,7 +12791,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="66" spans="1:43">
+    <row r="66" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
@@ -12867,7 +12892,7 @@
         <v>46259</v>
       </c>
       <c r="AH66">
-        <v>5.753424657534246</v>
+        <v>5.7534246575342456</v>
       </c>
       <c r="AI66">
         <v>21</v>
@@ -12897,7 +12922,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="67" spans="1:43">
+    <row r="67" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>64</v>
       </c>
@@ -12998,7 +13023,7 @@
         <v>46259</v>
       </c>
       <c r="AH67">
-        <v>18.04657534246575</v>
+        <v>18.046575342465751</v>
       </c>
       <c r="AI67">
         <v>30</v>
@@ -13028,7 +13053,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="68" spans="1:43">
+    <row r="68" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>65</v>
       </c>
@@ -13129,7 +13154,7 @@
         <v>46259</v>
       </c>
       <c r="AH68">
-        <v>9.531506849315068</v>
+        <v>9.5315068493150683</v>
       </c>
       <c r="AI68">
         <v>30</v>
@@ -13159,7 +13184,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="69" spans="1:43">
+    <row r="69" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>66</v>
       </c>
@@ -13290,7 +13315,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="70" spans="1:43">
+    <row r="70" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>67</v>
       </c>
@@ -13391,7 +13416,7 @@
         <v>46259</v>
       </c>
       <c r="AH70">
-        <v>10.60821917808219</v>
+        <v>10.608219178082191</v>
       </c>
       <c r="AI70">
         <v>30</v>
@@ -13421,7 +13446,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="71" spans="1:43">
+    <row r="71" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>68</v>
       </c>
@@ -13522,7 +13547,7 @@
         <v>46259</v>
       </c>
       <c r="AH71">
-        <v>0.3342465753424658</v>
+        <v>0.33424657534246582</v>
       </c>
       <c r="AI71">
         <v>21</v>
@@ -13552,7 +13577,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="72" spans="1:43">
+    <row r="72" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>69</v>
       </c>
@@ -13653,7 +13678,7 @@
         <v>46259</v>
       </c>
       <c r="AH72">
-        <v>0.3342465753424658</v>
+        <v>0.33424657534246582</v>
       </c>
       <c r="AI72">
         <v>21</v>
@@ -13683,7 +13708,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="73" spans="1:43">
+    <row r="73" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>70</v>
       </c>
@@ -13784,7 +13809,7 @@
         <v>46259</v>
       </c>
       <c r="AH73">
-        <v>2.96986301369863</v>
+        <v>2.9698630136986299</v>
       </c>
       <c r="AI73">
         <v>21</v>
@@ -13814,7 +13839,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="74" spans="1:43">
+    <row r="74" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>71</v>
       </c>
@@ -13945,7 +13970,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="75" spans="1:43">
+    <row r="75" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>72</v>
       </c>
@@ -14046,7 +14071,7 @@
         <v>46259</v>
       </c>
       <c r="AH75">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AI75">
         <v>21</v>
@@ -14076,7 +14101,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="76" spans="1:43">
+    <row r="76" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>73</v>
       </c>
@@ -14177,7 +14202,7 @@
         <v>46259</v>
       </c>
       <c r="AH76">
-        <v>4.068493150684931</v>
+        <v>4.0684931506849313</v>
       </c>
       <c r="AI76">
         <v>21</v>
@@ -14207,7 +14232,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="77" spans="1:43">
+    <row r="77" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>74</v>
       </c>
@@ -14338,7 +14363,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="78" spans="1:43">
+    <row r="78" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>75</v>
       </c>
@@ -14469,7 +14494,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="79" spans="1:43">
+    <row r="79" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>76</v>
       </c>
@@ -14570,7 +14595,7 @@
         <v>46259</v>
       </c>
       <c r="AH79">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AI79">
         <v>21</v>
@@ -14600,7 +14625,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="80" spans="1:43">
+    <row r="80" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>77</v>
       </c>
@@ -14701,7 +14726,7 @@
         <v>46259</v>
       </c>
       <c r="AH80">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AI80">
         <v>21</v>
@@ -14731,7 +14756,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="81" spans="1:43">
+    <row r="81" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>78</v>
       </c>
@@ -14832,7 +14857,7 @@
         <v>46259</v>
       </c>
       <c r="AH81">
-        <v>1.819178082191781</v>
+        <v>1.8191780821917809</v>
       </c>
       <c r="AI81">
         <v>21</v>
@@ -14862,7 +14887,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="82" spans="1:43">
+    <row r="82" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>79</v>
       </c>
@@ -14963,7 +14988,7 @@
         <v>46259</v>
       </c>
       <c r="AH82">
-        <v>1.654794520547945</v>
+        <v>1.6547945205479451</v>
       </c>
       <c r="AI82">
         <v>21</v>
@@ -14993,7 +15018,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="83" spans="1:43">
+    <row r="83" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>80</v>
       </c>
@@ -15094,7 +15119,7 @@
         <v>46259</v>
       </c>
       <c r="AH83">
-        <v>15.16712328767123</v>
+        <v>15.167123287671229</v>
       </c>
       <c r="AI83">
         <v>30</v>
@@ -15124,7 +15149,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="84" spans="1:43">
+    <row r="84" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>80</v>
       </c>
@@ -15165,7 +15190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:43">
+    <row r="85" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>81</v>
       </c>
@@ -15266,7 +15291,7 @@
         <v>46259</v>
       </c>
       <c r="AH85">
-        <v>8.975342465753425</v>
+        <v>8.9753424657534246</v>
       </c>
       <c r="AI85">
         <v>30</v>
@@ -15296,7 +15321,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="86" spans="1:43">
+    <row r="86" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>82</v>
       </c>
@@ -15397,7 +15422,7 @@
         <v>46259</v>
       </c>
       <c r="AH86">
-        <v>6.70958904109589</v>
+        <v>6.7095890410958896</v>
       </c>
       <c r="AI86">
         <v>30</v>
@@ -15427,7 +15452,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="87" spans="1:43">
+    <row r="87" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>83</v>
       </c>
@@ -15528,7 +15553,7 @@
         <v>46259</v>
       </c>
       <c r="AH87">
-        <v>9.323287671232876</v>
+        <v>9.3232876712328761</v>
       </c>
       <c r="AI87">
         <v>30</v>
@@ -15558,7 +15583,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="88" spans="1:43">
+    <row r="88" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>84</v>
       </c>
@@ -15659,7 +15684,7 @@
         <v>46259</v>
       </c>
       <c r="AH88">
-        <v>14.03561643835616</v>
+        <v>14.035616438356159</v>
       </c>
       <c r="AI88">
         <v>30</v>
@@ -15689,7 +15714,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="89" spans="1:43">
+    <row r="89" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>85</v>
       </c>
@@ -15790,7 +15815,7 @@
         <v>46259</v>
       </c>
       <c r="AH89">
-        <v>1.772602739726027</v>
+        <v>1.7726027397260271</v>
       </c>
       <c r="AI89">
         <v>21</v>
@@ -15820,7 +15845,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="90" spans="1:43">
+    <row r="90" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>86</v>
       </c>
@@ -15921,7 +15946,7 @@
         <v>46259</v>
       </c>
       <c r="AH90">
-        <v>8.408219178082192</v>
+        <v>8.4082191780821915</v>
       </c>
       <c r="AI90">
         <v>30</v>
@@ -15951,7 +15976,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="91" spans="1:43">
+    <row r="91" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>87</v>
       </c>
@@ -16052,7 +16077,7 @@
         <v>46259</v>
       </c>
       <c r="AH91">
-        <v>10.95068493150685</v>
+        <v>10.950684931506849</v>
       </c>
       <c r="AI91">
         <v>30</v>
@@ -16082,7 +16107,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="92" spans="1:43">
+    <row r="92" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>88</v>
       </c>
@@ -16183,7 +16208,7 @@
         <v>46259</v>
       </c>
       <c r="AH92">
-        <v>6.682191780821918</v>
+        <v>6.6821917808219178</v>
       </c>
       <c r="AI92">
         <v>21</v>
@@ -16213,7 +16238,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="93" spans="1:43">
+    <row r="93" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>89</v>
       </c>
@@ -16314,7 +16339,7 @@
         <v>46259</v>
       </c>
       <c r="AH93">
-        <v>5.627397260273972</v>
+        <v>5.6273972602739724</v>
       </c>
       <c r="AI93">
         <v>21</v>
@@ -16344,7 +16369,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="94" spans="1:43">
+    <row r="94" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>90</v>
       </c>
@@ -16445,7 +16470,7 @@
         <v>46259</v>
       </c>
       <c r="AH94">
-        <v>5.315068493150685</v>
+        <v>5.3150684931506849</v>
       </c>
       <c r="AI94">
         <v>30</v>
@@ -16475,7 +16500,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="95" spans="1:43">
+    <row r="95" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>91</v>
       </c>
@@ -16576,7 +16601,7 @@
         <v>46259</v>
       </c>
       <c r="AH95">
-        <v>5.06027397260274</v>
+        <v>5.0602739726027401</v>
       </c>
       <c r="AI95">
         <v>30</v>
@@ -16606,7 +16631,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="96" spans="1:43">
+    <row r="96" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>92</v>
       </c>
@@ -16707,7 +16732,7 @@
         <v>46259</v>
       </c>
       <c r="AH96">
-        <v>5.06027397260274</v>
+        <v>5.0602739726027401</v>
       </c>
       <c r="AI96">
         <v>21</v>
@@ -16737,7 +16762,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="97" spans="1:43">
+    <row r="97" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>93</v>
       </c>
@@ -16838,7 +16863,7 @@
         <v>46259</v>
       </c>
       <c r="AH97">
-        <v>4.753424657534246</v>
+        <v>4.7534246575342456</v>
       </c>
       <c r="AI97">
         <v>21</v>
@@ -16868,7 +16893,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="98" spans="1:43">
+    <row r="98" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>94</v>
       </c>
@@ -16969,7 +16994,7 @@
         <v>46259</v>
       </c>
       <c r="AH98">
-        <v>0.5835616438356165</v>
+        <v>0.58356164383561648</v>
       </c>
       <c r="AI98">
         <v>21</v>
@@ -16999,7 +17024,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="99" spans="1:43">
+    <row r="99" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>95</v>
       </c>
@@ -17100,7 +17125,7 @@
         <v>46259</v>
       </c>
       <c r="AH99">
-        <v>0.5835616438356165</v>
+        <v>0.58356164383561648</v>
       </c>
       <c r="AI99">
         <v>21</v>
@@ -17130,7 +17155,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="100" spans="1:43">
+    <row r="100" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>96</v>
       </c>
@@ -17231,7 +17256,7 @@
         <v>46259</v>
       </c>
       <c r="AH100">
-        <v>4.739726027397261</v>
+        <v>4.7397260273972606</v>
       </c>
       <c r="AI100">
         <v>21</v>
@@ -17261,7 +17286,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="101" spans="1:43">
+    <row r="101" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>97</v>
       </c>
@@ -17362,7 +17387,7 @@
         <v>46259</v>
       </c>
       <c r="AH101">
-        <v>4.67945205479452</v>
+        <v>4.6794520547945204</v>
       </c>
       <c r="AI101">
         <v>21</v>
@@ -17392,7 +17417,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="102" spans="1:43">
+    <row r="102" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>98</v>
       </c>
@@ -17493,7 +17518,7 @@
         <v>46259</v>
       </c>
       <c r="AH102">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AI102">
         <v>21</v>
@@ -17523,7 +17548,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="103" spans="1:43">
+    <row r="103" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>99</v>
       </c>
@@ -17624,7 +17649,7 @@
         <v>46259</v>
       </c>
       <c r="AH103">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AI103">
         <v>21</v>
@@ -17654,7 +17679,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="104" spans="1:43">
+    <row r="104" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>100</v>
       </c>
@@ -17755,7 +17780,7 @@
         <v>46259</v>
       </c>
       <c r="AH104">
-        <v>3.964383561643836</v>
+        <v>3.9643835616438361</v>
       </c>
       <c r="AI104">
         <v>21</v>
@@ -17785,7 +17810,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="105" spans="1:43">
+    <row r="105" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>101</v>
       </c>
@@ -17886,7 +17911,7 @@
         <v>46259</v>
       </c>
       <c r="AH105">
-        <v>7.523287671232877</v>
+        <v>7.5232876712328771</v>
       </c>
       <c r="AI105">
         <v>30</v>
@@ -17916,7 +17941,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="106" spans="1:43">
+    <row r="106" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>102</v>
       </c>
@@ -18017,7 +18042,7 @@
         <v>46259</v>
       </c>
       <c r="AH106">
-        <v>4.972602739726027</v>
+        <v>4.9726027397260273</v>
       </c>
       <c r="AI106">
         <v>21</v>
@@ -18047,7 +18072,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="107" spans="1:43">
+    <row r="107" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>103</v>
       </c>
@@ -18148,7 +18173,7 @@
         <v>46259</v>
       </c>
       <c r="AH107">
-        <v>1.96986301369863</v>
+        <v>1.9698630136986299</v>
       </c>
       <c r="AI107">
         <v>21</v>
@@ -18178,7 +18203,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="108" spans="1:43">
+    <row r="108" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>104</v>
       </c>
@@ -18279,7 +18304,7 @@
         <v>46259</v>
       </c>
       <c r="AH108">
-        <v>22.44657534246575</v>
+        <v>22.446575342465749</v>
       </c>
       <c r="AI108">
         <v>30</v>
@@ -18309,7 +18334,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="109" spans="1:43">
+    <row r="109" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>105</v>
       </c>
@@ -18410,7 +18435,7 @@
         <v>46259</v>
       </c>
       <c r="AH109">
-        <v>3.986301369863014</v>
+        <v>3.9863013698630141</v>
       </c>
       <c r="AI109">
         <v>21</v>
@@ -18440,7 +18465,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="110" spans="1:43">
+    <row r="110" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>106</v>
       </c>
@@ -18493,7 +18518,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="111" spans="1:43">
+    <row r="111" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>107</v>
       </c>
@@ -18594,7 +18619,7 @@
         <v>46259</v>
       </c>
       <c r="AH111">
-        <v>0.3589041095890411</v>
+        <v>0.35890410958904112</v>
       </c>
       <c r="AI111">
         <v>21</v>
@@ -18624,7 +18649,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="112" spans="1:43">
+    <row r="112" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>108</v>
       </c>
@@ -18725,7 +18750,7 @@
         <v>46259</v>
       </c>
       <c r="AH112">
-        <v>5.372602739726028</v>
+        <v>5.3726027397260276</v>
       </c>
       <c r="AI112">
         <v>21</v>
@@ -18755,7 +18780,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="113" spans="1:43">
+    <row r="113" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>109</v>
       </c>
@@ -18856,7 +18881,7 @@
         <v>46259</v>
       </c>
       <c r="AH113">
-        <v>4.528767123287671</v>
+        <v>4.5287671232876709</v>
       </c>
       <c r="AI113">
         <v>21</v>
@@ -18886,7 +18911,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="114" spans="1:43">
+    <row r="114" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>110</v>
       </c>
@@ -18987,7 +19012,7 @@
         <v>46259</v>
       </c>
       <c r="AH114">
-        <v>4.583561643835616</v>
+        <v>4.5835616438356164</v>
       </c>
       <c r="AI114">
         <v>21</v>
@@ -19017,7 +19042,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="115" spans="1:43">
+    <row r="115" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>111</v>
       </c>
@@ -19118,7 +19143,7 @@
         <v>46259</v>
       </c>
       <c r="AH115">
-        <v>4.526027397260274</v>
+        <v>4.5260273972602736</v>
       </c>
       <c r="AI115">
         <v>21</v>
@@ -19148,7 +19173,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="116" spans="1:43">
+    <row r="116" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>112</v>
       </c>
@@ -19249,7 +19274,7 @@
         <v>46259</v>
       </c>
       <c r="AH116">
-        <v>4.528767123287671</v>
+        <v>4.5287671232876709</v>
       </c>
       <c r="AI116">
         <v>21</v>
@@ -19279,7 +19304,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="117" spans="1:43">
+    <row r="117" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B117">
         <v>1336</v>
       </c>
@@ -19407,7 +19432,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="118" spans="1:43">
+    <row r="118" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>113</v>
       </c>
@@ -19538,7 +19563,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="119" spans="1:43">
+    <row r="119" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>114</v>
       </c>
@@ -19639,7 +19664,7 @@
         <v>46259</v>
       </c>
       <c r="AH119">
-        <v>2.63013698630137</v>
+        <v>2.6301369863013702</v>
       </c>
       <c r="AI119">
         <v>21</v>
@@ -19669,7 +19694,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="120" spans="1:43">
+    <row r="120" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>115</v>
       </c>
@@ -19770,7 +19795,7 @@
         <v>46259</v>
       </c>
       <c r="AH120">
-        <v>2.410958904109589</v>
+        <v>2.4109589041095889</v>
       </c>
       <c r="AI120">
         <v>21</v>
@@ -19800,7 +19825,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="121" spans="1:43">
+    <row r="121" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>116</v>
       </c>
@@ -19931,7 +19956,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="122" spans="1:43">
+    <row r="122" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>117</v>
       </c>
@@ -20062,7 +20087,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="123" spans="1:43">
+    <row r="123" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>118</v>
       </c>
@@ -20193,7 +20218,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="124" spans="1:43">
+    <row r="124" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>119</v>
       </c>
@@ -20294,7 +20319,7 @@
         <v>46259</v>
       </c>
       <c r="AH124">
-        <v>2.263013698630137</v>
+        <v>2.2630136986301368</v>
       </c>
       <c r="AI124">
         <v>21</v>
@@ -20324,7 +20349,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="125" spans="1:43">
+    <row r="125" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>120</v>
       </c>
@@ -20425,7 +20450,7 @@
         <v>46259</v>
       </c>
       <c r="AH125">
-        <v>6.586301369863014</v>
+        <v>6.5863013698630137</v>
       </c>
       <c r="AI125">
         <v>30</v>
@@ -20455,7 +20480,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="126" spans="1:43">
+    <row r="126" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>120</v>
       </c>
@@ -20468,6 +20493,9 @@
       <c r="D126" t="s">
         <v>352</v>
       </c>
+      <c r="L126">
+        <v>3793421656</v>
+      </c>
       <c r="AG126" s="1">
         <v>46259</v>
       </c>
@@ -20478,7 +20506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:43">
+    <row r="127" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>121</v>
       </c>
@@ -20579,7 +20607,7 @@
         <v>46259</v>
       </c>
       <c r="AH127">
-        <v>12.26575342465753</v>
+        <v>12.265753424657531</v>
       </c>
       <c r="AI127">
         <v>30</v>
@@ -20609,7 +20637,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="128" spans="1:43">
+    <row r="128" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>122</v>
       </c>
@@ -20710,7 +20738,7 @@
         <v>46259</v>
       </c>
       <c r="AH128">
-        <v>5.964383561643835</v>
+        <v>5.9643835616438352</v>
       </c>
       <c r="AI128">
         <v>30</v>
@@ -20740,7 +20768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:43">
+    <row r="129" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>123</v>
       </c>
@@ -20841,7 +20869,7 @@
         <v>46259</v>
       </c>
       <c r="AH129">
-        <v>5.797260273972602</v>
+        <v>5.7972602739726016</v>
       </c>
       <c r="AI129">
         <v>21</v>
@@ -20871,7 +20899,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="130" spans="1:43">
+    <row r="130" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>124</v>
       </c>
@@ -20972,7 +21000,7 @@
         <v>46259</v>
       </c>
       <c r="AH130">
-        <v>5.153424657534247</v>
+        <v>5.1534246575342468</v>
       </c>
       <c r="AI130">
         <v>30</v>
@@ -21002,7 +21030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:43">
+    <row r="131" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>125</v>
       </c>
@@ -21103,7 +21131,7 @@
         <v>46259</v>
       </c>
       <c r="AH131">
-        <v>5.178082191780822</v>
+        <v>5.1780821917808222</v>
       </c>
       <c r="AI131">
         <v>30</v>
@@ -21133,7 +21161,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="132" spans="1:43">
+    <row r="132" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B132">
         <v>1135</v>
       </c>
@@ -21231,7 +21259,7 @@
         <v>46259</v>
       </c>
       <c r="AH132">
-        <v>0.1506849315068493</v>
+        <v>0.15068493150684931</v>
       </c>
       <c r="AI132">
         <v>21</v>
@@ -21261,7 +21289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:43">
+    <row r="133" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>126</v>
       </c>
@@ -21362,7 +21390,7 @@
         <v>46259</v>
       </c>
       <c r="AH133">
-        <v>4.235616438356164</v>
+        <v>4.2356164383561641</v>
       </c>
       <c r="AI133">
         <v>21</v>
@@ -21392,7 +21420,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="134" spans="1:43">
+    <row r="134" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>127</v>
       </c>
@@ -21493,7 +21521,7 @@
         <v>46259</v>
       </c>
       <c r="AH134">
-        <v>4.235616438356164</v>
+        <v>4.2356164383561641</v>
       </c>
       <c r="AI134">
         <v>21</v>
@@ -21523,7 +21551,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="135" spans="1:43">
+    <row r="135" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>128</v>
       </c>
@@ -21624,7 +21652,7 @@
         <v>46259</v>
       </c>
       <c r="AH135">
-        <v>4.723287671232876</v>
+        <v>4.7232876712328764</v>
       </c>
       <c r="AI135">
         <v>21</v>
@@ -21654,7 +21682,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="136" spans="1:43">
+    <row r="136" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>129</v>
       </c>
@@ -21755,7 +21783,7 @@
         <v>46259</v>
       </c>
       <c r="AH136">
-        <v>4.29041095890411</v>
+        <v>4.2904109589041104</v>
       </c>
       <c r="AI136">
         <v>21</v>
@@ -21785,7 +21813,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="137" spans="1:43">
+    <row r="137" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>130</v>
       </c>
@@ -21886,7 +21914,7 @@
         <v>46259</v>
       </c>
       <c r="AH137">
-        <v>4.553424657534246</v>
+        <v>4.5534246575342463</v>
       </c>
       <c r="AI137">
         <v>21</v>
@@ -21916,7 +21944,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="138" spans="1:43">
+    <row r="138" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>131</v>
       </c>
@@ -22017,7 +22045,7 @@
         <v>46259</v>
       </c>
       <c r="AH138">
-        <v>1.498630136986301</v>
+        <v>1.4986301369863011</v>
       </c>
       <c r="AI138">
         <v>21</v>
@@ -22047,7 +22075,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="139" spans="1:43">
+    <row r="139" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>132</v>
       </c>
@@ -22178,7 +22206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:43">
+    <row r="140" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>133</v>
       </c>
@@ -22309,7 +22337,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="141" spans="1:43">
+    <row r="141" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>134</v>
       </c>
@@ -22440,7 +22468,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="142" spans="1:43">
+    <row r="142" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>135</v>
       </c>
@@ -22571,7 +22599,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="143" spans="1:43">
+    <row r="143" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>136</v>
       </c>
@@ -22672,7 +22700,7 @@
         <v>46259</v>
       </c>
       <c r="AH143">
-        <v>4.487671232876712</v>
+        <v>4.4876712328767123</v>
       </c>
       <c r="AI143">
         <v>21</v>
@@ -22702,7 +22730,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="144" spans="1:43">
+    <row r="144" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>137</v>
       </c>
@@ -22803,7 +22831,7 @@
         <v>46259</v>
       </c>
       <c r="AH144">
-        <v>4.468493150684932</v>
+        <v>4.4684931506849317</v>
       </c>
       <c r="AI144">
         <v>21</v>
@@ -22833,7 +22861,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="145" spans="1:43">
+    <row r="145" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>138</v>
       </c>
@@ -22934,7 +22962,7 @@
         <v>46259</v>
       </c>
       <c r="AH145">
-        <v>1.857534246575342</v>
+        <v>1.8575342465753419</v>
       </c>
       <c r="AI145">
         <v>21</v>
@@ -22964,7 +22992,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="146" spans="1:43">
+    <row r="146" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>139</v>
       </c>
@@ -23065,7 +23093,7 @@
         <v>46259</v>
       </c>
       <c r="AH146">
-        <v>4.389041095890411</v>
+        <v>4.3890410958904109</v>
       </c>
       <c r="AI146">
         <v>21</v>
@@ -23095,7 +23123,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="147" spans="1:43">
+    <row r="147" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>140</v>
       </c>
@@ -23196,7 +23224,7 @@
         <v>46259</v>
       </c>
       <c r="AH147">
-        <v>3.791780821917808</v>
+        <v>3.7917808219178082</v>
       </c>
       <c r="AI147">
         <v>21</v>
@@ -23226,7 +23254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:43">
+    <row r="148" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>141</v>
       </c>
@@ -23327,7 +23355,7 @@
         <v>46259</v>
       </c>
       <c r="AH148">
-        <v>3.786301369863014</v>
+        <v>3.7863013698630139</v>
       </c>
       <c r="AI148">
         <v>21</v>
@@ -23357,7 +23385,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="149" spans="1:43">
+    <row r="149" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>142</v>
       </c>
@@ -23458,7 +23486,7 @@
         <v>46259</v>
       </c>
       <c r="AH149">
-        <v>3.736986301369863</v>
+        <v>3.7369863013698632</v>
       </c>
       <c r="AI149">
         <v>21</v>
@@ -23488,7 +23516,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="150" spans="1:43">
+    <row r="150" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>143</v>
       </c>
@@ -23589,7 +23617,7 @@
         <v>46259</v>
       </c>
       <c r="AH150">
-        <v>2.545205479452055</v>
+        <v>2.5452054794520551</v>
       </c>
       <c r="AI150">
         <v>21</v>
@@ -23619,7 +23647,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="151" spans="1:43">
+    <row r="151" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>144</v>
       </c>
@@ -23720,7 +23748,7 @@
         <v>46259</v>
       </c>
       <c r="AH151">
-        <v>5.967123287671233</v>
+        <v>5.9671232876712326</v>
       </c>
       <c r="AI151">
         <v>21</v>
@@ -23750,7 +23778,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="152" spans="1:43">
+    <row r="152" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>145</v>
       </c>
@@ -23851,7 +23879,7 @@
         <v>46259</v>
       </c>
       <c r="AH152">
-        <v>3.101369863013699</v>
+        <v>3.1013698630136992</v>
       </c>
       <c r="AI152">
         <v>21</v>
@@ -23881,7 +23909,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="153" spans="1:43">
+    <row r="153" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>146</v>
       </c>
@@ -23982,7 +24010,7 @@
         <v>46259</v>
       </c>
       <c r="AH153">
-        <v>5.64931506849315</v>
+        <v>5.6493150684931503</v>
       </c>
       <c r="AI153">
         <v>21</v>
@@ -24012,7 +24040,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="154" spans="1:43">
+    <row r="154" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>147</v>
       </c>
@@ -24113,7 +24141,7 @@
         <v>46259</v>
       </c>
       <c r="AH154">
-        <v>5.402739726027397</v>
+        <v>5.4027397260273968</v>
       </c>
       <c r="AI154">
         <v>21</v>
@@ -24143,7 +24171,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="155" spans="1:43">
+    <row r="155" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>148</v>
       </c>
@@ -24244,7 +24272,7 @@
         <v>46259</v>
       </c>
       <c r="AH155">
-        <v>5.30958904109589</v>
+        <v>5.3095890410958901</v>
       </c>
       <c r="AI155">
         <v>21</v>
@@ -24274,7 +24302,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="156" spans="1:43">
+    <row r="156" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>149</v>
       </c>
@@ -24375,7 +24403,7 @@
         <v>46259</v>
       </c>
       <c r="AH156">
-        <v>5.038356164383561</v>
+        <v>5.0383561643835613</v>
       </c>
       <c r="AI156">
         <v>21</v>
@@ -24405,7 +24433,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="157" spans="1:43">
+    <row r="157" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>150</v>
       </c>
@@ -24506,7 +24534,7 @@
         <v>46259</v>
       </c>
       <c r="AH157">
-        <v>5.038356164383561</v>
+        <v>5.0383561643835613</v>
       </c>
       <c r="AI157">
         <v>21</v>
@@ -24536,7 +24564,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="158" spans="1:43">
+    <row r="158" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>151</v>
       </c>
@@ -24637,7 +24665,7 @@
         <v>46259</v>
       </c>
       <c r="AH158">
-        <v>5.038356164383561</v>
+        <v>5.0383561643835613</v>
       </c>
       <c r="AI158">
         <v>21</v>
@@ -24667,7 +24695,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="159" spans="1:43">
+    <row r="159" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>152</v>
       </c>
@@ -24768,7 +24796,7 @@
         <v>46259</v>
       </c>
       <c r="AH159">
-        <v>5.038356164383561</v>
+        <v>5.0383561643835613</v>
       </c>
       <c r="AI159">
         <v>21</v>
@@ -24798,7 +24826,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="160" spans="1:43">
+    <row r="160" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>153</v>
       </c>
@@ -24899,7 +24927,7 @@
         <v>46259</v>
       </c>
       <c r="AH160">
-        <v>1.83013698630137</v>
+        <v>1.8301369863013699</v>
       </c>
       <c r="AI160">
         <v>21</v>
@@ -24929,7 +24957,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="161" spans="1:43">
+    <row r="161" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>154</v>
       </c>
@@ -25030,7 +25058,7 @@
         <v>46259</v>
       </c>
       <c r="AH161">
-        <v>4.528767123287671</v>
+        <v>4.5287671232876709</v>
       </c>
       <c r="AI161">
         <v>21</v>
@@ -25060,7 +25088,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="162" spans="1:43">
+    <row r="162" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>155</v>
       </c>
@@ -25161,7 +25189,7 @@
         <v>46259</v>
       </c>
       <c r="AH162">
-        <v>4.389041095890411</v>
+        <v>4.3890410958904109</v>
       </c>
       <c r="AI162">
         <v>21</v>
@@ -25191,7 +25219,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="163" spans="1:43">
+    <row r="163" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>156</v>
       </c>
@@ -25292,7 +25320,7 @@
         <v>46259</v>
       </c>
       <c r="AH163">
-        <v>4.389041095890411</v>
+        <v>4.3890410958904109</v>
       </c>
       <c r="AI163">
         <v>21</v>
@@ -25322,7 +25350,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="164" spans="1:43">
+    <row r="164" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>157</v>
       </c>
@@ -25453,7 +25481,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="165" spans="1:43">
+    <row r="165" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>158</v>
       </c>
@@ -25554,7 +25582,7 @@
         <v>46259</v>
       </c>
       <c r="AH165">
-        <v>3.994520547945205</v>
+        <v>3.9945205479452048</v>
       </c>
       <c r="AI165">
         <v>21</v>
@@ -25584,7 +25612,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="166" spans="1:43">
+    <row r="166" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>159</v>
       </c>
@@ -25685,7 +25713,7 @@
         <v>46259</v>
       </c>
       <c r="AH166">
-        <v>3.964383561643836</v>
+        <v>3.9643835616438361</v>
       </c>
       <c r="AI166">
         <v>21</v>
@@ -25715,7 +25743,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="167" spans="1:43">
+    <row r="167" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>161</v>
       </c>
@@ -25816,7 +25844,7 @@
         <v>46259</v>
       </c>
       <c r="AH167">
-        <v>2.33972602739726</v>
+        <v>2.3397260273972602</v>
       </c>
       <c r="AI167">
         <v>21</v>
@@ -25846,7 +25874,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="168" spans="1:43">
+    <row r="168" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>162</v>
       </c>
@@ -25947,7 +25975,7 @@
         <v>46259</v>
       </c>
       <c r="AH168">
-        <v>13.54794520547945</v>
+        <v>13.547945205479451</v>
       </c>
       <c r="AI168">
         <v>30</v>
@@ -25977,7 +26005,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="169" spans="1:43">
+    <row r="169" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>163</v>
       </c>
@@ -26078,7 +26106,7 @@
         <v>46259</v>
       </c>
       <c r="AH169">
-        <v>5.153424657534247</v>
+        <v>5.1534246575342468</v>
       </c>
       <c r="AI169">
         <v>30</v>
@@ -26108,7 +26136,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="170" spans="1:43">
+    <row r="170" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>164</v>
       </c>
@@ -26209,7 +26237,7 @@
         <v>46259</v>
       </c>
       <c r="AH170">
-        <v>5.345205479452055</v>
+        <v>5.3452054794520549</v>
       </c>
       <c r="AI170">
         <v>30</v>
@@ -26239,7 +26267,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="171" spans="1:43">
+    <row r="171" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>165</v>
       </c>
@@ -26370,7 +26398,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="172" spans="1:43">
+    <row r="172" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>166</v>
       </c>
@@ -26471,7 +26499,7 @@
         <v>46259</v>
       </c>
       <c r="AH172">
-        <v>2.843835616438356</v>
+        <v>2.8438356164383558</v>
       </c>
       <c r="AI172">
         <v>21</v>
@@ -26501,7 +26529,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="173" spans="1:43">
+    <row r="173" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>167</v>
       </c>
@@ -26632,7 +26660,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="174" spans="1:43">
+    <row r="174" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>168</v>
       </c>
@@ -26733,7 +26761,7 @@
         <v>46259</v>
       </c>
       <c r="AH174">
-        <v>1.96986301369863</v>
+        <v>1.9698630136986299</v>
       </c>
       <c r="AI174">
         <v>21</v>
@@ -26763,7 +26791,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="175" spans="1:43">
+    <row r="175" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>169</v>
       </c>
@@ -26894,7 +26922,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="176" spans="1:43">
+    <row r="176" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>170</v>
       </c>
@@ -26995,7 +27023,7 @@
         <v>46259</v>
       </c>
       <c r="AH176">
-        <v>5.876712328767123</v>
+        <v>5.8767123287671232</v>
       </c>
       <c r="AI176">
         <v>30</v>
@@ -27025,7 +27053,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="177" spans="1:43">
+    <row r="177" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>171</v>
       </c>
@@ -27156,7 +27184,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="178" spans="1:43">
+    <row r="178" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>172</v>
       </c>
@@ -27257,7 +27285,7 @@
         <v>46259</v>
       </c>
       <c r="AH178">
-        <v>2.961643835616438</v>
+        <v>2.9616438356164378</v>
       </c>
       <c r="AI178">
         <v>21</v>
@@ -27287,7 +27315,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="179" spans="1:43">
+    <row r="179" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>173</v>
       </c>
@@ -27388,7 +27416,7 @@
         <v>46259</v>
       </c>
       <c r="AH179">
-        <v>2.468493150684932</v>
+        <v>2.4684931506849321</v>
       </c>
       <c r="AI179">
         <v>21</v>
@@ -27418,7 +27446,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="180" spans="1:43">
+    <row r="180" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>174</v>
       </c>
@@ -27519,7 +27547,7 @@
         <v>46259</v>
       </c>
       <c r="AH180">
-        <v>2.252054794520548</v>
+        <v>2.2520547945205478</v>
       </c>
       <c r="AI180">
         <v>21</v>
@@ -27549,7 +27577,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="181" spans="1:43">
+    <row r="181" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>175</v>
       </c>
@@ -27680,7 +27708,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="182" spans="1:43">
+    <row r="182" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>176</v>
       </c>
@@ -27811,7 +27839,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="183" spans="1:43">
+    <row r="183" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>177</v>
       </c>
@@ -27942,7 +27970,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="184" spans="1:43">
+    <row r="184" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>178</v>
       </c>
@@ -28073,7 +28101,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="185" spans="1:43">
+    <row r="185" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>179</v>
       </c>
@@ -28204,7 +28232,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="186" spans="1:43">
+    <row r="186" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>180</v>
       </c>
@@ -28305,7 +28333,7 @@
         <v>46259</v>
       </c>
       <c r="AH186">
-        <v>1.745205479452055</v>
+        <v>1.7452054794520551</v>
       </c>
       <c r="AI186">
         <v>21</v>
@@ -28335,7 +28363,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="187" spans="1:43">
+    <row r="187" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>181</v>
       </c>
@@ -28436,7 +28464,7 @@
         <v>46259</v>
       </c>
       <c r="AH187">
-        <v>1.389041095890411</v>
+        <v>1.3890410958904109</v>
       </c>
       <c r="AI187">
         <v>21</v>
@@ -28468,7 +28496,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="S170" r:id="rId1"/>
+    <hyperlink ref="S170" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Staffdata.xlsx
+++ b/Staffdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3113719057d24bf/Desktop/HR-Forms-Site/HRFORMAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_05E48499FC67680F1964AE368160343238AA41AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91AF1319-B794-4D52-BCC5-584C93E2EB2B}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_05E48499FC67680F1964AE368160343238AA41AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F288600-B817-4090-BF95-79519530827E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4759" uniqueCount="1294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4766" uniqueCount="1295">
   <si>
     <t>#</t>
   </si>
@@ -3911,6 +3911,9 @@
   </si>
   <si>
     <t>SA8220000002422633189940</t>
+  </si>
+  <si>
+    <t>سورية</t>
   </si>
 </sst>
 </file>
@@ -20493,17 +20496,56 @@
       <c r="D126" t="s">
         <v>352</v>
       </c>
+      <c r="E126" t="s">
+        <v>1294</v>
+      </c>
       <c r="L126">
         <v>3793421656</v>
       </c>
+      <c r="U126" t="s">
+        <v>908</v>
+      </c>
+      <c r="V126" t="s">
+        <v>972</v>
+      </c>
+      <c r="W126" t="s">
+        <v>908</v>
+      </c>
+      <c r="X126" t="s">
+        <v>972</v>
+      </c>
+      <c r="Z126" t="s">
+        <v>1077</v>
+      </c>
+      <c r="AA126" t="s">
+        <v>1084</v>
+      </c>
+      <c r="AB126" t="s">
+        <v>1084</v>
+      </c>
+      <c r="AC126" t="s">
+        <v>1105</v>
+      </c>
       <c r="AG126" s="1">
         <v>46259</v>
       </c>
       <c r="AH126">
         <v>126.7369863013699</v>
       </c>
+      <c r="AJ126">
+        <v>4444</v>
+      </c>
+      <c r="AK126">
+        <v>1111</v>
+      </c>
+      <c r="AL126">
+        <v>445</v>
+      </c>
+      <c r="AM126">
+        <v>0</v>
+      </c>
       <c r="AN126">
-        <v>0</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="127" spans="1:43" x14ac:dyDescent="0.25">
@@ -21223,12 +21265,6 @@
         <v>908</v>
       </c>
       <c r="V132" t="s">
-        <v>972</v>
-      </c>
-      <c r="W132" t="s">
-        <v>908</v>
-      </c>
-      <c r="X132" t="s">
         <v>972</v>
       </c>
       <c r="Y132" t="s">
